--- a/results/scraped_Cape_Town_Health_and_Wellness.xlsx
+++ b/results/scraped_Cape_Town_Health_and_Wellness.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="274">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -40,124 +40,361 @@
     <t>Source</t>
   </si>
   <si>
-    <t>community（英语单词）_百度百科</t>
+    <t>Community Information-West Bloomfield Township,Michigan</t>
+  </si>
+  <si>
+    <t>Official Website ofWest Bloomfield Township,MI</t>
   </si>
   <si>
     <t>Community-Wikipedia</t>
   </si>
   <si>
-    <t>COMMUNITY中文 (简体)翻译：剑桥词典</t>
-  </si>
-  <si>
-    <t>community是什么意思_community的翻译_音标_读音_用法_例句_爱词 …</t>
-  </si>
-  <si>
-    <t>COMMUNITY| English meaning - Cambridge Dictionary</t>
-  </si>
-  <si>
     <t>COMMUNITYDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
-    <t>浅谈词汇多重意义之三："community" 未必是“社区” - 知乎</t>
-  </si>
-  <si>
-    <t>COMMUNITY释义 | 柯林斯英语词典</t>
-  </si>
-  <si>
-    <t>Community (TV series) -Wikipedia</t>
-  </si>
-  <si>
-    <t>community- 搜索 词典</t>
+    <t>Home - Bloomfield Township</t>
+  </si>
+  <si>
+    <t>West Bloomfield Twp,MI- Facebook</t>
+  </si>
+  <si>
+    <t>Home - WB Parks</t>
+  </si>
+  <si>
+    <t>West Bloomfield Township,Michigan-Wikipedia</t>
+  </si>
+  <si>
+    <t>CommunityDefinition | What IsCommunity- Greater Good</t>
+  </si>
+  <si>
+    <t>What isCommunity? Basic Concepts in Sociology (updated 2025)</t>
+  </si>
+  <si>
+    <t>HospiceofAlabama- Serving NortheastAlabama</t>
   </si>
   <si>
     <t>What ishospice? -HospiceFoundation of America</t>
   </si>
   <si>
+    <t>Alabama Hospiceand Palliative Care Organization</t>
+  </si>
+  <si>
+    <t>HospiceinAlabama| AHPCO</t>
+  </si>
+  <si>
+    <t>HospiceCare inAlabama|Hospice&amp; Palliative Care - Compassus</t>
+  </si>
+  <si>
+    <t>Hospiceof NorthAlabama: An Adoration Health Partner Website</t>
+  </si>
+  <si>
     <t>Hospice- Wikipedia</t>
   </si>
   <si>
-    <t>Frequently Asked Questions AboutHospiceCare - National Institute …</t>
-  </si>
-  <si>
-    <t>18 Hospice Facilities in Wahiawa, HI- Find Reviews, Photos</t>
-  </si>
-  <si>
-    <t>Hospices inWahiawa,Hawaii| Ever Loved</t>
-  </si>
-  <si>
-    <t>What Are Palliative Care andHospiceCare? - National Institute on Aging</t>
-  </si>
-  <si>
-    <t>THE BEST 10HospicenearWahiawa,HI96786 - Yelp</t>
-  </si>
-  <si>
-    <t>hospiceprograms inWahiawa,hi| findhelp.org</t>
-  </si>
-  <si>
-    <t>What IsHospiceCare? - Cleveland Clinic</t>
-  </si>
-  <si>
-    <t>HospiceCare NearWahiawa,HI96786 - Healthcare Compare</t>
+    <t>ColumbusHospiceof Georgia &amp;Alabama</t>
+  </si>
+  <si>
+    <t>Alabama Hospice Care of Birmingham- CentralAlabama- LHC Group</t>
+  </si>
+  <si>
+    <t>Hospiceof WestAlabama– A 501 (c) (3) non-profit, community-based ...</t>
   </si>
   <si>
     <t>MENTALDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
+    <t>Mental health-Wikipedia</t>
+  </si>
+  <si>
     <t>AboutMentalHealth |MentalHealth | CDC</t>
   </si>
   <si>
     <t>Mental disorders-World Health Organization(WHO)</t>
   </si>
   <si>
-    <t>Mental health-Wikipedia</t>
+    <t>Mentaldisorder -Wikipedia</t>
+  </si>
+  <si>
+    <t>MENTAL| English meaning - Cambridge Dictionary</t>
   </si>
   <si>
     <t>Mentalhealth: What's normal, what's not -Mayo Clinic</t>
   </si>
   <si>
+    <t>Mental health: Definition, common disorders, early signs, and more</t>
+  </si>
+  <si>
     <t>MentalDisorders: Types, Causes &amp; Symptoms -Cleveland Clinic</t>
   </si>
   <si>
-    <t>MENTAL| English meaning - Cambridge Dictionary</t>
-  </si>
-  <si>
-    <t>Mentaldisorder -Wikipedia</t>
-  </si>
-  <si>
     <t>MentalHealth: Causes, Symptoms, Treatment &amp; Help | SAMHSA</t>
   </si>
   <si>
-    <t>Mentalillness - Symptoms and causes -Mayo Clinic</t>
-  </si>
-  <si>
-    <t>Health&amp; Human Services Department - City ofLong Beach</t>
+    <t>Kansas City HealthDepartment - City ofKansas City,MO</t>
+  </si>
+  <si>
+    <t>The University of KansasHealthSystem</t>
   </si>
   <si>
     <t>Health- Wikipedia</t>
   </si>
   <si>
-    <t>Student Health Services-CaliforniaState UniversityLong Beach</t>
-  </si>
-  <si>
-    <t>Long BeachComprehensiveHealthCenter -HealthCenters</t>
-  </si>
-  <si>
-    <t>What ishealth?: Defining and preservinggood health</t>
-  </si>
-  <si>
-    <t>WebMD- Better information. Betterhealth.</t>
+    <t>UniversityHealth|Kansas CityHospital</t>
+  </si>
+  <si>
+    <t>Kansas City HealthDepartment -MissouriDepartment ofHealthand ...</t>
+  </si>
+  <si>
+    <t>Patient portal | NKCHealth</t>
+  </si>
+  <si>
+    <t>myUHealth| UniversityHealthPatient Portal</t>
+  </si>
+  <si>
+    <t>NKCHealth</t>
+  </si>
+  <si>
+    <t>Home - SwopeHealth</t>
   </si>
   <si>
     <t>HEALTH: Longevity for All</t>
   </si>
   <si>
-    <t>Home -HealthServices Los Angeles County</t>
-  </si>
-  <si>
-    <t>PIHHealth| YourHealth&amp; Wellness Partner</t>
-  </si>
-  <si>
-    <t>Long Beach- WelbeHealth</t>
+    <t>Microsoft– AI, Cloud, Productivity, Computing, Gaming &amp; Apps</t>
+  </si>
+  <si>
+    <t>Microsoftaccount | Sign In or Create Your Account Today –Microsoft</t>
+  </si>
+  <si>
+    <t>Sign in to your account</t>
+  </si>
+  <si>
+    <t>Microsoft365 for Individuals: Subscription for Productivity Apps</t>
+  </si>
+  <si>
+    <t>Outlook</t>
+  </si>
+  <si>
+    <t>Microsoft- Wikipedia</t>
+  </si>
+  <si>
+    <t>MicrosoftStore - Download apps,games&amp; more for your Windows PC</t>
+  </si>
+  <si>
+    <t>Create yourMicrosoftaccount</t>
+  </si>
+  <si>
+    <t>Sign in to your account - myaccount.microsoft.com</t>
+  </si>
+  <si>
+    <t>What is Wellness? -Global Wellness Institute</t>
+  </si>
+  <si>
+    <t>What is Wellness?</t>
+  </si>
+  <si>
+    <t>Wellness (alternative medicine) - Wikipedia</t>
+  </si>
+  <si>
+    <t>WellnessTopics - Healthline</t>
+  </si>
+  <si>
+    <t>Luxury Spa in Erlanger,Edgewood&amp; Fort Mitchell,KY</t>
+  </si>
+  <si>
+    <t>Sea of Tranquility Massage andWellness-Edgewood,KY</t>
+  </si>
+  <si>
+    <t>About Us | SandalwoodWellnessand Spa</t>
+  </si>
+  <si>
+    <t>Sea of Tranquility Massage andWellness, LLC</t>
+  </si>
+  <si>
+    <t>WellnessResource Center - Everyday Health</t>
+  </si>
+  <si>
+    <t>WellnessDefined</t>
+  </si>
+  <si>
+    <t>Home -San AntonioCounseling &amp; Behavioral Center</t>
+  </si>
+  <si>
+    <t>Neely Counseling | Counseling inSan Antonio,Texas</t>
+  </si>
+  <si>
+    <t>Counseling inSan Antonio|TexasCounseling Center</t>
+  </si>
+  <si>
+    <t>Free or Low-Cost Counseling in San Antonio,TX- OpenCounseling</t>
+  </si>
+  <si>
+    <t>Counseling4Life, LLC.</t>
+  </si>
+  <si>
+    <t>A New Start Counseling Services -San AntonioTherapists - A New …</t>
+  </si>
+  <si>
+    <t>Counseling Services –Catholic Charities</t>
+  </si>
+  <si>
+    <t>Community Counseling Service- Our Lady of the Lake University</t>
+  </si>
+  <si>
+    <t>Counseling | College of Education and Human Development</t>
+  </si>
+  <si>
+    <t>Counseling inSan Antonio,TX| Aligned Mind Counseling</t>
+  </si>
+  <si>
+    <t>Home - MethodistRehabilitation</t>
+  </si>
+  <si>
+    <t>Rehabilitation- MedlinePlus</t>
+  </si>
+  <si>
+    <t>Mississippi- Home | mdrs</t>
+  </si>
+  <si>
+    <t>MississippiDepartment ofRehabilitationServices -MS.GOV</t>
+  </si>
+  <si>
+    <t>JacksonInpatient Hospital - MethodistRehabilitation</t>
+  </si>
+  <si>
+    <t>Rehabilitation- University ofMississippiMedical Center</t>
+  </si>
+  <si>
+    <t>MethodistRehabilitationCenter -Jackson,MS| Rehab.com</t>
+  </si>
+  <si>
+    <t>Office of VocationalRehabilitation| mdrs -Mississippi</t>
+  </si>
+  <si>
+    <t>Drug &amp; Alcohol Rehabs inJackson,MS- recovery.com</t>
+  </si>
+  <si>
+    <t>INMOTIONREHABLLC |</t>
+  </si>
+  <si>
+    <t>WebMD- Better information. Better health.</t>
+  </si>
+  <si>
+    <t>Family Healthcare &amp; Doctors |Conroe, Spring &amp; WillisTexas– A full ...</t>
+  </si>
+  <si>
+    <t>Medicine- Wikipedia</t>
+  </si>
+  <si>
+    <t>Hospital, ER &amp; Trauma Center inConroe,TX|Conroe</t>
+  </si>
+  <si>
+    <t>Primary Care Providers inConroe,TX| CLS Health</t>
+  </si>
+  <si>
+    <t>GenesisMedicalGroup</t>
+  </si>
+  <si>
+    <t>Primary Care - Baylor St. Luke'sMedicalGroup -Conroe,TX</t>
+  </si>
+  <si>
+    <t>1120 N Loop 336 W,Conroe,TX, 77301 - VillageMedical</t>
+  </si>
+  <si>
+    <t>Family LifeMedical: Family Medicine Physicians:Conroe,TX</t>
+  </si>
+  <si>
+    <t>A-Med, Inc. -MedicalEquipment and Supply -Conroe,Texas</t>
+  </si>
+  <si>
+    <t>BusinessTax FormFiling Made Easy – 1099 &amp; W-2 eFile |Adams</t>
+  </si>
+  <si>
+    <t>Adams Tax Forms</t>
+  </si>
+  <si>
+    <t>E-File BusinessTax Forms– 1099 &amp; W-2Online|Adams Tax Forms</t>
+  </si>
+  <si>
+    <t>What's New: 2025-2026TaxSeason |Adams Tax Forms</t>
+  </si>
+  <si>
+    <t>Home |Adams Tax Forms HelpCenter</t>
+  </si>
+  <si>
+    <t>About eFiling |Adams Tax Forms HelpCenter</t>
+  </si>
+  <si>
+    <t>I TestedAdams Tax Forms Helperand Here’s Why It’s a Must-Have …</t>
+  </si>
+  <si>
+    <t>Viewing Previous Years'FormswithAdams®Tax Forms Helper®</t>
+  </si>
+  <si>
+    <t>Logging In &amp; Sign Up |Adams Tax Forms HelpCenter</t>
+  </si>
+  <si>
+    <t>Logging In &amp; Your Account |Adams Tax Forms HelpCenter</t>
+  </si>
+  <si>
+    <t>Property value -84 Kirk Street, Otaki- realestate.co.nz</t>
+  </si>
+  <si>
+    <t>84 Kirk Street, Otaki, Kapiti Coast, Wellington</t>
+  </si>
+  <si>
+    <t>84 Kirk St, Otaki, Wellington - Property Profile</t>
+  </si>
+  <si>
+    <t>84 Kirk St, Otaki, Wellington - House Sold on 15 02 2024</t>
+  </si>
+  <si>
+    <t>Kirk Street, Otaki, Kapiti Coast District - PropertyValue.co.nz</t>
+  </si>
+  <si>
+    <t>21 available houses, cottages and villas for rent inŌtaki</t>
+  </si>
+  <si>
+    <t>Rental property inŌtaki– 23 available homes for rent | Rentola</t>
+  </si>
+  <si>
+    <t>House (713.89 m²) for rent inŌtaki(47Kirk Street,Ōtaki 5512, New ...</t>
+  </si>
+  <si>
+    <t>OtakiHomes and Real Estate for Sale- realestate.co.nz</t>
+  </si>
+  <si>
+    <t>Google Maps</t>
+  </si>
+  <si>
+    <t>AirPods - Apple</t>
+  </si>
+  <si>
+    <t>AirPods - Apple (DE)</t>
+  </si>
+  <si>
+    <t>AirPods User Guide - Apple Support</t>
+  </si>
+  <si>
+    <t>AirPods Manuals and Downloads - Apple Support</t>
+  </si>
+  <si>
+    <t>My AirPods are not recognized by my iPhon… - Apple Community</t>
+  </si>
+  <si>
+    <t>3rd Gen AirPods Won’t Pair - Apple Community</t>
+  </si>
+  <si>
+    <t>Connecter AirPods au PC - Communauté Apple</t>
+  </si>
+  <si>
+    <t>AirPods - Apple (IN)</t>
+  </si>
+  <si>
+    <t>AirPods - Apple (BR)</t>
+  </si>
+  <si>
+    <t>AirPods Max 2 - Apple</t>
   </si>
   <si>
     <t>PrimaryClothing - Brilliant Basics for Baby &amp; Kids</t>
@@ -166,427 +403,436 @@
     <t>PRIMARYDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
-    <t>Colorado GovernorPrimaryResults 2026 - NBC News</t>
-  </si>
-  <si>
     <t>PRIMARY| English meaning - Cambridge Dictionary</t>
   </si>
   <si>
+    <t>MinnesotaPrimaryResults 2026: Senate, House and Governor</t>
+  </si>
+  <si>
+    <t>Primary— reporting assembled from records</t>
+  </si>
+  <si>
+    <t>Games, Videos, Holidays &amp; Crafts |PrimaryGames</t>
+  </si>
+  <si>
     <t>PRIMARY| definition in the Cambridge English Dictionary</t>
   </si>
   <si>
-    <t>Games, Videos, Holidays &amp; Crafts |PrimaryGames</t>
+    <t>National Elections 2026 Live Results and Map: Delaware Primaries</t>
+  </si>
+  <si>
+    <t>PRIMARYDefinition &amp; Meaning |Dictionary.com</t>
   </si>
   <si>
     <t>2026 Election Results, Latest News &amp; Updates | Fox News Elections …</t>
   </si>
   <si>
-    <t>National Elections 2026 Live Results and Map: Delaware Primaries</t>
-  </si>
-  <si>
-    <t>Primary— reporting assembled from records</t>
-  </si>
-  <si>
-    <t>PRIMARYDefinition &amp; Meaning |Dictionary.com</t>
-  </si>
-  <si>
-    <t>Modesto,CA- WellnessMart</t>
-  </si>
-  <si>
-    <t>WellnessMart</t>
-  </si>
-  <si>
-    <t>What is Wellness? -Global Wellness Institute</t>
-  </si>
-  <si>
-    <t>Med Spa inModesto,CAand Lodi,CA| Ego Beauty AndWellness</t>
-  </si>
-  <si>
-    <t>Liu'sWellness-Modesto,CA</t>
-  </si>
-  <si>
-    <t>Alternative Care Center inModesto,CA| AccessWellnessServices</t>
-  </si>
-  <si>
-    <t>thewellnesscenterModesto,CA- Yelp</t>
-  </si>
-  <si>
-    <t>What is Wellness?</t>
-  </si>
-  <si>
-    <t>What IsWellness? The 9 Dimensions Explained</t>
-  </si>
-  <si>
-    <t>Mantra Health andWellness| Med Spa inModesto,CA</t>
-  </si>
-  <si>
-    <t>Free or Low-Cost Counseling in San Fernando,CA- OpenCounseling</t>
-  </si>
-  <si>
-    <t>West Valley Counseling Center –San FernandoValley</t>
-  </si>
-  <si>
-    <t>SAN FERNANDOVALLEY COUNSELING CENTER | Family Counseling</t>
-  </si>
-  <si>
-    <t>San FernandoValley Counseling Center - LA County Parks Locator</t>
-  </si>
-  <si>
-    <t>Valley Community Counseling Clinic</t>
-  </si>
-  <si>
-    <t>THE BEST 10 COUNSELING &amp; MENTAL HEALTH INSAN FERNANDOVALLEY,CA...</t>
-  </si>
-  <si>
-    <t>San Fernando Valley Counseling Center| CCRC</t>
-  </si>
-  <si>
-    <t>Therapists in San Fernando,CA- Psychology Today</t>
-  </si>
-  <si>
-    <t>In Person Therapists inSan Fernando,CA- Psychology Today</t>
-  </si>
-  <si>
-    <t>Child &amp; Teen Counseling - Affordable Therapy for Families in Los ...</t>
-  </si>
-  <si>
-    <t>Rehabilitation- MedlinePlus</t>
-  </si>
-  <si>
-    <t>Rehabilitation- World Health Organization (WHO)</t>
-  </si>
-  <si>
-    <t>Physical Therapy &amp;RehabilitationCenter inGrand Prairie,TX</t>
-  </si>
-  <si>
-    <t>THE BEST 10REHABILITATION CENTER IN GRAND PRAIRIE,TX</t>
-  </si>
-  <si>
-    <t>Rehab Center Near Dallas,TX| Greenhouse Treatment Center</t>
-  </si>
-  <si>
-    <t>10 Best Drug &amp; Alcohol Rehab Centers nearGrand Prairie,TX2026 ...</t>
-  </si>
-  <si>
-    <t>Alcohol &amp; Drug Rehabs inGrand Prairie,Texas-Addictions</t>
-  </si>
-  <si>
-    <t>Highest Reviewed Drug Rehab Centers InGrand Prairie,TX</t>
-  </si>
-  <si>
-    <t>VocationalRehabilitationProgram -TexasWorkforce Commission</t>
-  </si>
-  <si>
-    <t>Physical Therapy Rehab Centers DFW | Outpatient Clinic Dallas,Texas</t>
-  </si>
-  <si>
-    <t>Medicine- Wikipedia</t>
-  </si>
-  <si>
-    <t>Medi-Cal</t>
-  </si>
-  <si>
-    <t>medical_百度百科</t>
-  </si>
-  <si>
-    <t>MEDICAL中文 (简体)翻译：剑桥词典 - Cambridge Dictionary</t>
-  </si>
-  <si>
-    <t>Medicaland health information | MedicalNewsToday</t>
-  </si>
-  <si>
-    <t>WebMD- Better information. Better health.</t>
-  </si>
-  <si>
-    <t>PubMed</t>
-  </si>
-  <si>
-    <t>MedicalNews |MedicalArticles</t>
-  </si>
-  <si>
-    <t>MEDICAL释义 | 柯林斯英语词典 - Collins Online Dictionary</t>
-  </si>
-  <si>
-    <t>Medi-CalProviders</t>
-  </si>
-  <si>
     <t>Health &amp; Wellness</t>
   </si>
   <si>
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5800866de63e6d1169bd573b4d96a5ec9c8b4989d5063cea33d50385a90ddb1bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=289a8efd-3829-6633-365d-991c397467b0&amp;u=a1aHR0cHM6Ly9iYWlrZS5iYWlkdS5jb20vaXRlbS9jb21tdW5pdHkvOTM3MjM0OQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cb0014b9152b9ef55f94692bed992871adf1374e2e921f2ed14ba2aa7e7934adJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=289a8efd-3829-6633-365d-991c397467b0&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Db21tdW5pdHk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dcdd14b99f31fac14e6fc0efed83062cb775290908c69565b59a04802aeb12eaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=289a8efd-3829-6633-365d-991c397467b0&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvemhzLyVFOCVBRiU4RCVFNSU4NSVCOC8lRTglOEIlQjElRTglQUYlQUQtJUU2JUIxJTg5JUU4JUFGJUFELSVFNyVBRSU4MCVFNCVCRCU5My9jb21tdW5pdHk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1f2437e29abc620ddb50c03fbbd87aa8bbb179a4527da5b4cb23e82ed6e5d7d2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=289a8efd-3829-6633-365d-991c397467b0&amp;u=a1aHR0cHM6Ly93d3cuaWNpYmEuY29tL3dvcmQ_dz1jb21tdW5pdHk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8b52b0826d13c4a9c2d361fda37b1579d11a1641a73b708655e43346e6984aaaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=289a8efd-3829-6633-365d-991c397467b0&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2NvbW11bml0eQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9b043c3845d7e165993b6a3ac7a5bf7adfc93f6f9fc37f17926543c32ae27346JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=289a8efd-3829-6633-365d-991c397467b0&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2NvbW11bml0eQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5c2edfbb0713d8bb5bc591e705c478f32585201e9cb4d3897ec54a92ba8c1a91JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=289a8efd-3829-6633-365d-991c397467b0&amp;u=a1aHR0cHM6Ly96aHVhbmxhbi56aGlodS5jb20vcC80MDIxODA0MTE&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=203605bda6ab3d7eb357f4011cb1c066205ecf18642804c0bf6ae88ba3f5aec6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=289a8efd-3829-6633-365d-991c397467b0&amp;u=a1aHR0cHM6Ly93d3cuY29sbGluc2RpY3Rpb25hcnkuY29tL3poL2RpY3Rpb25hcnkvZW5nbGlzaC9jb21tdW5pdHk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=66cf9e5653279d3f92e951764e8b639650877322d2848a9e5b5bea3fce278b3dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=289a8efd-3829-6633-365d-991c397467b0&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Db21tdW5pdHlfKFRWX3Nlcmllcyk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=400b8426eadcb0ad09907dde17718cbbb1545d35d9e3b84db8f4ac5ffddbcf63JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=289a8efd-3829-6633-365d-991c397467b0&amp;u=a1aHR0cHM6Ly9nbG9iYWwuYmluZy5jb20vZGljdC9zZWFyY2g_cT1jb21tdW5pdHkmRk9STT1CRFZTUDYmY2M9Y24&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8da494e4f1a74dd0e208801640a93a0647a05a19271a826f2185d9e9d07074f1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0346b21c-a61b-6379-1d25-a5fda7f66265&amp;u=a1aHR0cHM6Ly9ob3NwaWNlZm91bmRhdGlvbi5vcmcvd2hhdC1pcy1ob3NwaWNlLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c443de32964898447a2f58f779fae312580460b720dcbf3180f0dd19f64a97adJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0346b21c-a61b-6379-1d25-a5fda7f66265&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Ib3NwaWNl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=94f899821937c00ba9590ae791b80d9436b6466c0278cb303dfdf4bfe868396bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0346b21c-a61b-6379-1d25-a5fda7f66265&amp;u=a1aHR0cHM6Ly93d3cubmlhLm5paC5nb3YvaGVhbHRoL2hvc3BpY2UtYW5kLXBhbGxpYXRpdmUtY2FyZS9mcmVxdWVudGx5LWFza2VkLXF1ZXN0aW9ucy1hYm91dC1ob3NwaWNlLWNhcmU&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=670aa54fed290f7dab2b2ea4f82dcfb0724860b7c1545b2d6ea067004eef874dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0346b21c-a61b-6379-1d25-a5fda7f66265&amp;u=a1aHR0cHM6Ly93d3cuc2VuaW9yYWR2aWNlLmNvbS9ob3NwaWNlL3dhaGlhd2EtaGk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=57099846b67bd40f5e20db03b8b554fae8607d59de0cfcd4bfebf9f74a2e5169JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0346b21c-a61b-6379-1d25-a5fda7f66265&amp;u=a1aHR0cHM6Ly9ldmVybG92ZWQuY29tL2hvc3BpY2VzL0hJL3dhaGlhd2Ev&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f1482014a11aa73e4b997b10bc49d674f99d8163ef0ceab9520ec155de89f147JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0346b21c-a61b-6379-1d25-a5fda7f66265&amp;u=a1aHR0cHM6Ly93d3cubmlhLm5paC5nb3YvaGVhbHRoL2hvc3BpY2UtYW5kLXBhbGxpYXRpdmUtY2FyZS93aGF0LWFyZS1wYWxsaWF0aXZlLWNhcmUtYW5kLWhvc3BpY2UtY2FyZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=07e7f730948df04da23a984b2d8aa961d1da977c6eb06f95bb9552b3b7366232JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0346b21c-a61b-6379-1d25-a5fda7f66265&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vc2VhcmNoP2NmbHQ9aG9zcGljZSZmaW5kX2xvYz1XYWhpYXdhJTJDK0hJKzk2Nzg2Jm1zb2NraWQ9MDM0NmIyMWNhNjFiNjM3OTFkMjVhNWZkYTdmNjYyNjU&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=34ac2d54e8b2ae81cf322f755cc807e47160376b046868fd4dcf3206d607172eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0346b21c-a61b-6379-1d25-a5fda7f66265&amp;u=a1aHR0cHM6Ly93d3cuZmluZGhlbHAub3JnL2NhcmUvaG9zcGljZS0td2FoaWF3YS1oaQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=eac471452cf03cbde423d63da328d5f246fadcbe3d0119d26bdcfbd36fcbd153JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0346b21c-a61b-6379-1d25-a5fda7f66265&amp;u=a1aHR0cHM6Ly9teS5jbGV2ZWxhbmRjbGluaWMub3JnL2hlYWx0aC9hcnRpY2xlcy8yMTY3My1ob3NwaWNl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=48a1177b651b50a7afa23618c88cedaae34e6674ffb78e7bb13dc33a1527f2c9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0346b21c-a61b-6379-1d25-a5fda7f66265&amp;u=a1aHR0cHM6Ly9oZWFsdGhjYXJlY29tcHMuY29tL2hvc3BpY2UvaGkvP3ppcD05Njc4Ng&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=55e5c6f0da54647c7955aa7966007683c1e7d6ae03ebdfb45b217f360e236212JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ea1a350-82c9-6649-0d00-b4b1838d67f7&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L21lbnRhbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ce6969f5e8e92219c47d1c8f0fd792dee4408f1d65eda2898687746dea303134JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ea1a350-82c9-6649-0d00-b4b1838d67f7&amp;u=a1aHR0cHM6Ly93d3cuY2RjLmdvdi9tZW50YWwtaGVhbHRoL2Fib3V0L2luZGV4Lmh0bWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6e4277625e4ec56476fd80567e81182dba7df0df434b5888283133e5dfa02d9dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ea1a350-82c9-6649-0d00-b4b1838d67f7&amp;u=a1aHR0cHM6Ly93d3cud2hvLmludC9uZXdzLXJvb20vZmFjdC1zaGVldHMvZGV0YWlsL21lbnRhbC1kaXNvcmRlcnM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=13418e66b915acaf8f7af617f7dc4fd04b9aa3584e078fe5fa35a8b83ce4fcd0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ea1a350-82c9-6649-0d00-b4b1838d67f7&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWVudGFsX2hlYWx0aA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cd279d3a63890f349b60126dcee0f8da98b96566cac51b60e22a622e630e1bb2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ea1a350-82c9-6649-0d00-b4b1838d67f7&amp;u=a1aHR0cHM6Ly93d3cubWF5b2NsaW5pYy5vcmcvaGVhbHRoeS1saWZlc3R5bGUvYWR1bHQtaGVhbHRoL2luLWRlcHRoL21lbnRhbC1oZWFsdGgvYXJ0LTIwMDQ0MDk4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f871320b93c5c8248d637f6824aa9a736c02f285112db620bd405bee91831c33JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ea1a350-82c9-6649-0d00-b4b1838d67f7&amp;u=a1aHR0cHM6Ly9teS5jbGV2ZWxhbmRjbGluaWMub3JnL2hlYWx0aC9kaXNlYXNlcy8yMjI5NS1tZW50YWwtaGVhbHRoLWRpc29yZGVycw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ab281902c1ad3a44c18efb047ddf211072515b75a313433975406f9aa5e9381dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ea1a350-82c9-6649-0d00-b4b1838d67f7&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL21lbnRhbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4ebede5fcb319c1acb06aadfec6b5243b94676e9707b66e5738de5aa6c5669d8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ea1a350-82c9-6649-0d00-b4b1838d67f7&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWVudGFsX2Rpc29yZGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7b5b7dd547c14f2cc87953e60b27d024c60768b31d79cf99efc5821555fd9f7cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ea1a350-82c9-6649-0d00-b4b1838d67f7&amp;u=a1aHR0cHM6Ly93d3cuc2FtaHNhLmdvdi9tZW50YWwtaGVhbHRo&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6679d867cf55fc7f25e32ce1cfe7aeb18e7fd3cbe26fccc9f71daba03397c8fcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ea1a350-82c9-6649-0d00-b4b1838d67f7&amp;u=a1aHR0cHM6Ly93d3cubWF5b2NsaW5pYy5vcmcvZGlzZWFzZXMtY29uZGl0aW9ucy9tZW50YWwtaWxsbmVzcy9zeW1wdG9tcy1jYXVzZXMvc3ljLTIwMzc0OTY4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4d422e6b60c99b6e71bf596dd6a2879db793197a939416616aa22f7b4a1ecf1dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34c0ccff-4eb4-6ddd-1d0c-db1e4f196c7a&amp;u=a1aHR0cHM6Ly93d3cubG9uZ2JlYWNoLmdvdi9oZWFsdGg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=722ffdde6f141c89fa7efb82eb03f5a56b157bab62f505f28c42c83b52ce444bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34c0ccff-4eb4-6ddd-1d0c-db1e4f196c7a&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvSGVhbHRo&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6dbfbcf2cb515ad853331485c765b1bba3ffe4beef82893572af0f9d79e74cd6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34c0ccff-4eb4-6ddd-1d0c-db1e4f196c7a&amp;u=a1aHR0cHM6Ly93d3cuY3N1bGIuZWR1L3N0dWRlbnQtYWZmYWlycy9zdHVkZW50LWhlYWx0aC1zZXJ2aWNlcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b94091c03aa67d8e2db9739fb173cb93993eb81967fb7f50af551279a64cafadJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34c0ccff-4eb4-6ddd-1d0c-db1e4f196c7a&amp;u=a1aHR0cHM6Ly9kaHMubGFjb3VudHkuZ292L2hlYWx0aC1jZW50ZXJzL2hvbWUvbG9uZ2JlYWNoLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a52789abaf1c82b187d7922409ea0eceb5a2af3d6634f6a11fcd4f29a52a7320JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34c0ccff-4eb4-6ddd-1d0c-db1e4f196c7a&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhbG5ld3N0b2RheS5jb20vYXJ0aWNsZXMvMTUwOTk5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=581ebd04eec97c5c3253f7833cae374ce0ed58ff8bd77c32d005a5306f3c04f1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34c0ccff-4eb4-6ddd-1d0c-db1e4f196c7a&amp;u=a1aHR0cHM6Ly93d3cud2VibWQuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3aa92ad0e8fffe6d45c6e051ffebdddecb0bbf78e396db60872af8bfd1b95f9bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34c0ccff-4eb4-6ddd-1d0c-db1e4f196c7a&amp;u=a1aHR0cHM6Ly93d3cuaGVhbHRoLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a1728fae62c0f6df1668a52cbc6e83a0ab00ce9649e66164b6ff2a858d0ae4ceJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34c0ccff-4eb4-6ddd-1d0c-db1e4f196c7a&amp;u=a1aHR0cHM6Ly9kaHMubGFjb3VudHkuZ292Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8e4a5ecba68a3679062f1c28aaeaee22b9876d801c94ef41085f63ea9c11594cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34c0ccff-4eb4-6ddd-1d0c-db1e4f196c7a&amp;u=a1aHR0cHM6Ly93d3cucGloaGVhbHRoLm9yZy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=76d2932aea37d95ff0021db67f43512c00acb439e867b4e0ad86bb840a4a116aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34c0ccff-4eb4-6ddd-1d0c-db1e4f196c7a&amp;u=a1aHR0cHM6Ly93ZWxiZWhlYWx0aC5jb20vbG9jYXRpb25zL2xvbmctYmVhY2gv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d98d6fb168da35a90fa315385d41b150c8a654c51318ab4db16ca64a6ebfb5c7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d4eff96-e532-64de-095c-e877e4ca656f&amp;u=a1aHR0cHM6Ly93d3cucHJpbWFyeS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ba04a03f71e5deaada5a90948091bd4fcfe354b3039a7d0ab8b9d709c2ba5170JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d4eff96-e532-64de-095c-e877e4ca656f&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3ByaW1hcnk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ead808e426207600b712bf081b869b6eb5d1d0e17be1c140bd468b0defbff334JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d4eff96-e532-64de-095c-e877e4ca656f&amp;u=a1aHR0cHM6Ly93d3cubmJjbmV3cy5jb20vcG9saXRpY3MvMjAyNi1wcmltYXJ5LWVsZWN0aW9ucy9jb2xvcmFkby1nb3Zlcm5vci1yZXN1bHRz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5497f1114aec6452ebddd7097cb1874a3f60aca774d4ef1047a29bcc1b322e7eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d4eff96-e532-64de-095c-e877e4ca656f&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3ByaW1hcnk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f5ea85bde25033016140977d74f97b29edeb46875e29ca42932dac69a97156bcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d4eff96-e532-64de-095c-e877e4ca656f&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL3ByaW1hcnk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=056e705179e050c24c4e7470009620716b597d869cac7aa506301a598835b494JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d4eff96-e532-64de-095c-e877e4ca656f&amp;u=a1aHR0cHM6Ly93d3cucHJpbWFyeWdhbWVzLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7109447b2b7a7506a37ab4c681e5927f95cc7a6d1f4978f66293bc2d7618b3c2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d4eff96-e532-64de-095c-e877e4ca656f&amp;u=a1aHR0cHM6Ly93d3cuZm94bmV3cy5jb20vZWxlY3Rpb25zLzIwMjYvcHJpbWFyeS1yZXN1bHRzP21zb2NraWQ9M2Q0ZWZmOTZlNTMyNjRkZTA5NWNlODc3ZTRjYTY1NmY&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=141f38c927d7d4b7368c9974b67a96951d2651316738a2d2110b9b8ce7fe198cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d4eff96-e532-64de-095c-e877e4ca656f&amp;u=a1aHR0cHM6Ly93d3cubmJjbmV3cy5jb20vcG9saXRpY3MvMjAyNi1wcmltYXJ5LWVsZWN0aW9ucy9uYXRpb25hbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=87c9c65c514cc3db56e95c9e31e21c988a7dd1ba13b915a1b69b55eab612cadfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d4eff96-e532-64de-095c-e877e4ca656f&amp;u=a1aHR0cHM6Ly90aGVwcmltYXJ5LmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d525884d125e74658deacf01f179aa9cd882fad3af1348251297d272cccc66dbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d4eff96-e532-64de-095c-e877e4ca656f&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3ByaW1hcnk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=155e9d5251ba687e24d76b867971d6944de73b231ad0e66c58d6e4ab25a23e2aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09c63010-30f4-6da8-33d1-27f131976c5e&amp;u=a1aHR0cHM6Ly93ZWxsbmVzc21hcnQuY29tL3dtX2xvY2F0aW9ucy9tb2Rlc3RvY2Ev&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ef715a6ba809072eddcd89ef556def9ccdb03328146dfe30123de778b033eed6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09c63010-30f4-6da8-33d1-27f131976c5e&amp;u=a1aHR0cHM6Ly93ZWxsbmVzc21hcnQuY29tLz9wb3N0X3R5cGU9d21fbG9jYXRpb25z&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=66a5781481c6f7310d00603c138767f2e70ef06d625575fcb6f265375896f3aaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09c63010-30f4-6da8-33d1-27f131976c5e&amp;u=a1aHR0cHM6Ly9nbG9iYWx3ZWxsbmVzc2luc3RpdHV0ZS5vcmcvd2hhdC1pcy13ZWxsbmVzcy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b0498d5c8b9bef470e5cebcfa92787bc3cdd2c52fcaa68bdfd83df4fed42f900JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09c63010-30f4-6da8-33d1-27f131976c5e&amp;u=a1aHR0cHM6Ly9lZ29kZWZpbmVkLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=468b79d26754592f4833523a86417c3cf8e7f8e636aa755d63764e7c59f6f60dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09c63010-30f4-6da8-33d1-27f131976c5e&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vYml6L2xpdXMtd2VsbG5lc3MtbW9kZXN0bz9tc29ja2lkPTA5YzYzMDEwMzBmNDZkYTgzM2QxMjdmMTMxOTc2YzVl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=18c9c9e85e1b2f360146b641b19359cda41d8685f45c5d3315aa59b83e976f06JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09c63010-30f4-6da8-33d1-27f131976c5e&amp;u=a1aHR0cHM6Ly9hY2Nlc3N3ZWxsbmVzcy5zZXJ2aWNlcy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=453d464278ccaa96dc5304d166eb56e2f9444e9bccf2623abcbc8bd36c395145JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09c63010-30f4-6da8-33d1-27f131976c5e&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vc2VhcmNoP2ZpbmRfZGVzYz10aGUrd2VsbG5lc3MrY2VudGVyK21vZGVzdG8mZmluZF9sb2M9TW9kZXN0byUyQytDQSZtc29ja2lkPTA5YzYzMDEwMzBmNDZkYTgzM2QxMjdmMTMxOTc2YzVl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5fcd3bf1f939c4ebcfa318c2d69ef8e779969a149ac72f5893efd904a38e5f50JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09c63010-30f4-6da8-33d1-27f131976c5e&amp;u=a1aHR0cHM6Ly93d3cud2VsbG5lc3MuY29tL3doYXQtaXMtd2VsbG5lc3M&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fb4d02144cffe2288addd131e3bb7e825b1ca7f1108f02db33ed239030dc3a91JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09c63010-30f4-6da8-33d1-27f131976c5e&amp;u=a1aHR0cHM6Ly93d3cudmFudGFnZWZpdC5pby9lbi9ibG9nL3doYXQtaXMtd2VsbG5lc3Mv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d870f945f541ab011722c0669193b948f463facd954bc590d617a3901c8c079fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09c63010-30f4-6da8-33d1-27f131976c5e&amp;u=a1aHR0cHM6Ly9tYW50cmFoZWFsdGhhbmR3ZWxsbmVzcy5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8f747cc3993cb1d8ddb4d7e9516d1ec154bb6cd3a44acb2af8d9ac628b73b922JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33decbeb-4268-6b80-2204-dc0a43306a19&amp;u=a1aHR0cHM6Ly93d3cub3BlbmNvdW5zZWxpbmcuY29tL2NhbGlmb3JuaWEvc2FuLWZlcm5hbmRv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6366a365aeb577e14a664f8908eee7483d1450ceee193371a78bb16fe638099fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33decbeb-4268-6b80-2204-dc0a43306a19&amp;u=a1aHR0cHM6Ly93ZXN0dmFsbGV5Y291bnNlbGluZy5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ab91dedc732ebda060b15baaeeae08143588dfbe3f2465535721a41dba58be3aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33decbeb-4268-6b80-2204-dc0a43306a19&amp;u=a1aHR0cHM6Ly9yZWVudHJ5Lm5ldHdvcmtvZmNhcmUub3JnL2xvc2FuZ2VsZXMvc2VydmljZXMvYWdlbmN5P3BpZD1TQU5GRVJOQU5ET1ZBTExFWUNPVU5TRUxJTkdDRU5URVJGYW1pbHlDb3Vuc2VsaW5nXzE3NzZfMjFfMQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8877960adb8e375d6c0eaaff715c7e61f5d8eff0f97d8438f0c62f8d225d7b49JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33decbeb-4268-6b80-2204-dc0a43306a19&amp;u=a1aHR0cHM6Ly9sb2NhdG9yLmxhY291bnR5Lmdvdi9sYWMvTG9jYXRpb24vMzA0MTMzNi9zYW4tZmVybmFuZG8tdmFsbGV5LWNvdW5zZWxpbmctY2VudGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c6cbd823a29955292b10083483f4391678b92e2467cbab348d5d416841f68ec6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33decbeb-4268-6b80-2204-dc0a43306a19&amp;u=a1aHR0cHM6Ly93d3cudmFsbGV5Y29tbXVuaXR5Y291bnNlbGluZ2NsaW5pYy5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4ea4dc00e71e8a34b12c9fdc6baaebc90c59793123a7f26a10f32225473b8224JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33decbeb-4268-6b80-2204-dc0a43306a19&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vc2VhcmNoP2NmbHQ9Y19hbmRfbWgmZmluZF9sb2M9U2FuK0Zlcm5hbmRvK1ZhbGxleSUyQytDQSZtc29ja2lkPTMzZGVjYmViNDI2ODZiODAyMjA0ZGMwYTQzMzA2YTE5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=72cc01b4902f86ea4e5e8c630e0d8baa81f007c8d8e63f32671e532c232010daJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33decbeb-4268-6b80-2204-dc0a43306a19&amp;u=a1aHR0cHM6Ly93d3cuY2NyY2NhLm9yZy9yZXNvdXJjZXMvZmFtaWx5LXJlc291cmNlLWRpcmVjdG9yeS9pdGVtL3Nhbi1mZXJuYW5kby12YWxsZXktY291bnNlbGluZy1jZW50ZXIv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c4fe89583cd9ad33581f769c1a3e0c97baa837653d7ff48116eda4c26a912fa9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33decbeb-4268-6b80-2204-dc0a43306a19&amp;u=a1aHR0cHM6Ly93d3cucHN5Y2hvbG9neXRvZGF5LmNvbS91cy90aGVyYXBpc3RzL2NhL3Nhbi1mZXJuYW5kbz9tc29ja2lkPTMzZGVjYmViNDI2ODZiODAyMjA0ZGMwYTQzMzA2YTE5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f86ff4be4797b218d864ce50a11c69d0cd72d7f694a182c7adb7570811642a76JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33decbeb-4268-6b80-2204-dc0a43306a19&amp;u=a1aHR0cHM6Ly93d3cucHN5Y2hvbG9neXRvZGF5LmNvbS91cy90aGVyYXBpc3RzL2NhL3Nhbi1mZXJuYW5kbz9jYXRlZ29yeT1pbi1wZXJzb24mbXNvY2tpZD0zM2RlY2JlYjQyNjg2YjgwMjIwNGRjMGE0MzMwNmExOQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=82366a7d3280b427ee98454e3e83a0e841ae10c10dc44f0b06f8a0bff9ebe893JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33decbeb-4268-6b80-2204-dc0a43306a19&amp;u=a1aHR0cHM6Ly9jaGlsZHRlZW5jb3Vuc2VsaW5nLm9yZy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8120d1d0391afff931f17af9b30fd4a1b5ab3abacd5407a8b17c7f2fce8bcb3bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28f565b9-5d0a-66ed-0b3f-72585c00670b&amp;u=a1aHR0cHM6Ly9tZWRsaW5lcGx1cy5nb3YvcmVoYWJpbGl0YXRpb24uaHRtbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e3a682c0ad3d58d96d0fc9a31dd62f104de75d00da16970e4ec14fade86051a6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28f565b9-5d0a-66ed-0b3f-72585c00670b&amp;u=a1aHR0cHM6Ly93d3cud2hvLmludC9uZXdzLXJvb20vZmFjdC1zaGVldHMvZGV0YWlsL3JlaGFiaWxpdGF0aW9u&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=49346b2690471b81ddc9d7c4193ec944744a955cc97a7c05f7ab9849478518b3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28f565b9-5d0a-66ed-0b3f-72585c00670b&amp;u=a1aHR0cHM6Ly9jbGFzc2ljcmVoYWJpbGl0YXRpb24uY29tL2dyYW5kLXByYWlyaWUv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8f43fe6b37b066b15ef5550f9ba436134765981c9779e5e25b5a63aa6e5b62c4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28f565b9-5d0a-66ed-0b3f-72585c00670b&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vc2VhcmNoP2NmbHQ9cmVoYWJpbGl0YXRpb25fY2VudGVyJmZpbmRfbG9jPUdyYW5kK1ByYWlyaWUlMkMrVFgmbXNvY2tpZD0yOGY1NjViOTVkMGE2NmVkMGIzZjcyNTg1YzAwNjcwYg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b2cab7800db66ea2e6c3ba895a79dd8c1bb0f776ca87faa037d09abeed6d1a1dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28f565b9-5d0a-66ed-0b3f-72585c00670b&amp;u=a1aHR0cHM6Ly9ncmVlbmhvdXNldHJlYXRtZW50LmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4a54a7fad24860eb8c235861e2613ca5b953a4245c4353965794a6586794d5d8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28f565b9-5d0a-66ed-0b3f-72585c00670b&amp;u=a1aHR0cHM6Ly9yZWNvdmVyeS5jb20vZ3JhbmQtcHJhaXJpZS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=106a5295ebef5cc5ec1eabeed91584feb67a34f4b9bae8d0135cc50f3631f5dbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28f565b9-5d0a-66ed-0b3f-72585c00670b&amp;u=a1aHR0cHM6Ly93d3cuYWRkaWN0aW9ucy5jb20vcmVoYWJzL3RleGFzL2dyYW5kLXByYWlyaWUv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c0966168226b9a05f33d8860e7ea2eb22929e46ead5513c5eba336ddf5e9cce9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28f565b9-5d0a-66ed-0b3f-72585c00670b&amp;u=a1aHR0cHM6Ly93d3cucmVoYWIuY29tL3RleGFzL2dyYW5kLXByYWlyaWU&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=34c11892d95715ea25cb51f2882925c0baf55adf2a8a7e4fcc756d56e1ed8c75JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28f565b9-5d0a-66ed-0b3f-72585c00670b&amp;u=a1aHR0cHM6Ly93d3cudHdjLnRleGFzLmdvdi9wcm9ncmFtcy92b2NhdGlvbmFsLXJlaGFiaWxpdGF0aW9u&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5c36a9c5abe5ea1e823f09ce0cda9c5e26eba26cd8708e85bb21ba412750d8eeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28f565b9-5d0a-66ed-0b3f-72585c00670b&amp;u=a1aHR0cHM6Ly9jbGFzc2ljcmVoYWJpbGl0YXRpb24uY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d9efcf16e2edccc7e7c44a54e2aa6e91cbea9632b1ca030a507eda6755c880f2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d143909-face-6eaa-0e08-2ee8fbbe6fa6&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWVkaWNpbmU&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=69261069c63762212db8651439f657cd874b5b8463410839de8ab404e7174313JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d143909-face-6eaa-0e08-2ee8fbbe6fa6&amp;u=a1aHR0cDovL21lZGktY2FsLmRoY3MuY2EuZ292Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d2eb4617270d33b93383bd96e9d71674cfb431fb305a7de7866fd48e5671f5faJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d143909-face-6eaa-0e08-2ee8fbbe6fa6&amp;u=a1aHR0cHM6Ly9iYWlrZS5iYWlkdS5jb20vaXRlbS9tZWRpY2FsLzEwNzc0NDgy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bf4d2413afb25a93022fde370c4b1e60c467df1556b226bfca14ae6fc96fa828JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d143909-face-6eaa-0e08-2ee8fbbe6fa6&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvemhzLyVFOCVBRiU4RCVFNSU4NSVCOC8lRTglOEIlQjElRTglQUYlQUQtJUU2JUIxJTg5JUU4JUFGJUFELSVFNyVBRSU4MCVFNCVCRCU5My9tZWRpY2Fs&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0c6c2ed515e8d42517c6c27097689dc8ab67eb0cb607a67c8c7f46f2943a8edbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d143909-face-6eaa-0e08-2ee8fbbe6fa6&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhbG5ld3N0b2RheS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ad020aea39a5a9143bc74f71e9b28d60f575e495fe27f1b50722ec9f974556f5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d143909-face-6eaa-0e08-2ee8fbbe6fa6&amp;u=a1aHR0cHM6Ly93d3cud2VibWQuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=398be6acafadbd18c3440b9d4c77b7a73be0e32bd679962dd8fb7d1711ec1545JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d143909-face-6eaa-0e08-2ee8fbbe6fa6&amp;u=a1aHR0cHM6Ly9wdWJtZWQubmNiaS5ubG0ubmloLmdvdi8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8c8e3f48dad517137024ca1ca9b9fe302fc67b8b27652a98d560b2973d43501dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d143909-face-6eaa-0e08-2ee8fbbe6fa6&amp;u=a1aHR0cHM6Ly93d3cubmV3cy1tZWRpY2FsLm5ldC8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ed67c2469756be50b9f3b2219d19fa595d59394248ce9308a5b0eca7bd105487JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d143909-face-6eaa-0e08-2ee8fbbe6fa6&amp;u=a1aHR0cHM6Ly93d3cuY29sbGluc2RpY3Rpb25hcnkuY29tL3poL2RpY3Rpb25hcnkvZW5nbGlzaC9tZWRpY2Fs&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d6f2d5099ab6dd8985580fdff3916cb09a810af2a1833abb751f63834d5d52e0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d143909-face-6eaa-0e08-2ee8fbbe6fa6&amp;u=a1aHR0cHM6Ly9tY3dlYi5hcHBzLnByZC5jYW1taXMubWVkaS1jYWwuY2EuZ292Lw&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=97f7b5c22601d90624144e4fe52b79cf2aa01306d6671ccb5600f7afd3849a52JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e011b70-b599-61fa-03bc-0c91b417606f&amp;u=a1aHR0cHM6Ly93d3cud2J0b3duc2hpcC5vcmcvdmlzaXRvcnMvY29tbXVuaXR5X2luZm9ybWF0aW9uL2luZGV4LnBocA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=29092d433d1c50bdf856b332026eeb3c8961bb9a615dd9ef0c3996de1965baf9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e011b70-b599-61fa-03bc-0c91b417606f&amp;u=a1aHR0cHM6Ly93YnRvd25zaGlwLm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=de5f7646f8c9a2d1adc6c78542149b3d1bda033288eef668c4f8c5d4b63d5c11JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e011b70-b599-61fa-03bc-0c91b417606f&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ29tbXVuaXR5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=24e9bbbb3c34ef4dfbbfb2b77997dc162c58bdbaf4c90aeaa6076a47e78c7469JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e011b70-b599-61fa-03bc-0c91b417606f&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2NvbW11bml0eQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3916fd78f9b906ecfe2dbddb0203f19462fc9eb6bbe8e2c7c88be0d9695d0c1cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e011b70-b599-61fa-03bc-0c91b417606f&amp;u=a1aHR0cHM6Ly93d3cuYmxvb21maWVsZHR3cC5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e0105a288c5a7bf528eeda922bc975b84cdc850a92a310b86bf073b493bee8fcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e011b70-b599-61fa-03bc-0c91b417606f&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL2dyb3Vwcy8xMDIyNTM5NjE5ODYxMDgwLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7d17a2860169212fa2ffec436c52f651d27c2327805ed700e9125db5ec24a8d7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e011b70-b599-61fa-03bc-0c91b417606f&amp;u=a1aHR0cHM6Ly93YnBhcmtzLm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9fceb66492d0eb1fd3cd1b8a3857346c2fe83574990d87edf8bd7ec401e04a6cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e011b70-b599-61fa-03bc-0c91b417606f&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvV2VzdF9CbG9vbWZpZWxkX1Rvd25zaGlwLF9NaWNoaWdhbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6d296e97aa9986673379f1d993453f373eab6fd6c66213cc6aa736fca161b078JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e011b70-b599-61fa-03bc-0c91b417606f&amp;u=a1aHR0cHM6Ly9ncmVhdGVyZ29vZC5iZXJrZWxleS5lZHUvY29tbXVuaXR5L2RlZmluaXRpb24&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=467e921ae955f104f7cd50fbcc03f3a45214f5d20386c85727cf3a5742b60fa2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e011b70-b599-61fa-03bc-0c91b417606f&amp;u=a1aHR0cHM6Ly9wdXJlc29jaW9sb2d5LmNvbS93aGF0LWlzLWNvbW11bml0eS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b44ef89822908c3d1df5bb79af743715b6f426b83e7226ade4e944d3d7e92ec1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19f04966-9a9b-6e7c-1d6e-5e879b536f47&amp;u=a1aHR0cHM6Ly93d3cuaG9zcGljZW9mYWxhYmFtYS5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b7967ce185250048de84e37172020d187eec16bca72151b7c0566f83188cbdd1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19f04966-9a9b-6e7c-1d6e-5e879b536f47&amp;u=a1aHR0cHM6Ly9ob3NwaWNlZm91bmRhdGlvbi5vcmcvd2hhdC1pcy1ob3NwaWNlLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f0fc33785793632493879803bd94f0dd33d431af25fa8f812762bda9cb164aadJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19f04966-9a9b-6e7c-1d6e-5e879b536f47&amp;u=a1aHR0cHM6Ly9hbGhvc3BpY2Uub3JnLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=70f4c2eb6684cfdc74877b30b0eb571ee1b2bda1a337d85a2d2befb121ee46c9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19f04966-9a9b-6e7c-1d6e-5e879b536f47&amp;u=a1aHR0cHM6Ly9hbGhvc3BpY2Uub3JnL2hvc3BpY2Uv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0bde4f3192458ae4d41158d6fc5c9e6e7b7853ce7f6f447bc8dff9d535c9c032JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19f04966-9a9b-6e7c-1d6e-5e879b536f47&amp;u=a1aHR0cHM6Ly93d3cuY29tcGFzc3VzLmNvbS9sb2NhdGlvbnMvYWxhYmFtYS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b8859f61fdc7db6ba0c86a03481920a817132f36cdcc5da92d8c318d4fe39d14JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19f04966-9a9b-6e7c-1d6e-5e879b536f47&amp;u=a1aHR0cHM6Ly9ob3NwaWNlb2Zub3J0aGFsYWJhbWEuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3a5c01bd1a2a2c52a7d262f26a6c9d3f7f896a8caac200ebeb6de5f46e258f71JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19f04966-9a9b-6e7c-1d6e-5e879b536f47&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvSG9zcGljZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=071c847e347e01afcf7ddcc4df7b0c83b7cc8d3f923fbfa8f6c08a326827c094JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19f04966-9a9b-6e7c-1d6e-5e879b536f47&amp;u=a1aHR0cHM6Ly93d3cuY29sdW1idXNob3NwaWNlLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=91d2fc50bc38949941a52a96c23cfe1abfa44bb886241817ff08217967a99d9cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19f04966-9a9b-6e7c-1d6e-5e879b536f47&amp;u=a1aHR0cHM6Ly9saGNncm91cC5jb20vbG9jYXRpb25zL2FsYWJhbWEtaG9zcGljZS1jYXJlLW9mLWJpcm1pbmdoYW0v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=27946c9880ff1332c8dfb690f7d5c535e8ea506d31be79f13e0bd23c5e9654bdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19f04966-9a9b-6e7c-1d6e-5e879b536f47&amp;u=a1aHR0cHM6Ly93d3cuaG9zcGljZW9md2VzdGFsLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=31ecf5721167f9b5be34e3544e9d734a634f9788cb0979568ce4071868935d20JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=16908cdf-ad7d-608b-04a6-9b3eac8561eb&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L21lbnRhbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d8e15d9a8ee47e401e4cac1a1087591fb5f81a3925c1619ecc9a161c38808e52JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=16908cdf-ad7d-608b-04a6-9b3eac8561eb&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9NZW50YWxfaGVhbHRo&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2a69221e97450fe4f95cee19cf521a721cca429749bd367a1fc99d3e44f1737fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=16908cdf-ad7d-608b-04a6-9b3eac8561eb&amp;u=a1aHR0cHM6Ly93d3cuY2RjLmdvdi9tZW50YWwtaGVhbHRoL2Fib3V0L2luZGV4Lmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9b30ef51f1f832f5807815305c3f4b7da6052f84732220ac5749c196f6048820JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=16908cdf-ad7d-608b-04a6-9b3eac8561eb&amp;u=a1aHR0cHM6Ly93d3cud2hvLmludC9uZXdzLXJvb20vZmFjdC1zaGVldHMvZGV0YWlsL21lbnRhbC1kaXNvcmRlcnM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=96f3727b239ec26b42a0fd2f0f8dde4c4b7a8443417aee9206dd2e33e038766aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=16908cdf-ad7d-608b-04a6-9b3eac8561eb&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9NZW50YWxfZGlzb3JkZXI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bebcf3f914786d397214a8e7aaa2655812291eaefbd797bb9ac2a8c936c6908aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=16908cdf-ad7d-608b-04a6-9b3eac8561eb&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL21lbnRhbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3d0fac8334beba6f13a6d9e59a0190a7932924792ecb22ca42e5c892b3950435JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=16908cdf-ad7d-608b-04a6-9b3eac8561eb&amp;u=a1aHR0cHM6Ly93d3cubWF5b2NsaW5pYy5vcmcvaGVhbHRoeS1saWZlc3R5bGUvYWR1bHQtaGVhbHRoL2luLWRlcHRoL21lbnRhbC1oZWFsdGgvYXJ0LTIwMDQ0MDk4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1676c887e162d8f0068729f8bacba3464f3e827d7ca27fe33c8ef5bf562c1182JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=16908cdf-ad7d-608b-04a6-9b3eac8561eb&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhbG5ld3N0b2RheS5jb20vYXJ0aWNsZXMvMTU0NTQz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=61896053ef3df1036369593f08d29b8792b76441c7e5d0cf95b7e0bb993c26afJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=16908cdf-ad7d-608b-04a6-9b3eac8561eb&amp;u=a1aHR0cHM6Ly9teS5jbGV2ZWxhbmRjbGluaWMub3JnL2hlYWx0aC9kaXNlYXNlcy8yMjI5NS1tZW50YWwtaGVhbHRoLWRpc29yZGVycw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=110173df8089b1bdce90cf00f72854495a3db8bbff08224d63cd70f522296b3fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=16908cdf-ad7d-608b-04a6-9b3eac8561eb&amp;u=a1aHR0cHM6Ly93d3cuc2FtaHNhLmdvdi9tZW50YWwtaGVhbHRo&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d91f40dd44833ddc893ddbea873f2147ea75e872bb5c2aba7cb392ee882b482cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ca945be-0d3a-6da7-3c87-525f0c8f6c87&amp;u=a1aHR0cHM6Ly93d3cua2Ntby5nb3YvY2l0eS1oYWxsL2RlcGFydG1lbnRzL2hlYWx0aA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cabccc461fc3e2fdd51adb6e8b4cd48ec9dcb8fbbb6376a38e123ae94294646fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ca945be-0d3a-6da7-3c87-525f0c8f6c87&amp;u=a1aHR0cHM6Ly93d3cua2Fuc2FzaGVhbHRoc3lzdGVtLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5a59c232d8f3cb0fb2767c68458247676bb46ea5c8cdd166e8715ad40cb3e105JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ca945be-0d3a-6da7-3c87-525f0c8f6c87&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvSGVhbHRo&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e34705752bd68307915563aa336bb7ae8e45fda6e7f82607d7e46922b4a4bd8bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ca945be-0d3a-6da7-3c87-525f0c8f6c87&amp;u=a1aHR0cHM6Ly93d3cudW5pdmVyc2l0eWhlYWx0aGtjLm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=26d9e6f234e91e0569e38d6ceb6070b8fac5e8cd43525b343a6a8dc0b9ee3e7cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ca945be-0d3a-6da7-3c87-525f0c8f6c87&amp;u=a1aHR0cHM6Ly9oZWFsdGgubW8uZ292L2xvY2FsL2ZpbmQteW91ci1sb2NhbC1wdWJsaWMtaGVhbHRoLWFnZW5jeS9rYW5zYXMtY2l0eS1oZWFsdGgtZGVwYXJ0bWVudA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2e0a3c9eb5c5c436eb4729fcdd482c356f93511c97fdaf6f07e99e38c2bdb1b4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ca945be-0d3a-6da7-3c87-525f0c8f6c87&amp;u=a1aHR0cHM6Ly93d3cubmtjaGVhbHRoLm9yZy9wYXRpZW50cy1hbmQtZ3Vlc3RzL2Zvci1wYXRpZW50cy9hZnRlci15b3VyLXZpc2l0L3lvdXItbWVkaWNhbC1yZWNvcmQvcGF0aWVudC1wb3J0YWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dccb0bf5c82bc053d76902138cb93fb1d48ff3179de0136d83c5ca427268c8beJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ca945be-0d3a-6da7-3c87-525f0c8f6c87&amp;u=a1aHR0cHM6Ly93d3cudW5pdmVyc2l0eWhlYWx0aGtjLm9yZy9wYXRpZW50cy12aXNpdG9ycy9teXVoZWFsdGgv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=590cc4ff2c05d0d983d87a9a0c5eb4979735073c217d4a235be5f62e581d3a25JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ca945be-0d3a-6da7-3c87-525f0c8f6c87&amp;u=a1aHR0cHM6Ly93d3cubmtjaGVhbHRoLm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9c6e92e948d304dbb7a5f138cb465109988d02ba17823fa703ecb634e220d7ecJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ca945be-0d3a-6da7-3c87-525f0c8f6c87&amp;u=a1aHR0cHM6Ly9zd29wZWhlYWx0aC5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=67b0ba4c3b98ecfc6b47a32aa8e87017c074244e5b7784fbeb1ac8fb3c3c8532JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ca945be-0d3a-6da7-3c87-525f0c8f6c87&amp;u=a1aHR0cHM6Ly93d3cuaGVhbHRoLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bdcd57095e9b022aaa846e375ca5eed72c1b71ad947974b2a2708be528e30774JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=112519bb-8fc6-6da7-3850-0e5a8e776c1b&amp;u=a1aHR0cHM6Ly93d3cubWljcm9zb2Z0LmNvbS9lbi11cz9tc29ja2lkPTExMjUxOWJiOGZjNjZkYTczODUwMGU1YThlNzc2YzFi&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=13c139bfad0834e11812d35b00140035213ad6ce16bf018394596c76a1d307ecJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=112519bb-8fc6-6da7-3850-0e5a8e776c1b&amp;u=a1aHR0cHM6Ly9hY2NvdW50Lm1pY3Jvc29mdC5jb20vYWNjb3VudA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ca09c449f63d15f2aa7d434b12a92b8d1662dbcdab46c93b7983b4bafb91a5b5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=112519bb-8fc6-6da7-3850-0e5a8e776c1b&amp;u=a1aHR0cHM6Ly9teWFjY291bnQubWljcm9zb2Z0LmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=df20a3e2fb3fbc38b316d28d020c6e34be2badfbd0e72f922884c944f788f76dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=112519bb-8fc6-6da7-3850-0e5a8e776c1b&amp;u=a1aHR0cHM6Ly93d3cubWljcm9zb2Z0LmNvbS9lbi11cy9taWNyb3NvZnQtMzY1P21zb2NraWQ9MTEyNTE5YmI4ZmM2NmRhNzM4NTAwZTVhOGU3NzZjMWI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9de40afc072880d3b85dfd4526844efbfc20dca80d6278391493e2b1a3bace39JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=112519bb-8fc6-6da7-3850-0e5a8e776c1b&amp;u=a1aHR0cHM6Ly9vdXRsb29rLm9mZmljZS5jb20vbWFpbC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=98a0a969d7df2841fc3a2e8de75c2a094cc1faf8416c5f993ab06f7ff5cc801bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=112519bb-8fc6-6da7-3850-0e5a8e776c1b&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWljcm9zb2Z0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9855872feddaf1823aaab06302935e83b31d8135fbe9b5e682d92155424d9663JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=112519bb-8fc6-6da7-3850-0e5a8e776c1b&amp;u=a1aHR0cHM6Ly9hcHBzLm1pY3Jvc29mdC5jb20vaG9tZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1b6788a712925c23a37dae158743b26e8c7a6fd49946eeebaa2ae2853c1d3c1eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=112519bb-8fc6-6da7-3850-0e5a8e776c1b&amp;u=a1aHR0cHM6Ly9zaWdudXAubGl2ZS5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4abd1b08eafccfa2264bf36c9c476891cb8e9a145a16fa6756b7c93dd10ea83eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=112519bb-8fc6-6da7-3850-0e5a8e776c1b&amp;u=a1aHR0cHM6Ly9teWFjY291bnQubWljcm9zb2Z0LmNvbS9tL2hvbWU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=642bafdf0dabc1bffb1af0d1770a857fa56ba96c06605c203e01462dd2764934JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2912cc04-52fe-61e1-2b31-dbe553166045&amp;u=a1aHR0cHM6Ly9nbG9iYWx3ZWxsbmVzc2luc3RpdHV0ZS5vcmcvd2hhdC1pcy13ZWxsbmVzcy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=98c9550f535cdd9ef6bc300faceef3cb0ac27de99d038f98082afded4834d7d7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2912cc04-52fe-61e1-2b31-dbe553166045&amp;u=a1aHR0cHM6Ly93d3cud2VsbG5lc3MuY29tL3doYXQtaXMtd2VsbG5lc3M&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1683c44c5c47d9d42380ffbf5d728a4bb58e1de51cd57e79223823802fc813d1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2912cc04-52fe-61e1-2b31-dbe553166045&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvV2VsbG5lc3NfKGFsdGVybmF0aXZlX21lZGljaW5lKQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1176fea1b24fc87837eab12f60cadd87db5fe97f8eb6f276130769154ad6783bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2912cc04-52fe-61e1-2b31-dbe553166045&amp;u=a1aHR0cHM6Ly93d3cuaGVhbHRobGluZS5jb20vd2VsbG5lc3M&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0a44411209ca03422d9e65e8cf6a46be01ebac06671f96f927316cbae2691a24JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2912cc04-52fe-61e1-2b31-dbe553166045&amp;u=a1aHR0cHM6Ly93d3cuc2FuZGFsd29vZHdlbGxuZXNzYW5kc3BhLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9841caa585eb7a48da4d29ac0b7be3ebe19eefa78ddf3f300e6e1583aa155ce2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2912cc04-52fe-61e1-2b31-dbe553166045&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vYml6L3NlYS1vZi10cmFucXVpbGl0eS1tYXNzYWdlLWFuZC13ZWxsbmVzcy1lZGdld29vZD9tc29ja2lkPTI5MTJjYzA0NTJmZTYxZTEyYjMxZGJlNTUzMTY2MDQ1&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f6be7dcc90cadc2ad1824eb097071f97b8d8dac22362a9cfb38615245aa88547JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2912cc04-52fe-61e1-2b31-dbe553166045&amp;u=a1aHR0cHM6Ly93d3cuc2FuZGFsd29vZHdlbGxuZXNzYW5kc3BhLmNvbS9hYm91dC11cw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=267f0d5af65b4ccc443f7c1dfeadcfe80447d0f3d7ab55dd26e5f7eff10fa7ebJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2912cc04-52fe-61e1-2b31-dbe553166045&amp;u=a1aHR0cHM6Ly93d3cubWFzc2FnZWJvb2suY29tL3RoZXJhcGlzdHMvU2Vhb2Z0cmFucXVpbGl0eWxsYw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=72e71435176ab4b443cd8a010497382b7dadde2a3dae3004e6e295de3fba9efeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2912cc04-52fe-61e1-2b31-dbe553166045&amp;u=a1aHR0cHM6Ly93d3cuZXZlcnlkYXloZWFsdGguY29tL3dlbGxuZXNzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=09c6bdd8e85ab41fff80b8b5b6bd00c8e1c1c90ed7bf77d57d1cf4d39a8f17c7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2912cc04-52fe-61e1-2b31-dbe553166045&amp;u=a1aHR0cHM6Ly93d3cud2VsbG5lc3NhbGxpYW5jZS5vcmcvcmVzb3VyY2VzLWFuZC10b29scy93ZWxsbmVzcy1kZWZpbmVk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e9690b0cbfd601bcde709d8b223f804c920b3f211876ce0e1343f51cc3e27ba8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=388cad8b-429e-6345-11a6-ba6a432f62c7&amp;u=a1aHR0cHM6Ly9zYWNvdW5zZWxpbmdjZW50ZXIuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c737252c3b561431732154560ea46b77e997e9967391f31144e1aa0f5d282e7dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=388cad8b-429e-6345-11a6-ba6a432f62c7&amp;u=a1aHR0cHM6Ly9uZWVseWNvdW5zZWxpbmcuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=71c97b5fad5ae351178d1bdf57b89ddb55c2b1b76550448f3b6b64a695640dc5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=388cad8b-429e-6345-11a6-ba6a432f62c7&amp;u=a1aHR0cHM6Ly90ZXhhc2NvdW5zZWxpbmcuY2VudGVyL3Nhbi1hbnRvbmlvLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6bdaede70dba8491dd9073ca790e18272def4705670f22c1a9c2758c156ea265JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=388cad8b-429e-6345-11a6-ba6a432f62c7&amp;u=a1aHR0cHM6Ly93d3cub3BlbmNvdW5zZWxpbmcuY29tL1RleGFzL1Nhbi1BbnRvbmlv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=075493b0d7fda5d72262b5d2d80ae3920c6fbddb74febad8823447c6d3166244JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=388cad8b-429e-6345-11a6-ba6a432f62c7&amp;u=a1aHR0cHM6Ly9jb3Vuc2VsaW5nNGxpZmVsbGMuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a62d33a2323e333804931bf30eaec13384a583502e66fa3b61eea34d557fa3f5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=388cad8b-429e-6345-11a6-ba6a432f62c7&amp;u=a1aHR0cHM6Ly93d3cuYW5zY291bnNlbGluZy5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=970962762bdc5fd59e1d17d7c4e734e62a2e78cbfbc8bf251cfad3ccba552f7bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=388cad8b-429e-6345-11a6-ba6a432f62c7&amp;u=a1aHR0cHM6Ly9jY2Fvc2Eub3JnL2NvdW5zZWxpbmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8711a8130a0e17bb1a3e91b4bdba57fa3dec7af6d6974e95a7c870e843cc29cdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=388cad8b-429e-6345-11a6-ba6a432f62c7&amp;u=a1aHR0cHM6Ly93d3cub2xsdXNhLmVkdS9jb21tdW5pdHktY291bnNlbGluZy1zZXJ2aWNlL2luZGV4Lmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1be76dc794f0aada22677f5831f04e1984da38e21afaa9e00083914a33022ffdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=388cad8b-429e-6345-11a6-ba6a432f62c7&amp;u=a1aHR0cHM6Ly9lZHVjYXRpb24udXRzYS5lZHUvY291bnNlbGluZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e74e581ae3019f36f83646d755f9005565374e5a096e9f882b712c06436dbb0dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=388cad8b-429e-6345-11a6-ba6a432f62c7&amp;u=a1aHR0cHM6Ly93d3cuYWxpZ25lZG1pbmRjb3Vuc2VsaW5nLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=21fc84b1fde29cb9f3a34818413333a98856583ec82e98561b3014cb7c89d800JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b45a2c4-fead-61ba-141e-b525ff8a60ed&amp;u=a1aHR0cHM6Ly9tZXRob2Rpc3RyZWhhYi5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e6df2bf98e9600c6dce495cbca8f0e52bd839d9f2e6354de583e413f3728b844JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b45a2c4-fead-61ba-141e-b525ff8a60ed&amp;u=a1aHR0cHM6Ly9tZWRsaW5lcGx1cy5nb3YvcmVoYWJpbGl0YXRpb24uaHRtbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c0b3250c92da0879df8b67003997e1da92498d3da57db71efd542265c1d863b8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b45a2c4-fead-61ba-141e-b525ff8a60ed&amp;u=a1aHR0cDovL3d3dy5tZHJzLm1zLmdvdi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c989b4b4c183d2fcfa12e6e93d3a9c34e34497f140b86a6030d992f162909032JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b45a2c4-fead-61ba-141e-b525ff8a60ed&amp;u=a1aHR0cHM6Ly93d3cubXMuZ292L2FnZW5jaWVzL21pc3Npc3NpcHBpLWRlcGFydG1lbnQtcmVoYWJpbGl0YXRpb24tc2VydmljZXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f73db1786c91dd48d59abde62bc31e3eced06d49159e5f9fd5d28e1dfb1ba672JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b45a2c4-fead-61ba-141e-b525ff8a60ed&amp;u=a1aHR0cHM6Ly9tZXRob2Rpc3RyZWhhYi5vcmcvbG9jYXRpb25zL2phY2tzb24vaW5wYXRpZW50Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7ea844a0986dc1f5943de9cf250c0eaa7a483f6f72656241420c5c4ea49087b7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b45a2c4-fead-61ba-141e-b525ff8a60ed&amp;u=a1aHR0cHM6Ly93d3cudW1jLmVkdS9oZWFsdGhjYXJlL3JlaGFiaWxpdGF0aW9uJTIwc2VydmljZXMvcmVoYWJpbGl0YXRpb25faG9tZS5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=70d110688346d02bb595e62e15adb85fddaa276ea53d406d241bcc80df8c8a28JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b45a2c4-fead-61ba-141e-b525ff8a60ed&amp;u=a1aHR0cHM6Ly93d3cucmVoYWIuY29tL21yYy1lYXN0LWNhbXB1cy1tZXRob2Rpc3QtcmVoYWJpbGl0YXRpb24tY2VudGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e45f3d7248326393a7ad861c8cd5e832fa951725f2f526f119d9d559a4f6e1aeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b45a2c4-fead-61ba-141e-b525ff8a60ed&amp;u=a1aHR0cHM6Ly93d3cubWRycy5tcy5nb3Yvdm9jYXRpb25hbC1yZWhhYmlsaXRhdGlvbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b3f4c4a1c1e169aab26758bffe6d8327a53622556218cf65bd279d8904fd11caJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b45a2c4-fead-61ba-141e-b525ff8a60ed&amp;u=a1aHR0cHM6Ly9yZWNvdmVyeS5jb20vamFja3Nvbi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a930d01d42faffc9c59ea24224626cac59fecb98e710784c145b3203957d62d0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b45a2c4-fead-61ba-141e-b525ff8a60ed&amp;u=a1aHR0cHM6Ly9pbm1vdGlvbnJlaGFibGxjLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b2ae9dd0a06b51585a58c5de242c00f3c9395c4e1f7c7e24e959f4e2f1456d5cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0dbafb52-5ee8-6d04-21c0-ecb35f1e6c65&amp;u=a1aHR0cHM6Ly93d3cud2VibWQuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=16f3b0b5677135a208a9551426203e78e3fee13b62991db1a19e2a8aabed6749JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0dbafb52-5ee8-6d04-21c0-ecb35f1e6c65&amp;u=a1aHR0cHM6Ly93d3cubG9uZXN0YXJmYW1pbHkub3JnLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a309a0b862c56dcc8e39bbefd9f6b31cfc6e95bfafd8d5b3910fd1fb28320c6fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0dbafb52-5ee8-6d04-21c0-ecb35f1e6c65&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9NZWRpY2luZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6b7efb0d43210d3d395116d001ed979d9741aa08ad88cc02e88ec62e66fe1e55JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0dbafb52-5ee8-6d04-21c0-ecb35f1e6c65&amp;u=a1aHR0cHM6Ly93d3cuaGNhaG91c3RvbmhlYWx0aGNhcmUuY29tL2xvY2F0aW9ucy9jb25yb2U&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5b9609d10cff60317f1d8bc230defb2b2082e3079e516056520fcbdcb38e6feaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0dbafb52-5ee8-6d04-21c0-ecb35f1e6c65&amp;u=a1aHR0cHM6Ly9jbHMuaGVhbHRoL2xvY2F0aW9ucy9wcmltYXJ5LWNhcmUtY29ucm9l&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cb23583a7128e8d25b7de1b9728221b6429bafdba5ff4ea4503fc7544e763ee7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0dbafb52-5ee8-6d04-21c0-ecb35f1e6c65&amp;u=a1aHR0cHM6Ly9nZW5lc2lzZG9jdG9ycy5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=70aaa903bb52fef6f5e32b0e67b523afdda3d4a5c9e4201518567c9b909732a2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0dbafb52-5ee8-6d04-21c0-ecb35f1e6c65&amp;u=a1aHR0cHM6Ly93d3cuY29tbW9uc3Bpcml0Lm9yZy9maW5kLWEtbG9jYXRpb24vcHJpbWFyeS1jYXJlLWJheWxvci1zdC1sdWtlcy1tZWRpY2FsLWdyb3VwLWNvbnJvZS10eC0xMzY0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b4e9067ee0f9680959313bc045798705b331b2d1e220c278c94a5959bb906cbbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0dbafb52-5ee8-6d04-21c0-ecb35f1e6c65&amp;u=a1aHR0cHM6Ly93d3cudmlsbGFnZW1lZGljYWwuY29tL2xvY2F0aW9ucy90ZXhhcy8xMTIwLW4tbG9vcC0zMzYtdy1zdWl0ZS1hLWNvbnJvZS10eC03NzMwMQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5e0e7e8b0af4d95f29a8c211f3fac9d5af36d00cb6f294fac1501b38f604ffa6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0dbafb52-5ee8-6d04-21c0-ecb35f1e6c65&amp;u=a1aHR0cHM6Ly93d3cuZmFtaWx5bGlmZW1lZGljYWwuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6e27b438a1641b0cb746edb43e74d7d6cc0deccc4f9279b24c9eae0efb204b2bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0dbafb52-5ee8-6d04-21c0-ecb35f1e6c65&amp;u=a1aHR0cHM6Ly93d3cuYS1tZWRpbmMuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e79af2326df29e743d23a46e1ddf1e55cf34502badf0ed7f8fed7b1ec42ae653JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0edfd352-e58e-6f03-3c30-c4b3e4456ede&amp;u=a1aHR0cHM6Ly93d3cuYWRhbXN0YXguY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=54afd389c7ab46ad8f22dbe6955c0a5d028658689df5f64f91e320304957b363JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0edfd352-e58e-6f03-3c30-c4b3e4456ede&amp;u=a1aHR0cHM6Ly9oZWxwZXIuYWRhbXN0YXhmb3Jtcy5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=99b75b0ec684351ad9d9fc79f2adc2c09160f78b35f7f62beb1392fe0d5c6d92JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0edfd352-e58e-6f03-3c30-c4b3e4456ede&amp;u=a1aHR0cHM6Ly93d3cuYWRhbXN0YXguY29tL2VmaWxl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=74cda10473ca230c807fb3bb42273d7554e1b5d7bb4c6d196f8c5c21dbdd753fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0edfd352-e58e-6f03-3c30-c4b3e4456ede&amp;u=a1aHR0cHM6Ly93d3cuYWRhbXN0YXguY29tL3doYXRzLW5ldw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ed5f80047878aacb7904f7c2ff34e244e84b790f20b29d2f8fb2f63bac9490d5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0edfd352-e58e-6f03-3c30-c4b3e4456ede&amp;u=a1aHR0cHM6Ly9hcnRpY2xlcy5hZGFtc3RheGZvcm1zLmNvbS9lbi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e9cf1947d7b41d25947f67fadaab0154a5ba597f75a85c309cad2f4ca4a599d8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0edfd352-e58e-6f03-3c30-c4b3e4456ede&amp;u=a1aHR0cHM6Ly9hcnRpY2xlcy5hZGFtc3RheGZvcm1zLmNvbS9lbi9hcnRpY2xlcy81ODg2Nzk4LWFib3V0LWVmaWxpbmc&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=63d740d81ad42871c81b8d9074f0c82fe140c9cd7bba731d1e0d0e9c4f04a776JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0edfd352-e58e-6f03-3c30-c4b3e4456ede&amp;u=a1aHR0cHM6Ly9jbXBsaW1pdGVkLmNvbS9hZGFtcy10YXgtZm9ybXMtaGVscGVyLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=06275c36f13c1e74a56f880280fb766a1d5be69c5f35f87be0bf83fe7c0611ccJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0edfd352-e58e-6f03-3c30-c4b3e4456ede&amp;u=a1aHR0cHM6Ly9hcnRpY2xlcy5hZGFtc3RheGZvcm1zLmNvbS9lbi9hcnRpY2xlcy8xMTMyNzYxOC12aWV3aW5nLXByZXZpb3VzLXllYXJzLWZvcm1zLXdpdGgtYWRhbXMtdGF4LWZvcm1zLWhlbHBlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bcaf8b1b975d5e8a3a668c8eb598188292102b8fbf64c204db6c46f7b3f8ecb4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0edfd352-e58e-6f03-3c30-c4b3e4456ede&amp;u=a1aHR0cHM6Ly9hcnRpY2xlcy5hZGFtc3RheGZvcm1zLmNvbS9lbi9jb2xsZWN0aW9ucy8xMDI0MjQyMC1sb2dnaW5nLWluLXNpZ24tdXA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b24e771d77375bfab11640354cf4660dea0ef6cc41e91f64752015e89adfb548JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0edfd352-e58e-6f03-3c30-c4b3e4456ede&amp;u=a1aHR0cHM6Ly9hcnRpY2xlcy5hZGFtc3RheGZvcm1zLmNvbS9lbi9jb2xsZWN0aW9ucy8zMTU2NjY1LWxvZ2dpbmctaW4teW91ci1hY2NvdW50&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=eadf9b8dfb35f973224758b36129d72bbf814db0a4fbec950b20e7e9965b3dfbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01cfa96a-8a80-6cca-147f-be8b8b0e6dba&amp;u=a1aHR0cHM6Ly93d3cucmVhbGVzdGF0ZS5jby5uei9wcm9wZXJ0eS84NC1raXJrLXN0cmVldC1vdGFraS1rYXBpdGktY29hc3Qtd2VsbGluZ3Rvbi90NTBjN2s5bmM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=89d1d9e63d823bb0832410d3208609781c6b94b8989948d9c132043b57c53c70JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01cfa96a-8a80-6cca-147f-be8b8b0e6dba&amp;u=a1aHR0cHM6Ly93d3cudGFsbHBvcHB5LmNvLm56L2hvbWVzLWZvci1zYWxlL3Byb3BlcnR5LWRldGFpbC9UUE9UNjI1Mw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f26ac56659a88884d23d26c7bc9d033167f359a05082ca94d35e4e0d45c0c603JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01cfa96a-8a80-6cca-147f-be8b8b0e6dba&amp;u=a1aHR0cHM6Ly93d3cucmF0ZW15YWdlbnQuY28ubnovcHJvcGVydHkvODQta2lyay1zdC1vdGFraS13ZWxsaW5ndG9uLTRkeWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e1f72ee8867ac7fbb6d947a1f6f53417815b5c3ae8fce2af04127e236db44722JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01cfa96a-8a80-6cca-147f-be8b8b0e6dba&amp;u=a1aHR0cHM6Ly93d3cucmF0ZW15YWdlbnQuY28ubnovcmVhbC1lc3RhdGUtYWdlbmN5L2tlbGx5Y28tb3Rha2ktYW5kY28tcmVhbHR5LTExLWx0ZC9wcm9wZXJ0eS1saXN0aW5ncy84NC1raXJrLXN0LW90YWtpLWFhcGlmMQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0f502b389218cc4fe5f739d2fe1375f7b554e0a4114ddb2d83f813db012b11b6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01cfa96a-8a80-6cca-147f-be8b8b0e6dba&amp;u=a1aHR0cHM6Ly93d3cucHJvcGVydHl2YWx1ZS5jby5uei93ZWxsaW5ndG9uL2thcGl0aS1jb2FzdC1kaXN0cmljdC9vdGFraS01NTEyL2tpcmstc3RyZWV0LzM0MDUzP3BhZ2U9NA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7368cdbc993202df0c930313f9005d3ef73a695d6edf56970c157325783a3304JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01cfa96a-8a80-6cca-147f-be8b8b0e6dba&amp;u=a1aHR0cHM6Ly9yZW50b2xhLmNvbS9mb3ItcmVudC9ob3VzZS9uei9vdGFraQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dd654462fc4a6a04bd18b20d4b4cd8c27cac70099c78bcde1dabd97f9502a636JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01cfa96a-8a80-6cca-147f-be8b8b0e6dba&amp;u=a1aHR0cHM6Ly9yZW50b2xhLmNvbS9mb3ItcmVudC9uei9vdGFraQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=817e541be181237e8179b713d7963b8319b7cdae5c1fdca302a7b0a8ba36b0a0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01cfa96a-8a80-6cca-147f-be8b8b0e6dba&amp;u=a1aHR0cHM6Ly9yZW50b2xhLmNvLm56L2xpc3RpbmdzL290YWtpLTQtYmVkcm9vbXMtcDBiYzhkYQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=db480156c9b64b64ea2aeec5001080ccbcbcbdb398ff0dd7ad8f0b4627b51630JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01cfa96a-8a80-6cca-147f-be8b8b0e6dba&amp;u=a1aHR0cHM6Ly93d3cucmVhbGVzdGF0ZS5jby5uei9yZXNpZGVudGlhbC9zYWxlL3dlbGxpbmd0b24va2FwaXRpLWNvYXN0L290YWtp&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cae33915b0997f633e1c74b0d4d285ab62159d6dc3ba4dfa580107d7348f814dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01cfa96a-8a80-6cca-147f-be8b8b0e6dba&amp;u=a1aHR0cHM6Ly9tYXBzLmdvb2dsZS5jby5uei9tYXBmaWxlcy9ob21lMy5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fc48f501c9dc53571c7543d9b9954c335b0683e843cfaee8bd3d34866d89fa8dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13e5b4be-a957-61be-24c3-a35fa86560ac&amp;u=a1aHR0cHM6Ly93d3cuYXBwbGUuY29tL2FpcnBvZHMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3c16b87a5f72b4252850ba93eb9bcadc9a206d424ed0d6c2150bd8b961d2c62bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13e5b4be-a957-61be-24c3-a35fa86560ac&amp;u=a1aHR0cHM6Ly93d3cuYXBwbGUuY29tL2RlL2FpcnBvZHMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cec0e7deff28dbc0f94c0d9ba38aae9e19881e1c9e63d490306f74f01164ed4dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13e5b4be-a957-61be-24c3-a35fa86560ac&amp;u=a1aHR0cHM6Ly9zdXBwb3J0LmFwcGxlLmNvbS9ndWlkZS9haXJwb2RzL3dlbGNvbWUvd2Vi&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a99bd75c27c5def0547a70fd83df96b4104f9a867dfb5fd94c018cc8f0f39bb2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13e5b4be-a957-61be-24c3-a35fa86560ac&amp;u=a1aHR0cHM6Ly9zdXBwb3J0LmFwcGxlLmNvbS9lbi11cy9kb2NzL2FpcnBvZHM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=23e73b1d375ad7502380002a64b12d758baf2ec5677c7bc4b21a5c677639b47cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13e5b4be-a957-61be-24c3-a35fa86560ac&amp;u=a1aHR0cHM6Ly9kaXNjdXNzaW9ucy5hcHBsZS5jb20vdGhyZWFkLzI1NDQxOTA2OA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a5b86fc0e3fe8334803a711bf09b6c9292e75b9c7d7a39eff364bd4edb1ca1dfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13e5b4be-a957-61be-24c3-a35fa86560ac&amp;u=a1aHR0cHM6Ly9kaXNjdXNzaW9ucy5hcHBsZS5jb20vdGhyZWFkLzI1NTA1NDUyOA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0b8af1dbea31a0e1ebb4ae3590b48216c54eed41f0ea17bd68bdb51880a0544bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13e5b4be-a957-61be-24c3-a35fa86560ac&amp;u=a1aHR0cHM6Ly9jb21tdW5pdGllcy5hcHBsZS5jb20vZnIvdGhyZWFkLzI1NTc2OTUyMQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=47136d5c61ea5142b90435e18c1dda8bb2b90f8f72bea495f8f000d4ffba837dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13e5b4be-a957-61be-24c3-a35fa86560ac&amp;u=a1aHR0cHM6Ly93d3cuYXBwbGUuY29tL2luL2FpcnBvZHMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a7e06fc726a8f9e185965d5a43d885ff5dec9110e61c9e4c27c14bc10ca6fe2aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13e5b4be-a957-61be-24c3-a35fa86560ac&amp;u=a1aHR0cHM6Ly93d3cuYXBwbGUuY29tL2JyL2FpcnBvZHMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=164b2ec748d75897e4e63ee32c2a07d0bb0b0d6f3789b67cdc254c8414ef04a8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13e5b4be-a957-61be-24c3-a35fa86560ac&amp;u=a1aHR0cHM6Ly93d3cuYXBwbGUuY29tL2FpcnBvZHMtbWF4Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=feef49ca361fc5e74f71ff0ecd436819a148ff3408dc0321a2fdb3deab0283a2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dd6dc8e-92ad-6178-31fd-cb6f936f60f0&amp;u=a1aHR0cHM6Ly93d3cucHJpbWFyeS5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0a61e7d0331807a70f4df011ead298f3f337a164d9bae0723ccd53472a7ea949JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dd6dc8e-92ad-6178-31fd-cb6f936f60f0&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3ByaW1hcnk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bebd2726e5d42cf6c71032dcb6ac802e0709a11cace6308a2b946f6815780ef0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dd6dc8e-92ad-6178-31fd-cb6f936f60f0&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3ByaW1hcnk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c0c039d54cfdc270f4888abb959f20d3212862ad850f47dd1067d16c392e71c3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dd6dc8e-92ad-6178-31fd-cb6f936f60f0&amp;u=a1aHR0cHM6Ly9hcG5ld3MuY29tL3Byb2plY3RzL2VsZWN0aW9ucy0yMDI2L21pbm5lc290YS1wcmltYXJ5LXJlc3VsdHMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e18a12c02c03965d786bb452395c3e4fb6e8b9a859ff7351ca653baff8e7c81aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dd6dc8e-92ad-6178-31fd-cb6f936f60f0&amp;u=a1aHR0cHM6Ly90aGVwcmltYXJ5LmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4d2d03ea22f683706934f150c48eb457d588c5443c69ba190bb294f8cea1d6ddJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dd6dc8e-92ad-6178-31fd-cb6f936f60f0&amp;u=a1aHR0cHM6Ly93d3cucHJpbWFyeWdhbWVzLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0224f7fcd8440706dc8866a401604c9668120d7f6be952b2b0ca3697d52f413fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dd6dc8e-92ad-6178-31fd-cb6f936f60f0&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL3ByaW1hcnk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9e7d374d43be8cdfd50f7bf3872a43a2af8ce00c8e1cdce590cd062c1283e0c1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dd6dc8e-92ad-6178-31fd-cb6f936f60f0&amp;u=a1aHR0cHM6Ly93d3cubmJjbmV3cy5jb20vcG9saXRpY3MvMjAyNi1wcmltYXJ5LWVsZWN0aW9ucy9uYXRpb25hbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bf846f35b3385ce28ae330c30616bc65c0c6c55d6198b727110e10b819fd60caJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dd6dc8e-92ad-6178-31fd-cb6f936f60f0&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3ByaW1hcnk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=147e347c60c3c282c87f178a6af9ed4020b87364114edef467f024242fc4ca74JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dd6dc8e-92ad-6178-31fd-cb6f936f60f0&amp;u=a1aHR0cHM6Ly93d3cuZm94bmV3cy5jb20vZWxlY3Rpb25zLzIwMjYvcHJpbWFyeS1yZXN1bHRzP21zb2NraWQ9M2RkNmRjOGU5MmFkNjE3ODMxZmRjYjZmOTM2ZjYwZjA&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>
+  </si>
+  <si>
+    <t>Sea Point</t>
+  </si>
+  <si>
+    <t>Green Point</t>
+  </si>
+  <si>
+    <t>Woodstock</t>
+  </si>
+  <si>
+    <t>Observatory</t>
   </si>
   <si>
     <t>Bing</t>
@@ -934,7 +1180,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H130"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -968,19 +1214,19 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C2" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="G2" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H2" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -988,19 +1234,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="G3" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H3" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1008,19 +1254,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C4" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="G4" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H4" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1028,19 +1274,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="G5" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H5" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1048,19 +1294,19 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C6" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="G6" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H6" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1068,19 +1314,19 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="G7" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H7" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1088,19 +1334,19 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="G8" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H8" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1108,19 +1354,19 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="G9" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H9" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1128,19 +1374,19 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="G10" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H10" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1148,19 +1394,19 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="G11" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H11" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1168,19 +1414,19 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>110</v>
+        <v>149</v>
       </c>
       <c r="G12" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H12" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1188,19 +1434,19 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>111</v>
+        <v>150</v>
       </c>
       <c r="G13" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H13" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1208,19 +1454,19 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="G14" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H14" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1228,19 +1474,19 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>113</v>
+        <v>152</v>
       </c>
       <c r="G15" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H15" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1248,19 +1494,19 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="G16" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H16" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1268,19 +1514,19 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>115</v>
+        <v>154</v>
       </c>
       <c r="G17" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H17" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1288,19 +1534,19 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C18" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>116</v>
+        <v>155</v>
       </c>
       <c r="G18" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H18" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1308,19 +1554,19 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>117</v>
+        <v>156</v>
       </c>
       <c r="G19" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H19" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1328,19 +1574,19 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C20" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>118</v>
+        <v>157</v>
       </c>
       <c r="G20" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H20" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1348,19 +1594,19 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C21" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>119</v>
+        <v>158</v>
       </c>
       <c r="G21" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H21" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1368,19 +1614,19 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C22" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="G22" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H22" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1388,19 +1634,19 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C23" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="G23" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H23" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1408,19 +1654,19 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C24" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>122</v>
+        <v>161</v>
       </c>
       <c r="G24" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H24" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1428,19 +1674,19 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C25" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>123</v>
+        <v>162</v>
       </c>
       <c r="G25" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H25" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1448,19 +1694,19 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C26" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>124</v>
+        <v>163</v>
       </c>
       <c r="G26" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H26" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1468,19 +1714,19 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C27" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>125</v>
+        <v>164</v>
       </c>
       <c r="G27" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H27" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1488,19 +1734,19 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C28" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>126</v>
+        <v>165</v>
       </c>
       <c r="G28" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H28" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1508,19 +1754,19 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C29" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>127</v>
+        <v>166</v>
       </c>
       <c r="G29" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H29" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1528,19 +1774,19 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C30" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>128</v>
+        <v>167</v>
       </c>
       <c r="G30" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H30" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1548,19 +1794,19 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C31" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>129</v>
+        <v>168</v>
       </c>
       <c r="G31" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H31" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1568,19 +1814,19 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C32" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>130</v>
+        <v>169</v>
       </c>
       <c r="G32" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H32" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1588,19 +1834,19 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C33" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>131</v>
+        <v>170</v>
       </c>
       <c r="G33" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H33" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1608,19 +1854,19 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>132</v>
+        <v>171</v>
       </c>
       <c r="G34" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H34" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1628,19 +1874,19 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C35" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>133</v>
+        <v>172</v>
       </c>
       <c r="G35" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H35" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1648,19 +1894,19 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C36" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="G36" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H36" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1668,19 +1914,19 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C37" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>135</v>
+        <v>174</v>
       </c>
       <c r="G37" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H37" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1688,19 +1934,19 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C38" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>136</v>
+        <v>175</v>
       </c>
       <c r="G38" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H38" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1708,19 +1954,19 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C39" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>137</v>
+        <v>176</v>
       </c>
       <c r="G39" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H39" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1728,19 +1974,19 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C40" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>138</v>
+        <v>177</v>
       </c>
       <c r="G40" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H40" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1748,19 +1994,19 @@
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C41" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="G41" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H41" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1768,19 +2014,19 @@
         <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C42" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>140</v>
+        <v>179</v>
       </c>
       <c r="G42" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H42" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1788,19 +2034,19 @@
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C43" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="G43" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H43" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1808,19 +2054,19 @@
         <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C44" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>142</v>
+        <v>181</v>
       </c>
       <c r="G44" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H44" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1828,19 +2074,19 @@
         <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C45" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>143</v>
+        <v>182</v>
       </c>
       <c r="G45" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H45" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1848,19 +2094,19 @@
         <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C46" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>144</v>
+        <v>183</v>
       </c>
       <c r="G46" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H46" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -1868,19 +2114,19 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C47" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>145</v>
+        <v>184</v>
       </c>
       <c r="G47" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H47" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -1888,19 +2134,19 @@
         <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C48" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>146</v>
+        <v>185</v>
       </c>
       <c r="G48" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H48" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -1908,19 +2154,19 @@
         <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C49" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
       <c r="G49" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H49" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -1928,19 +2174,19 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C50" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>148</v>
+        <v>187</v>
       </c>
       <c r="G50" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H50" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -1948,19 +2194,19 @@
         <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C51" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>149</v>
+        <v>188</v>
       </c>
       <c r="G51" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H51" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -1968,19 +2214,19 @@
         <v>58</v>
       </c>
       <c r="B52" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C52" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>150</v>
+        <v>189</v>
       </c>
       <c r="G52" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H52" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -1988,19 +2234,19 @@
         <v>59</v>
       </c>
       <c r="B53" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C53" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>151</v>
+        <v>190</v>
       </c>
       <c r="G53" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H53" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -2008,19 +2254,19 @@
         <v>60</v>
       </c>
       <c r="B54" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C54" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>152</v>
+        <v>191</v>
       </c>
       <c r="G54" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H54" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -2028,19 +2274,19 @@
         <v>61</v>
       </c>
       <c r="B55" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C55" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>153</v>
+        <v>192</v>
       </c>
       <c r="G55" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H55" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -2048,19 +2294,19 @@
         <v>62</v>
       </c>
       <c r="B56" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C56" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>154</v>
+        <v>193</v>
       </c>
       <c r="G56" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H56" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -2068,19 +2314,19 @@
         <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C57" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>155</v>
+        <v>194</v>
       </c>
       <c r="G57" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H57" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -2088,19 +2334,19 @@
         <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C58" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>156</v>
+        <v>195</v>
       </c>
       <c r="G58" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H58" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -2108,19 +2354,19 @@
         <v>65</v>
       </c>
       <c r="B59" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C59" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>157</v>
+        <v>196</v>
       </c>
       <c r="G59" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H59" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -2128,19 +2374,19 @@
         <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C60" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>158</v>
+        <v>197</v>
       </c>
       <c r="G60" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H60" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2148,19 +2394,19 @@
         <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C61" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>159</v>
+        <v>198</v>
       </c>
       <c r="G61" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H61" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2168,19 +2414,19 @@
         <v>68</v>
       </c>
       <c r="B62" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C62" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>160</v>
+        <v>199</v>
       </c>
       <c r="G62" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H62" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2188,19 +2434,19 @@
         <v>69</v>
       </c>
       <c r="B63" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C63" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>161</v>
+        <v>200</v>
       </c>
       <c r="G63" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H63" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2208,19 +2454,19 @@
         <v>70</v>
       </c>
       <c r="B64" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C64" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="G64" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H64" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2228,19 +2474,19 @@
         <v>71</v>
       </c>
       <c r="B65" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C65" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>163</v>
+        <v>202</v>
       </c>
       <c r="G65" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H65" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2248,19 +2494,19 @@
         <v>72</v>
       </c>
       <c r="B66" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C66" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>164</v>
+        <v>203</v>
       </c>
       <c r="G66" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H66" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2268,19 +2514,19 @@
         <v>73</v>
       </c>
       <c r="B67" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C67" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>165</v>
+        <v>204</v>
       </c>
       <c r="G67" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H67" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2288,19 +2534,19 @@
         <v>74</v>
       </c>
       <c r="B68" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C68" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>166</v>
+        <v>205</v>
       </c>
       <c r="G68" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H68" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2308,19 +2554,19 @@
         <v>75</v>
       </c>
       <c r="B69" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C69" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>167</v>
+        <v>206</v>
       </c>
       <c r="G69" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H69" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -2328,19 +2574,19 @@
         <v>76</v>
       </c>
       <c r="B70" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C70" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>168</v>
+        <v>207</v>
       </c>
       <c r="G70" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H70" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2348,19 +2594,19 @@
         <v>77</v>
       </c>
       <c r="B71" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C71" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="G71" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H71" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -2368,19 +2614,19 @@
         <v>78</v>
       </c>
       <c r="B72" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C72" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>170</v>
+        <v>209</v>
       </c>
       <c r="G72" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H72" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -2388,19 +2634,19 @@
         <v>79</v>
       </c>
       <c r="B73" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C73" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>171</v>
+        <v>210</v>
       </c>
       <c r="G73" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H73" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -2408,19 +2654,19 @@
         <v>80</v>
       </c>
       <c r="B74" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C74" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>172</v>
+        <v>211</v>
       </c>
       <c r="G74" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H74" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -2428,19 +2674,19 @@
         <v>81</v>
       </c>
       <c r="B75" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C75" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>173</v>
+        <v>212</v>
       </c>
       <c r="G75" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H75" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -2448,19 +2694,19 @@
         <v>82</v>
       </c>
       <c r="B76" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C76" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>174</v>
+        <v>213</v>
       </c>
       <c r="G76" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H76" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -2468,19 +2714,19 @@
         <v>83</v>
       </c>
       <c r="B77" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C77" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>175</v>
+        <v>214</v>
       </c>
       <c r="G77" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H77" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -2488,19 +2734,19 @@
         <v>84</v>
       </c>
       <c r="B78" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C78" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>176</v>
+        <v>215</v>
       </c>
       <c r="G78" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H78" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -2508,19 +2754,19 @@
         <v>85</v>
       </c>
       <c r="B79" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C79" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>177</v>
+        <v>216</v>
       </c>
       <c r="G79" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H79" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -2528,19 +2774,19 @@
         <v>86</v>
       </c>
       <c r="B80" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C80" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>178</v>
+        <v>217</v>
       </c>
       <c r="G80" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H80" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -2548,19 +2794,19 @@
         <v>87</v>
       </c>
       <c r="B81" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C81" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>179</v>
+        <v>218</v>
       </c>
       <c r="G81" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H81" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -2568,19 +2814,19 @@
         <v>88</v>
       </c>
       <c r="B82" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C82" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>180</v>
+        <v>219</v>
       </c>
       <c r="G82" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H82" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -2588,19 +2834,19 @@
         <v>89</v>
       </c>
       <c r="B83" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C83" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>181</v>
+        <v>220</v>
       </c>
       <c r="G83" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H83" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -2608,19 +2854,19 @@
         <v>90</v>
       </c>
       <c r="B84" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C84" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>182</v>
+        <v>221</v>
       </c>
       <c r="G84" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H84" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -2628,19 +2874,19 @@
         <v>91</v>
       </c>
       <c r="B85" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C85" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>183</v>
+        <v>222</v>
       </c>
       <c r="G85" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H85" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -2648,19 +2894,19 @@
         <v>92</v>
       </c>
       <c r="B86" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C86" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>184</v>
+        <v>223</v>
       </c>
       <c r="G86" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H86" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -2668,19 +2914,19 @@
         <v>93</v>
       </c>
       <c r="B87" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C87" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>185</v>
+        <v>224</v>
       </c>
       <c r="G87" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H87" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -2688,19 +2934,19 @@
         <v>94</v>
       </c>
       <c r="B88" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C88" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="G88" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H88" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -2708,19 +2954,19 @@
         <v>95</v>
       </c>
       <c r="B89" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C89" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>187</v>
+        <v>226</v>
       </c>
       <c r="G89" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H89" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -2728,19 +2974,19 @@
         <v>96</v>
       </c>
       <c r="B90" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C90" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>188</v>
+        <v>227</v>
       </c>
       <c r="G90" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H90" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -2748,19 +2994,799 @@
         <v>97</v>
       </c>
       <c r="B91" t="s">
+        <v>137</v>
+      </c>
+      <c r="C91" t="s">
+        <v>138</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="G91" t="s">
+        <v>269</v>
+      </c>
+      <c r="H91" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" t="s">
         <v>98</v>
       </c>
-      <c r="C91" t="s">
+      <c r="B92" t="s">
+        <v>137</v>
+      </c>
+      <c r="C92" t="s">
+        <v>138</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G92" t="s">
+        <v>269</v>
+      </c>
+      <c r="H92" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" t="s">
         <v>99</v>
       </c>
-      <c r="F91" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="G91" t="s">
-        <v>190</v>
-      </c>
-      <c r="H91" t="s">
-        <v>191</v>
+      <c r="B93" t="s">
+        <v>137</v>
+      </c>
+      <c r="C93" t="s">
+        <v>138</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G93" t="s">
+        <v>269</v>
+      </c>
+      <c r="H93" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" t="s">
+        <v>100</v>
+      </c>
+      <c r="B94" t="s">
+        <v>137</v>
+      </c>
+      <c r="C94" t="s">
+        <v>138</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G94" t="s">
+        <v>269</v>
+      </c>
+      <c r="H94" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" t="s">
+        <v>101</v>
+      </c>
+      <c r="B95" t="s">
+        <v>137</v>
+      </c>
+      <c r="C95" t="s">
+        <v>138</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G95" t="s">
+        <v>269</v>
+      </c>
+      <c r="H95" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96" t="s">
+        <v>102</v>
+      </c>
+      <c r="B96" t="s">
+        <v>137</v>
+      </c>
+      <c r="C96" t="s">
+        <v>138</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="G96" t="s">
+        <v>269</v>
+      </c>
+      <c r="H96" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" t="s">
+        <v>103</v>
+      </c>
+      <c r="B97" t="s">
+        <v>137</v>
+      </c>
+      <c r="C97" t="s">
+        <v>138</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G97" t="s">
+        <v>269</v>
+      </c>
+      <c r="H97" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" t="s">
+        <v>104</v>
+      </c>
+      <c r="B98" t="s">
+        <v>137</v>
+      </c>
+      <c r="C98" t="s">
+        <v>138</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="G98" t="s">
+        <v>269</v>
+      </c>
+      <c r="H98" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" t="s">
+        <v>105</v>
+      </c>
+      <c r="B99" t="s">
+        <v>137</v>
+      </c>
+      <c r="C99" t="s">
+        <v>138</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="G99" t="s">
+        <v>269</v>
+      </c>
+      <c r="H99" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" t="s">
+        <v>106</v>
+      </c>
+      <c r="B100" t="s">
+        <v>137</v>
+      </c>
+      <c r="C100" t="s">
+        <v>138</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="G100" t="s">
+        <v>269</v>
+      </c>
+      <c r="H100" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" t="s">
+        <v>107</v>
+      </c>
+      <c r="B101" t="s">
+        <v>137</v>
+      </c>
+      <c r="C101" t="s">
+        <v>138</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="G101" t="s">
+        <v>270</v>
+      </c>
+      <c r="H101" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102" t="s">
+        <v>108</v>
+      </c>
+      <c r="B102" t="s">
+        <v>137</v>
+      </c>
+      <c r="C102" t="s">
+        <v>138</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="G102" t="s">
+        <v>270</v>
+      </c>
+      <c r="H102" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103" t="s">
+        <v>109</v>
+      </c>
+      <c r="B103" t="s">
+        <v>137</v>
+      </c>
+      <c r="C103" t="s">
+        <v>138</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="G103" t="s">
+        <v>270</v>
+      </c>
+      <c r="H103" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104" t="s">
+        <v>110</v>
+      </c>
+      <c r="B104" t="s">
+        <v>137</v>
+      </c>
+      <c r="C104" t="s">
+        <v>138</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="G104" t="s">
+        <v>270</v>
+      </c>
+      <c r="H104" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105" t="s">
+        <v>111</v>
+      </c>
+      <c r="B105" t="s">
+        <v>137</v>
+      </c>
+      <c r="C105" t="s">
+        <v>138</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="G105" t="s">
+        <v>270</v>
+      </c>
+      <c r="H105" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106" t="s">
+        <v>112</v>
+      </c>
+      <c r="B106" t="s">
+        <v>137</v>
+      </c>
+      <c r="C106" t="s">
+        <v>138</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="G106" t="s">
+        <v>270</v>
+      </c>
+      <c r="H106" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107" t="s">
+        <v>113</v>
+      </c>
+      <c r="B107" t="s">
+        <v>137</v>
+      </c>
+      <c r="C107" t="s">
+        <v>138</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G107" t="s">
+        <v>270</v>
+      </c>
+      <c r="H107" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108" t="s">
+        <v>114</v>
+      </c>
+      <c r="B108" t="s">
+        <v>137</v>
+      </c>
+      <c r="C108" t="s">
+        <v>138</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="G108" t="s">
+        <v>270</v>
+      </c>
+      <c r="H108" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
+      <c r="A109" t="s">
+        <v>115</v>
+      </c>
+      <c r="B109" t="s">
+        <v>137</v>
+      </c>
+      <c r="C109" t="s">
+        <v>138</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="G109" t="s">
+        <v>270</v>
+      </c>
+      <c r="H109" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
+      <c r="A110" t="s">
+        <v>116</v>
+      </c>
+      <c r="B110" t="s">
+        <v>137</v>
+      </c>
+      <c r="C110" t="s">
+        <v>138</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="G110" t="s">
+        <v>270</v>
+      </c>
+      <c r="H110" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="A111" t="s">
+        <v>117</v>
+      </c>
+      <c r="B111" t="s">
+        <v>137</v>
+      </c>
+      <c r="C111" t="s">
+        <v>138</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="G111" t="s">
+        <v>271</v>
+      </c>
+      <c r="H111" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
+      <c r="A112" t="s">
+        <v>118</v>
+      </c>
+      <c r="B112" t="s">
+        <v>137</v>
+      </c>
+      <c r="C112" t="s">
+        <v>138</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="G112" t="s">
+        <v>271</v>
+      </c>
+      <c r="H112" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113" t="s">
+        <v>119</v>
+      </c>
+      <c r="B113" t="s">
+        <v>137</v>
+      </c>
+      <c r="C113" t="s">
+        <v>138</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="G113" t="s">
+        <v>271</v>
+      </c>
+      <c r="H113" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114" t="s">
+        <v>120</v>
+      </c>
+      <c r="B114" t="s">
+        <v>137</v>
+      </c>
+      <c r="C114" t="s">
+        <v>138</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="G114" t="s">
+        <v>271</v>
+      </c>
+      <c r="H114" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115" t="s">
+        <v>121</v>
+      </c>
+      <c r="B115" t="s">
+        <v>137</v>
+      </c>
+      <c r="C115" t="s">
+        <v>138</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G115" t="s">
+        <v>271</v>
+      </c>
+      <c r="H115" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
+      <c r="A116" t="s">
+        <v>122</v>
+      </c>
+      <c r="B116" t="s">
+        <v>137</v>
+      </c>
+      <c r="C116" t="s">
+        <v>138</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="G116" t="s">
+        <v>271</v>
+      </c>
+      <c r="H116" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="A117" t="s">
+        <v>123</v>
+      </c>
+      <c r="B117" t="s">
+        <v>137</v>
+      </c>
+      <c r="C117" t="s">
+        <v>138</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="G117" t="s">
+        <v>271</v>
+      </c>
+      <c r="H117" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
+      <c r="A118" t="s">
+        <v>124</v>
+      </c>
+      <c r="B118" t="s">
+        <v>137</v>
+      </c>
+      <c r="C118" t="s">
+        <v>138</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="G118" t="s">
+        <v>271</v>
+      </c>
+      <c r="H118" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119" t="s">
+        <v>125</v>
+      </c>
+      <c r="B119" t="s">
+        <v>137</v>
+      </c>
+      <c r="C119" t="s">
+        <v>138</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="G119" t="s">
+        <v>271</v>
+      </c>
+      <c r="H119" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120" t="s">
+        <v>126</v>
+      </c>
+      <c r="B120" t="s">
+        <v>137</v>
+      </c>
+      <c r="C120" t="s">
+        <v>138</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="G120" t="s">
+        <v>271</v>
+      </c>
+      <c r="H120" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8">
+      <c r="A121" t="s">
+        <v>127</v>
+      </c>
+      <c r="B121" t="s">
+        <v>137</v>
+      </c>
+      <c r="C121" t="s">
+        <v>138</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G121" t="s">
+        <v>272</v>
+      </c>
+      <c r="H121" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122" t="s">
+        <v>128</v>
+      </c>
+      <c r="B122" t="s">
+        <v>137</v>
+      </c>
+      <c r="C122" t="s">
+        <v>138</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="G122" t="s">
+        <v>272</v>
+      </c>
+      <c r="H122" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="A123" t="s">
+        <v>129</v>
+      </c>
+      <c r="B123" t="s">
+        <v>137</v>
+      </c>
+      <c r="C123" t="s">
+        <v>138</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="G123" t="s">
+        <v>272</v>
+      </c>
+      <c r="H123" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124" t="s">
+        <v>130</v>
+      </c>
+      <c r="B124" t="s">
+        <v>137</v>
+      </c>
+      <c r="C124" t="s">
+        <v>138</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="G124" t="s">
+        <v>272</v>
+      </c>
+      <c r="H124" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125" t="s">
+        <v>131</v>
+      </c>
+      <c r="B125" t="s">
+        <v>137</v>
+      </c>
+      <c r="C125" t="s">
+        <v>138</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="G125" t="s">
+        <v>272</v>
+      </c>
+      <c r="H125" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126" t="s">
+        <v>132</v>
+      </c>
+      <c r="B126" t="s">
+        <v>137</v>
+      </c>
+      <c r="C126" t="s">
+        <v>138</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G126" t="s">
+        <v>272</v>
+      </c>
+      <c r="H126" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127" t="s">
+        <v>133</v>
+      </c>
+      <c r="B127" t="s">
+        <v>137</v>
+      </c>
+      <c r="C127" t="s">
+        <v>138</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="G127" t="s">
+        <v>272</v>
+      </c>
+      <c r="H127" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
+      <c r="A128" t="s">
+        <v>134</v>
+      </c>
+      <c r="B128" t="s">
+        <v>137</v>
+      </c>
+      <c r="C128" t="s">
+        <v>138</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="G128" t="s">
+        <v>272</v>
+      </c>
+      <c r="H128" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8">
+      <c r="A129" t="s">
+        <v>135</v>
+      </c>
+      <c r="B129" t="s">
+        <v>137</v>
+      </c>
+      <c r="C129" t="s">
+        <v>138</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G129" t="s">
+        <v>272</v>
+      </c>
+      <c r="H129" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8">
+      <c r="A130" t="s">
+        <v>136</v>
+      </c>
+      <c r="B130" t="s">
+        <v>137</v>
+      </c>
+      <c r="C130" t="s">
+        <v>138</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="G130" t="s">
+        <v>272</v>
+      </c>
+      <c r="H130" t="s">
+        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -2855,6 +3881,45 @@
     <hyperlink ref="F89" r:id="rId88"/>
     <hyperlink ref="F90" r:id="rId89"/>
     <hyperlink ref="F91" r:id="rId90"/>
+    <hyperlink ref="F92" r:id="rId91"/>
+    <hyperlink ref="F93" r:id="rId92"/>
+    <hyperlink ref="F94" r:id="rId93"/>
+    <hyperlink ref="F95" r:id="rId94"/>
+    <hyperlink ref="F96" r:id="rId95"/>
+    <hyperlink ref="F97" r:id="rId96"/>
+    <hyperlink ref="F98" r:id="rId97"/>
+    <hyperlink ref="F99" r:id="rId98"/>
+    <hyperlink ref="F100" r:id="rId99"/>
+    <hyperlink ref="F101" r:id="rId100"/>
+    <hyperlink ref="F102" r:id="rId101"/>
+    <hyperlink ref="F103" r:id="rId102"/>
+    <hyperlink ref="F104" r:id="rId103"/>
+    <hyperlink ref="F105" r:id="rId104"/>
+    <hyperlink ref="F106" r:id="rId105"/>
+    <hyperlink ref="F107" r:id="rId106"/>
+    <hyperlink ref="F108" r:id="rId107"/>
+    <hyperlink ref="F109" r:id="rId108"/>
+    <hyperlink ref="F110" r:id="rId109"/>
+    <hyperlink ref="F111" r:id="rId110"/>
+    <hyperlink ref="F112" r:id="rId111"/>
+    <hyperlink ref="F113" r:id="rId112"/>
+    <hyperlink ref="F114" r:id="rId113"/>
+    <hyperlink ref="F115" r:id="rId114"/>
+    <hyperlink ref="F116" r:id="rId115"/>
+    <hyperlink ref="F117" r:id="rId116"/>
+    <hyperlink ref="F118" r:id="rId117"/>
+    <hyperlink ref="F119" r:id="rId118"/>
+    <hyperlink ref="F120" r:id="rId119"/>
+    <hyperlink ref="F121" r:id="rId120"/>
+    <hyperlink ref="F122" r:id="rId121"/>
+    <hyperlink ref="F123" r:id="rId122"/>
+    <hyperlink ref="F124" r:id="rId123"/>
+    <hyperlink ref="F125" r:id="rId124"/>
+    <hyperlink ref="F126" r:id="rId125"/>
+    <hyperlink ref="F127" r:id="rId126"/>
+    <hyperlink ref="F128" r:id="rId127"/>
+    <hyperlink ref="F129" r:id="rId128"/>
+    <hyperlink ref="F130" r:id="rId129"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/scraped_Cape_Town_Health_and_Wellness.xlsx
+++ b/results/scraped_Cape_Town_Health_and_Wellness.xlsx
@@ -43,31 +43,31 @@
     <t>Community-Wikipedia</t>
   </si>
   <si>
+    <t>CommunityPartners - Creating more equitable, just, and vibrant …</t>
+  </si>
+  <si>
+    <t>Community (TV series) -Wikipedia</t>
+  </si>
+  <si>
+    <t>Home | 211LA</t>
+  </si>
+  <si>
+    <t>California Community Foundation| A Good Life for All</t>
+  </si>
+  <si>
     <t>COMMUNITYDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
-    <t>SeattleDepartment ofNeighborhoods</t>
-  </si>
-  <si>
     <t>Community(TV Series 2009–2015) - IMDb</t>
   </si>
   <si>
-    <t>CommunityCenters - Parks |seattle.gov</t>
-  </si>
-  <si>
-    <t>What isCommunity? Basic Concepts in Sociology (updated 2025)</t>
-  </si>
-  <si>
-    <t>Community (TV series) -Wikipedia</t>
-  </si>
-  <si>
-    <t>What is aCommunity? (14 Key Points) - Simplicable</t>
-  </si>
-  <si>
-    <t>Key Characteristics That Define aCommunity- Sociology Institute</t>
-  </si>
-  <si>
-    <t>COMMUNITY| definition in the Cambridge English Dictionary</t>
+    <t>Community– Parks &amp; Recreation</t>
+  </si>
+  <si>
+    <t>Homepage |LACCD</t>
+  </si>
+  <si>
+    <t>Home | Neighborhood Info</t>
   </si>
   <si>
     <t>Hospiceof the ValleyArizona| CompassionateHospiceCare</t>
@@ -130,64 +130,64 @@
     <t>MentalDisorders: Types, Causes &amp; Symptoms -Cleveland Clinic</t>
   </si>
   <si>
+    <t>Health- Wikipedia</t>
+  </si>
+  <si>
+    <t>Contact &amp; Hours - All ForHealth,HealthFor All</t>
+  </si>
+  <si>
+    <t>HEALTH: Longevity for All</t>
+  </si>
+  <si>
+    <t>AdventistHealth GlendaleMedical Center</t>
+  </si>
+  <si>
     <t>WebMD- Better information. Betterhealth.</t>
   </si>
   <si>
     <t>Health| Definition &amp; Importance | Britannica</t>
   </si>
   <si>
+    <t>DignityHealth-GlendaleMemorial Hospital andHealthCenter,CA...</t>
+  </si>
+  <si>
+    <t>CaliforniaDepartment of PublicHealth</t>
+  </si>
+  <si>
     <t>What ishealth?: Defining and preservinggood health</t>
   </si>
   <si>
-    <t>Health Information| National Institutes ofHealth(NIH)</t>
-  </si>
-  <si>
-    <t>Health-CNN</t>
-  </si>
-  <si>
-    <t>Health- Wikipedia</t>
-  </si>
-  <si>
-    <t>HealthInformation and Medical Information -Harvard Health</t>
-  </si>
-  <si>
-    <t>Contact &amp; Hours - All ForHealth,HealthFor All</t>
-  </si>
-  <si>
-    <t>HEALTH: Longevity for All</t>
-  </si>
-  <si>
-    <t>AdventistHealth GlendaleMedical Center</t>
-  </si>
-  <si>
-    <t>primary是什么意思_primary的翻译_音标_读音_用法_例句_爱词霸在线 …</t>
-  </si>
-  <si>
-    <t>primary（英语单词）_百度百科</t>
-  </si>
-  <si>
-    <t>PRIMARY中文 (简体)翻译：剑桥词典 - Cambridge Dictionary</t>
+    <t>LA County Department of PublicHealth- SPA 2</t>
   </si>
   <si>
     <t>PrimaryClothing - Brilliant Basics for Baby &amp; Kids</t>
   </si>
   <si>
+    <t>PRIMARYDefinition &amp; Meaning -Merriam-Webster</t>
+  </si>
+  <si>
+    <t>Games, Videos, Holidays &amp; Crafts |PrimaryGames</t>
+  </si>
+  <si>
+    <t>PRIMARY| English meaning - Cambridge Dictionary</t>
+  </si>
+  <si>
     <t>Primary— reporting assembled from records</t>
   </si>
   <si>
-    <t>Spring中@Primary注解-CSDN博客</t>
-  </si>
-  <si>
-    <t>primary是什么意思_primary在线翻译_英语_读音_用法_例句_海词词典</t>
-  </si>
-  <si>
-    <t>PRIMARY| English meaning - Cambridge Dictionary</t>
-  </si>
-  <si>
-    <t>primary的解释和发音 「欧路词典」英汉-汉英词典 为您提供权威的英 …</t>
-  </si>
-  <si>
-    <t>欧路词典|英汉-汉英词典primary是什么意思_primary的中文解释和发音_primary的翻译_primary…</t>
+    <t>PRIMARYDefinition &amp; Meaning |Dictionary.com</t>
+  </si>
+  <si>
+    <t>Primary- Definition, Meaning &amp; Synonyms | Vocabulary.com</t>
+  </si>
+  <si>
+    <t>12.Primary- The Church of Jesus Christ of Latter-day Saints</t>
+  </si>
+  <si>
+    <t>Primary- definition ofprimaryby The Free Dictionary</t>
+  </si>
+  <si>
+    <t>National Elections 2026 Live Results and Map: Delaware Primaries</t>
   </si>
   <si>
     <t>What is Wellness? -Global Wellness Institute</t>
@@ -316,274 +316,274 @@
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=29c0a8ffd3a71e95bebad21c6e5a644f9be7f27acb6e344fb827373e11eccd2dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d8c773b-34e6-6610-3b0c-60da359c6715&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ29tbXVuaXR5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=20de21b21883307f4217754420f6d4c0ec55fc2206b60dae420df448c79f3cc8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d8c773b-34e6-6610-3b0c-60da359c6715&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2NvbW11bml0eQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f006a4d96266f9ea7c8cce9e3ef464e48f743016b423056af09e4d542400d806JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d8c773b-34e6-6610-3b0c-60da359c6715&amp;u=a1aHR0cHM6Ly93d3cuc2VhdHRsZS5nb3YvbmVpZ2hib3Job29kcy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=61da06f445a618ba4fda9d881fe00b9199c6f278d77e55a8475bcadad2d31230JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d8c773b-34e6-6610-3b0c-60da359c6715&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQxNDM5NjI5Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=619752a05d30c757245af7b1bcf84eae19edcfd04547f42f146a26da4b2e7605JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d8c773b-34e6-6610-3b0c-60da359c6715&amp;u=a1aHR0cHM6Ly93d3cuc2VhdHRsZS5nb3YvcGFya3MvY29tbXVuaXR5LWNlbnRlcnM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cd0705e00ac307ee2fbdd574140352b88ecbed2dcae028659a11256181d7f9a9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d8c773b-34e6-6610-3b0c-60da359c6715&amp;u=a1aHR0cHM6Ly9wdXJlc29jaW9sb2d5LmNvbS93aGF0LWlzLWNvbW11bml0eS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=01b08667d06d17ddb88a629065ddbec74da39356e7fd2c7e86266d954a4fb9e8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d8c773b-34e6-6610-3b0c-60da359c6715&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ29tbXVuaXR5XyhUVl9zZXJpZXMp&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1b1274827066c6434984be9fda6f2c13e8fa064ea8a49a654353e9a5b3b3fdbaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d8c773b-34e6-6610-3b0c-60da359c6715&amp;u=a1aHR0cHM6Ly9zaW1wbGljYWJsZS5jb20vc29jaWV0eS93aGF0LWlzLWNvbW11bml0eQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=155b8af7e5d248d3e46cf6bbf3bfb19db8da48afd43af7ecca600365d97fc777JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d8c773b-34e6-6610-3b0c-60da359c6715&amp;u=a1aHR0cHM6Ly9zb2Npb2xvZ3kuaW5zdGl0dXRlL2ludHJvZHVjdGlvbi10by1zb2Npb2xvZ3kvY2hhcmFjdGVyaXN0aWNzLWRlZmluaW5nLWNvbW11bml0eS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6f35ecfc2b86a0054fc75e3ddb31260c8de3640a9a7b3b55b8eccba2a4b7ee86JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d8c773b-34e6-6610-3b0c-60da359c6715&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2NvbW11bml0eQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=32556885e3cba3ab9922542c19b8f18e987bdf25a32f33ee14b42a0e288983e5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=18a820b6-3436-6fc6-3bb5-375735156e54&amp;u=a1aHR0cHM6Ly9ob3Yub3JnLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=525943189380518697f711f98bba9acf9694c34501275a6f7b80ac042aff70c0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=18a820b6-3436-6fc6-3bb5-375735156e54&amp;u=a1aHR0cHM6Ly9ob3NwaWNlZm91bmRhdGlvbi5vcmcvd2hhdC1pcy1ob3NwaWNlLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e3ca59f5b524331e86faabf7cdb9f1ef5ae84ca04f22a422ba352eff89ed615cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=18a820b6-3436-6fc6-3bb5-375735156e54&amp;u=a1aHR0cHM6Ly9ob3Yub3JnL2xvY2F0aW9ucw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7920f08b42faf0d3e34f1c5d1b27e9b6377ebc35955c09d9f0fdf6a78f2491b8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=18a820b6-3436-6fc6-3bb5-375735156e54&amp;u=a1aHR0cHM6Ly93d3cuc2F2aW9yaG9zcGljZS5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=acdac5b45e233cf01b962724a3549faea9ab7f3a03e9df72f66f9294a1488de4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=18a820b6-3436-6fc6-3bb5-375735156e54&amp;u=a1aHR0cHM6Ly93d3cuc3VuY3Jlc3RjYXJlLmNvbS9sb2NhdGlvbi9waG9lbml4Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=eaf353c900298ec159d3692bf83550c9d174631e6ddaf801cd7b8e41fa827c72JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=18a820b6-3436-6fc6-3bb5-375735156e54&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vc2VhcmNoP2NmbHQ9aG9zcGljZSZmaW5kX2xvYz1QaG9lbml4JTJDK0FaJm1zb2NraWQ9MThhODIwYjYzNDM2NmZjNjNiYjUzNzU3MzUxNTZlNTQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6b7bcd55327c458c716556fa6d7e26202672b64be3c4b621ecae421b1771b6e8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=18a820b6-3436-6fc6-3bb5-375735156e54&amp;u=a1aHR0cHM6Ly93d3cuY29tcGFzc3VzLmNvbS9sb2NhdGlvbnMvYXJpem9uYS9waG9lbml4Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e64cbd5cb18c2174fe6accf73cb0c14de9547c8d8d4dd76c4bfa53e70649da74JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=18a820b6-3436-6fc6-3bb5-375735156e54&amp;u=a1aHR0cHM6Ly9ob3NwaWNld2VzdGF6LmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a1d5d050e4a2970e32c4d081d6dd0a623db2d5ee780bf9bc44aca2764c25c5a9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=18a820b6-3436-6fc6-3bb5-375735156e54&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Ib3NwaWNl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5511c32f72cb184d073999ed4dbb01015fda1a291715301de47e3ee9459944acJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=18a820b6-3436-6fc6-3bb5-375735156e54&amp;u=a1aHR0cHM6Ly9ob3NwaWNlLmlvL2hvc3BpY2UvaG9zcGljZS1vZi10aGUtdmFsbGV5LXBob2VuaXgtYXov&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ffd63ac7d34c22486f485119bc925d01a5898dce58c5762393b2d8251b1c4ceeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=263a5641-12f7-649e-0e76-41a013a7655e&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L21lbnRhbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2149f8075070cbe71ecdcd9790e8c3cf3417f17b548904a3709578407f15b8afJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=263a5641-12f7-649e-0e76-41a013a7655e&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWVudGFsX2hlYWx0aA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c0644176a3bc1f86a4e351173304b7d300571fb898ffe2b1368333106d1d5301JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=263a5641-12f7-649e-0e76-41a013a7655e&amp;u=a1aHR0cHM6Ly93d3cuY2RjLmdvdi9tZW50YWwtaGVhbHRoL2Fib3V0L2luZGV4Lmh0bWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c7d67b0bbe09e4b2da155a8195f4fd051bc07394f07f1cf18b790a1d85745332JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=263a5641-12f7-649e-0e76-41a013a7655e&amp;u=a1aHR0cHM6Ly93d3cud2hvLmludC9uZXdzLXJvb20vZmFjdC1zaGVldHMvZGV0YWlsL21lbnRhbC1kaXNvcmRlcnM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d8677d023261ab64bb6a9c5873e029422ed2bcc617c64ff533fcdb1d17b0718aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=263a5641-12f7-649e-0e76-41a013a7655e&amp;u=a1aHR0cHM6Ly93d3cubWF5b2NsaW5pYy5vcmcvaGVhbHRoeS1saWZlc3R5bGUvYWR1bHQtaGVhbHRoL2luLWRlcHRoL21lbnRhbC1oZWFsdGgvYXJ0LTIwMDQ0MDk4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=67089058e41908bb72e517cc4384222d9a028cce50acaf08aef04d2b384970a7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=263a5641-12f7-649e-0e76-41a013a7655e&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWVudGFsX2Rpc29yZGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=37a31a4d2e3c7107e4aed2dd38bb1ac8999ebec70d8e890065700674df0f73e1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=263a5641-12f7-649e-0e76-41a013a7655e&amp;u=a1aHR0cHM6Ly93d3cuc2FtaHNhLmdvdi9tZW50YWwtaGVhbHRo&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=732cd105d6de876a12256d5cf2a551e172c6f26c16f86e121e0955de3209741bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=263a5641-12f7-649e-0e76-41a013a7655e&amp;u=a1aHR0cHM6Ly9teS5jbGV2ZWxhbmRjbGluaWMub3JnL2hlYWx0aC9hcnRpY2xlcy9tZW50YWwtaGVhbHRo&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=eece81c72a86c39f979b452e67b132fd080f1e392b0fa7e718fa3f2e37fae5bfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=263a5641-12f7-649e-0e76-41a013a7655e&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhbG5ld3N0b2RheS5jb20vYXJ0aWNsZXMvMTU0NTQz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=823b12f5a3f7985485322f49054586349768d0ab1aa0e8f7fcc9c22b13d4716cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=263a5641-12f7-649e-0e76-41a013a7655e&amp;u=a1aHR0cHM6Ly9teS5jbGV2ZWxhbmRjbGluaWMub3JnL2hlYWx0aC9kaXNlYXNlcy8yMjI5NS1tZW50YWwtaGVhbHRoLWRpc29yZGVycw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=53bb25d85f78dff15604c47700b8fb3b7bfdb22ff235e15542ee739c9620e588JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d75797a-cb74-6095-22b8-6e9bca576157&amp;u=a1aHR0cHM6Ly93d3cud2VibWQuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a4a5b9b0be1dc5167c33b4f1f81ee493167b2b46fd2bf2e63dd29cadd9c44ddfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d75797a-cb74-6095-22b8-6e9bca576157&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvaGVhbHRo&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d4aa099bcd1a89b9e10834519849c40217412be42acd950290da4777566f374aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d75797a-cb74-6095-22b8-6e9bca576157&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhbG5ld3N0b2RheS5jb20vYXJ0aWNsZXMvMTUwOTk5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=60d5a1796a064ec32ff18783043465908abb183ad163b89daa51370e7f8efa70JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d75797a-cb74-6095-22b8-6e9bca576157&amp;u=a1aHR0cHM6Ly93d3cubmloLmdvdi9oZWFsdGgtaW5mb3JtYXRpb24&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=10b157a6a64ef9f7133fc88d598af2f14f775f22f098a78a9f1c2ccc2b31b25aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d75797a-cb74-6095-22b8-6e9bca576157&amp;u=a1aHR0cHM6Ly93d3cuY25uLmNvbS9oZWFsdGg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b9d39306438e1ac2d01fd3524e0db454c13a49df2ed453ee0e9790d15c7e5664JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d75797a-cb74-6095-22b8-6e9bca576157&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvSGVhbHRo&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4f3425be61e1ac73769c4e79087a7342fc720153040a035ead560770eac5ca36JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d75797a-cb74-6095-22b8-6e9bca576157&amp;u=a1aHR0cHM6Ly93d3cuaGVhbHRoLmhhcnZhcmQuZWR1Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2373a55ab267343dd39ac4db1f8f56c5c79a0b59c5068e9baf414908a1e173bbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d75797a-cb74-6095-22b8-6e9bca576157&amp;u=a1aHR0cHM6Ly9hbGw0aGVhbHRoLm9yZy9jb250YWN0LXVzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e2b76e7bb80fb87374a372b2ac21c0b7674557b9677d0cfae1429bcbb14310efJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d75797a-cb74-6095-22b8-6e9bca576157&amp;u=a1aHR0cHM6Ly93d3cuaGVhbHRoLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ff9fd4474302ed2db45477e47330a459b8f2bc823cf73484aedf5ceab8f437bbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d75797a-cb74-6095-22b8-6e9bca576157&amp;u=a1aHR0cHM6Ly93d3cuYWR2ZW50aXN0aGVhbHRoLm9yZy9nbGVuZGFsZS9sb2NhdGlvbnMvYWR2ZW50aXN0LWhlYWx0aC1nbGVuZGFsZS1tZWRpY2FsLWNlbnRlci00NDQ2Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c49bfc91e257aa91f0bd1c5f2aa399d1e545042549c6c8f95fcda25beffc103dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03b96f20-9daa-6f3d-2497-78c19cec6eee&amp;u=a1aHR0cHM6Ly93d3cuaWNpYmEuY29tL3dvcmQ_dz1wcmltYXJ5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bab93e6baf95221a797ad0546656268f397686ca10365b359fa7b059d61c169bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03b96f20-9daa-6f3d-2497-78c19cec6eee&amp;u=a1aHR0cHM6Ly9iYWlrZS5iYWlkdS5jb20vaXRlbS9wcmltYXJ5LzE5NjI4Mzky&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7336f1ddcbff33e96d043eac5cffd4e9b43e588be59716fe3ce5d1ebd84de4e3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03b96f20-9daa-6f3d-2497-78c19cec6eee&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvemhzLyVFOCVBRiU4RCVFNSU4NSVCOC8lRTglOEIlQjElRTglQUYlQUQtJUU2JUIxJTg5JUU4JUFGJUFELSVFNyVBRSU4MCVFNCVCRCU5My9wcmltYXJ5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=da0a5193ebdf43bb7edb7140b9f5d8b508ce7c8f9a43b940364fa366fb88d844JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03b96f20-9daa-6f3d-2497-78c19cec6eee&amp;u=a1aHR0cHM6Ly93d3cucHJpbWFyeS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a0dad420f308569ffd1543bd7a7ea966706c532410308959a6d1c4bd7c5e7789JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03b96f20-9daa-6f3d-2497-78c19cec6eee&amp;u=a1aHR0cHM6Ly90aGVwcmltYXJ5LmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=14a6960d2c90fe7b66296c7a63591bc8549b48d2dd80fd3d21889b9f05fdaab0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03b96f20-9daa-6f3d-2497-78c19cec6eee&amp;u=a1aHR0cHM6Ly9ibG9nLmNzZG4ubmV0L25pdWdhbmcwOTIwL2FydGljbGUvZGV0YWlscy8xMTYyNzU3NDg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6a282b9964a2b4347950f9d46211f6780271bf26e716e32dd1bea567daf0b763JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03b96f20-9daa-6f3d-2497-78c19cec6eee&amp;u=a1aHR0cHM6Ly9jb3JwLmRpY3QuY24vcHJpbWFyeQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c83589ba6251e19ac789574312c2409255d81ee43aa9a33121b8ffe91c1743cfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03b96f20-9daa-6f3d-2497-78c19cec6eee&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3ByaW1hcnk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=11d78ee265358e01a8bfd66cb7ad3b2f0d4b6b31ede0ea086ba57eb403cbd581JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03b96f20-9daa-6f3d-2497-78c19cec6eee&amp;u=a1aHR0cHM6Ly9kaWN0LmV1ZGljLm5ldC9tZGljdHMvZW4vcHJpbWFyeQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a041be9e5a8158cc2dbde46181f5356360bb3b0c1c3bd87fa61d5fda74400ec4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03b96f20-9daa-6f3d-2497-78c19cec6eee&amp;u=a1aHR0cHM6Ly9kaWN0LmV1ZGljLm5ldC9kaWN0cy9lbi9wcmltYXJ5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c08d419f401b38134c19fdba0154c079b41726b30240eea74e145e7e9bece963JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=08767dbf-0cf2-65f6-2b50-6a5e0db0646e&amp;u=a1aHR0cHM6Ly9nbG9iYWx3ZWxsbmVzc2luc3RpdHV0ZS5vcmcvd2hhdC1pcy13ZWxsbmVzcy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0b4ef120ca5ecac5d7aebd5e6cc277ab5ea997992ea537df3146a3cf07ef051cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=08767dbf-0cf2-65f6-2b50-6a5e0db0646e&amp;u=a1aHR0cHM6Ly9leHRlbnNpb24ucHN1LmVkdS9oZWFsdGgtYW5kLXdlbGxuZXNzLXdoeS1saWZlLWJhbGFuY2UtbWF0dGVycw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0c198378b2556111ef2da751c513ca8704641e648d40a7174eb31b66eca6429bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=08767dbf-0cf2-65f6-2b50-6a5e0db0646e&amp;u=a1aHR0cHM6Ly93d3cud2VsbG5lc3MuY29tL3doYXQtaXMtd2VsbG5lc3M&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=20adfa855bf82a26eb135a13df22f8422b62b693a7615965ad1be238e9554e13JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=08767dbf-0cf2-65f6-2b50-6a5e0db0646e&amp;u=a1aHR0cHM6Ly93d3cudmFudGFnZWZpdC5pby9lbi9ibG9nL3doYXQtaXMtd2VsbG5lc3Mv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9cb87553c0585e647193831ef2158eae4692a40833cdea08395c39c5f51332cdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=08767dbf-0cf2-65f6-2b50-6a5e0db0646e&amp;u=a1aHR0cHM6Ly93d3cuaGVhbHRobGluZS5jb20vd2VsbG5lc3M&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3488c5f22a9a0bb512100e772361b4b52010a1e2eb62a79a87d950382c732e73JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=08767dbf-0cf2-65f6-2b50-6a5e0db0646e&amp;u=a1aHR0cHM6Ly93d3cuaWhzbS5vcmcvZ3VpZGUvdW5kZXJzdGFuZGluZy13ZWxsbmVzcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9e411e88d12c6b81354c3410b1d6719856cb07710b808d8c172e0ab226fc6a43JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=08767dbf-0cf2-65f6-2b50-6a5e0db0646e&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9XZWxsbmVzc18oYWx0ZXJuYXRpdmVfbWVkaWNpbmUp&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=310d59ab09a169b1c6a0029fbfa03e54c51e0f3e56f0560b92471aee6d75f68bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=08767dbf-0cf2-65f6-2b50-6a5e0db0646e&amp;u=a1aHR0cHM6Ly93d3cudHdjLmhlYWx0aC9wYWdlcy93ZWxsbmVzcy1wYWNrYWdlcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3e41510813023cce7cf8dd01eb61a46ca8bbc6d33d2f57a74698ee6fe223b51dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=08767dbf-0cf2-65f6-2b50-6a5e0db0646e&amp;u=a1aHR0cHM6Ly93d3cudHJhdmVsYW5kbGVpc3VyZS5jb20vdHJpcC1pZGVhcy95b2dhLXdlbGxuZXNzL2Jlc3Qtd2VsbG5lc3MtcmV0cmVhdHMtdXM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0b3116f7a9022851058632d7b2ad5055eed0fec08e966535f6ae6e694377fc77JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=08767dbf-0cf2-65f6-2b50-6a5e0db0646e&amp;u=a1aHR0cHM6Ly9zaGNzLnVjZGF2aXMuZWR1L2hlYWx0aC1hbmQtd2VsbG5lc3MvZWlnaHQtZGltZW5zaW9ucy13ZWxsbmVzcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=57c58ba07211cae688625ac7bfe108551edaa65fb5e548eec6e6a39d3ec31e0bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fff0f0f-6622-6f79-14ee-18ee67ac6e29&amp;u=a1aHR0cHM6Ly93d3cuc2V2YWRzbS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9a71afcdea5510b87f52a3eba734f21c4c30bdff7ce85d434b3949ed37751d04JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fff0f0f-6622-6f79-14ee-18ee67ac6e29&amp;u=a1aHR0cHM6Ly9pbm5vdmF0aXZlLWNvdW5zZWxpbmcub3JnLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3b5e70d3227cee846caf6c16cffcb8e44ea245a6612a18547ccb5d0ce981ff6dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fff0f0f-6622-6f79-14ee-18ee67ac6e29&amp;u=a1aHR0cHM6Ly9taW5kc3Bpcml0Y2VudGVyLm9yZy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=23fa47ab81945530cdc4fbadf487d620708134a477408d4fc878f206e6fb8dcbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fff0f0f-6622-6f79-14ee-18ee67ac6e29&amp;u=a1aHR0cHM6Ly93d3cuZ3JlZW5jb3Vuc2VsaW5nc2VydmljZS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9bb3eb52b86d34c55b73820d9a6d490d1b060045256943b4cc354a6324c0dfceJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fff0f0f-6622-6f79-14ee-18ee67ac6e29&amp;u=a1aHR0cHM6Ly9tb3NhaWNmYW1pbHlpbmMuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5b049472f930b8f8169fb2cf8d9776baf70d6e615f6df6717f19b56e95048ab2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fff0f0f-6622-6f79-14ee-18ee67ac6e29&amp;u=a1aHR0cHM6Ly9mYW1pbHlsZWdhY3ljb3Vuc2VsaW5nLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9913d278cff99335006c065c8dffb267feab1d17760fa8f55a5caf0fc4b7a224JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fff0f0f-6622-6f79-14ee-18ee67ac6e29&amp;u=a1aHR0cHM6Ly93d3cub3BlbmNvdW5zZWxpbmcuY29tL2lvd2EvZGVzLW1vaW5lcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7ba2ed486a1e61c9033d1e25c33466bae50f7998281159f6fbba15941ec4876cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fff0f0f-6622-6f79-14ee-18ee67ac6e29&amp;u=a1aHR0cHM6Ly90dXJuaW5ncG9pbnRjb3Vuc2VsaW5nZHNtLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bb95d41ef057fa8cb6770b58d262b621bf0b97254196e7b5172c9ad552f63803JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fff0f0f-6622-6f79-14ee-18ee67ac6e29&amp;u=a1aHR0cHM6Ly9uZXdsaWZlLWNvdW5zZWxpbmcuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=608905af8ea4bb12294bd25afec9cb047b1578bc159e3cd6858a5feb214002deJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fff0f0f-6622-6f79-14ee-18ee67ac6e29&amp;u=a1aHR0cHM6Ly93d3cucHN5Y2hvbG9neXRvZGF5LmNvbS91cy90aGVyYXBpc3RzL2lhL2Rlcy1tb2luZXM_bXNvY2tpZD0wZmZmMGYwZjY2MjI2Zjc5MTRlZTE4ZWU2N2FjNmUyOQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fdf05ea3727a8241cc245cb48624415e0cf79b059ec0a1e100ba81adc68d43ebJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e9655a1-3167-6048-06de-424030ca61b9&amp;u=a1aHR0cHM6Ly9tZWRsaW5lcGx1cy5nb3YvcmVoYWJpbGl0YXRpb24uaHRtbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6397bb97cf4a31965d37f1131f5256025d25c4f8798e877345ab6f02c8c4ac4dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e9655a1-3167-6048-06de-424030ca61b9&amp;u=a1aHR0cHM6Ly93d3cucHJvdmlkZW5jZS5vcmcvbG9jYXRpb25zL29yL3BvcnRsYW5kLW1lZGljYWwtY2VudGVyL2FjdXRlLXJlaGFiaWxpdGF0aW9uLXByb2dyYW0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0c47f56a80c8a437637aa3edd7645f04bfcaa93c7297a93d0bb1870218146eefJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e9655a1-3167-6048-06de-424030ca61b9&amp;u=a1aHR0cHM6Ly93d3cuY3Jlc3R2aWV3cmVjb3ZlcnkuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ffd1d6615ccdbfe62c1a94f6cb7a15758de4e6453cef3b50c99e542bd7d50a9aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e9655a1-3167-6048-06de-424030ca61b9&amp;u=a1aHR0cHM6Ly93d3cuYWRkaWN0aW9ucmVzb3VyY2UubmV0L2Jlc3QtZHJ1Zy1yZWhhYi1jZW50ZXJzL29yZWdvbi8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=64bd14a3613a59bcde9e40b22631524a5170ba18887245573535f99cc8905f07JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e9655a1-3167-6048-06de-424030ca61b9&amp;u=a1aHR0cHM6Ly93d3cubGVnYWN5aGVhbHRoLm9yZy9zZXJ2aWNlcy1hbmQtcmVzb3VyY2VzL3NlcnZpY2VzL2FkdWx0L3JlaGFiaWxpdGF0aW9uLWluc3RpdHV0ZS1vZi1vcmVnb24v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5ecbeaa3ab1dab7669e85ae8116af6cab7bd8c88c727aa56455ceb631e7acaa7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e9655a1-3167-6048-06de-424030ca61b9&amp;u=a1aHR0cHM6Ly93d3cuYWRkaWN0aW9ucy5jb20vcmVoYWJzL29yZWdvbi9wb3J0bGFuZC8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d0950ad17ef0e7ebbe0a0582d80fdfd415ad6602ea643ee65d06a0d2adf4c8cdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e9655a1-3167-6048-06de-424030ca61b9&amp;u=a1aHR0cHM6Ly93d3cud2hvLmludC9uZXdzLXJvb20vZmFjdC1zaGVldHMvZGV0YWlsL3JlaGFiaWxpdGF0aW9u&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b2e58e15b4b0bf3e05d693f839e4e9a46539a66caa1b6585c0506bd24430875dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e9655a1-3167-6048-06de-424030ca61b9&amp;u=a1aHR0cHM6Ly9yZWhhYm5ldC5jb20vb3JlZ29uL3BvcnRsYW5kLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0c11a32f06c68b1fddfb607ae94376b9fa5288129ec2aae4bffc351009bbfb70JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e9655a1-3167-6048-06de-424030ca61b9&amp;u=a1aHR0cHM6Ly9yZWNvdmVyeS5jb20vcG9ydGxhbmQv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=73ec18484f9d614fb4b531df149e614146b9190897c3374f5791a1e798173a44JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e9655a1-3167-6048-06de-424030ca61b9&amp;u=a1aHR0cHM6Ly93d3cucmVoYWIuY29tL29yZWdvbi9wb3J0bGFuZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=252c5af4f8c1dc6af307d6a41cc0572567c2bcc2540d4c2ac9fde70ec3368b47JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bf46ff4-9dbf-667c-3513-78159c146716&amp;u=a1aHR0cHM6Ly93d3cuZGhjcy5jYS5nb3YvbWVkaS1jYWwv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9c693f8d7475968076335bbc337d06654b68620dea58914edbd02a261c8b1e24JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bf46ff4-9dbf-667c-3513-78159c146716&amp;u=a1aHR0cHM6Ly93d3cuZGhjcy5jYS5nb3YvTWVkaS1DYWwvUGFnZXMvY29udGFjdC5hc3B4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8c63cc61745aefe01b3f940ff5b8ee9bf194a7dfc9dd6bb37e579976fdc92926JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bf46ff4-9dbf-667c-3513-78159c146716&amp;u=a1aHR0cHM6Ly9iZW5lZml0c2NhbC5jb20vSGVscC9wcm9ncmFtL21lZGljYWwvSENQREU_bGFuZz1lbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=584f2d3920236c112316057d0146cf1a0eb32066f5fa609756d5e256b4bee8dfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bf46ff4-9dbf-667c-3513-78159c146716&amp;u=a1aHR0cHM6Ly93d3cubGFjYXJlLm9yZy9oZWFsdGgtcGxhbnMvbWVkaS1jYWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b42d02424981c86164c32fd497da0807753be908ab59752f285e4a0f8c2655a0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bf46ff4-9dbf-667c-3513-78159c146716&amp;u=a1aHR0cHM6Ly9kcHNzLmxhY291bnR5Lmdvdi9lbi9oZWFsdGguaHRtbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=744e9fb4576f9a62609ecffd4f6f6bad9558f478e16d4d424d28153f16cbef08JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bf46ff4-9dbf-667c-3513-78159c146716&amp;u=a1aHR0cHM6Ly93d3cuaGVhbHRoY2FyZW9wdGlvbnMuZGhjcy5jYS5nb3YvZW4vZmluZC1wcm92aWRlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b2bad83cde24c2616d8c2ab6fabf01c0fe9ea9db5f964cdf54504e1faf9784cdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bf46ff4-9dbf-667c-3513-78159c146716&amp;u=a1aHR0cHM6Ly93d3cuY2EuZ292L2RlcGFydG1lbnRzLzIxNy9zZXJ2aWNlcy8zNy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7a43ff9d2ee71181691cf296bc02adbd5dada7fa50788b55365a0ab234f6ceeaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bf46ff4-9dbf-667c-3513-78159c146716&amp;u=a1aHR0cHM6Ly9tZS5sYWNvdW50eS5nb3Yv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=82a5759c4cdc7155421a4266401bcf67502dd1595100037b55f0466051790af2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bf46ff4-9dbf-667c-3513-78159c146716&amp;u=a1aHR0cHM6Ly9tY3dlYi5hcHBzLnByZC5jYW1taXMubWVkaS1jYWwuY2EuZ292L2NvbnRhY3Q&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3756a4b45f3a1f3ff2d8e49a8c9a2891578b13ad06f73b8b0707b87689fe0b98JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bf46ff4-9dbf-667c-3513-78159c146716&amp;u=a1aHR0cHM6Ly93d3cuYmx1ZXNoaWVsZGNhLmNvbS9lbi9ic3Avb3VyLXBsYW5zL21lZGktY2Fs&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e46e95ccfffd17a022baf71a2bb3abd4ddd3f981472f411bb5a6900517eff48fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14230537-d428-6aa7-3596-12d6d53c6bc3&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Db21tdW5pdHk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3daaab5c5cbc0fea841f789ff9f607b9ed85499ffae9d43011f59b0b451d0e26JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14230537-d428-6aa7-3596-12d6d53c6bc3&amp;u=a1aHR0cHM6Ly9jb21tdW5pdHlwYXJ0bmVycy5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fed7807f5b144c0b60fd18e3eb41c39a1ffd1c88edadfcc6962f3336b86f1a08JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14230537-d428-6aa7-3596-12d6d53c6bc3&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Db21tdW5pdHlfKFRWX3Nlcmllcyk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=849c91ba6a36bf6a5257412295a19e94ebc31b941a9caba2d97ff270511b32f9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14230537-d428-6aa7-3596-12d6d53c6bc3&amp;u=a1aHR0cHM6Ly8yMTFsYS5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c1cd741bce0c8ecc2cf6812cbe8f3fe78bf568272ac7771c3e889aa21e13e7f6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14230537-d428-6aa7-3596-12d6d53c6bc3&amp;u=a1aHR0cHM6Ly93d3cuY2FsZnVuZC5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e9760a99adaf0025d30d9508bd7425bd64854452ebb413a8024d66ff190c709cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14230537-d428-6aa7-3596-12d6d53c6bc3&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2NvbW11bml0eQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=caf8114a8aaa886c66b08055978821a0494dac7ce005786c2ee3deeffd81482cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14230537-d428-6aa7-3596-12d6d53c6bc3&amp;u=a1aHR0cHM6Ly9tLmltZGIuY29tL3RpdGxlL3R0MTQzOTYyOS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=836537609a1154073aa9ad0af3fdfa2a3e07d3940f596063235f0b3e5589847eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14230537-d428-6aa7-3596-12d6d53c6bc3&amp;u=a1aHR0cHM6Ly9wYXJrcy5sYWNvdW50eS5nb3YvY29tbXVuaXR5Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6c574c8cf5cde6839c0d61be90c55389758c9272276b4b055aad795d4e5f7210JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14230537-d428-6aa7-3596-12d6d53c6bc3&amp;u=a1aHR0cHM6Ly93d3cubGFjY2QuZWR1Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fe4586c5d0dfbf26414f9a6969a5040f36fc381ef148efeac0fdfd148cffbc27JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14230537-d428-6aa7-3596-12d6d53c6bc3&amp;u=a1aHR0cHM6Ly9uZWlnaGJvcmhvb2RpbmZvLmxhY2l0eS5nb3Yv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=01923d09f9a116ae72feb75f20ad7b5849643938795f835c4ebe378faa4f4f5eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d024db9-b0e4-6da4-0767-5a58b15b6c46&amp;u=a1aHR0cHM6Ly9ob3Yub3JnLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fe24fb537ef2c5ae298949d750fb756871a72f19fd8c8ffde66af918e86189d6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d024db9-b0e4-6da4-0767-5a58b15b6c46&amp;u=a1aHR0cHM6Ly9ob3NwaWNlZm91bmRhdGlvbi5vcmcvd2hhdC1pcy1ob3NwaWNlLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f71fbe13f620461b2ebd56fbd2c70757f3123b8345e3b9299825f12ed38aa53dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d024db9-b0e4-6da4-0767-5a58b15b6c46&amp;u=a1aHR0cHM6Ly9ob3Yub3JnL2xvY2F0aW9ucw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=47f93050170d7742d95651793822e46c4f5343716824ddc4ade0f1ac60e9cb63JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d024db9-b0e4-6da4-0767-5a58b15b6c46&amp;u=a1aHR0cHM6Ly93d3cuc2F2aW9yaG9zcGljZS5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6cec586042defed575f6db5fdcef2acef3db5ca54852469215f936d38b70d5dfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d024db9-b0e4-6da4-0767-5a58b15b6c46&amp;u=a1aHR0cHM6Ly93d3cuc3VuY3Jlc3RjYXJlLmNvbS9sb2NhdGlvbi9waG9lbml4Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3a513eaced06d420eaf5074d53fdb3ca4cfcf821dc5c44d0e685ec131913ac9cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d024db9-b0e4-6da4-0767-5a58b15b6c46&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vc2VhcmNoP2NmbHQ9aG9zcGljZSZmaW5kX2xvYz1QaG9lbml4JTJDK0FaJm1zb2NraWQ9MGQwMjRkYjliMGU0NmRhNDA3Njc1YTU4YjE1YjZjNDY&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=57c34a7d663b7c55f7784c53b593cc7da7c8999f225d8ede79ec243baca6125dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d024db9-b0e4-6da4-0767-5a58b15b6c46&amp;u=a1aHR0cHM6Ly93d3cuY29tcGFzc3VzLmNvbS9sb2NhdGlvbnMvYXJpem9uYS9waG9lbml4Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=384646789cc76e5432053fe2032caa12dd0a42d122b5cb19a91b5ed5b8132889JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d024db9-b0e4-6da4-0767-5a58b15b6c46&amp;u=a1aHR0cHM6Ly9ob3NwaWNld2VzdGF6LmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0fd07b9bc4f45878ac175737f26c277afdadf34cd194da375a8bf79f497d1417JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d024db9-b0e4-6da4-0767-5a58b15b6c46&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Ib3NwaWNl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=75bd0bdc3c46fe82d3835961fdb8ed0faea11073cb4b1e8bc1bec6a2b072b7f1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d024db9-b0e4-6da4-0767-5a58b15b6c46&amp;u=a1aHR0cHM6Ly9ob3NwaWNlLmlvL2hvc3BpY2UvaG9zcGljZS1vZi10aGUtdmFsbGV5LXBob2VuaXgtYXov&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8e3d69bfcb412edb197576597d874fbe2f17c900f07eac126d53d7ff8228b1b5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1996176f-a25a-6736-15be-008ea3e5668d&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L21lbnRhbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=122a89c79a00144ab64b2f6f15cfe11ee3a55cfd3f23e54d9c6eb88963afc059JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1996176f-a25a-6736-15be-008ea3e5668d&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWVudGFsX2hlYWx0aA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aed6f81a921393c84a0a64ec18693989c42edba546b5fe899fb0f62db153408fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1996176f-a25a-6736-15be-008ea3e5668d&amp;u=a1aHR0cHM6Ly93d3cuY2RjLmdvdi9tZW50YWwtaGVhbHRoL2Fib3V0L2luZGV4Lmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c2a59644720e0a6858f6fa21072a1e904a653c4ac7e5e9cf0fc95ab94bc4c2a0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1996176f-a25a-6736-15be-008ea3e5668d&amp;u=a1aHR0cHM6Ly93d3cud2hvLmludC9uZXdzLXJvb20vZmFjdC1zaGVldHMvZGV0YWlsL21lbnRhbC1kaXNvcmRlcnM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0c953e352b5059e29d5b5ecaa76fc057e396d03ecc362122315aaeb030acdb55JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1996176f-a25a-6736-15be-008ea3e5668d&amp;u=a1aHR0cHM6Ly93d3cubWF5b2NsaW5pYy5vcmcvaGVhbHRoeS1saWZlc3R5bGUvYWR1bHQtaGVhbHRoL2luLWRlcHRoL21lbnRhbC1oZWFsdGgvYXJ0LTIwMDQ0MDk4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=108192349a316a251dc62282911f4634366019ed98b825431acebf3a5b87d147JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1996176f-a25a-6736-15be-008ea3e5668d&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWVudGFsX2Rpc29yZGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2b8f542d7c4d9b9068e0c485990967c3c2a81cd4524ced0b1af64b5c74c8be52JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1996176f-a25a-6736-15be-008ea3e5668d&amp;u=a1aHR0cHM6Ly93d3cuc2FtaHNhLmdvdi9tZW50YWwtaGVhbHRo&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=784792bf5970da72ac366f107eb0eb94e9bbe8a5f221d0ad2724df53d93816f8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1996176f-a25a-6736-15be-008ea3e5668d&amp;u=a1aHR0cHM6Ly9teS5jbGV2ZWxhbmRjbGluaWMub3JnL2hlYWx0aC9hcnRpY2xlcy9tZW50YWwtaGVhbHRo&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=54cf3f63d722981071176c30fe1d083f0004a7b5f8884631d2f8b564f4bcafddJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1996176f-a25a-6736-15be-008ea3e5668d&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhbG5ld3N0b2RheS5jb20vYXJ0aWNsZXMvMTU0NTQz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d5243b371e6185255bc136ff2083a75d56caaf6c37144388cbecfcab7f6765a1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1996176f-a25a-6736-15be-008ea3e5668d&amp;u=a1aHR0cHM6Ly9teS5jbGV2ZWxhbmRjbGluaWMub3JnL2hlYWx0aC9kaXNlYXNlcy8yMjI5NS1tZW50YWwtaGVhbHRoLWRpc29yZGVycw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fba57f1d60cdeca59fa143d4632e647eb00585ebc45da53f3110e797fd3afd59JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ae6837c-17a5-676b-05ac-949d160466da&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvSGVhbHRo&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0f65bf7c9d1e9cc2cdaa56101dc9137e2641620964d52da7dcf63174a7a7ec14JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ae6837c-17a5-676b-05ac-949d160466da&amp;u=a1aHR0cHM6Ly9hbGw0aGVhbHRoLm9yZy9jb250YWN0LXVzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=167c69196326814dd67b64e27ffb6c56de5734ca730ec6f723ab22610b99d125JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ae6837c-17a5-676b-05ac-949d160466da&amp;u=a1aHR0cHM6Ly93d3cuaGVhbHRoLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0e5645a2fa15f261086ec9d9f670535f304d70fb875571c44412dc8d464aa5bdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ae6837c-17a5-676b-05ac-949d160466da&amp;u=a1aHR0cHM6Ly93d3cuYWR2ZW50aXN0aGVhbHRoLm9yZy9nbGVuZGFsZS9sb2NhdGlvbnMvYWR2ZW50aXN0LWhlYWx0aC1nbGVuZGFsZS1tZWRpY2FsLWNlbnRlci00NDQ2Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a5e799c6d3c50b85a559f39ea1fcff188497979229d87342565107c923dcf50aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ae6837c-17a5-676b-05ac-949d160466da&amp;u=a1aHR0cHM6Ly93d3cud2VibWQuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=61e1d4dc74f2af72b2c092fcf7f86d6eab4b50b72b3fd2d9c7fe498705cf7785JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ae6837c-17a5-676b-05ac-949d160466da&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvaGVhbHRo&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f2c37b18061f24de4c178ab3976a9dbcbf21b89b00fae43771274988422abba2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ae6837c-17a5-676b-05ac-949d160466da&amp;u=a1aHR0cHM6Ly93d3cuY29tbW9uc3Bpcml0Lm9yZy9maW5kLWEtbG9jYXRpb24vZGlnbml0eS1oZWFsdGgtZ2xlbmRhbGUtbWVtb3JpYWwtaG9zcGl0YWwtYW5kLWhlYWx0aC1jZW50ZXItMzIwMg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=929b9778a2bbf0c008f9feda7c4467e2ce63a8ac0472a94a7468355c87116c37JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ae6837c-17a5-676b-05ac-949d160466da&amp;u=a1aHR0cHM6Ly93d3cuY2RwaC5jYS5nb3Yv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ee78a7c3e4ace8ed5d3eac05489b77c88d85534a84b5afa11ff2e91d48d43069JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ae6837c-17a5-676b-05ac-949d160466da&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhbG5ld3N0b2RheS5jb20vYXJ0aWNsZXMvMTUwOTk5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=87d0f6063decdf1aaa1774ef985af523205a62330d93acb4378b476951d78969JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ae6837c-17a5-676b-05ac-949d160466da&amp;u=a1aHR0cDovL3d3dy5wdWJsaWNoZWFsdGgubGFjb3VudHkuZ292L2Nocy9TUEEyLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=45470f779a4d0930ce0fa22e653f90901061615fe6df1b4b0612ed033cf0f776JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=347f0252-ac6d-6e37-2076-15b3ad306f0e&amp;u=a1aHR0cHM6Ly93d3cucHJpbWFyeS5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=79c8781317a6b7b1514b2a834c8f4456bfb647aa94f1a33db956bb94e6076493JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=347f0252-ac6d-6e37-2076-15b3ad306f0e&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3ByaW1hcnk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=25bb99d6136e4cd51a51aee18c9d3ccffc508cde71a0cb0242b98534da27a5e3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=347f0252-ac6d-6e37-2076-15b3ad306f0e&amp;u=a1aHR0cHM6Ly93d3cucHJpbWFyeWdhbWVzLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c8f450113da0aa486ec93319848481fd4e46fe7543d732a585de1710cf66852aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=347f0252-ac6d-6e37-2076-15b3ad306f0e&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3ByaW1hcnk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ef4db3616f47101d6fca84f13f64b0c611629a72b34b1a6529896ae409594b44JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=347f0252-ac6d-6e37-2076-15b3ad306f0e&amp;u=a1aHR0cHM6Ly90aGVwcmltYXJ5LmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6b4e981fb924b29705c1494680f83626c6e85a0e2a3a926eb15cf16fe8d38743JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=347f0252-ac6d-6e37-2076-15b3ad306f0e&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3ByaW1hcnk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=41795ba5f913948f443346917ab6ef65c209980a90cd079352cdd9ea95ff356aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=347f0252-ac6d-6e37-2076-15b3ad306f0e&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9wcmltYXJ5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4d900065cc9bfbfd3fdf4c3589f31de5e442e0780821746a846a82dc4b855345JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=347f0252-ac6d-6e37-2076-15b3ad306f0e&amp;u=a1aHR0cHM6Ly93d3cuY2h1cmNob2ZqZXN1c2NocmlzdC5vcmcvc3R1ZHkvbWFudWFsL2dlbmVyYWwtaGFuZGJvb2svMTItcHJpbWFyeT9sYW5nPWVuZw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=28b694e5fe5a1b22c0801397978f6302283ffb16f252edf0e99aea82a45e012aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=347f0252-ac6d-6e37-2076-15b3ad306f0e&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL3ByaW1hcnk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fb358cb6ee2968e80a884f8d7a4ef118a41edd8b11a85743b9b4dfe0f265fb0aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=347f0252-ac6d-6e37-2076-15b3ad306f0e&amp;u=a1aHR0cHM6Ly93d3cubmJjbmV3cy5jb20vcG9saXRpY3MvMjAyNi1wcmltYXJ5LWVsZWN0aW9ucy9uYXRpb25hbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=68fa42f9d49bb8f52908cd1e38d6be8bb0339dc4dafa0dadb9352b7ad96d88a3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba394e3-c305-6ceb-0e2b-8302c2026d39&amp;u=a1aHR0cHM6Ly9nbG9iYWx3ZWxsbmVzc2luc3RpdHV0ZS5vcmcvd2hhdC1pcy13ZWxsbmVzcy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=54946a7e04a5b4921efb41ed73fda50c62f095bfcc69945958785f6a98e94d46JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba394e3-c305-6ceb-0e2b-8302c2026d39&amp;u=a1aHR0cHM6Ly9leHRlbnNpb24ucHN1LmVkdS9oZWFsdGgtYW5kLXdlbGxuZXNzLXdoeS1saWZlLWJhbGFuY2UtbWF0dGVycw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9d02337cb4659675b4eb8b7ddf5b9d1310428a93387ebb407bac7b487619f4a8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba394e3-c305-6ceb-0e2b-8302c2026d39&amp;u=a1aHR0cHM6Ly93d3cud2VsbG5lc3MuY29tL3doYXQtaXMtd2VsbG5lc3M&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=faf93693894a3b39689769d2a818ac077c7ed0959aa02e47d3737716f11f317eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba394e3-c305-6ceb-0e2b-8302c2026d39&amp;u=a1aHR0cHM6Ly93d3cudmFudGFnZWZpdC5pby9lbi9ibG9nL3doYXQtaXMtd2VsbG5lc3Mv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fd69196234db309680f6ef5d61eb0951b7f746cff1ce71880c65f87cedddaa7bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba394e3-c305-6ceb-0e2b-8302c2026d39&amp;u=a1aHR0cHM6Ly93d3cuaGVhbHRobGluZS5jb20vd2VsbG5lc3M&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3bd4f8ddb947af171b8fbf9434d0aaf011d1c4f2cde2779ba2c424f6cb672f8dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba394e3-c305-6ceb-0e2b-8302c2026d39&amp;u=a1aHR0cHM6Ly93d3cuaWhzbS5vcmcvZ3VpZGUvdW5kZXJzdGFuZGluZy13ZWxsbmVzcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b5a42c5311d36b3c6fb468cef35414a3ea0d23df1f77ac61909a3fb26461759eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba394e3-c305-6ceb-0e2b-8302c2026d39&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9XZWxsbmVzc18oYWx0ZXJuYXRpdmVfbWVkaWNpbmUp&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aac8c52a82983f167717e8dcba6fc3daafb0cef7e4dde720bedf1d2c97731695JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba394e3-c305-6ceb-0e2b-8302c2026d39&amp;u=a1aHR0cHM6Ly93d3cudHdjLmhlYWx0aC9wYWdlcy93ZWxsbmVzcy1wYWNrYWdlcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f0dc6f0f8e06f0fe519413e20217c4180565c96ed206426904501fb71869d198JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba394e3-c305-6ceb-0e2b-8302c2026d39&amp;u=a1aHR0cHM6Ly93d3cudHJhdmVsYW5kbGVpc3VyZS5jb20vdHJpcC1pZGVhcy95b2dhLXdlbGxuZXNzL2Jlc3Qtd2VsbG5lc3MtcmV0cmVhdHMtdXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6e9b42d936794515839ea1c77f3139d048f3d2c792dc6e14e623b9a486cd3ce6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba394e3-c305-6ceb-0e2b-8302c2026d39&amp;u=a1aHR0cHM6Ly9zaGNzLnVjZGF2aXMuZWR1L2hlYWx0aC1hbmQtd2VsbG5lc3MvZWlnaHQtZGltZW5zaW9ucy13ZWxsbmVzcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=56885dc3e4d43bc7445bfeb2607c578f428ad08befcceadea96cc6a479ffc857JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11ea67ef-ad85-6ac8-207e-700eac066b3f&amp;u=a1aHR0cHM6Ly93d3cuc2V2YWRzbS5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=56bc2c116aeffc2ec26e6daf65cc6449c1dd797d84a9bf048152f30b93867c0bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11ea67ef-ad85-6ac8-207e-700eac066b3f&amp;u=a1aHR0cHM6Ly9pbm5vdmF0aXZlLWNvdW5zZWxpbmcub3JnLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ae0d7f9a24edd281158f91ec82d82b2a8164d5b7e05194364e35e7a75ad0cc04JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11ea67ef-ad85-6ac8-207e-700eac066b3f&amp;u=a1aHR0cHM6Ly9taW5kc3Bpcml0Y2VudGVyLm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9696684bcc3f6be3d0ae71abf0c698a7dd7201bca5a1eaf353346f45d2ca37e3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11ea67ef-ad85-6ac8-207e-700eac066b3f&amp;u=a1aHR0cHM6Ly93d3cuZ3JlZW5jb3Vuc2VsaW5nc2VydmljZS5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dee846d1dfb0ce8d116ff156b8f17df5ee8547b9511a352233703aef426639c8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11ea67ef-ad85-6ac8-207e-700eac066b3f&amp;u=a1aHR0cHM6Ly9tb3NhaWNmYW1pbHlpbmMuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=01107d0ea94ff7234fb1b5994c8964575c09378d64a073e54d503692630928b5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11ea67ef-ad85-6ac8-207e-700eac066b3f&amp;u=a1aHR0cHM6Ly9mYW1pbHlsZWdhY3ljb3Vuc2VsaW5nLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8d34ac16c6d36284679ae9175851cd25c80ff16bfd2ac805329a28d4004efc17JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11ea67ef-ad85-6ac8-207e-700eac066b3f&amp;u=a1aHR0cHM6Ly93d3cub3BlbmNvdW5zZWxpbmcuY29tL2lvd2EvZGVzLW1vaW5lcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cb9939f0ea7496fd28b9b6fae5693aeba1446ba04e6ffd832f3289c241863784JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11ea67ef-ad85-6ac8-207e-700eac066b3f&amp;u=a1aHR0cHM6Ly90dXJuaW5ncG9pbnRjb3Vuc2VsaW5nZHNtLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=72069bb5467f62f360badedc69a6f45f91b1091d5d815d96a9d083e97c08396cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11ea67ef-ad85-6ac8-207e-700eac066b3f&amp;u=a1aHR0cHM6Ly9uZXdsaWZlLWNvdW5zZWxpbmcuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f4938c709ce1b2512b3c59a7cddacd9239ec97fd6980dda63b821d87eac8a935JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11ea67ef-ad85-6ac8-207e-700eac066b3f&amp;u=a1aHR0cHM6Ly93d3cucHN5Y2hvbG9neXRvZGF5LmNvbS91cy90aGVyYXBpc3RzL2lhL2Rlcy1tb2luZXM_bXNvY2tpZD0xMWVhNjdlZmFkODU2YWM4MjA3ZTcwMGVhYzA2NmIzZg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=08a08275cd8a41a9fc6ec9e24ab363ad805c8e6c5ddac9a36af7543124e921dfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26303abd-711e-627b-191e-2d5c70506315&amp;u=a1aHR0cHM6Ly9tZWRsaW5lcGx1cy5nb3YvcmVoYWJpbGl0YXRpb24uaHRtbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aac3a42ef03e0e55aa0c6f8f0e0ce005d4b914c042b9704755bfcde4e6acf276JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26303abd-711e-627b-191e-2d5c70506315&amp;u=a1aHR0cHM6Ly93d3cucHJvdmlkZW5jZS5vcmcvbG9jYXRpb25zL29yL3BvcnRsYW5kLW1lZGljYWwtY2VudGVyL2FjdXRlLXJlaGFiaWxpdGF0aW9uLXByb2dyYW0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=47329af0bcf627a9adcc29fe64e86dde5152812914ea691ac2d678488ecc349dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26303abd-711e-627b-191e-2d5c70506315&amp;u=a1aHR0cHM6Ly93d3cuY3Jlc3R2aWV3cmVjb3ZlcnkuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=06daacaf6f16ff711ec1163cc33aa95a1819ec71523b58a2aa36974bd167c27cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26303abd-711e-627b-191e-2d5c70506315&amp;u=a1aHR0cHM6Ly93d3cuYWRkaWN0aW9ucmVzb3VyY2UubmV0L2Jlc3QtZHJ1Zy1yZWhhYi1jZW50ZXJzL29yZWdvbi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a052cc85d071e74928e5056e8f0a2e630694b4101201b24c0a4b3a1de5690ea2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26303abd-711e-627b-191e-2d5c70506315&amp;u=a1aHR0cHM6Ly93d3cubGVnYWN5aGVhbHRoLm9yZy9zZXJ2aWNlcy1hbmQtcmVzb3VyY2VzL3NlcnZpY2VzL2FkdWx0L3JlaGFiaWxpdGF0aW9uLWluc3RpdHV0ZS1vZi1vcmVnb24v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a2d6d3b94a55e04a1ba6ec68dc9cc04b168524d17719c1d68e569bb189440ac2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26303abd-711e-627b-191e-2d5c70506315&amp;u=a1aHR0cHM6Ly93d3cuYWRkaWN0aW9ucy5jb20vcmVoYWJzL29yZWdvbi9wb3J0bGFuZC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b58bae217404cbe19bbc6b966c824a54115a5d8469822069a47f20ff5ca9dd2eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26303abd-711e-627b-191e-2d5c70506315&amp;u=a1aHR0cHM6Ly93d3cud2hvLmludC9uZXdzLXJvb20vZmFjdC1zaGVldHMvZGV0YWlsL3JlaGFiaWxpdGF0aW9u&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=98b3fd997cce84f21f76859a142d6ef1b8e73789adcaa2bcd5e48340d3b74b6aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26303abd-711e-627b-191e-2d5c70506315&amp;u=a1aHR0cHM6Ly9yZWhhYm5ldC5jb20vb3JlZ29uL3BvcnRsYW5kLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f3694a6b8f7bedba41268ef642b432957de540774305a134e9bb2e0f6f11c363JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26303abd-711e-627b-191e-2d5c70506315&amp;u=a1aHR0cHM6Ly9yZWNvdmVyeS5jb20vcG9ydGxhbmQv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9644f68c40d6dd02f4f242855a5d662aebe143019a79343de5b27abc4330caf3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26303abd-711e-627b-191e-2d5c70506315&amp;u=a1aHR0cHM6Ly93d3cucmVoYWIuY29tL29yZWdvbi9wb3J0bGFuZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2d7e66363760a6cf1b6a2339e236e1773dca5f24c05031e15497fe7097c41f95JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25356a88-b948-63a6-15c5-7d69b8396247&amp;u=a1aHR0cHM6Ly93d3cuZGhjcy5jYS5nb3YvbWVkaS1jYWwv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=539e88a40625deb6aec842d6188b4e1c148d3810098e4b95f317501060f56df3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25356a88-b948-63a6-15c5-7d69b8396247&amp;u=a1aHR0cHM6Ly93d3cuZGhjcy5jYS5nb3YvTWVkaS1DYWwvUGFnZXMvY29udGFjdC5hc3B4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a1864406e4fd5d7e61f7dafb6bf1f0cd902c72408c537005ea14b33ad27c61f3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25356a88-b948-63a6-15c5-7d69b8396247&amp;u=a1aHR0cHM6Ly9iZW5lZml0c2NhbC5jb20vSGVscC9wcm9ncmFtL21lZGljYWwvSENQREU_bGFuZz1lbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b431fda622c73cf698a163d78a1b2588fd7561eabbcb2f36d341c421782d6609JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25356a88-b948-63a6-15c5-7d69b8396247&amp;u=a1aHR0cHM6Ly93d3cubGFjYXJlLm9yZy9oZWFsdGgtcGxhbnMvbWVkaS1jYWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=97afee25e83b4cd2620e8aed1dfff8afc432011d2d1d26da9d714ca29fd525baJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25356a88-b948-63a6-15c5-7d69b8396247&amp;u=a1aHR0cHM6Ly9kcHNzLmxhY291bnR5Lmdvdi9lbi9oZWFsdGguaHRtbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=08a1431e1f39b4ef031d780d96212b63681e327d635b613cc4abf62d77be3a91JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25356a88-b948-63a6-15c5-7d69b8396247&amp;u=a1aHR0cHM6Ly93d3cuaGVhbHRoY2FyZW9wdGlvbnMuZGhjcy5jYS5nb3YvZW4vZmluZC1wcm92aWRlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8132febbe84ed9ac2c75930800425e8d46d170588fd880f42fc61a7d5ab907bdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25356a88-b948-63a6-15c5-7d69b8396247&amp;u=a1aHR0cHM6Ly93d3cuY2EuZ292L2RlcGFydG1lbnRzLzIxNy9zZXJ2aWNlcy8zNy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=93f1db4c3cd7ef809cf6d9779c85502df6df95b73b190ea3574a022f13b7f213JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25356a88-b948-63a6-15c5-7d69b8396247&amp;u=a1aHR0cHM6Ly9tZS5sYWNvdW50eS5nb3Yv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=74434a0163419bde719f96762807ca375c4a102e4f33aa4fe1244eceddb3b50aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25356a88-b948-63a6-15c5-7d69b8396247&amp;u=a1aHR0cHM6Ly9tY3dlYi5hcHBzLnByZC5jYW1taXMubWVkaS1jYWwuY2EuZ292L2NvbnRhY3Q&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6cdeae1086c4c9479329db538cf011ed1a2f4602679d5d3ab391cfe843dd3571JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25356a88-b948-63a6-15c5-7d69b8396247&amp;u=a1aHR0cHM6Ly93d3cuYmx1ZXNoaWVsZGNhLmNvbS9lbi9ic3Avb3VyLXBsYW5zL21lZGktY2Fs&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>

--- a/results/scraped_Cape_Town_Health_and_Wellness.xlsx
+++ b/results/scraped_Cape_Town_Health_and_Wellness.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="274">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -40,274 +40,391 @@
     <t>Source</t>
   </si>
   <si>
+    <t>Community Information-West Bloomfield Township,Michigan</t>
+  </si>
+  <si>
+    <t>Official Website ofWest Bloomfield Township,MI</t>
+  </si>
+  <si>
     <t>Community-Wikipedia</t>
   </si>
   <si>
-    <t>CommunityPartners - Creating more equitable, just, and vibrant …</t>
-  </si>
-  <si>
-    <t>Community (TV series) -Wikipedia</t>
-  </si>
-  <si>
-    <t>Home | 211LA</t>
-  </si>
-  <si>
-    <t>California Community Foundation| A Good Life for All</t>
-  </si>
-  <si>
     <t>COMMUNITYDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
-    <t>Community(TV Series 2009–2015) - IMDb</t>
-  </si>
-  <si>
-    <t>Community– Parks &amp; Recreation</t>
-  </si>
-  <si>
-    <t>Homepage |LACCD</t>
-  </si>
-  <si>
-    <t>Home | Neighborhood Info</t>
-  </si>
-  <si>
-    <t>Hospiceof the ValleyArizona| CompassionateHospiceCare</t>
+    <t>Home - Bloomfield Township</t>
+  </si>
+  <si>
+    <t>West Bloomfield Twp,MI- Facebook</t>
+  </si>
+  <si>
+    <t>Home - WB Parks</t>
+  </si>
+  <si>
+    <t>West Bloomfield Township,Michigan-Wikipedia</t>
+  </si>
+  <si>
+    <t>CommunityDefinition | What IsCommunity- Greater Good</t>
+  </si>
+  <si>
+    <t>What isCommunity? Basic Concepts in Sociology (updated 2025)</t>
+  </si>
+  <si>
+    <t>HospiceofAlabama- Serving NortheastAlabama</t>
   </si>
   <si>
     <t>What ishospice? -HospiceFoundation of America</t>
   </si>
   <si>
-    <t>Locations</t>
-  </si>
-  <si>
-    <t>Hospiceand Palliative CarePhoenix| SaviorHospice</t>
-  </si>
-  <si>
-    <t>HospiceCarePhoenix,AZ| SuncrestHospice</t>
-  </si>
-  <si>
-    <t>THEBEST 10 HOSPICE IN PHOENIX, AZ- UPDATED SEPTEMBER …</t>
-  </si>
-  <si>
-    <t>HospiceCare inPhoenix,AZ|Compassus</t>
-  </si>
-  <si>
-    <t>Hospiceof the West - ServingPhoenix,Arizona</t>
+    <t>Alabama Hospiceand Palliative Care Organization</t>
+  </si>
+  <si>
+    <t>HospiceinAlabama| AHPCO</t>
+  </si>
+  <si>
+    <t>HospiceCare inAlabama|Hospice&amp; Palliative Care - Compassus</t>
+  </si>
+  <si>
+    <t>Hospiceof NorthAlabama: An Adoration Health Partner Website</t>
   </si>
   <si>
     <t>Hospice- Wikipedia</t>
   </si>
   <si>
-    <t>HospiceOf The Valley -HospiceinPhoenix,AZ</t>
+    <t>ColumbusHospiceof Georgia &amp;Alabama</t>
+  </si>
+  <si>
+    <t>Alabama Hospice Care of Birmingham- CentralAlabama- LHC Group</t>
+  </si>
+  <si>
+    <t>Hospiceof WestAlabama– A 501 (c) (3) non-profit, community-based ...</t>
+  </si>
+  <si>
+    <t>mental是什么意思_mental的翻译_音标_读音_用法_例句_爱词霸在线词典</t>
+  </si>
+  <si>
+    <t>MENTAL中文 (简体)翻译：剑桥词典 - Cambridge Dictionary</t>
+  </si>
+  <si>
+    <t>mental_百度百科</t>
+  </si>
+  <si>
+    <t>Mental health-Wikipedia</t>
   </si>
   <si>
     <t>MENTALDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
-    <t>Mental health-Wikipedia</t>
+    <t>Mental disorders-World Health Organization(WHO)</t>
   </si>
   <si>
     <t>AboutMentalHealth |MentalHealth | CDC</t>
   </si>
   <si>
-    <t>Mental disorders-World Health Organization(WHO)</t>
-  </si>
-  <si>
-    <t>Mentalhealth: What's normal, what's not -Mayo Clinic</t>
+    <t>MENTAL在剑桥英语词典中的解释及翻译 - Cambridge Dictionary</t>
   </si>
   <si>
     <t>Mentaldisorder -Wikipedia</t>
   </si>
   <si>
-    <t>MentalHealth: Causes, Symptoms, Treatment &amp; Help | SAMHSA</t>
-  </si>
-  <si>
-    <t>MentalHealth: What It Is &amp; Why It’s Important - Cleveland Clinic</t>
-  </si>
-  <si>
-    <t>Mental health: Definition, common disorders, early signs, and more</t>
-  </si>
-  <si>
-    <t>MentalDisorders: Types, Causes &amp; Symptoms -Cleveland Clinic</t>
+    <t>MENTAL释义 | 柯林斯英语词典 - Collins Online Dictionary</t>
+  </si>
+  <si>
+    <t>Kansas City HealthDepartment - City ofKansas City,MO</t>
+  </si>
+  <si>
+    <t>The University of KansasHealthSystem</t>
   </si>
   <si>
     <t>Health- Wikipedia</t>
   </si>
   <si>
-    <t>Contact &amp; Hours - All ForHealth,HealthFor All</t>
+    <t>UniversityHealth|Kansas CityHospital</t>
+  </si>
+  <si>
+    <t>Kansas City HealthDepartment -MissouriDepartment ofHealthand ...</t>
+  </si>
+  <si>
+    <t>Patient portal | NKCHealth</t>
+  </si>
+  <si>
+    <t>myUHealth| UniversityHealthPatient Portal</t>
+  </si>
+  <si>
+    <t>NKCHealth</t>
+  </si>
+  <si>
+    <t>Home - SwopeHealth</t>
   </si>
   <si>
     <t>HEALTH: Longevity for All</t>
   </si>
   <si>
-    <t>AdventistHealth GlendaleMedical Center</t>
-  </si>
-  <si>
-    <t>WebMD- Better information. Betterhealth.</t>
-  </si>
-  <si>
-    <t>Health| Definition &amp; Importance | Britannica</t>
-  </si>
-  <si>
-    <t>DignityHealth-GlendaleMemorial Hospital andHealthCenter,CA...</t>
-  </si>
-  <si>
-    <t>CaliforniaDepartment of PublicHealth</t>
-  </si>
-  <si>
-    <t>What ishealth?: Defining and preservinggood health</t>
-  </si>
-  <si>
-    <t>LA County Department of PublicHealth- SPA 2</t>
-  </si>
-  <si>
     <t>PrimaryClothing - Brilliant Basics for Baby &amp; Kids</t>
   </si>
   <si>
     <t>PRIMARYDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
+    <t>PRIMARY| English meaning - Cambridge Dictionary</t>
+  </si>
+  <si>
+    <t>MinnesotaPrimaryResults 2026: Senate, House and Governor</t>
+  </si>
+  <si>
+    <t>Primary— reporting assembled from records</t>
+  </si>
+  <si>
     <t>Games, Videos, Holidays &amp; Crafts |PrimaryGames</t>
   </si>
   <si>
-    <t>PRIMARY| English meaning - Cambridge Dictionary</t>
-  </si>
-  <si>
-    <t>Primary— reporting assembled from records</t>
+    <t>PRIMARY| definition in the Cambridge English Dictionary</t>
+  </si>
+  <si>
+    <t>National Elections 2026 Live Results and Map: Delaware Primaries</t>
   </si>
   <si>
     <t>PRIMARYDefinition &amp; Meaning |Dictionary.com</t>
   </si>
   <si>
-    <t>Primary- Definition, Meaning &amp; Synonyms | Vocabulary.com</t>
-  </si>
-  <si>
-    <t>12.Primary- The Church of Jesus Christ of Latter-day Saints</t>
-  </si>
-  <si>
-    <t>Primary- definition ofprimaryby The Free Dictionary</t>
-  </si>
-  <si>
-    <t>National Elections 2026 Live Results and Map: Delaware Primaries</t>
+    <t>2026 Election Results, Latest News &amp; Updates | Fox News Elections …</t>
   </si>
   <si>
     <t>What is Wellness? -Global Wellness Institute</t>
   </si>
   <si>
-    <t>Health andWellness: Why Life Balance Matters</t>
-  </si>
-  <si>
     <t>What is Wellness?</t>
   </si>
   <si>
-    <t>What IsWellness? The 9 Dimensions Explained</t>
+    <t>Wellness (alternative medicine) - Wikipedia</t>
   </si>
   <si>
     <t>WellnessTopics - Healthline</t>
   </si>
   <si>
-    <t>UnderstandingWellness: Guide to a Healthier Life | IHSM</t>
-  </si>
-  <si>
-    <t>Wellness (alternative medicine) - Wikipedia</t>
-  </si>
-  <si>
-    <t>WellnessPackages – TheWellnessCompany</t>
-  </si>
-  <si>
-    <t>15 BestWellnessRetreats in the U.S. - Leisure</t>
-  </si>
-  <si>
-    <t>Eight Dimensions ofWellness- Student Health and Counseling Services</t>
-  </si>
-  <si>
-    <t>Seva Counseling — Therapists inDes Moines, Iowa</t>
-  </si>
-  <si>
-    <t>Innovative Counseling and Consulting |Des Moines,IA</t>
-  </si>
-  <si>
-    <t>Mind &amp; Spirit Counseling Center | Home</t>
-  </si>
-  <si>
-    <t>Green Counseling Services - Mental Health Counseling inIowa</t>
-  </si>
-  <si>
-    <t>MOSAIC Family Counseling Center | EMDR &amp; Counseling inDes Moines,IA</t>
-  </si>
-  <si>
-    <t>Family Legacy Counseling</t>
-  </si>
-  <si>
-    <t>Free or Low-Cost Counseling in Des Moines,IA- OpenCounseling</t>
-  </si>
-  <si>
-    <t>Turning Point Counseling |Des Moines, Iowa</t>
-  </si>
-  <si>
-    <t>Home | New Life Counseling</t>
-  </si>
-  <si>
-    <t>Therapistsin Des Moines, IA- Psychology Today</t>
+    <t>Luxury Spa in Erlanger,Edgewood&amp; Fort Mitchell,KY</t>
+  </si>
+  <si>
+    <t>Sea of Tranquility Massage andWellness-Edgewood,KY</t>
+  </si>
+  <si>
+    <t>About Us | SandalwoodWellnessand Spa</t>
+  </si>
+  <si>
+    <t>Sea of Tranquility Massage andWellness, LLC</t>
+  </si>
+  <si>
+    <t>WellnessResource Center - Everyday Health</t>
+  </si>
+  <si>
+    <t>WellnessDefined</t>
+  </si>
+  <si>
+    <t>Treeside Psychological Clinic |Lake Orion,MI| Psychological Help ...</t>
+  </si>
+  <si>
+    <t>Home -Lake OrionCounseling Center</t>
+  </si>
+  <si>
+    <t>Beyond Mindful Counseling and Wellness</t>
+  </si>
+  <si>
+    <t>Counseling in Lake Orion, MI- greatlakespsychologygroup.com</t>
+  </si>
+  <si>
+    <t>Family Counseling TherapistsinLake Orion,MI</t>
+  </si>
+  <si>
+    <t>Amy Moore, Licensed Counselor | Therapy inLake Orion,MI</t>
+  </si>
+  <si>
+    <t>Counseling Center inLake Orion,MI- oakpsych.com</t>
+  </si>
+  <si>
+    <t>Therapists in Lake Orion,MI- Psychology Today</t>
+  </si>
+  <si>
+    <t>Lake OrionCounseling - Bald Mountain Behavioral Medicine</t>
+  </si>
+  <si>
+    <t>Marriage Counseling inLake Orion,MI- Oakland Psychological Clinic …</t>
+  </si>
+  <si>
+    <t>Home - MethodistRehabilitation</t>
   </si>
   <si>
     <t>Rehabilitation- MedlinePlus</t>
   </si>
   <si>
-    <t>Providence AcuteRehabilitationCenter</t>
-  </si>
-  <si>
-    <t>Drug &amp; Alcohol Rehab inPortland,Oregon- Crestview Recovery</t>
-  </si>
-  <si>
-    <t>9 BestRehab Centers In Oregon(2026) - Addiction Resource</t>
-  </si>
-  <si>
-    <t>Legacy Rehabilitation Institute of Oregon (RIO)</t>
-  </si>
-  <si>
-    <t>Alcohol &amp; Drug Rehabs inPortland,Oregon- Addictions</t>
-  </si>
-  <si>
-    <t>Rehabilitation- World Health Organization (WHO)</t>
-  </si>
-  <si>
-    <t>68 Best Alcohol &amp; Drug Rehab Centers inPortland,OR</t>
-  </si>
-  <si>
-    <t>Drug &amp; Alcohol Rehabs inPortland,OR- Recovery.com</t>
-  </si>
-  <si>
-    <t>Highest Reviewed Drug Rehab Centers InPortland,OR</t>
-  </si>
-  <si>
-    <t>Medi-Cal- DHCS</t>
-  </si>
-  <si>
-    <t>Contact |Medi-Cal- DHCS</t>
-  </si>
-  <si>
-    <t>Program Descriptions A | BenefitsCal. Together, we benefit.</t>
-  </si>
-  <si>
-    <t>Medi-CalPlan | L.A. Care Health Plan</t>
-  </si>
-  <si>
-    <t>Health Care - Department of Public Social Services</t>
-  </si>
-  <si>
-    <t>Find a provider |Medi-CalManaged Care Health Care Options</t>
-  </si>
-  <si>
-    <t>Apply forMedi-Cal|CA.gov</t>
-  </si>
-  <si>
-    <t>County ofLos Angeles MedicalExaminer</t>
-  </si>
-  <si>
-    <t>Medi-CalProviders</t>
-  </si>
-  <si>
-    <t>Medi-Cal| Blue Shield ofCAPromise Health Plan</t>
+    <t>Mississippi- Home | mdrs</t>
+  </si>
+  <si>
+    <t>MississippiDepartment ofRehabilitationServices -MS.GOV</t>
+  </si>
+  <si>
+    <t>JacksonInpatient Hospital - MethodistRehabilitation</t>
+  </si>
+  <si>
+    <t>Rehabilitation- University ofMississippiMedical Center</t>
+  </si>
+  <si>
+    <t>MethodistRehabilitationCenter -Jackson,MS| Rehab.com</t>
+  </si>
+  <si>
+    <t>Office of VocationalRehabilitation| mdrs -Mississippi</t>
+  </si>
+  <si>
+    <t>Drug &amp; Alcohol Rehabs inJackson,MS- recovery.com</t>
+  </si>
+  <si>
+    <t>INMOTIONREHABLLC |</t>
+  </si>
+  <si>
+    <t>Fenton MedicalCenter – Patient Centered Healthcare</t>
+  </si>
+  <si>
+    <t>WebMD- Better information. Better health.</t>
+  </si>
+  <si>
+    <t>McLaren FentonHomepage</t>
+  </si>
+  <si>
+    <t>Patient Portal –Fenton MedicalCenter</t>
+  </si>
+  <si>
+    <t>McLaren Flint – Fenton Family Medicine</t>
+  </si>
+  <si>
+    <t>Medicine- Wikipedia</t>
+  </si>
+  <si>
+    <t>Regional Medical Imaging: Advanced ImagingMichigan</t>
+  </si>
+  <si>
+    <t>MedicalEquipment Online Store</t>
+  </si>
+  <si>
+    <t>Fenton MedicalCenter,Fenton,MI- Healthgrades</t>
+  </si>
+  <si>
+    <t>MedicalDiseases &amp;Conditions- Mayo Clinic</t>
+  </si>
+  <si>
+    <t>MTP drivers for windows 10 64 bit - HP Support Community</t>
+  </si>
+  <si>
+    <t>Printer Setup, Software &amp; Drivers - HP Support Community</t>
+  </si>
+  <si>
+    <t>Home - HP Support Community</t>
+  </si>
+  <si>
+    <t>I need to download HP drivers without using HP App and the M... - HP ...</t>
+  </si>
+  <si>
+    <t>Latest touchpad driver Windows 11 - HP Support Community</t>
+  </si>
+  <si>
+    <t>Install old HP product drivers after end of support</t>
+  </si>
+  <si>
+    <t>HP Camera drivers not shown in Device Manager, Camera not found</t>
+  </si>
+  <si>
+    <t>HP Stream 11 Touchpad Drivers - HP Support Community</t>
+  </si>
+  <si>
+    <t>HP MediaTek MT7921 Wireless Lan Driver for Windows 11 update</t>
+  </si>
+  <si>
+    <t>HP Support Assistant - Driver updates</t>
+  </si>
+  <si>
+    <t>Microsoft– AI, Cloud, Productivity, Computing, Gaming &amp; Apps</t>
+  </si>
+  <si>
+    <t>Microsoftaccount | Sign In or Create Your Account Today –Microsoft</t>
+  </si>
+  <si>
+    <t>My Account</t>
+  </si>
+  <si>
+    <t>Microsoft365 for Individuals: Subscription for Productivity Apps</t>
+  </si>
+  <si>
+    <t>Outlook</t>
+  </si>
+  <si>
+    <t>Microsoft- Wikipedia</t>
+  </si>
+  <si>
+    <t>MicrosoftStore - Download apps,games&amp; more for your Windows PC</t>
+  </si>
+  <si>
+    <t>Create yourMicrosoftaccount</t>
+  </si>
+  <si>
+    <t>Sign in to your account - myaccount.microsoft.com</t>
+  </si>
+  <si>
+    <t>Hornfans</t>
+  </si>
+  <si>
+    <t>Women’s Basketball | Hornfans</t>
+  </si>
+  <si>
+    <t>Tennessee vs Texas 12/13/20 | Hornfans</t>
+  </si>
+  <si>
+    <t>2026 Football Schedule &amp; Scores | Hornfans</t>
+  </si>
+  <si>
+    <t>On The Field | Hornfans</t>
+  </si>
+  <si>
+    <t>Texas @ Missouri | Page 2 | Hornfans</t>
+  </si>
+  <si>
+    <t>100 Day Countdown 2026 | Page 4 | Hornfans</t>
+  </si>
+  <si>
+    <t>Tennessee at Texas 01/23/2025 | Hornfans</t>
+  </si>
+  <si>
+    <t>Women’s Basketball | Page 2 | Hornfans</t>
+  </si>
+  <si>
+    <t>Tennessee—we dropped the Series, 1-2. | Page 4 | Hornfans</t>
+  </si>
+  <si>
+    <t>YouTube TV Help</t>
+  </si>
+  <si>
+    <t>Manage your home area or current location for YouTube TV</t>
+  </si>
+  <si>
+    <t>Advanced Scene Switcher | OBS Forums</t>
+  </si>
+  <si>
+    <t>youtube | OBS Forums</t>
+  </si>
+  <si>
+    <t>NFL Sunday Ticket pricing &amp; billing - YouTube TV Help</t>
+  </si>
+  <si>
+    <t>Can’t access YouTube - YouTube Help - Google Help</t>
+  </si>
+  <si>
+    <t>Get help signing in to YouTube - YouTube Help - Google Help</t>
+  </si>
+  <si>
+    <t>Dispute a copyright claim - Android - YouTube Help</t>
+  </si>
+  <si>
+    <t>View, delete, or turn on or off watch history - Computer - YouTube Help</t>
+  </si>
+  <si>
+    <t>Join a meeting - Computer - Google Meet Help</t>
   </si>
   <si>
     <t>Health &amp; Wellness</t>
@@ -316,277 +433,406 @@
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e46e95ccfffd17a022baf71a2bb3abd4ddd3f981472f411bb5a6900517eff48fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14230537-d428-6aa7-3596-12d6d53c6bc3&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Db21tdW5pdHk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3daaab5c5cbc0fea841f789ff9f607b9ed85499ffae9d43011f59b0b451d0e26JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14230537-d428-6aa7-3596-12d6d53c6bc3&amp;u=a1aHR0cHM6Ly9jb21tdW5pdHlwYXJ0bmVycy5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fed7807f5b144c0b60fd18e3eb41c39a1ffd1c88edadfcc6962f3336b86f1a08JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14230537-d428-6aa7-3596-12d6d53c6bc3&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Db21tdW5pdHlfKFRWX3Nlcmllcyk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=849c91ba6a36bf6a5257412295a19e94ebc31b941a9caba2d97ff270511b32f9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14230537-d428-6aa7-3596-12d6d53c6bc3&amp;u=a1aHR0cHM6Ly8yMTFsYS5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c1cd741bce0c8ecc2cf6812cbe8f3fe78bf568272ac7771c3e889aa21e13e7f6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14230537-d428-6aa7-3596-12d6d53c6bc3&amp;u=a1aHR0cHM6Ly93d3cuY2FsZnVuZC5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e9760a99adaf0025d30d9508bd7425bd64854452ebb413a8024d66ff190c709cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14230537-d428-6aa7-3596-12d6d53c6bc3&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2NvbW11bml0eQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=caf8114a8aaa886c66b08055978821a0494dac7ce005786c2ee3deeffd81482cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14230537-d428-6aa7-3596-12d6d53c6bc3&amp;u=a1aHR0cHM6Ly9tLmltZGIuY29tL3RpdGxlL3R0MTQzOTYyOS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=836537609a1154073aa9ad0af3fdfa2a3e07d3940f596063235f0b3e5589847eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14230537-d428-6aa7-3596-12d6d53c6bc3&amp;u=a1aHR0cHM6Ly9wYXJrcy5sYWNvdW50eS5nb3YvY29tbXVuaXR5Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6c574c8cf5cde6839c0d61be90c55389758c9272276b4b055aad795d4e5f7210JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14230537-d428-6aa7-3596-12d6d53c6bc3&amp;u=a1aHR0cHM6Ly93d3cubGFjY2QuZWR1Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fe4586c5d0dfbf26414f9a6969a5040f36fc381ef148efeac0fdfd148cffbc27JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14230537-d428-6aa7-3596-12d6d53c6bc3&amp;u=a1aHR0cHM6Ly9uZWlnaGJvcmhvb2RpbmZvLmxhY2l0eS5nb3Yv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=01923d09f9a116ae72feb75f20ad7b5849643938795f835c4ebe378faa4f4f5eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d024db9-b0e4-6da4-0767-5a58b15b6c46&amp;u=a1aHR0cHM6Ly9ob3Yub3JnLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fe24fb537ef2c5ae298949d750fb756871a72f19fd8c8ffde66af918e86189d6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d024db9-b0e4-6da4-0767-5a58b15b6c46&amp;u=a1aHR0cHM6Ly9ob3NwaWNlZm91bmRhdGlvbi5vcmcvd2hhdC1pcy1ob3NwaWNlLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f71fbe13f620461b2ebd56fbd2c70757f3123b8345e3b9299825f12ed38aa53dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d024db9-b0e4-6da4-0767-5a58b15b6c46&amp;u=a1aHR0cHM6Ly9ob3Yub3JnL2xvY2F0aW9ucw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=47f93050170d7742d95651793822e46c4f5343716824ddc4ade0f1ac60e9cb63JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d024db9-b0e4-6da4-0767-5a58b15b6c46&amp;u=a1aHR0cHM6Ly93d3cuc2F2aW9yaG9zcGljZS5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6cec586042defed575f6db5fdcef2acef3db5ca54852469215f936d38b70d5dfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d024db9-b0e4-6da4-0767-5a58b15b6c46&amp;u=a1aHR0cHM6Ly93d3cuc3VuY3Jlc3RjYXJlLmNvbS9sb2NhdGlvbi9waG9lbml4Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3a513eaced06d420eaf5074d53fdb3ca4cfcf821dc5c44d0e685ec131913ac9cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d024db9-b0e4-6da4-0767-5a58b15b6c46&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vc2VhcmNoP2NmbHQ9aG9zcGljZSZmaW5kX2xvYz1QaG9lbml4JTJDK0FaJm1zb2NraWQ9MGQwMjRkYjliMGU0NmRhNDA3Njc1YTU4YjE1YjZjNDY&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=57c34a7d663b7c55f7784c53b593cc7da7c8999f225d8ede79ec243baca6125dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d024db9-b0e4-6da4-0767-5a58b15b6c46&amp;u=a1aHR0cHM6Ly93d3cuY29tcGFzc3VzLmNvbS9sb2NhdGlvbnMvYXJpem9uYS9waG9lbml4Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=384646789cc76e5432053fe2032caa12dd0a42d122b5cb19a91b5ed5b8132889JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d024db9-b0e4-6da4-0767-5a58b15b6c46&amp;u=a1aHR0cHM6Ly9ob3NwaWNld2VzdGF6LmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0fd07b9bc4f45878ac175737f26c277afdadf34cd194da375a8bf79f497d1417JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d024db9-b0e4-6da4-0767-5a58b15b6c46&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Ib3NwaWNl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=75bd0bdc3c46fe82d3835961fdb8ed0faea11073cb4b1e8bc1bec6a2b072b7f1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d024db9-b0e4-6da4-0767-5a58b15b6c46&amp;u=a1aHR0cHM6Ly9ob3NwaWNlLmlvL2hvc3BpY2UvaG9zcGljZS1vZi10aGUtdmFsbGV5LXBob2VuaXgtYXov&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8e3d69bfcb412edb197576597d874fbe2f17c900f07eac126d53d7ff8228b1b5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1996176f-a25a-6736-15be-008ea3e5668d&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L21lbnRhbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=122a89c79a00144ab64b2f6f15cfe11ee3a55cfd3f23e54d9c6eb88963afc059JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1996176f-a25a-6736-15be-008ea3e5668d&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWVudGFsX2hlYWx0aA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aed6f81a921393c84a0a64ec18693989c42edba546b5fe899fb0f62db153408fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1996176f-a25a-6736-15be-008ea3e5668d&amp;u=a1aHR0cHM6Ly93d3cuY2RjLmdvdi9tZW50YWwtaGVhbHRoL2Fib3V0L2luZGV4Lmh0bWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c2a59644720e0a6858f6fa21072a1e904a653c4ac7e5e9cf0fc95ab94bc4c2a0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1996176f-a25a-6736-15be-008ea3e5668d&amp;u=a1aHR0cHM6Ly93d3cud2hvLmludC9uZXdzLXJvb20vZmFjdC1zaGVldHMvZGV0YWlsL21lbnRhbC1kaXNvcmRlcnM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0c953e352b5059e29d5b5ecaa76fc057e396d03ecc362122315aaeb030acdb55JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1996176f-a25a-6736-15be-008ea3e5668d&amp;u=a1aHR0cHM6Ly93d3cubWF5b2NsaW5pYy5vcmcvaGVhbHRoeS1saWZlc3R5bGUvYWR1bHQtaGVhbHRoL2luLWRlcHRoL21lbnRhbC1oZWFsdGgvYXJ0LTIwMDQ0MDk4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=108192349a316a251dc62282911f4634366019ed98b825431acebf3a5b87d147JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1996176f-a25a-6736-15be-008ea3e5668d&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWVudGFsX2Rpc29yZGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2b8f542d7c4d9b9068e0c485990967c3c2a81cd4524ced0b1af64b5c74c8be52JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1996176f-a25a-6736-15be-008ea3e5668d&amp;u=a1aHR0cHM6Ly93d3cuc2FtaHNhLmdvdi9tZW50YWwtaGVhbHRo&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=784792bf5970da72ac366f107eb0eb94e9bbe8a5f221d0ad2724df53d93816f8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1996176f-a25a-6736-15be-008ea3e5668d&amp;u=a1aHR0cHM6Ly9teS5jbGV2ZWxhbmRjbGluaWMub3JnL2hlYWx0aC9hcnRpY2xlcy9tZW50YWwtaGVhbHRo&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=54cf3f63d722981071176c30fe1d083f0004a7b5f8884631d2f8b564f4bcafddJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1996176f-a25a-6736-15be-008ea3e5668d&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhbG5ld3N0b2RheS5jb20vYXJ0aWNsZXMvMTU0NTQz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d5243b371e6185255bc136ff2083a75d56caaf6c37144388cbecfcab7f6765a1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1996176f-a25a-6736-15be-008ea3e5668d&amp;u=a1aHR0cHM6Ly9teS5jbGV2ZWxhbmRjbGluaWMub3JnL2hlYWx0aC9kaXNlYXNlcy8yMjI5NS1tZW50YWwtaGVhbHRoLWRpc29yZGVycw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fba57f1d60cdeca59fa143d4632e647eb00585ebc45da53f3110e797fd3afd59JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ae6837c-17a5-676b-05ac-949d160466da&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvSGVhbHRo&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0f65bf7c9d1e9cc2cdaa56101dc9137e2641620964d52da7dcf63174a7a7ec14JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ae6837c-17a5-676b-05ac-949d160466da&amp;u=a1aHR0cHM6Ly9hbGw0aGVhbHRoLm9yZy9jb250YWN0LXVzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=167c69196326814dd67b64e27ffb6c56de5734ca730ec6f723ab22610b99d125JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ae6837c-17a5-676b-05ac-949d160466da&amp;u=a1aHR0cHM6Ly93d3cuaGVhbHRoLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0e5645a2fa15f261086ec9d9f670535f304d70fb875571c44412dc8d464aa5bdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ae6837c-17a5-676b-05ac-949d160466da&amp;u=a1aHR0cHM6Ly93d3cuYWR2ZW50aXN0aGVhbHRoLm9yZy9nbGVuZGFsZS9sb2NhdGlvbnMvYWR2ZW50aXN0LWhlYWx0aC1nbGVuZGFsZS1tZWRpY2FsLWNlbnRlci00NDQ2Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a5e799c6d3c50b85a559f39ea1fcff188497979229d87342565107c923dcf50aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ae6837c-17a5-676b-05ac-949d160466da&amp;u=a1aHR0cHM6Ly93d3cud2VibWQuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=61e1d4dc74f2af72b2c092fcf7f86d6eab4b50b72b3fd2d9c7fe498705cf7785JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ae6837c-17a5-676b-05ac-949d160466da&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvaGVhbHRo&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f2c37b18061f24de4c178ab3976a9dbcbf21b89b00fae43771274988422abba2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ae6837c-17a5-676b-05ac-949d160466da&amp;u=a1aHR0cHM6Ly93d3cuY29tbW9uc3Bpcml0Lm9yZy9maW5kLWEtbG9jYXRpb24vZGlnbml0eS1oZWFsdGgtZ2xlbmRhbGUtbWVtb3JpYWwtaG9zcGl0YWwtYW5kLWhlYWx0aC1jZW50ZXItMzIwMg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=929b9778a2bbf0c008f9feda7c4467e2ce63a8ac0472a94a7468355c87116c37JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ae6837c-17a5-676b-05ac-949d160466da&amp;u=a1aHR0cHM6Ly93d3cuY2RwaC5jYS5nb3Yv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ee78a7c3e4ace8ed5d3eac05489b77c88d85534a84b5afa11ff2e91d48d43069JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ae6837c-17a5-676b-05ac-949d160466da&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhbG5ld3N0b2RheS5jb20vYXJ0aWNsZXMvMTUwOTk5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=87d0f6063decdf1aaa1774ef985af523205a62330d93acb4378b476951d78969JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ae6837c-17a5-676b-05ac-949d160466da&amp;u=a1aHR0cDovL3d3dy5wdWJsaWNoZWFsdGgubGFjb3VudHkuZ292L2Nocy9TUEEyLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=45470f779a4d0930ce0fa22e653f90901061615fe6df1b4b0612ed033cf0f776JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=347f0252-ac6d-6e37-2076-15b3ad306f0e&amp;u=a1aHR0cHM6Ly93d3cucHJpbWFyeS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=79c8781317a6b7b1514b2a834c8f4456bfb647aa94f1a33db956bb94e6076493JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=347f0252-ac6d-6e37-2076-15b3ad306f0e&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3ByaW1hcnk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=25bb99d6136e4cd51a51aee18c9d3ccffc508cde71a0cb0242b98534da27a5e3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=347f0252-ac6d-6e37-2076-15b3ad306f0e&amp;u=a1aHR0cHM6Ly93d3cucHJpbWFyeWdhbWVzLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c8f450113da0aa486ec93319848481fd4e46fe7543d732a585de1710cf66852aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=347f0252-ac6d-6e37-2076-15b3ad306f0e&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3ByaW1hcnk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ef4db3616f47101d6fca84f13f64b0c611629a72b34b1a6529896ae409594b44JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=347f0252-ac6d-6e37-2076-15b3ad306f0e&amp;u=a1aHR0cHM6Ly90aGVwcmltYXJ5LmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6b4e981fb924b29705c1494680f83626c6e85a0e2a3a926eb15cf16fe8d38743JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=347f0252-ac6d-6e37-2076-15b3ad306f0e&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3ByaW1hcnk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=41795ba5f913948f443346917ab6ef65c209980a90cd079352cdd9ea95ff356aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=347f0252-ac6d-6e37-2076-15b3ad306f0e&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9wcmltYXJ5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4d900065cc9bfbfd3fdf4c3589f31de5e442e0780821746a846a82dc4b855345JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=347f0252-ac6d-6e37-2076-15b3ad306f0e&amp;u=a1aHR0cHM6Ly93d3cuY2h1cmNob2ZqZXN1c2NocmlzdC5vcmcvc3R1ZHkvbWFudWFsL2dlbmVyYWwtaGFuZGJvb2svMTItcHJpbWFyeT9sYW5nPWVuZw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=28b694e5fe5a1b22c0801397978f6302283ffb16f252edf0e99aea82a45e012aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=347f0252-ac6d-6e37-2076-15b3ad306f0e&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL3ByaW1hcnk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fb358cb6ee2968e80a884f8d7a4ef118a41edd8b11a85743b9b4dfe0f265fb0aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=347f0252-ac6d-6e37-2076-15b3ad306f0e&amp;u=a1aHR0cHM6Ly93d3cubmJjbmV3cy5jb20vcG9saXRpY3MvMjAyNi1wcmltYXJ5LWVsZWN0aW9ucy9uYXRpb25hbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=68fa42f9d49bb8f52908cd1e38d6be8bb0339dc4dafa0dadb9352b7ad96d88a3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba394e3-c305-6ceb-0e2b-8302c2026d39&amp;u=a1aHR0cHM6Ly9nbG9iYWx3ZWxsbmVzc2luc3RpdHV0ZS5vcmcvd2hhdC1pcy13ZWxsbmVzcy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=54946a7e04a5b4921efb41ed73fda50c62f095bfcc69945958785f6a98e94d46JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba394e3-c305-6ceb-0e2b-8302c2026d39&amp;u=a1aHR0cHM6Ly9leHRlbnNpb24ucHN1LmVkdS9oZWFsdGgtYW5kLXdlbGxuZXNzLXdoeS1saWZlLWJhbGFuY2UtbWF0dGVycw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9d02337cb4659675b4eb8b7ddf5b9d1310428a93387ebb407bac7b487619f4a8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba394e3-c305-6ceb-0e2b-8302c2026d39&amp;u=a1aHR0cHM6Ly93d3cud2VsbG5lc3MuY29tL3doYXQtaXMtd2VsbG5lc3M&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=faf93693894a3b39689769d2a818ac077c7ed0959aa02e47d3737716f11f317eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba394e3-c305-6ceb-0e2b-8302c2026d39&amp;u=a1aHR0cHM6Ly93d3cudmFudGFnZWZpdC5pby9lbi9ibG9nL3doYXQtaXMtd2VsbG5lc3Mv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fd69196234db309680f6ef5d61eb0951b7f746cff1ce71880c65f87cedddaa7bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba394e3-c305-6ceb-0e2b-8302c2026d39&amp;u=a1aHR0cHM6Ly93d3cuaGVhbHRobGluZS5jb20vd2VsbG5lc3M&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3bd4f8ddb947af171b8fbf9434d0aaf011d1c4f2cde2779ba2c424f6cb672f8dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba394e3-c305-6ceb-0e2b-8302c2026d39&amp;u=a1aHR0cHM6Ly93d3cuaWhzbS5vcmcvZ3VpZGUvdW5kZXJzdGFuZGluZy13ZWxsbmVzcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b5a42c5311d36b3c6fb468cef35414a3ea0d23df1f77ac61909a3fb26461759eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba394e3-c305-6ceb-0e2b-8302c2026d39&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9XZWxsbmVzc18oYWx0ZXJuYXRpdmVfbWVkaWNpbmUp&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aac8c52a82983f167717e8dcba6fc3daafb0cef7e4dde720bedf1d2c97731695JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba394e3-c305-6ceb-0e2b-8302c2026d39&amp;u=a1aHR0cHM6Ly93d3cudHdjLmhlYWx0aC9wYWdlcy93ZWxsbmVzcy1wYWNrYWdlcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f0dc6f0f8e06f0fe519413e20217c4180565c96ed206426904501fb71869d198JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba394e3-c305-6ceb-0e2b-8302c2026d39&amp;u=a1aHR0cHM6Ly93d3cudHJhdmVsYW5kbGVpc3VyZS5jb20vdHJpcC1pZGVhcy95b2dhLXdlbGxuZXNzL2Jlc3Qtd2VsbG5lc3MtcmV0cmVhdHMtdXM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6e9b42d936794515839ea1c77f3139d048f3d2c792dc6e14e623b9a486cd3ce6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba394e3-c305-6ceb-0e2b-8302c2026d39&amp;u=a1aHR0cHM6Ly9zaGNzLnVjZGF2aXMuZWR1L2hlYWx0aC1hbmQtd2VsbG5lc3MvZWlnaHQtZGltZW5zaW9ucy13ZWxsbmVzcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=56885dc3e4d43bc7445bfeb2607c578f428ad08befcceadea96cc6a479ffc857JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11ea67ef-ad85-6ac8-207e-700eac066b3f&amp;u=a1aHR0cHM6Ly93d3cuc2V2YWRzbS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=56bc2c116aeffc2ec26e6daf65cc6449c1dd797d84a9bf048152f30b93867c0bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11ea67ef-ad85-6ac8-207e-700eac066b3f&amp;u=a1aHR0cHM6Ly9pbm5vdmF0aXZlLWNvdW5zZWxpbmcub3JnLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ae0d7f9a24edd281158f91ec82d82b2a8164d5b7e05194364e35e7a75ad0cc04JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11ea67ef-ad85-6ac8-207e-700eac066b3f&amp;u=a1aHR0cHM6Ly9taW5kc3Bpcml0Y2VudGVyLm9yZy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9696684bcc3f6be3d0ae71abf0c698a7dd7201bca5a1eaf353346f45d2ca37e3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11ea67ef-ad85-6ac8-207e-700eac066b3f&amp;u=a1aHR0cHM6Ly93d3cuZ3JlZW5jb3Vuc2VsaW5nc2VydmljZS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dee846d1dfb0ce8d116ff156b8f17df5ee8547b9511a352233703aef426639c8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11ea67ef-ad85-6ac8-207e-700eac066b3f&amp;u=a1aHR0cHM6Ly9tb3NhaWNmYW1pbHlpbmMuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=01107d0ea94ff7234fb1b5994c8964575c09378d64a073e54d503692630928b5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11ea67ef-ad85-6ac8-207e-700eac066b3f&amp;u=a1aHR0cHM6Ly9mYW1pbHlsZWdhY3ljb3Vuc2VsaW5nLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8d34ac16c6d36284679ae9175851cd25c80ff16bfd2ac805329a28d4004efc17JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11ea67ef-ad85-6ac8-207e-700eac066b3f&amp;u=a1aHR0cHM6Ly93d3cub3BlbmNvdW5zZWxpbmcuY29tL2lvd2EvZGVzLW1vaW5lcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cb9939f0ea7496fd28b9b6fae5693aeba1446ba04e6ffd832f3289c241863784JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11ea67ef-ad85-6ac8-207e-700eac066b3f&amp;u=a1aHR0cHM6Ly90dXJuaW5ncG9pbnRjb3Vuc2VsaW5nZHNtLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=72069bb5467f62f360badedc69a6f45f91b1091d5d815d96a9d083e97c08396cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11ea67ef-ad85-6ac8-207e-700eac066b3f&amp;u=a1aHR0cHM6Ly9uZXdsaWZlLWNvdW5zZWxpbmcuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f4938c709ce1b2512b3c59a7cddacd9239ec97fd6980dda63b821d87eac8a935JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=11ea67ef-ad85-6ac8-207e-700eac066b3f&amp;u=a1aHR0cHM6Ly93d3cucHN5Y2hvbG9neXRvZGF5LmNvbS91cy90aGVyYXBpc3RzL2lhL2Rlcy1tb2luZXM_bXNvY2tpZD0xMWVhNjdlZmFkODU2YWM4MjA3ZTcwMGVhYzA2NmIzZg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=08a08275cd8a41a9fc6ec9e24ab363ad805c8e6c5ddac9a36af7543124e921dfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26303abd-711e-627b-191e-2d5c70506315&amp;u=a1aHR0cHM6Ly9tZWRsaW5lcGx1cy5nb3YvcmVoYWJpbGl0YXRpb24uaHRtbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aac3a42ef03e0e55aa0c6f8f0e0ce005d4b914c042b9704755bfcde4e6acf276JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26303abd-711e-627b-191e-2d5c70506315&amp;u=a1aHR0cHM6Ly93d3cucHJvdmlkZW5jZS5vcmcvbG9jYXRpb25zL29yL3BvcnRsYW5kLW1lZGljYWwtY2VudGVyL2FjdXRlLXJlaGFiaWxpdGF0aW9uLXByb2dyYW0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=47329af0bcf627a9adcc29fe64e86dde5152812914ea691ac2d678488ecc349dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26303abd-711e-627b-191e-2d5c70506315&amp;u=a1aHR0cHM6Ly93d3cuY3Jlc3R2aWV3cmVjb3ZlcnkuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=06daacaf6f16ff711ec1163cc33aa95a1819ec71523b58a2aa36974bd167c27cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26303abd-711e-627b-191e-2d5c70506315&amp;u=a1aHR0cHM6Ly93d3cuYWRkaWN0aW9ucmVzb3VyY2UubmV0L2Jlc3QtZHJ1Zy1yZWhhYi1jZW50ZXJzL29yZWdvbi8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a052cc85d071e74928e5056e8f0a2e630694b4101201b24c0a4b3a1de5690ea2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26303abd-711e-627b-191e-2d5c70506315&amp;u=a1aHR0cHM6Ly93d3cubGVnYWN5aGVhbHRoLm9yZy9zZXJ2aWNlcy1hbmQtcmVzb3VyY2VzL3NlcnZpY2VzL2FkdWx0L3JlaGFiaWxpdGF0aW9uLWluc3RpdHV0ZS1vZi1vcmVnb24v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a2d6d3b94a55e04a1ba6ec68dc9cc04b168524d17719c1d68e569bb189440ac2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26303abd-711e-627b-191e-2d5c70506315&amp;u=a1aHR0cHM6Ly93d3cuYWRkaWN0aW9ucy5jb20vcmVoYWJzL29yZWdvbi9wb3J0bGFuZC8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b58bae217404cbe19bbc6b966c824a54115a5d8469822069a47f20ff5ca9dd2eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26303abd-711e-627b-191e-2d5c70506315&amp;u=a1aHR0cHM6Ly93d3cud2hvLmludC9uZXdzLXJvb20vZmFjdC1zaGVldHMvZGV0YWlsL3JlaGFiaWxpdGF0aW9u&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=98b3fd997cce84f21f76859a142d6ef1b8e73789adcaa2bcd5e48340d3b74b6aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26303abd-711e-627b-191e-2d5c70506315&amp;u=a1aHR0cHM6Ly9yZWhhYm5ldC5jb20vb3JlZ29uL3BvcnRsYW5kLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f3694a6b8f7bedba41268ef642b432957de540774305a134e9bb2e0f6f11c363JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26303abd-711e-627b-191e-2d5c70506315&amp;u=a1aHR0cHM6Ly9yZWNvdmVyeS5jb20vcG9ydGxhbmQv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9644f68c40d6dd02f4f242855a5d662aebe143019a79343de5b27abc4330caf3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26303abd-711e-627b-191e-2d5c70506315&amp;u=a1aHR0cHM6Ly93d3cucmVoYWIuY29tL29yZWdvbi9wb3J0bGFuZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2d7e66363760a6cf1b6a2339e236e1773dca5f24c05031e15497fe7097c41f95JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25356a88-b948-63a6-15c5-7d69b8396247&amp;u=a1aHR0cHM6Ly93d3cuZGhjcy5jYS5nb3YvbWVkaS1jYWwv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=539e88a40625deb6aec842d6188b4e1c148d3810098e4b95f317501060f56df3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25356a88-b948-63a6-15c5-7d69b8396247&amp;u=a1aHR0cHM6Ly93d3cuZGhjcy5jYS5nb3YvTWVkaS1DYWwvUGFnZXMvY29udGFjdC5hc3B4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a1864406e4fd5d7e61f7dafb6bf1f0cd902c72408c537005ea14b33ad27c61f3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25356a88-b948-63a6-15c5-7d69b8396247&amp;u=a1aHR0cHM6Ly9iZW5lZml0c2NhbC5jb20vSGVscC9wcm9ncmFtL21lZGljYWwvSENQREU_bGFuZz1lbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b431fda622c73cf698a163d78a1b2588fd7561eabbcb2f36d341c421782d6609JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25356a88-b948-63a6-15c5-7d69b8396247&amp;u=a1aHR0cHM6Ly93d3cubGFjYXJlLm9yZy9oZWFsdGgtcGxhbnMvbWVkaS1jYWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=97afee25e83b4cd2620e8aed1dfff8afc432011d2d1d26da9d714ca29fd525baJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25356a88-b948-63a6-15c5-7d69b8396247&amp;u=a1aHR0cHM6Ly9kcHNzLmxhY291bnR5Lmdvdi9lbi9oZWFsdGguaHRtbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=08a1431e1f39b4ef031d780d96212b63681e327d635b613cc4abf62d77be3a91JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25356a88-b948-63a6-15c5-7d69b8396247&amp;u=a1aHR0cHM6Ly93d3cuaGVhbHRoY2FyZW9wdGlvbnMuZGhjcy5jYS5nb3YvZW4vZmluZC1wcm92aWRlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8132febbe84ed9ac2c75930800425e8d46d170588fd880f42fc61a7d5ab907bdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25356a88-b948-63a6-15c5-7d69b8396247&amp;u=a1aHR0cHM6Ly93d3cuY2EuZ292L2RlcGFydG1lbnRzLzIxNy9zZXJ2aWNlcy8zNy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=93f1db4c3cd7ef809cf6d9779c85502df6df95b73b190ea3574a022f13b7f213JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25356a88-b948-63a6-15c5-7d69b8396247&amp;u=a1aHR0cHM6Ly9tZS5sYWNvdW50eS5nb3Yv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=74434a0163419bde719f96762807ca375c4a102e4f33aa4fe1244eceddb3b50aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25356a88-b948-63a6-15c5-7d69b8396247&amp;u=a1aHR0cHM6Ly9tY3dlYi5hcHBzLnByZC5jYW1taXMubWVkaS1jYWwuY2EuZ292L2NvbnRhY3Q&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6cdeae1086c4c9479329db538cf011ed1a2f4602679d5d3ab391cfe843dd3571JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25356a88-b948-63a6-15c5-7d69b8396247&amp;u=a1aHR0cHM6Ly93d3cuYmx1ZXNoaWVsZGNhLmNvbS9lbi9ic3Avb3VyLXBsYW5zL21lZGktY2Fs&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=344ca4cea269d3d2793be25db838e6f0798f8fa155ee54f179f0df1fbfe41f99JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25b5130d-1ed0-6f21-26ae-04ec1f5d6e3c&amp;u=a1aHR0cHM6Ly93d3cud2J0b3duc2hpcC5vcmcvdmlzaXRvcnMvY29tbXVuaXR5X2luZm9ybWF0aW9uL2luZGV4LnBocA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=302d9a1fc9bebab2e6be753a40ce8e0eaf9ecc764b66b6c335deb8194a95097bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25b5130d-1ed0-6f21-26ae-04ec1f5d6e3c&amp;u=a1aHR0cHM6Ly93YnRvd25zaGlwLm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d10215d6885ecfb25f167dd6c09235b954e0e7fcc8bc7a6d0c9cbd93e542ecb6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25b5130d-1ed0-6f21-26ae-04ec1f5d6e3c&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ29tbXVuaXR5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e477b6de7aec8d21289c28a8f3e897589ba6bf791ab5dc26a2c0fd006d38b2c3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25b5130d-1ed0-6f21-26ae-04ec1f5d6e3c&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2NvbW11bml0eQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7bdd85ea10d86cfc0c7339768539d92a519d19128a63c9341827d7975eaf1e61JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25b5130d-1ed0-6f21-26ae-04ec1f5d6e3c&amp;u=a1aHR0cHM6Ly93d3cuYmxvb21maWVsZHR3cC5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2bafcb6d575b58d7e56dd8fda56a3a568547caa4c7ed84746a66cac76ce4a87cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25b5130d-1ed0-6f21-26ae-04ec1f5d6e3c&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL2dyb3Vwcy8xMDIyNTM5NjE5ODYxMDgwLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c7c483f8952bc89705692c9477b6dadff2b4ef7d1a4682fc63407407cf7a6e76JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25b5130d-1ed0-6f21-26ae-04ec1f5d6e3c&amp;u=a1aHR0cHM6Ly93YnBhcmtzLm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b5d35df082e92d9be212c4517bfc5e29bb390403b62863d460a2683f86d94931JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25b5130d-1ed0-6f21-26ae-04ec1f5d6e3c&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvV2VzdF9CbG9vbWZpZWxkX1Rvd25zaGlwLF9NaWNoaWdhbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0ab01e2c616306eb46b57124e9c8dec8fc47a1f0de28ebb4a66081a86f0e665dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25b5130d-1ed0-6f21-26ae-04ec1f5d6e3c&amp;u=a1aHR0cHM6Ly9ncmVhdGVyZ29vZC5iZXJrZWxleS5lZHUvY29tbXVuaXR5L2RlZmluaXRpb24&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=359a90b3fb16b1a2bc17c4c326636c110057fe3691b6d02029768b3fb844fbbaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25b5130d-1ed0-6f21-26ae-04ec1f5d6e3c&amp;u=a1aHR0cHM6Ly9wdXJlc29jaW9sb2d5LmNvbS93aGF0LWlzLWNvbW11bml0eS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dab02293ab33464c5f9fca877c778a399fbaa50506cc554fc2c105a9922b0334JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22d091ab-03ed-6122-0b2a-864a02d160d8&amp;u=a1aHR0cHM6Ly93d3cuaG9zcGljZW9mYWxhYmFtYS5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=14b58bb2d8e097d841cd0abf318649d752632fa38ea4e868fe3c96c5c1ae516cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22d091ab-03ed-6122-0b2a-864a02d160d8&amp;u=a1aHR0cHM6Ly9ob3NwaWNlZm91bmRhdGlvbi5vcmcvd2hhdC1pcy1ob3NwaWNlLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=04db3e2c9034a4dd65bb14f041e2015d6bfa5008e95fe82abcc8bb64c020cc35JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22d091ab-03ed-6122-0b2a-864a02d160d8&amp;u=a1aHR0cHM6Ly9hbGhvc3BpY2Uub3JnLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=22dd2cc67ca84b23ddccb12991574ede32a71312acab5ff7bb5186cfad6df154JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22d091ab-03ed-6122-0b2a-864a02d160d8&amp;u=a1aHR0cHM6Ly9hbGhvc3BpY2Uub3JnL2hvc3BpY2Uv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=819e6a66b199ef3d353c51350cf5d1048230e6a60c76fed6acad5f93672f451eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22d091ab-03ed-6122-0b2a-864a02d160d8&amp;u=a1aHR0cHM6Ly93d3cuY29tcGFzc3VzLmNvbS9sb2NhdGlvbnMvYWxhYmFtYS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cb3cdabb8b635855ffd2afaae54e223d2f23dd8c50ff354fa331ecdd9ecff91aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22d091ab-03ed-6122-0b2a-864a02d160d8&amp;u=a1aHR0cHM6Ly9ob3NwaWNlb2Zub3J0aGFsYWJhbWEuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=43b592f4e76d8d75058a7382d2018b39544edf6255e2df02a0a735de2829d4faJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22d091ab-03ed-6122-0b2a-864a02d160d8&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvSG9zcGljZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9351f33300b4d620cb723a4048bae8f1bfd10110be009e0a521f767404ff5e10JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22d091ab-03ed-6122-0b2a-864a02d160d8&amp;u=a1aHR0cHM6Ly93d3cuY29sdW1idXNob3NwaWNlLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f07eb71c9ba4843bbec8db8ea16860ebfa5116bf041fdc8bffa4e6f8f4272b64JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22d091ab-03ed-6122-0b2a-864a02d160d8&amp;u=a1aHR0cHM6Ly9saGNncm91cC5jb20vbG9jYXRpb25zL2FsYWJhbWEtaG9zcGljZS1jYXJlLW9mLWJpcm1pbmdoYW0v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cbea804b4842cee98c7736eb67d40ef2f67d3e860248d9081219f61d72f49013JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22d091ab-03ed-6122-0b2a-864a02d160d8&amp;u=a1aHR0cHM6Ly93d3cuaG9zcGljZW9md2VzdGFsLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3c6f45e37271f66281cf7f82c97306305d1c5376773144c410f611641c3fd642JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36850942-ccf7-6001-245d-1ea3cdbc6158&amp;u=a1aHR0cHM6Ly93d3cuaWNpYmEuY29tL3dvcmQ_dz1tZW50YWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2e3b2d95a5d113d564d9a96d0b8bad60cdb6f58f4e941b70fbfac4bddd2b4e90JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36850942-ccf7-6001-245d-1ea3cdbc6158&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvemhzLyVFOCVBRiU4RCVFNSU4NSVCOC8lRTglOEIlQjElRTglQUYlQUQtJUU2JUIxJTg5JUU4JUFGJUFELSVFNyVBRSU4MCVFNCVCRCU5My9tZW50YWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c507dfa016d6ea50f1b3158d2c221eac0b98fa8a2ed9b36d76dc044ec7a95738JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36850942-ccf7-6001-245d-1ea3cdbc6158&amp;u=a1aHR0cHM6Ly9iYWlrZS5iYWlkdS5jb20vaXRlbS9tZW50YWwvMjI1NTczMA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=04b4cc47ce919a11c2be9fc84dd985c36fdc06474ea441f0a7410d949949a574JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36850942-ccf7-6001-245d-1ea3cdbc6158&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWVudGFsX2hlYWx0aA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1b56835756486ba8882f08c94e81fc273af79e6e16dd48c1f93867916b4eb7c3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36850942-ccf7-6001-245d-1ea3cdbc6158&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L21lbnRhbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d106aac4beebf561efe9e5130183bcade8d3248584006387a53ea9813cac597bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36850942-ccf7-6001-245d-1ea3cdbc6158&amp;u=a1aHR0cHM6Ly93d3cud2hvLmludC9uZXdzLXJvb20vZmFjdC1zaGVldHMvZGV0YWlsL21lbnRhbC1kaXNvcmRlcnM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5ae0e1ca0afa074846fd8a544961599d43b7ddca9d7e8eb0e3ec90587e04c93fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36850942-ccf7-6001-245d-1ea3cdbc6158&amp;u=a1aHR0cHM6Ly93d3cuY2RjLmdvdi9tZW50YWwtaGVhbHRoL2Fib3V0L2luZGV4Lmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ec82330b930797d8410347f1e291ca1f06912d69c89a02cefcb1140834e7cf07JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36850942-ccf7-6001-245d-1ea3cdbc6158&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvemhzLyVFOCVBRiU4RCVFNSU4NSVCOC8lRTglOEIlQjElRTglQUYlQUQvbWVudGFs&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ade9f1bea03a5a81ce414ee35a884dc727a6870e3e310f23e8a1724d33b8f330JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36850942-ccf7-6001-245d-1ea3cdbc6158&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWVudGFsX2Rpc29yZGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b6b2a71c41655ccfbe267640abbb4d2cf8b3f0e28ae7a4f847229825e8f20915JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36850942-ccf7-6001-245d-1ea3cdbc6158&amp;u=a1aHR0cHM6Ly93d3cuY29sbGluc2RpY3Rpb25hcnkuY29tL3poL2RpY3Rpb25hcnkvZW5nbGlzaC9tZW50YWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f5cd49bc969fd3e7bd7b1eb1eb4347ebe5b7298a6b83bb2d1706bd7cf85acf56JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03112c34-f3ea-68e3-022b-3bd5f29e69a6&amp;u=a1aHR0cHM6Ly93d3cua2Ntby5nb3YvY2l0eS1oYWxsL2RlcGFydG1lbnRzL2hlYWx0aA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=682edc3ac07505009fe7dc6ce82a3674dbc52f33d38e7427e4c1042fa851da9eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03112c34-f3ea-68e3-022b-3bd5f29e69a6&amp;u=a1aHR0cHM6Ly93d3cua2Fuc2FzaGVhbHRoc3lzdGVtLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=64ae43ac7e39b8caf64d38c9dd277759038df4909632ca9d8154362132443170JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03112c34-f3ea-68e3-022b-3bd5f29e69a6&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvSGVhbHRo&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5a68193ba956692073cc93ccafee48f8ffb2b2cc7d0888aa49b6e77cf10ffb40JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03112c34-f3ea-68e3-022b-3bd5f29e69a6&amp;u=a1aHR0cHM6Ly93d3cudW5pdmVyc2l0eWhlYWx0aGtjLm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a39b687098c9bf6e9b5ba0ae369eb51bdd871625eb431e5cbe1284106f57521bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03112c34-f3ea-68e3-022b-3bd5f29e69a6&amp;u=a1aHR0cHM6Ly9oZWFsdGgubW8uZ292L2xvY2FsL2ZpbmQteW91ci1sb2NhbC1wdWJsaWMtaGVhbHRoLWFnZW5jeS9rYW5zYXMtY2l0eS1oZWFsdGgtZGVwYXJ0bWVudA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=52aaa5f2fc6c590c4fd203da62fafb566feb2be00bebb1fa06a478adcaea1b2cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03112c34-f3ea-68e3-022b-3bd5f29e69a6&amp;u=a1aHR0cHM6Ly93d3cubmtjaGVhbHRoLm9yZy9wYXRpZW50cy1hbmQtZ3Vlc3RzL2Zvci1wYXRpZW50cy9hZnRlci15b3VyLXZpc2l0L3lvdXItbWVkaWNhbC1yZWNvcmQvcGF0aWVudC1wb3J0YWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b0bfa21557edb29b5448a1f2e963db9f6d756aaa9cf02b6517dbab517c31c293JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03112c34-f3ea-68e3-022b-3bd5f29e69a6&amp;u=a1aHR0cHM6Ly93d3cudW5pdmVyc2l0eWhlYWx0aGtjLm9yZy9wYXRpZW50cy12aXNpdG9ycy9teXVoZWFsdGgv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ccf66f20c03dbb1806b26c10d95ad108ab577531fe2eb05d3d06d8e1341a5c3cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03112c34-f3ea-68e3-022b-3bd5f29e69a6&amp;u=a1aHR0cHM6Ly93d3cubmtjaGVhbHRoLm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=db5fa871890da46a58106729bdf0a76bae8224fef505c63214f4aeee4d30f36dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03112c34-f3ea-68e3-022b-3bd5f29e69a6&amp;u=a1aHR0cHM6Ly9zd29wZWhlYWx0aC5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2fd9b8b66f49c9dec87134da9809d57e19526a0d2720322176bc46bdbe7de23bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03112c34-f3ea-68e3-022b-3bd5f29e69a6&amp;u=a1aHR0cHM6Ly93d3cuaGVhbHRoLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1da0e9aeda353295613ce5a93ac91340059d84e13e79fd287ecba89649df90c8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24b06bd1-4e96-6bc4-29ae-7c304f5e6ad4&amp;u=a1aHR0cHM6Ly93d3cucHJpbWFyeS5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=69c2337ccafac28070c165376558fabba3eddc622c97c4ccb8cb9b896a84cf4dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24b06bd1-4e96-6bc4-29ae-7c304f5e6ad4&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3ByaW1hcnk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aa7b952c8d62d184b75c835b4b14b9e213c402a39a6470ae91efae5b72666702JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24b06bd1-4e96-6bc4-29ae-7c304f5e6ad4&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3ByaW1hcnk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dd5985dda976acdcd8b29d33b0199b4cba96da0d5490be043b90af268263f0beJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24b06bd1-4e96-6bc4-29ae-7c304f5e6ad4&amp;u=a1aHR0cHM6Ly9hcG5ld3MuY29tL3Byb2plY3RzL2VsZWN0aW9ucy0yMDI2L21pbm5lc290YS1wcmltYXJ5LXJlc3VsdHMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d30e8b47b1b245093c7a30ee19bc7ab5fa3afcd37cc08333d62293da5e34b614JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24b06bd1-4e96-6bc4-29ae-7c304f5e6ad4&amp;u=a1aHR0cHM6Ly90aGVwcmltYXJ5LmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2e85c1d4ecbf39118707294a4ca63ce4d3f041c1a31338f2c647c3ea2e47ec9fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24b06bd1-4e96-6bc4-29ae-7c304f5e6ad4&amp;u=a1aHR0cHM6Ly93d3cucHJpbWFyeWdhbWVzLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3cd135418b877835314155d96211080cc327189c09e76fcaecb0de887522b590JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24b06bd1-4e96-6bc4-29ae-7c304f5e6ad4&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL3ByaW1hcnk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f958d1f683901114c073f507f0a4d55c720f1afa7a13593a7e9029768933cef7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24b06bd1-4e96-6bc4-29ae-7c304f5e6ad4&amp;u=a1aHR0cHM6Ly93d3cubmJjbmV3cy5jb20vcG9saXRpY3MvMjAyNi1wcmltYXJ5LWVsZWN0aW9ucy9uYXRpb25hbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=20b942f8a526d87f413fa2bcd10e1dd7051dbc4e35157f1c023f76926740c1c9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24b06bd1-4e96-6bc4-29ae-7c304f5e6ad4&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3ByaW1hcnk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c606c5f8502df140b32669b748ff3ef249cb6fc9831123c2f0a2494c03d2de8fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24b06bd1-4e96-6bc4-29ae-7c304f5e6ad4&amp;u=a1aHR0cHM6Ly93d3cuZm94bmV3cy5jb20vZWxlY3Rpb25zLzIwMjYvcHJpbWFyeS1yZXN1bHRzP21zb2NraWQ9MjRiMDZiZDE0ZTk2NmJjNDI5YWU3YzMwNGY1ZTZhZDQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ff3e3e79c2d19a4fb236a88a391bb7e0a18dd6e119cab29a038cb589113741ebJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=049f677e-3ec7-6965-1da7-709f3fab6877&amp;u=a1aHR0cHM6Ly9nbG9iYWx3ZWxsbmVzc2luc3RpdHV0ZS5vcmcvd2hhdC1pcy13ZWxsbmVzcy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=52efe86ecc264d7954500c9e20faccd5d5772588ad3e843480c9375426fa3863JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=049f677e-3ec7-6965-1da7-709f3fab6877&amp;u=a1aHR0cHM6Ly93d3cud2VsbG5lc3MuY29tL3doYXQtaXMtd2VsbG5lc3M&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=990d4defa38877366b5cc82d2f33b6a005dc5eae757015a2a13c7365c66c580dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=049f677e-3ec7-6965-1da7-709f3fab6877&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvV2VsbG5lc3NfKGFsdGVybmF0aXZlX21lZGljaW5lKQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3b3b3a4c041ced91ef6073750b7a10d0f3a86a0e958187b742d2b69366c0acdcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=049f677e-3ec7-6965-1da7-709f3fab6877&amp;u=a1aHR0cHM6Ly93d3cuaGVhbHRobGluZS5jb20vd2VsbG5lc3M&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bb502f387318336c5362eb2f0f143d96e6fa114b3a4d436a45e8e501d1862027JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=049f677e-3ec7-6965-1da7-709f3fab6877&amp;u=a1aHR0cHM6Ly93d3cuc2FuZGFsd29vZHdlbGxuZXNzYW5kc3BhLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=65c2087f502bdf4f21c17994e9f81d8dcebfef618634d69578a46c9d9e13abf8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=049f677e-3ec7-6965-1da7-709f3fab6877&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vYml6L3NlYS1vZi10cmFucXVpbGl0eS1tYXNzYWdlLWFuZC13ZWxsbmVzcy1lZGdld29vZD9tc29ja2lkPTA0OWY2NzdlM2VjNzY5NjUxZGE3NzA5ZjNmYWI2ODc3&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f3113265f1e588c7917ab06ae760c93468cb50f4023b9894531f92a707571023JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=049f677e-3ec7-6965-1da7-709f3fab6877&amp;u=a1aHR0cHM6Ly93d3cuc2FuZGFsd29vZHdlbGxuZXNzYW5kc3BhLmNvbS9hYm91dC11cw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f209180b27969d06235d2b701691316d2399f2504afd333d475b54a9edc5442bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=049f677e-3ec7-6965-1da7-709f3fab6877&amp;u=a1aHR0cHM6Ly93d3cubWFzc2FnZWJvb2suY29tL3RoZXJhcGlzdHMvU2Vhb2Z0cmFucXVpbGl0eWxsYw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3d3fe1fc1eb40e610d144b419ba3324fd66d36a283d5f1d7397935adb97b3f17JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=049f677e-3ec7-6965-1da7-709f3fab6877&amp;u=a1aHR0cHM6Ly93d3cuZXZlcnlkYXloZWFsdGguY29tL3dlbGxuZXNzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e82aa7adb54575ab42983b306ee09efdd65de54198460c72908834ad0326c9f9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=049f677e-3ec7-6965-1da7-709f3fab6877&amp;u=a1aHR0cHM6Ly93d3cud2VsbG5lc3NhbGxpYW5jZS5vcmcvcmVzb3VyY2VzLWFuZC10b29scy93ZWxsbmVzcy1kZWZpbmVk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0f2e9a5908cd99431e1866dd26db971f2d8c8bf1865de3d01ff736362f225c3dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=197e64fc-8202-6ccd-333d-731d83bf6d15&amp;u=a1aHR0cHM6Ly90cmVlc2lkZWNvdW5zZWxpbmcuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7eb832a7e32eb938f058f961c213129f18bdc96e1a02cec647de21533181cc37JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=197e64fc-8202-6ccd-333d-731d83bf6d15&amp;u=a1aHR0cHM6Ly9sYWtlb3Jpb25jYy5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5373b69a3f323b24c5bf1a36d34e9d5a9fba966e3665420fdd3e111985ac9b92JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=197e64fc-8202-6ccd-333d-731d83bf6d15&amp;u=a1aHR0cHM6Ly93d3cuYmV5b25kbWluZGZ1bGNvdW5zZWxpbmdhbmR3ZWxsbmVzcy5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c50729d4152b8f7d72638a1742f4b4866b22c5bdea45cec97695f179071eca10JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=197e64fc-8202-6ccd-333d-731d83bf6d15&amp;u=a1aHR0cHM6Ly93d3cuZ3JlYXRsYWtlc3BzeWNob2xvZ3lncm91cC5jb20vbWkvY291bnNlbGluZy1pbi1sYWtlLW9yaW9uLW1pLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=568cccea2da4b0a6169d3317d32fbdd836c8f7b8177e49e663ddfb26bda5882cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=197e64fc-8202-6ccd-333d-731d83bf6d15&amp;u=a1aHR0cHM6Ly93d3cucHN5Y2hvbG9neXRvZGF5LmNvbS91cy90aGVyYXBpc3RzL2ZhbWlseS1jb3Vuc2VsaW5nL21pL2xha2Utb3Jpb24_bXNvY2tpZD0xOTdlNjRmYzgyMDI2Y2NkMzMzZDczMWQ4M2JmNmQxNQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=323ca47bdb33bc7b1195e77fcefdc190db9a813cc06ae21003b307577991af5dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=197e64fc-8202-6ccd-333d-731d83bf6d15&amp;u=a1aHR0cHM6Ly9hbXltb29yZWNvdW5zZWxvci5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7c6960747e50c46fc3d7d21fe06bbc6bf929f9fd4347081a4b1d7a82496a13f1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=197e64fc-8202-6ccd-333d-731d83bf6d15&amp;u=a1aHR0cHM6Ly93d3cub2FrcHN5Y2guY29tL2NvdW5zZWxpbmctY2VudGVyLWluLWxha2Utb3Jpb24tbWkv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9e9afdf667fa8a8162feda7f6b0216850d2128d395233319144931e3e99b3af4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=197e64fc-8202-6ccd-333d-731d83bf6d15&amp;u=a1aHR0cHM6Ly93d3cucHN5Y2hvbG9neXRvZGF5LmNvbS91cy90aGVyYXBpc3RzL21pL2xha2Utb3Jpb24_bXNvY2tpZD0xOTdlNjRmYzgyMDI2Y2NkMzMzZDczMWQ4M2JmNmQxNQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e58ced3983abf96b836294e8353a51e5c126e3ec07daf3001ad0254fc9b3f69cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=197e64fc-8202-6ccd-333d-731d83bf6d15&amp;u=a1aHR0cHM6Ly93d3cuYm1ibWVkaWNpbmUuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=eabde6a8f5f88f5bd368ca3b234ba4678e47acce89a5b5dbc4987ee04b3bf9a5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=197e64fc-8202-6ccd-333d-731d83bf6d15&amp;u=a1aHR0cHM6Ly93d3cub2FrcHN5Y2guY29tL21hcnJpYWdlLWNvdW5zZWxpbmctaW4tbGFrZS1vcmlvbi1taS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6b06dc890c2b2a3ea40a2aacc818543565af2bd3b2ec780f231e628038a13164JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27ccc013-4ba4-6153-14d0-d7f24a9260bb&amp;u=a1aHR0cHM6Ly9tZXRob2Rpc3RyZWhhYi5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4bda07875f3a199a3b30932991bcb65f4f013b22147c485e2ba4373107b06239JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27ccc013-4ba4-6153-14d0-d7f24a9260bb&amp;u=a1aHR0cHM6Ly9tZWRsaW5lcGx1cy5nb3YvcmVoYWJpbGl0YXRpb24uaHRtbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fab0c0a7da68b75d0735de313f27576e0e06d87aea1fcbc9b419bf80f9530c3fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27ccc013-4ba4-6153-14d0-d7f24a9260bb&amp;u=a1aHR0cDovL3d3dy5tZHJzLm1zLmdvdi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=70fae7625f39f5914db4a33f60761feee0577d057e299c2407742f05ca29ca6bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27ccc013-4ba4-6153-14d0-d7f24a9260bb&amp;u=a1aHR0cHM6Ly93d3cubXMuZ292L2FnZW5jaWVzL21pc3Npc3NpcHBpLWRlcGFydG1lbnQtcmVoYWJpbGl0YXRpb24tc2VydmljZXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3f465d5285ca9bc7030c61884921df592d61f1ea5a532294bbe9591451a72267JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27ccc013-4ba4-6153-14d0-d7f24a9260bb&amp;u=a1aHR0cHM6Ly9tZXRob2Rpc3RyZWhhYi5vcmcvbG9jYXRpb25zL2phY2tzb24vaW5wYXRpZW50Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e49f03ff0d7532bff8ce3a86142122c50a5ac19b2071d8c860eba03f6fb0e6afJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27ccc013-4ba4-6153-14d0-d7f24a9260bb&amp;u=a1aHR0cHM6Ly93d3cudW1jLmVkdS9oZWFsdGhjYXJlL3JlaGFiaWxpdGF0aW9uJTIwc2VydmljZXMvcmVoYWJpbGl0YXRpb25faG9tZS5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cfaa45d9974e63ec45928f5c0a048cacfa7b4890eec66bbadfe57c91d16b5443JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27ccc013-4ba4-6153-14d0-d7f24a9260bb&amp;u=a1aHR0cHM6Ly93d3cucmVoYWIuY29tL21yYy1lYXN0LWNhbXB1cy1tZXRob2Rpc3QtcmVoYWJpbGl0YXRpb24tY2VudGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=020bf1ad6a624b546c40f03a6ee13cea84bf202c0f029d2008095bd8f3f1e7a7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27ccc013-4ba4-6153-14d0-d7f24a9260bb&amp;u=a1aHR0cHM6Ly93d3cubWRycy5tcy5nb3Yvdm9jYXRpb25hbC1yZWhhYmlsaXRhdGlvbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=73abedeb73548ec2e5af740a2b07104fd8b24e46063cc38ea93ccaa8a5a8e7e7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27ccc013-4ba4-6153-14d0-d7f24a9260bb&amp;u=a1aHR0cHM6Ly9yZWNvdmVyeS5jb20vamFja3Nvbi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=064f5091f4e4b075f789917c98aa87ac9d3254bf08added1da89636e168bea0aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27ccc013-4ba4-6153-14d0-d7f24a9260bb&amp;u=a1aHR0cHM6Ly9pbm1vdGlvbnJlaGFibGxjLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a03be2a0af0dd8606e2ddb234d44fa4a86055405a76bf8c68ac4823cd9dabc5fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d580e02-b91a-6f1b-32cc-19e3b8696e09&amp;u=a1aHR0cHM6Ly93d3cuZmVudG9ubWVkaWNhbC5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=07c0dc6852ce2b130c98e90f55a5608c08d0b69b39dc6b2c20fad9243d58d2f1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d580e02-b91a-6f1b-32cc-19e3b8696e09&amp;u=a1aHR0cHM6Ly93d3cud2VibWQuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c8bfcf4e4cd891ae99371cca806fb14276a41782c1e674ddfb924609d3564ea1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d580e02-b91a-6f1b-32cc-19e3b8696e09&amp;u=a1aHR0cHM6Ly93d3cubWNsYXJlbi5vcmcvZmVudG9uL21jbGFyZW4tZmVudG9uLWhvbWU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7f746bd23fd89df8275193775d38284b462760655a95dd76a288584b97649c3fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d580e02-b91a-6f1b-32cc-19e3b8696e09&amp;u=a1aHR0cHM6Ly93d3cuZmVudG9ubWVkaWNhbC5jb20vcGF0aWVudHBvcnRhbC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=37537d6a05187e30ef922aa9f2d4df1107cee043c8f2630fd4fccd39eb11c126JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d580e02-b91a-6f1b-32cc-19e3b8696e09&amp;u=a1aHR0cHM6Ly93d3cubWNsYXJlbi5vcmcvbWFpbi9sb2NhdGlvbnMvbWNsYXJlbi1mbGludC1mZW50b24tZmFtaWx5LW1lZGljaW5lLTEzNDU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=05bb3783bda13fddaf56ec48ea681f0460e2aaaf66377efbfcb9bd437efda9ebJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d580e02-b91a-6f1b-32cc-19e3b8696e09&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWVkaWNpbmU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8bdcbaed27e78a26fa988a1941426becb6c76f17bf6c883a5b1c3ae462c29289JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d580e02-b91a-6f1b-32cc-19e3b8696e09&amp;u=a1aHR0cHM6Ly93d3cucm1pcGMubmV0Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=685e50073cb8913a6edda78b25bbcb3ad3fd9fa113e388720a507a2b7f7ba6faJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d580e02-b91a-6f1b-32cc-19e3b8696e09&amp;u=a1aHR0cHM6Ly9oYXJ0bWVkaWNhbC5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0629a3212f6138fbb9d816871b86c318b73d67d84ba20ae67b31bcd776ccd589JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d580e02-b91a-6f1b-32cc-19e3b8696e09&amp;u=a1aHR0cHM6Ly93d3cuaGVhbHRoZ3JhZGVzLmNvbS9ncm91cC1kaXJlY3RvcnkvbWktbWljaGlnYW4vZmVudG9uL2ZlbnRvbi1tZWRpY2FsLWNlbnRlci14cnY4NXc&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4faeb907f3c9b01062f55fabcc84624b31fdf68dd66cd99079e71b8fe031366aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d580e02-b91a-6f1b-32cc-19e3b8696e09&amp;u=a1aHR0cHM6Ly93d3cubWF5b2NsaW5pYy5vcmcvZGlzZWFzZXMtY29uZGl0aW9ucw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c0e602df727cad701333dd7a2399ebdd1fb23f6154cf63d38e6a833debc3dd64JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e9aad54-d5a2-6c97-3e6c-bab5d4c26d34&amp;u=a1aHR0cHM6Ly9oMzA0MzQud3d3My5ocC5jb20vdDUvTm90ZWJvb2tzLUFyY2hpdmUtUmVhZC1Pbmx5L01UUC1kcml2ZXJzLWZvci13aW5kb3dzLTEwLTY0LWJpdC90ZC1wLzU5MDM5ODE&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fd8962431195b919f1cb567fe9aeadad29f83b95d30da1f0d3c3f41bd8ea67b2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e9aad54-d5a2-6c97-3e6c-bab5d4c26d34&amp;u=a1aHR0cHM6Ly9oMzA0MzQud3d3My5ocC5jb20vdDUvUHJpbnRlci1TZXR1cC1Tb2Z0d2FyZS1Ecml2ZXJzL2JkLXAvU29mdHdhcmU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=47e1ce17a99695b6df89eaf344b1b529ea6306303943d24a721924a22d583c2cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e9aad54-d5a2-6c97-3e6c-bab5d4c26d34&amp;u=a1aHR0cHM6Ly9oMzA0MzQud3d3My5ocC5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=864915bdd424d1bcd78b85a706da0f5014be0f0dbcadaf862139385fbb41e044JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e9aad54-d5a2-6c97-3e6c-bab5d4c26d34&amp;u=a1aHR0cHM6Ly9oMzA0MzQud3d3My5ocC5jb20vdDUvUHJpbnRlcnMtQXJjaGl2ZS1SZWFkLU9ubHkvSS1uZWVkLXRvLWRvd25sb2FkLUhQLWRyaXZlcnMtd2l0aG91dC11c2luZy1IUC1BcHAtYW5kLXRoZS90ZC1wLzgwNjA4ODk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cfde496b40941b59cfa6a7339367a2aeeb11bd40c5fbbfd00598961fad349166JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e9aad54-d5a2-6c97-3e6c-bab5d4c26d34&amp;u=a1aHR0cHM6Ly9oMzA0MzQud3d3My5ocC5jb20vdDUvTm90ZWJvb2stVmlkZW8tRGlzcGxheS1hbmQtVG91Y2gvTGF0ZXN0LXRvdWNocGFkLWRyaXZlci1XaW5kb3dzLTExL3RkLXAvOTM1MTQ3NA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c65025c5801920dd34bf82d9e07123aba8f0a10e71d6e4b1bbe0ab6c860813b2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e9aad54-d5a2-6c97-3e6c-bab5d4c26d34&amp;u=a1aHR0cHM6Ly9oMzA0MzQud3d3My5ocC5jb20vdDUvTm90ZWJvb2stU29mdHdhcmUtYW5kLUhvdy1Uby1RdWVzdGlvbnMvSW5zdGFsbC1vbGQtSFAtcHJvZHVjdC1kcml2ZXJzLWFmdGVyLWVuZC1vZi1zdXBwb3J0L3RkLXAvODIwMTkzMg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3d0dfc2a9020c91ded5269afc2029cfad136f61a6efff39a0287a95b51a4832eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e9aad54-d5a2-6c97-3e6c-bab5d4c26d34&amp;u=a1aHR0cHM6Ly9oMzA0MzQud3d3My5ocC5jb20vdDUvTm90ZWJvb2stT3BlcmF0aW5nLVN5c3RlbS1hbmQtUmVjb3ZlcnkvSFAtQ2FtZXJhLWRyaXZlcnMtbm90LXNob3duLWluLURldmljZS1NYW5hZ2VyLUNhbWVyYS1ub3QvdGQtcC83Nzc2NTk4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6d117b9c4d673e6dcc3db450ccfe53dbc6cde3ca74ad43f7d47d219d9c4bb3b4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e9aad54-d5a2-6c97-3e6c-bab5d4c26d34&amp;u=a1aHR0cHM6Ly9oMzA0MzQud3d3My5ocC5jb20vdDUvTm90ZWJvb2stT3BlcmF0aW5nLVN5c3RlbS1hbmQtUmVjb3ZlcnkvSFAtU3RyZWFtLTExLVRvdWNocGFkLURyaXZlcnMvdGQtcC81MzI2MDU3&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=87e83445a7eb163b52054fd400d413ef11f7bec90a6a6883989bafbea8f905d9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e9aad54-d5a2-6c97-3e6c-bab5d4c26d34&amp;u=a1aHR0cHM6Ly9oMzA0MzQud3d3My5ocC5jb20vdDUvTm90ZWJvb2stV2lyZWxlc3MtYW5kLU5ldHdvcmtpbmcvSFAtTWVkaWFUZWstTVQ3OTIxLVdpcmVsZXNzLUxhbi1Ecml2ZXItZm9yLVdpbmRvd3MtMTEtdXBkYXRlL3RkLXAvODcyMDUxNw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c2f645df5fe0460c27866cc37ff3f598e8ccff9a8bf112b2878ba320ce06ed1dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e9aad54-d5a2-6c97-3e6c-bab5d4c26d34&amp;u=a1aHR0cHM6Ly9oMzA0MzQud3d3My5ocC5jb20vdDUvTm90ZWJvb2stU29mdHdhcmUtYW5kLUhvdy1Uby1RdWVzdGlvbnMvSFAtU3VwcG9ydC1Bc3Npc3RhbnQtRHJpdmVyLXVwZGF0ZXMvdGQtcC84NzA1NzM2&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=39f23bde9d39c88ef38fe762bcad8d4253be923bc708c2b6e5e7a14753f122dcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1de4d1fc-5f6b-689d-34ae-c61d5e9e6962&amp;u=a1aHR0cHM6Ly93d3cubWljcm9zb2Z0LmNvbS9lbi11cz9tc29ja2lkPTFkZTRkMWZjNWY2YjY4OWQzNGFlYzYxZDVlOWU2OTYy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c9cad90b611f838437a86993ebffa2e8921d4d86e8529426350cbfea121910fdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1de4d1fc-5f6b-689d-34ae-c61d5e9e6962&amp;u=a1aHR0cHM6Ly9hY2NvdW50Lm1pY3Jvc29mdC5jb20vYWNjb3VudA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=916aae1a2ebb48be0403d62f0f1e06bc6cfd3913729216312650b6428c2df170JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1de4d1fc-5f6b-689d-34ae-c61d5e9e6962&amp;u=a1aHR0cHM6Ly9teWFjY291bnQubWljcm9zb2Z0LmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=51c0ce4e324ebe69c080652474a0a6998a7f793d5364554faa4e09e13bafcb8dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1de4d1fc-5f6b-689d-34ae-c61d5e9e6962&amp;u=a1aHR0cHM6Ly93d3cubWljcm9zb2Z0LmNvbS9lbi11cy9taWNyb3NvZnQtMzY1P21zb2NraWQ9MWRlNGQxZmM1ZjZiNjg5ZDM0YWVjNjFkNWU5ZTY5NjI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b03f24b3ae52f8751f53cb1d4af477e2d97397bbb1be0dc5d75efffb7d02128bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1de4d1fc-5f6b-689d-34ae-c61d5e9e6962&amp;u=a1aHR0cHM6Ly9vdXRsb29rLm9mZmljZS5jb20vbWFpbC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=386786d8a0e842bd9cac4612da359a8d16967a63b69c1267320b7912ed2f70bcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1de4d1fc-5f6b-689d-34ae-c61d5e9e6962&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWljcm9zb2Z0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=47a07b12c32ecdba5191d910623598750eb7150f75dccee93059b10756fe02dfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1de4d1fc-5f6b-689d-34ae-c61d5e9e6962&amp;u=a1aHR0cHM6Ly9hcHBzLm1pY3Jvc29mdC5jb20vaG9tZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b6a95189f0f84bb105708e9039b70a8234bea11684c964aa84c970a91b0adf0eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1de4d1fc-5f6b-689d-34ae-c61d5e9e6962&amp;u=a1aHR0cHM6Ly9zaWdudXAubGl2ZS5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=270c59428cccd193260073d18905f284cf0a57947a234e283335c182264e8756JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1de4d1fc-5f6b-689d-34ae-c61d5e9e6962&amp;u=a1aHR0cHM6Ly9teWFjY291bnQubWljcm9zb2Z0LmNvbS9tL2hvbWU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c03b05957c9f58dfee7c54352aa7eab235fb8a3e80c52298e14735cc9497056fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3aa69037-d9bd-607a-0424-87d6d8146100&amp;u=a1aHR0cHM6Ly93d3cuaG9ybmZhbnMuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a9d0cabffcb63c04392eb51cbb6275491076a8bf67f9720238b75fc47e276097JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3aa69037-d9bd-607a-0424-87d6d8146100&amp;u=a1aHR0cHM6Ly93d3cuaG9ybmZhbnMuY29tL2ZvcnVtcy93YmIv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fe98bfc4705ca102839b9f1f593d55b7b0ddd5350846675503c32db07d6b71c3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3aa69037-d9bd-607a-0424-87d6d8146100&amp;u=a1aHR0cHM6Ly93d3cuaG9ybmZhbnMuY29tL3RocmVhZHMvdGVubmVzc2VlLXZzLXRleGFzLTEyLTEzLTIwLjExMTEyNi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dda55e5842e018c0e08a9148036517f2249780d9a4d8344f132823e248a95469JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3aa69037-d9bd-607a-0424-87d6d8146100&amp;u=a1aHR0cHM6Ly93d3cuaG9ybmZhbnMuY29tLzIwMjYtZm9vdGJhbGwtc2NoZWR1bGUv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=51d692271208fdaced219b6a5298108b9ac7701257937f396758bc2b1e02be01JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3aa69037-d9bd-607a-0424-87d6d8146100&amp;u=a1aHR0cHM6Ly93d3cuaG9ybmZhbnMuY29tL2ZvcnVtcy9mb290YmFsbC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fb0205875704d83c0c48802918454989e4c311e9bae5c80e6ae071c021b753b4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3aa69037-d9bd-607a-0424-87d6d8146100&amp;u=a1aHR0cHM6Ly93d3cuaG9ybmZhbnMuY29tL3RocmVhZHMvdGV4YXMtbWlzc291cmkuMTE2Mjk2L3BhZ2UtMg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5bc5488d0d2364b2ce792695143a5c1e4870ad20f37026b46abcbcc0108f0a0fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3aa69037-d9bd-607a-0424-87d6d8146100&amp;u=a1aHR0cHM6Ly93d3cuaG9ybmZhbnMuY29tL3RocmVhZHMvMTAwLWRheS1jb3VudGRvd24tMjAyNi4xMTY0ODEvcGFnZS00&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=04c725032d5ae0ef57996a088d3fba9035571da2cf0c8dfd4bdc84792a9fb421JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3aa69037-d9bd-607a-0424-87d6d8146100&amp;u=a1aHR0cHM6Ly93d3cuaG9ybmZhbnMuY29tL3RocmVhZHMvdGVubmVzc2VlLWF0LXRleGFzLTAxLTIzLTIwMjUuMTE1NzgyLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5581d827666eb514f13352b3766da23ec12b1192898bec2b000d3cefcfce7a0bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3aa69037-d9bd-607a-0424-87d6d8146100&amp;u=a1aHR0cHM6Ly93d3cuaG9ybmZhbnMuY29tL2ZvcnVtcy93YmIvcGFnZS0y&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a74ab11c4882881b6bb22bd3cd411750e727354d9e8431f685c8210651ce573fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3aa69037-d9bd-607a-0424-87d6d8146100&amp;u=a1aHR0cHM6Ly93d3cuaG9ybmZhbnMuY29tL3RocmVhZHMvdGVubmVzc2VlLXdlLWRyb3BwZWQtdGhlLXNlcmllcy0xLTIuMTE2NDY0L3BhZ2UtNA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5c7c66acd34375a3b0672ec350ad8f829f3310aa0ee292547e65decec67e570aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15a6a5c0-47c0-6cd0-1295-b22146b46ddb&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20veW91dHViZXR2Lz9obD1lbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1233e3311b23843ecb00a33f9c106eb9e3bc09caafe46599778bc622db0d29c8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15a6a5c0-47c0-6cd0-1295-b22146b46ddb&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20veW91dHViZXR2L2Fuc3dlci83MTI5NzY4P2hsPWVuJmNvPUdFTklFLlBsYXRmb3JtJTNERGVza3RvcA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4f103c44e754569ba5d60a8d396b93f9f4e9d5cad53898a34bc1cbc645cf963bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15a6a5c0-47c0-6cd0-1295-b22146b46ddb&amp;u=a1aHR0cHM6Ly9vYnNwcm9qZWN0LmNvbS9mb3J1bS9yZXNvdXJjZXMvYWR2YW5jZWQtc2NlbmUtc3dpdGNoZXIuMzk1Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=11bee3f6334436f23a85dda04a76ca394584b4e3d42ef33a97c3b829b25b60f4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15a6a5c0-47c0-6cd0-1295-b22146b46ddb&amp;u=a1aHR0cHM6Ly9vYnNwcm9qZWN0LmNvbS9mb3J1bS90YWdzL3lvdXR1YmUv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1d77ecf6f912d0f23af7942af5f2b2b275e07f6f8fb2b6fd0890dab5146972b6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15a6a5c0-47c0-6cd0-1295-b22146b46ddb&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20veW91dHViZXR2L2Fuc3dlci8xNTEzNzc3Mz9obD1lbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fca9ffcc6370177aa8e5b66112412b19add08f4b02f5b294b61437f2e41350a7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15a6a5c0-47c0-6cd0-1295-b22146b46ddb&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20veW91dHViZS9hbnN3ZXIvNjE1OTI1ND9obD1lbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d84b7bcfd152472145f30178222f857d3c3216deec45af47bb136271b6386ceeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15a6a5c0-47c0-6cd0-1295-b22146b46ddb&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20veW91dHViZS90cm91Ymxlc2hvb3Rlci8zMjE5MDk3P2hsPWVu&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bfd820fa8d85f3ff390174b9eba54a2c25712f1d80d0ad88feee5b8f5c4f8373JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15a6a5c0-47c0-6cd0-1295-b22146b46ddb&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20veW91dHViZS9hbnN3ZXIvMjc5NzQ1ND9obD1lbiZjbz1HRU5JRS5QbGF0Zm9ybSUzREFuZHJvaWQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1abbf507174a63b81f220ac48dc1d92ca8ae256fb7a175e58ef05387f43f9894JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15a6a5c0-47c0-6cd0-1295-b22146b46ddb&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20veW91dHViZS9hbnN3ZXIvOTU3MjU_aGw9ZW4mY289R0VOSUUuUGxhdGZvcm0lM0REZXNrdG9w&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=701b012f02a9afcdf70ef41794eb200382884e0cf18759e22b0fa6f3d65d2563JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15a6a5c0-47c0-6cd0-1295-b22146b46ddb&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20vbWVldC9hbnN3ZXIvOTMwMzA2OT9obD1lbi1HQiZjbz1HRU5JRS5QbGF0Zm9ybSUzRERlc2t0b3A&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>
+  </si>
+  <si>
+    <t>Green Point</t>
+  </si>
+  <si>
+    <t>Woodstock</t>
+  </si>
+  <si>
+    <t>Observatory</t>
+  </si>
+  <si>
+    <t>Salt River</t>
   </si>
   <si>
     <t>Bing</t>
@@ -934,7 +1180,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H130"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -968,19 +1214,19 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C2" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="G2" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H2" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -988,19 +1234,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="G3" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H3" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1008,19 +1254,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C4" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="G4" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H4" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1028,19 +1274,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="G5" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H5" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1048,19 +1294,19 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C6" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="G6" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H6" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1068,19 +1314,19 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="G7" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H7" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1088,19 +1334,19 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="G8" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H8" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1108,19 +1354,19 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="G9" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H9" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1128,19 +1374,19 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="G10" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H10" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1148,19 +1394,19 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="G11" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H11" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1168,19 +1414,19 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>110</v>
+        <v>149</v>
       </c>
       <c r="G12" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H12" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1188,19 +1434,19 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>111</v>
+        <v>150</v>
       </c>
       <c r="G13" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H13" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1208,19 +1454,19 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="G14" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H14" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1228,19 +1474,19 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>113</v>
+        <v>152</v>
       </c>
       <c r="G15" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H15" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1248,19 +1494,19 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="G16" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H16" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1268,19 +1514,19 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>115</v>
+        <v>154</v>
       </c>
       <c r="G17" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H17" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1288,19 +1534,19 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C18" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>116</v>
+        <v>155</v>
       </c>
       <c r="G18" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H18" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1308,19 +1554,19 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>117</v>
+        <v>156</v>
       </c>
       <c r="G19" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H19" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1328,19 +1574,19 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C20" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>118</v>
+        <v>157</v>
       </c>
       <c r="G20" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H20" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1348,19 +1594,19 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C21" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>119</v>
+        <v>158</v>
       </c>
       <c r="G21" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H21" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1368,19 +1614,19 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C22" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="G22" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H22" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1388,19 +1634,19 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C23" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="G23" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H23" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1408,19 +1654,19 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C24" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>122</v>
+        <v>161</v>
       </c>
       <c r="G24" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H24" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1428,19 +1674,19 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C25" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>123</v>
+        <v>162</v>
       </c>
       <c r="G25" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H25" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1448,19 +1694,19 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C26" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>124</v>
+        <v>163</v>
       </c>
       <c r="G26" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H26" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1468,19 +1714,19 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C27" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>125</v>
+        <v>164</v>
       </c>
       <c r="G27" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H27" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1488,19 +1734,19 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C28" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>126</v>
+        <v>165</v>
       </c>
       <c r="G28" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H28" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1508,19 +1754,19 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C29" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>127</v>
+        <v>166</v>
       </c>
       <c r="G29" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H29" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1528,19 +1774,19 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C30" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>128</v>
+        <v>167</v>
       </c>
       <c r="G30" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H30" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1548,19 +1794,19 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C31" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>129</v>
+        <v>168</v>
       </c>
       <c r="G31" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H31" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1568,19 +1814,19 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C32" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>130</v>
+        <v>169</v>
       </c>
       <c r="G32" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H32" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1588,19 +1834,19 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C33" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>131</v>
+        <v>170</v>
       </c>
       <c r="G33" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H33" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1608,19 +1854,19 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>132</v>
+        <v>171</v>
       </c>
       <c r="G34" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H34" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1628,19 +1874,19 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C35" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>133</v>
+        <v>172</v>
       </c>
       <c r="G35" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H35" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1648,19 +1894,19 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C36" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="G36" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H36" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1668,19 +1914,19 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C37" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>135</v>
+        <v>174</v>
       </c>
       <c r="G37" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H37" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1688,19 +1934,19 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C38" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>136</v>
+        <v>175</v>
       </c>
       <c r="G38" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H38" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1708,19 +1954,19 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C39" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>137</v>
+        <v>176</v>
       </c>
       <c r="G39" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H39" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1728,19 +1974,19 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C40" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>138</v>
+        <v>177</v>
       </c>
       <c r="G40" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H40" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1748,19 +1994,19 @@
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C41" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="G41" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H41" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1768,19 +2014,19 @@
         <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C42" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>140</v>
+        <v>179</v>
       </c>
       <c r="G42" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H42" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1788,19 +2034,19 @@
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C43" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="G43" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H43" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1808,19 +2054,19 @@
         <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C44" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>142</v>
+        <v>181</v>
       </c>
       <c r="G44" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H44" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1828,19 +2074,19 @@
         <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C45" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>143</v>
+        <v>182</v>
       </c>
       <c r="G45" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H45" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1848,19 +2094,19 @@
         <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C46" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>144</v>
+        <v>183</v>
       </c>
       <c r="G46" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H46" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -1868,19 +2114,19 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C47" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>145</v>
+        <v>184</v>
       </c>
       <c r="G47" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H47" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -1888,19 +2134,19 @@
         <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C48" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>146</v>
+        <v>185</v>
       </c>
       <c r="G48" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H48" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -1908,19 +2154,19 @@
         <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C49" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
       <c r="G49" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H49" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -1928,19 +2174,19 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C50" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>148</v>
+        <v>187</v>
       </c>
       <c r="G50" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H50" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -1948,19 +2194,19 @@
         <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C51" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>149</v>
+        <v>188</v>
       </c>
       <c r="G51" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H51" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -1968,19 +2214,19 @@
         <v>58</v>
       </c>
       <c r="B52" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C52" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>150</v>
+        <v>189</v>
       </c>
       <c r="G52" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H52" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -1988,19 +2234,19 @@
         <v>59</v>
       </c>
       <c r="B53" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C53" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>151</v>
+        <v>190</v>
       </c>
       <c r="G53" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H53" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -2008,19 +2254,19 @@
         <v>60</v>
       </c>
       <c r="B54" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C54" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>152</v>
+        <v>191</v>
       </c>
       <c r="G54" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H54" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -2028,19 +2274,19 @@
         <v>61</v>
       </c>
       <c r="B55" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C55" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>153</v>
+        <v>192</v>
       </c>
       <c r="G55" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H55" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -2048,19 +2294,19 @@
         <v>62</v>
       </c>
       <c r="B56" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C56" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>154</v>
+        <v>193</v>
       </c>
       <c r="G56" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H56" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -2068,19 +2314,19 @@
         <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C57" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>155</v>
+        <v>194</v>
       </c>
       <c r="G57" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H57" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -2088,19 +2334,19 @@
         <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C58" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>156</v>
+        <v>195</v>
       </c>
       <c r="G58" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H58" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -2108,19 +2354,19 @@
         <v>65</v>
       </c>
       <c r="B59" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C59" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>157</v>
+        <v>196</v>
       </c>
       <c r="G59" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H59" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -2128,19 +2374,19 @@
         <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C60" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>158</v>
+        <v>197</v>
       </c>
       <c r="G60" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H60" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2148,19 +2394,19 @@
         <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C61" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>159</v>
+        <v>198</v>
       </c>
       <c r="G61" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H61" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2168,19 +2414,19 @@
         <v>68</v>
       </c>
       <c r="B62" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C62" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>160</v>
+        <v>199</v>
       </c>
       <c r="G62" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H62" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2188,19 +2434,19 @@
         <v>69</v>
       </c>
       <c r="B63" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C63" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>161</v>
+        <v>200</v>
       </c>
       <c r="G63" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H63" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2208,19 +2454,19 @@
         <v>70</v>
       </c>
       <c r="B64" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C64" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="G64" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H64" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2228,19 +2474,19 @@
         <v>71</v>
       </c>
       <c r="B65" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C65" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>163</v>
+        <v>202</v>
       </c>
       <c r="G65" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H65" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2248,19 +2494,19 @@
         <v>72</v>
       </c>
       <c r="B66" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C66" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>164</v>
+        <v>203</v>
       </c>
       <c r="G66" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H66" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2268,19 +2514,19 @@
         <v>73</v>
       </c>
       <c r="B67" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C67" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>165</v>
+        <v>204</v>
       </c>
       <c r="G67" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H67" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2288,19 +2534,19 @@
         <v>74</v>
       </c>
       <c r="B68" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C68" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>166</v>
+        <v>205</v>
       </c>
       <c r="G68" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H68" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2308,19 +2554,19 @@
         <v>75</v>
       </c>
       <c r="B69" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C69" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>167</v>
+        <v>206</v>
       </c>
       <c r="G69" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H69" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -2328,19 +2574,19 @@
         <v>76</v>
       </c>
       <c r="B70" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C70" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>168</v>
+        <v>207</v>
       </c>
       <c r="G70" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H70" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2348,19 +2594,19 @@
         <v>77</v>
       </c>
       <c r="B71" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C71" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="G71" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H71" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -2368,19 +2614,19 @@
         <v>78</v>
       </c>
       <c r="B72" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C72" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>170</v>
+        <v>209</v>
       </c>
       <c r="G72" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H72" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -2388,19 +2634,19 @@
         <v>79</v>
       </c>
       <c r="B73" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C73" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>171</v>
+        <v>210</v>
       </c>
       <c r="G73" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H73" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -2408,19 +2654,19 @@
         <v>80</v>
       </c>
       <c r="B74" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C74" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>172</v>
+        <v>211</v>
       </c>
       <c r="G74" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H74" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -2428,19 +2674,19 @@
         <v>81</v>
       </c>
       <c r="B75" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C75" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>173</v>
+        <v>212</v>
       </c>
       <c r="G75" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H75" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -2448,19 +2694,19 @@
         <v>82</v>
       </c>
       <c r="B76" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C76" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>174</v>
+        <v>213</v>
       </c>
       <c r="G76" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H76" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -2468,19 +2714,19 @@
         <v>83</v>
       </c>
       <c r="B77" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C77" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>175</v>
+        <v>214</v>
       </c>
       <c r="G77" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H77" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -2488,19 +2734,19 @@
         <v>84</v>
       </c>
       <c r="B78" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C78" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>176</v>
+        <v>215</v>
       </c>
       <c r="G78" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H78" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -2508,19 +2754,19 @@
         <v>85</v>
       </c>
       <c r="B79" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C79" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>177</v>
+        <v>216</v>
       </c>
       <c r="G79" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H79" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -2528,19 +2774,19 @@
         <v>86</v>
       </c>
       <c r="B80" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C80" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>178</v>
+        <v>217</v>
       </c>
       <c r="G80" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H80" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -2548,19 +2794,19 @@
         <v>87</v>
       </c>
       <c r="B81" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C81" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>179</v>
+        <v>218</v>
       </c>
       <c r="G81" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H81" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -2568,19 +2814,19 @@
         <v>88</v>
       </c>
       <c r="B82" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C82" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>180</v>
+        <v>219</v>
       </c>
       <c r="G82" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H82" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -2588,19 +2834,19 @@
         <v>89</v>
       </c>
       <c r="B83" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C83" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>181</v>
+        <v>220</v>
       </c>
       <c r="G83" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H83" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -2608,19 +2854,19 @@
         <v>90</v>
       </c>
       <c r="B84" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C84" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>182</v>
+        <v>221</v>
       </c>
       <c r="G84" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H84" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -2628,19 +2874,19 @@
         <v>91</v>
       </c>
       <c r="B85" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C85" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>183</v>
+        <v>222</v>
       </c>
       <c r="G85" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H85" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -2648,19 +2894,19 @@
         <v>92</v>
       </c>
       <c r="B86" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C86" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>184</v>
+        <v>223</v>
       </c>
       <c r="G86" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H86" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -2668,19 +2914,19 @@
         <v>93</v>
       </c>
       <c r="B87" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C87" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>185</v>
+        <v>224</v>
       </c>
       <c r="G87" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H87" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -2688,19 +2934,19 @@
         <v>94</v>
       </c>
       <c r="B88" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C88" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="G88" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H88" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -2708,19 +2954,19 @@
         <v>95</v>
       </c>
       <c r="B89" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C89" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>187</v>
+        <v>226</v>
       </c>
       <c r="G89" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H89" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -2728,19 +2974,19 @@
         <v>96</v>
       </c>
       <c r="B90" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C90" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>188</v>
+        <v>227</v>
       </c>
       <c r="G90" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H90" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -2748,19 +2994,799 @@
         <v>97</v>
       </c>
       <c r="B91" t="s">
+        <v>137</v>
+      </c>
+      <c r="C91" t="s">
+        <v>138</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="G91" t="s">
+        <v>268</v>
+      </c>
+      <c r="H91" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" t="s">
         <v>98</v>
       </c>
-      <c r="C91" t="s">
+      <c r="B92" t="s">
+        <v>137</v>
+      </c>
+      <c r="C92" t="s">
+        <v>138</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G92" t="s">
+        <v>269</v>
+      </c>
+      <c r="H92" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" t="s">
         <v>99</v>
       </c>
-      <c r="F91" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="G91" t="s">
-        <v>190</v>
-      </c>
-      <c r="H91" t="s">
-        <v>191</v>
+      <c r="B93" t="s">
+        <v>137</v>
+      </c>
+      <c r="C93" t="s">
+        <v>138</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G93" t="s">
+        <v>269</v>
+      </c>
+      <c r="H93" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" t="s">
+        <v>100</v>
+      </c>
+      <c r="B94" t="s">
+        <v>137</v>
+      </c>
+      <c r="C94" t="s">
+        <v>138</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G94" t="s">
+        <v>269</v>
+      </c>
+      <c r="H94" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" t="s">
+        <v>101</v>
+      </c>
+      <c r="B95" t="s">
+        <v>137</v>
+      </c>
+      <c r="C95" t="s">
+        <v>138</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G95" t="s">
+        <v>269</v>
+      </c>
+      <c r="H95" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96" t="s">
+        <v>102</v>
+      </c>
+      <c r="B96" t="s">
+        <v>137</v>
+      </c>
+      <c r="C96" t="s">
+        <v>138</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="G96" t="s">
+        <v>269</v>
+      </c>
+      <c r="H96" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" t="s">
+        <v>103</v>
+      </c>
+      <c r="B97" t="s">
+        <v>137</v>
+      </c>
+      <c r="C97" t="s">
+        <v>138</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G97" t="s">
+        <v>269</v>
+      </c>
+      <c r="H97" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" t="s">
+        <v>104</v>
+      </c>
+      <c r="B98" t="s">
+        <v>137</v>
+      </c>
+      <c r="C98" t="s">
+        <v>138</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="G98" t="s">
+        <v>269</v>
+      </c>
+      <c r="H98" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" t="s">
+        <v>105</v>
+      </c>
+      <c r="B99" t="s">
+        <v>137</v>
+      </c>
+      <c r="C99" t="s">
+        <v>138</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="G99" t="s">
+        <v>269</v>
+      </c>
+      <c r="H99" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" t="s">
+        <v>106</v>
+      </c>
+      <c r="B100" t="s">
+        <v>137</v>
+      </c>
+      <c r="C100" t="s">
+        <v>138</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="G100" t="s">
+        <v>269</v>
+      </c>
+      <c r="H100" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" t="s">
+        <v>107</v>
+      </c>
+      <c r="B101" t="s">
+        <v>137</v>
+      </c>
+      <c r="C101" t="s">
+        <v>138</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="G101" t="s">
+        <v>269</v>
+      </c>
+      <c r="H101" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102" t="s">
+        <v>108</v>
+      </c>
+      <c r="B102" t="s">
+        <v>137</v>
+      </c>
+      <c r="C102" t="s">
+        <v>138</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="G102" t="s">
+        <v>270</v>
+      </c>
+      <c r="H102" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103" t="s">
+        <v>109</v>
+      </c>
+      <c r="B103" t="s">
+        <v>137</v>
+      </c>
+      <c r="C103" t="s">
+        <v>138</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="G103" t="s">
+        <v>270</v>
+      </c>
+      <c r="H103" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104" t="s">
+        <v>110</v>
+      </c>
+      <c r="B104" t="s">
+        <v>137</v>
+      </c>
+      <c r="C104" t="s">
+        <v>138</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="G104" t="s">
+        <v>270</v>
+      </c>
+      <c r="H104" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105" t="s">
+        <v>111</v>
+      </c>
+      <c r="B105" t="s">
+        <v>137</v>
+      </c>
+      <c r="C105" t="s">
+        <v>138</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="G105" t="s">
+        <v>270</v>
+      </c>
+      <c r="H105" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106" t="s">
+        <v>112</v>
+      </c>
+      <c r="B106" t="s">
+        <v>137</v>
+      </c>
+      <c r="C106" t="s">
+        <v>138</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="G106" t="s">
+        <v>270</v>
+      </c>
+      <c r="H106" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107" t="s">
+        <v>113</v>
+      </c>
+      <c r="B107" t="s">
+        <v>137</v>
+      </c>
+      <c r="C107" t="s">
+        <v>138</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G107" t="s">
+        <v>270</v>
+      </c>
+      <c r="H107" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108" t="s">
+        <v>114</v>
+      </c>
+      <c r="B108" t="s">
+        <v>137</v>
+      </c>
+      <c r="C108" t="s">
+        <v>138</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="G108" t="s">
+        <v>270</v>
+      </c>
+      <c r="H108" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
+      <c r="A109" t="s">
+        <v>115</v>
+      </c>
+      <c r="B109" t="s">
+        <v>137</v>
+      </c>
+      <c r="C109" t="s">
+        <v>138</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="G109" t="s">
+        <v>270</v>
+      </c>
+      <c r="H109" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
+      <c r="A110" t="s">
+        <v>116</v>
+      </c>
+      <c r="B110" t="s">
+        <v>137</v>
+      </c>
+      <c r="C110" t="s">
+        <v>138</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="G110" t="s">
+        <v>270</v>
+      </c>
+      <c r="H110" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="A111" t="s">
+        <v>117</v>
+      </c>
+      <c r="B111" t="s">
+        <v>137</v>
+      </c>
+      <c r="C111" t="s">
+        <v>138</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="G111" t="s">
+        <v>271</v>
+      </c>
+      <c r="H111" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
+      <c r="A112" t="s">
+        <v>118</v>
+      </c>
+      <c r="B112" t="s">
+        <v>137</v>
+      </c>
+      <c r="C112" t="s">
+        <v>138</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="G112" t="s">
+        <v>271</v>
+      </c>
+      <c r="H112" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113" t="s">
+        <v>119</v>
+      </c>
+      <c r="B113" t="s">
+        <v>137</v>
+      </c>
+      <c r="C113" t="s">
+        <v>138</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="G113" t="s">
+        <v>271</v>
+      </c>
+      <c r="H113" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114" t="s">
+        <v>120</v>
+      </c>
+      <c r="B114" t="s">
+        <v>137</v>
+      </c>
+      <c r="C114" t="s">
+        <v>138</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="G114" t="s">
+        <v>271</v>
+      </c>
+      <c r="H114" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115" t="s">
+        <v>121</v>
+      </c>
+      <c r="B115" t="s">
+        <v>137</v>
+      </c>
+      <c r="C115" t="s">
+        <v>138</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G115" t="s">
+        <v>271</v>
+      </c>
+      <c r="H115" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
+      <c r="A116" t="s">
+        <v>122</v>
+      </c>
+      <c r="B116" t="s">
+        <v>137</v>
+      </c>
+      <c r="C116" t="s">
+        <v>138</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="G116" t="s">
+        <v>271</v>
+      </c>
+      <c r="H116" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="A117" t="s">
+        <v>123</v>
+      </c>
+      <c r="B117" t="s">
+        <v>137</v>
+      </c>
+      <c r="C117" t="s">
+        <v>138</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="G117" t="s">
+        <v>271</v>
+      </c>
+      <c r="H117" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
+      <c r="A118" t="s">
+        <v>124</v>
+      </c>
+      <c r="B118" t="s">
+        <v>137</v>
+      </c>
+      <c r="C118" t="s">
+        <v>138</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="G118" t="s">
+        <v>271</v>
+      </c>
+      <c r="H118" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119" t="s">
+        <v>125</v>
+      </c>
+      <c r="B119" t="s">
+        <v>137</v>
+      </c>
+      <c r="C119" t="s">
+        <v>138</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="G119" t="s">
+        <v>271</v>
+      </c>
+      <c r="H119" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120" t="s">
+        <v>126</v>
+      </c>
+      <c r="B120" t="s">
+        <v>137</v>
+      </c>
+      <c r="C120" t="s">
+        <v>138</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="G120" t="s">
+        <v>271</v>
+      </c>
+      <c r="H120" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8">
+      <c r="A121" t="s">
+        <v>127</v>
+      </c>
+      <c r="B121" t="s">
+        <v>137</v>
+      </c>
+      <c r="C121" t="s">
+        <v>138</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G121" t="s">
+        <v>272</v>
+      </c>
+      <c r="H121" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122" t="s">
+        <v>128</v>
+      </c>
+      <c r="B122" t="s">
+        <v>137</v>
+      </c>
+      <c r="C122" t="s">
+        <v>138</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="G122" t="s">
+        <v>272</v>
+      </c>
+      <c r="H122" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="A123" t="s">
+        <v>129</v>
+      </c>
+      <c r="B123" t="s">
+        <v>137</v>
+      </c>
+      <c r="C123" t="s">
+        <v>138</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="G123" t="s">
+        <v>272</v>
+      </c>
+      <c r="H123" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124" t="s">
+        <v>130</v>
+      </c>
+      <c r="B124" t="s">
+        <v>137</v>
+      </c>
+      <c r="C124" t="s">
+        <v>138</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="G124" t="s">
+        <v>272</v>
+      </c>
+      <c r="H124" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125" t="s">
+        <v>131</v>
+      </c>
+      <c r="B125" t="s">
+        <v>137</v>
+      </c>
+      <c r="C125" t="s">
+        <v>138</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="G125" t="s">
+        <v>272</v>
+      </c>
+      <c r="H125" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126" t="s">
+        <v>132</v>
+      </c>
+      <c r="B126" t="s">
+        <v>137</v>
+      </c>
+      <c r="C126" t="s">
+        <v>138</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G126" t="s">
+        <v>272</v>
+      </c>
+      <c r="H126" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127" t="s">
+        <v>133</v>
+      </c>
+      <c r="B127" t="s">
+        <v>137</v>
+      </c>
+      <c r="C127" t="s">
+        <v>138</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="G127" t="s">
+        <v>272</v>
+      </c>
+      <c r="H127" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
+      <c r="A128" t="s">
+        <v>134</v>
+      </c>
+      <c r="B128" t="s">
+        <v>137</v>
+      </c>
+      <c r="C128" t="s">
+        <v>138</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="G128" t="s">
+        <v>272</v>
+      </c>
+      <c r="H128" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8">
+      <c r="A129" t="s">
+        <v>135</v>
+      </c>
+      <c r="B129" t="s">
+        <v>137</v>
+      </c>
+      <c r="C129" t="s">
+        <v>138</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G129" t="s">
+        <v>272</v>
+      </c>
+      <c r="H129" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8">
+      <c r="A130" t="s">
+        <v>136</v>
+      </c>
+      <c r="B130" t="s">
+        <v>137</v>
+      </c>
+      <c r="C130" t="s">
+        <v>138</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="G130" t="s">
+        <v>272</v>
+      </c>
+      <c r="H130" t="s">
+        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -2855,6 +3881,45 @@
     <hyperlink ref="F89" r:id="rId88"/>
     <hyperlink ref="F90" r:id="rId89"/>
     <hyperlink ref="F91" r:id="rId90"/>
+    <hyperlink ref="F92" r:id="rId91"/>
+    <hyperlink ref="F93" r:id="rId92"/>
+    <hyperlink ref="F94" r:id="rId93"/>
+    <hyperlink ref="F95" r:id="rId94"/>
+    <hyperlink ref="F96" r:id="rId95"/>
+    <hyperlink ref="F97" r:id="rId96"/>
+    <hyperlink ref="F98" r:id="rId97"/>
+    <hyperlink ref="F99" r:id="rId98"/>
+    <hyperlink ref="F100" r:id="rId99"/>
+    <hyperlink ref="F101" r:id="rId100"/>
+    <hyperlink ref="F102" r:id="rId101"/>
+    <hyperlink ref="F103" r:id="rId102"/>
+    <hyperlink ref="F104" r:id="rId103"/>
+    <hyperlink ref="F105" r:id="rId104"/>
+    <hyperlink ref="F106" r:id="rId105"/>
+    <hyperlink ref="F107" r:id="rId106"/>
+    <hyperlink ref="F108" r:id="rId107"/>
+    <hyperlink ref="F109" r:id="rId108"/>
+    <hyperlink ref="F110" r:id="rId109"/>
+    <hyperlink ref="F111" r:id="rId110"/>
+    <hyperlink ref="F112" r:id="rId111"/>
+    <hyperlink ref="F113" r:id="rId112"/>
+    <hyperlink ref="F114" r:id="rId113"/>
+    <hyperlink ref="F115" r:id="rId114"/>
+    <hyperlink ref="F116" r:id="rId115"/>
+    <hyperlink ref="F117" r:id="rId116"/>
+    <hyperlink ref="F118" r:id="rId117"/>
+    <hyperlink ref="F119" r:id="rId118"/>
+    <hyperlink ref="F120" r:id="rId119"/>
+    <hyperlink ref="F121" r:id="rId120"/>
+    <hyperlink ref="F122" r:id="rId121"/>
+    <hyperlink ref="F123" r:id="rId122"/>
+    <hyperlink ref="F124" r:id="rId123"/>
+    <hyperlink ref="F125" r:id="rId124"/>
+    <hyperlink ref="F126" r:id="rId125"/>
+    <hyperlink ref="F127" r:id="rId126"/>
+    <hyperlink ref="F128" r:id="rId127"/>
+    <hyperlink ref="F129" r:id="rId128"/>
+    <hyperlink ref="F130" r:id="rId129"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/scraped_Cape_Town_Health_and_Wellness.xlsx
+++ b/results/scraped_Cape_Town_Health_and_Wellness.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="186">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -40,274 +40,265 @@
     <t>Source</t>
   </si>
   <si>
-    <t>Community- City ofColumbus,Ohio</t>
-  </si>
-  <si>
-    <t>CRISOhio</t>
-  </si>
-  <si>
-    <t>Home |Columbus State Community College</t>
-  </si>
-  <si>
     <t>Community-Wikipedia</t>
   </si>
   <si>
-    <t>Facilities &amp; Venues - City ofColumbus,Ohio</t>
-  </si>
-  <si>
-    <t>CommunityCenters -Columbus Recreation and Parks Department</t>
-  </si>
-  <si>
-    <t>Community resources in Columbus</t>
-  </si>
-  <si>
-    <t>IMPACTCommunityAction</t>
+    <t>CommunityPartners - Creating more equitable, just, and vibrant …</t>
+  </si>
+  <si>
+    <t>Community (TV series) -Wikipedia</t>
+  </si>
+  <si>
+    <t>Home | 211LA</t>
+  </si>
+  <si>
+    <t>California Community Foundation| A Good Life for All</t>
   </si>
   <si>
     <t>COMMUNITYDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
-    <t>Home - GreaterColumbus CommunityHouse</t>
+    <t>Community(TV Series 2009–2015) - IMDb</t>
+  </si>
+  <si>
+    <t>Community– Parks &amp; Recreation</t>
+  </si>
+  <si>
+    <t>Homepage |LACCD</t>
+  </si>
+  <si>
+    <t>Home | Neighborhood Info</t>
   </si>
   <si>
     <t>What ishospice? -HospiceFoundation of America</t>
   </si>
   <si>
-    <t>Hospiceand Palliative Care at Sharon Regional Health System</t>
-  </si>
-  <si>
-    <t>FamilyHospiceAnd Palliative Care -HospiceinHermitage,PA</t>
-  </si>
-  <si>
-    <t>4 Hospices inHermitage,PA- CareListings</t>
-  </si>
-  <si>
     <t>Hospice- Wikipedia</t>
   </si>
   <si>
-    <t>Frequently Asked Questions AboutHospiceCare - National Institute …</t>
-  </si>
-  <si>
-    <t>The Best 10HospicenearHermitage,PA16148 - Yelp</t>
-  </si>
-  <si>
-    <t>Helping Hands Home Care Service -HospiceCare inHermitage,PA...</t>
-  </si>
-  <si>
-    <t>Hospice&amp; Community Care</t>
-  </si>
-  <si>
-    <t>Hospice| Department of Health | Commonwealth ofPennsylvania</t>
+    <t>THE BEST10 HOSPICE IN LOS ANGELES, CA- Yelp</t>
+  </si>
+  <si>
+    <t>Frequently Asked Questions AboutHospiceCare | National ...</t>
+  </si>
+  <si>
+    <t>Hospice Care- Care Options |CaliforniaDepartment of Aging ...</t>
+  </si>
+  <si>
+    <t>Welcome to theCalifornia Hospiceand Palliative Care Association</t>
+  </si>
+  <si>
+    <t>Hospice&amp; Palliative Care inLos Angeles|Silverado Hospice</t>
+  </si>
+  <si>
+    <t>TOP 10BEST Hospice in Los Angeles, CA- (2026 Guide ... - Yelp</t>
+  </si>
+  <si>
+    <t>HospiceCare and Palliative Care inLos Angeles CA</t>
+  </si>
+  <si>
+    <t>AgapeHospice&amp; Palliative Care in LA &amp; Orange Counties</t>
   </si>
   <si>
     <t>MENTALDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
+    <t>AboutMentalHealth |MentalHealth | CDC</t>
+  </si>
+  <si>
     <t>Mental health-Wikipedia</t>
   </si>
   <si>
-    <t>AboutMentalHealth |MentalHealth | CDC</t>
-  </si>
-  <si>
     <t>Mental disorders-World Health Organization(WHO)</t>
   </si>
   <si>
+    <t>MentalHealth: Causes, Symptoms, Treatment &amp; Help | SAMHSA</t>
+  </si>
+  <si>
+    <t>Mentalhealth: What's normal, what's not -Mayo Clinic</t>
+  </si>
+  <si>
+    <t>MentalDisorders: Types, Causes &amp; Symptoms -Cleveland Clinic</t>
+  </si>
+  <si>
     <t>Mentaldisorder -Wikipedia</t>
   </si>
   <si>
-    <t>MentalHealth: Causes, Symptoms, Treatment &amp; Help | SAMHSA</t>
-  </si>
-  <si>
-    <t>Mentalhealth: What's normal, what's not -Mayo Clinic</t>
-  </si>
-  <si>
-    <t>MentalHealth: What It Is &amp; Why It’s Important - Cleveland Clinic</t>
-  </si>
-  <si>
-    <t>MentalDisorders: Types, Causes &amp; Symptoms -Cleveland Clinic</t>
-  </si>
-  <si>
     <t>Mental health: Definition, common disorders, early signs, and more</t>
   </si>
   <si>
-    <t>IndianaUniversityHealth</t>
+    <t>Mental HealthDisorders Center: Types, Symptoms, Treatments ... -WebMD</t>
   </si>
   <si>
     <t>Health- Wikipedia</t>
   </si>
   <si>
-    <t>IUHealthPrimary Care -West Lafayette</t>
-  </si>
-  <si>
-    <t>ParkviewWest LafayetteHospital | ParkviewHealth</t>
-  </si>
-  <si>
-    <t>Patient Portal | MarathonHealth</t>
+    <t>Contact &amp; Hours - All ForHealth,HealthFor All</t>
+  </si>
+  <si>
+    <t>HEALTH: Longevity for All</t>
+  </si>
+  <si>
+    <t>AdventistHealth GlendaleMedical Center</t>
+  </si>
+  <si>
+    <t>WebMD- Better information. Betterhealth.</t>
+  </si>
+  <si>
+    <t>Health| Definition &amp; Importance | Britannica</t>
+  </si>
+  <si>
+    <t>DignityHealth-GlendaleMemorial Hospital andHealthCenter,CA...</t>
+  </si>
+  <si>
+    <t>CaliforniaDepartment of PublicHealth</t>
   </si>
   <si>
     <t>What ishealth?: Defining and preservinggood health</t>
   </si>
   <si>
-    <t>HEALTH: Longevity for All</t>
-  </si>
-  <si>
-    <t>Health| Definition &amp; Importance | Britannica</t>
-  </si>
-  <si>
-    <t>WebMD- Better information. Betterhealth.</t>
-  </si>
-  <si>
-    <t>EverydayHealth: Trusted Medical Information, ExpertHealthAdvice ...</t>
+    <t>LA County Department of PublicHealth- SPA 2</t>
+  </si>
+  <si>
+    <t>PRIMARYDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
     <t>PrimaryClothing - Brilliant Basics for Baby &amp; Kids</t>
   </si>
   <si>
-    <t>PRIMARYDefinition &amp; Meaning -Merriam-Webster</t>
-  </si>
-  <si>
     <t>PRIMARY| English meaning - Cambridge Dictionary</t>
   </si>
   <si>
+    <t>Games, Videos, Holidays &amp; Crafts |PrimaryGames</t>
+  </si>
+  <si>
+    <t>National Elections 2026 Live Results and Map: Delaware Primaries</t>
+  </si>
+  <si>
     <t>Primary— reporting assembled from records</t>
   </si>
   <si>
-    <t>Games, Videos, Holidays &amp; Crafts |PrimaryGames</t>
-  </si>
-  <si>
-    <t>PRIMARY| definition in the Cambridge English Dictionary</t>
-  </si>
-  <si>
-    <t>National Elections 2026 Live Results and Map: Delaware Primaries</t>
-  </si>
-  <si>
     <t>PRIMARYDefinition &amp; Meaning |Dictionary.com</t>
   </si>
   <si>
+    <t>12.Primary- The Church of Jesus Christ of Latter-day Saints</t>
+  </si>
+  <si>
     <t>Primary- Definition, Meaning &amp; Synonyms | Vocabulary.com</t>
   </si>
   <si>
-    <t>Primaryeducation -Wikipedia</t>
-  </si>
-  <si>
-    <t>Complete Health andWellness| THE WELL</t>
+    <t>Utah HousePrimaryElection 2026 Live Results - NBC News</t>
   </si>
   <si>
     <t>What is Wellness? -Global Wellness Institute</t>
   </si>
   <si>
-    <t>WellNYS Everyday - Office of Employee Relations</t>
-  </si>
-  <si>
-    <t>Well- TheNew YorkTimes</t>
-  </si>
-  <si>
-    <t>wellnesshome - NYC.gov</t>
-  </si>
-  <si>
-    <t>11 LavishWellnessRetreats Near NYC You Should Book This Winter</t>
-  </si>
-  <si>
-    <t>Top 20WellnessSpots to Unwind inNew YorkCity</t>
-  </si>
-  <si>
-    <t>Spa &amp;WellnessGuerlain | Waldorf AstoriaNew YorkHotel</t>
-  </si>
-  <si>
-    <t>THE 10 BESTNew YorkCity Spas &amp;WellnessCenters</t>
-  </si>
-  <si>
-    <t>Wellnessand Fitness Escape - AmanNew York</t>
-  </si>
-  <si>
-    <t>New YorkPsychotherapy &amp; Counseling Center (NYPCC)</t>
-  </si>
-  <si>
-    <t>NYCTherapists |ManhattanMental Health Counseling</t>
-  </si>
-  <si>
-    <t>Home -NYCCounseling | Individual and Couples Therapy |NYCand …</t>
-  </si>
-  <si>
-    <t>Home - New Horizon Counseling Center</t>
-  </si>
-  <si>
-    <t>NYCCounseling and Therapy |Manhattan New York City</t>
-  </si>
-  <si>
-    <t>Therapists in New York, NY- Psychology Today</t>
-  </si>
-  <si>
-    <t>Mental Health Counseling &amp; Therapy inNYC| myTherapyNYC</t>
-  </si>
-  <si>
-    <t>Mental Health Therapist inNYC| Comprehensive Counseling</t>
-  </si>
-  <si>
-    <t>ManhattanTherapy Individual and Couples Therapy</t>
-  </si>
-  <si>
-    <t>Free or Low-Cost Counseling in New York,NY- OpenCounseling</t>
+    <t>Corner OnWellness|Bothell,WAChiropractic Office</t>
+  </si>
+  <si>
+    <t>Welcome to Sound Health &amp;WellnessTrust</t>
+  </si>
+  <si>
+    <t>BothellChiropractic andWellnesslocated inBothell,WA</t>
+  </si>
+  <si>
+    <t>Welcome to Corner onWellness- Corner OnWellness</t>
+  </si>
+  <si>
+    <t>HolisticWellnessStudio | Zen Heart Center |Bothell</t>
+  </si>
+  <si>
+    <t>What is Wellness?</t>
+  </si>
+  <si>
+    <t>TOP 10 BESTWellnessCenter inBothell,WA- Yelp</t>
+  </si>
+  <si>
+    <t>Home - FreyWellness</t>
+  </si>
+  <si>
+    <t>Integrative Naturopathic Medicine Clinic inBothell| ISM Health &amp;Wellness</t>
+  </si>
+  <si>
+    <t>Seva Counseling — Therapists inDes Moines, Iowa</t>
+  </si>
+  <si>
+    <t>Innovative Counseling and Consulting |Des Moines,IA</t>
+  </si>
+  <si>
+    <t>Mind &amp; Spirit Counseling Center | Home</t>
+  </si>
+  <si>
+    <t>Green Counseling Services - Mental Health Counseling inIowa</t>
+  </si>
+  <si>
+    <t>MOSAIC Family Counseling Center | EMDR &amp; Counseling inDes Moines,IA</t>
+  </si>
+  <si>
+    <t>Family Legacy Counseling</t>
+  </si>
+  <si>
+    <t>Free or Low-Cost Counseling in Des Moines,IA- OpenCounseling</t>
+  </si>
+  <si>
+    <t>Turning Point Counseling |Des Moines, Iowa</t>
+  </si>
+  <si>
+    <t>Home | New Life Counseling</t>
+  </si>
+  <si>
+    <t>Therapistsin Des Moines, IA- Psychology Today</t>
+  </si>
+  <si>
+    <t>50 Best Drug &amp; Alcohol Rehab Centers inLos Angeles,CA2026 ...</t>
+  </si>
+  <si>
+    <t>18 Best Drug Rehabs inLos Angeles,CA(2026) - Supe</t>
   </si>
   <si>
     <t>Rehabilitation- MedlinePlus</t>
   </si>
   <si>
+    <t>12 BestRehab CentersInLos Angeles,CA- Addiction Resource</t>
+  </si>
+  <si>
+    <t>California RehabilitationInstitute | Home</t>
+  </si>
+  <si>
+    <t>71 Best Drug Rehabs inLos AngelesCounty,CA(2026)</t>
+  </si>
+  <si>
     <t>Rehabilitation- World Health Organization (WHO)</t>
   </si>
   <si>
-    <t>Inova Rehabilitation Services</t>
-  </si>
-  <si>
-    <t>REHABILITATIONDefinition &amp; Meaning - Merriam-Webster</t>
-  </si>
-  <si>
-    <t>The Best10 Rehabilitation Center near Ashburn, VA20147</t>
-  </si>
-  <si>
-    <t>FOXRehabilitation</t>
-  </si>
-  <si>
-    <t>Inova Physical Therapy -Ashburn</t>
-  </si>
-  <si>
-    <t>Rehabilitation- Wikipedia</t>
-  </si>
-  <si>
-    <t>SeniorRehabilitationinAshburn,Virginia| Ashby Ponds</t>
-  </si>
-  <si>
-    <t>THE BEST10 REHABILITATION CENTER IN LOUDOUN COUNTY,VA-Yelp</t>
-  </si>
-  <si>
-    <t>WebMD- Better information. Better health.</t>
-  </si>
-  <si>
-    <t>Medicine- Wikipedia</t>
-  </si>
-  <si>
-    <t>FamilyMedicalClinic - FamilyMedicalClinic ofTennessee</t>
-  </si>
-  <si>
-    <t>DeBusk College of Osteopathic Medicine</t>
+    <t>Medi-Cal- DHCS</t>
+  </si>
+  <si>
+    <t>Contact |Medi-Cal- DHCS</t>
+  </si>
+  <si>
+    <t>Program Descriptions A | BenefitsCal. Together, we benefit.</t>
+  </si>
+  <si>
+    <t>Medi-CalPlan | L.A. Care Health Plan</t>
+  </si>
+  <si>
+    <t>Health Care - Department of Public Social Services</t>
+  </si>
+  <si>
+    <t>Find a provider |Medi-CalManaged Care Health Care Options</t>
+  </si>
+  <si>
+    <t>Apply forMedi-Cal|CA.gov</t>
+  </si>
+  <si>
+    <t>County ofLos Angeles MedicalExaminer</t>
   </si>
   <si>
     <t>Medi-CalProviders</t>
   </si>
   <si>
-    <t>MedicalDiseases &amp;Conditions- Mayo Clinic</t>
-  </si>
-  <si>
-    <t>About Our Practice - FamilyMedicalClinic of Tennesssee</t>
-  </si>
-  <si>
-    <t>FamilyMedicalClinic ofHarrogate,Harrogate,TN- Healthgrades</t>
-  </si>
-  <si>
-    <t>FamilyMedicalClinic OfHarrogate, P.c. inHarrogate,TN...</t>
-  </si>
-  <si>
-    <t>LMUMedicalClinic (Harrogate) inHarrogate,TN37752</t>
+    <t>Medi-Cal| Blue Shield ofCAPromise Health Plan</t>
   </si>
   <si>
     <t>Health &amp; Wellness</t>
@@ -316,274 +307,265 @@
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a11917f8d9106f74141a0f757f7b659ebf045cdaee3cdd321646da034d20fc77JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ebc6c43-4286-67b1-3eb0-7ba243ed664b&amp;u=a1aHR0cHM6Ly93d3cuY29sdW1idXMuZ292L0NvbW11bml0eQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=901feb71ef90fe64e1af2707ba14f3ee5d6d8e3dfd951db17b362eea4750ab7eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ebc6c43-4286-67b1-3eb0-7ba243ed664b&amp;u=a1aHR0cHM6Ly93d3cuY3Jpc29oaW8ub3JnLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3397d244fff2556fc2e97d9f946bfd11669948508df2a748a5b69c25d54c6e44JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ebc6c43-4286-67b1-3eb0-7ba243ed664b&amp;u=a1aHR0cHM6Ly93d3cuY3NjYy5lZHUv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=61bc5b1a43f6fc120251d4cd26a6e7877fab08e137e8eff6f672c36fa60012f8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ebc6c43-4286-67b1-3eb0-7ba243ed664b&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Db21tdW5pdHk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=32e9233f85d044dcebd0a63270a45a4ac08de13d0b7f0f4bcdd27bd3d41b8c4fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ebc6c43-4286-67b1-3eb0-7ba243ed664b&amp;u=a1aHR0cHM6Ly93d3cuY29sdW1idXMuZ292L0NvbW11bml0eS9GYWNpbGl0aWVzLVZlbnVlcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5506f79b17f45260a92677b5b4c085960528f18788475088067a0352df304008JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ebc6c43-4286-67b1-3eb0-7ba243ed664b&amp;u=a1aHR0cHM6Ly9jb2x1bWJ1c3JlY3BhcmtzLmNvbS9mYWNpbGl0aWVzL2NvbW11bml0eWNlbnRlcnMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1a74a6fb6335c62011f5ecb5342e3adc3b8358d22ad11c8de587eed2aa7ff4dcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ebc6c43-4286-67b1-3eb0-7ba243ed664b&amp;u=a1aHR0cHM6Ly93d3cuY29sdW1idXNvbnRoZWNoZWFwLmNvbS9yZXNvdXJjZXMtaW4tY29sdW1idXMtb2gv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=11d649e4af33d18a4662d44138284df8c0e07a36711b7abc96d234d094701ce8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ebc6c43-4286-67b1-3eb0-7ba243ed664b&amp;u=a1aHR0cHM6Ly93d3cuaW1wYWN0Y2Eub3JnLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e1c2fdd0a3fd98c420c3ecf1a8409713eb9783c5ea500832b0e24989ee936f45JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ebc6c43-4286-67b1-3eb0-7ba243ed664b&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2NvbW11bml0eQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a1c4408928d5e6a7e7da00a019d3dd2994044e62619067f24b74e9e17334b6fbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ebc6c43-4286-67b1-3eb0-7ba243ed664b&amp;u=a1aHR0cHM6Ly9ncmVhdGVyY29sdW1idXNjaC5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=57aab551790ea8f0c373b7f2c605f09db7ceee50aacbc7aa8cc55d68606a71eeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1187d0e9-64f0-6a44-356d-c70865646bab&amp;u=a1aHR0cHM6Ly9ob3NwaWNlZm91bmRhdGlvbi5vcmcvd2hhdC1pcy1ob3NwaWNlLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a651aa7f55b586df2777af8803a56a4f67f7b617887fb74bea0ffa191e8b647bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1187d0e9-64f0-6a44-356d-c70865646bab&amp;u=a1aHR0cDovL3d3dy5zaGFyb25yZWdpb25hbC5vcmcvaG9zcGljZS5odG1s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ead7a91c90289c8903fec6f2d4666b8c400ebfb15c7ccac9323212ad4c6a8039JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1187d0e9-64f0-6a44-356d-c70865646bab&amp;u=a1aHR0cHM6Ly9ob3NwaWNlLmlvL2hvc3BpY2UvZmFtaWx5LWhvc3BpY2UtYW5kLXBhbGxpYXRpdmUtY2FyZS1oZXJtaXRhZ2UtcGEv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2fefae8a6a2924794ed4c7a658ca3abdc9313a6c1b7500edea7297e954c80d75JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1187d0e9-64f0-6a44-356d-c70865646bab&amp;u=a1aHR0cHM6Ly93d3cuY2FyZWxpc3RpbmdzLmNvbS9ob3NwaWNlcy9oZXJtaXRhZ2UtcGE&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=35847d10c37ed50da2434a6f0e1c91b757df0d7df693f8d8b287cd0f45d25c1dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1187d0e9-64f0-6a44-356d-c70865646bab&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Ib3NwaWNl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8f108ab96f07609a5373c8f7143c76497bd6c294aeb2c175cef978ed941f5b62JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1187d0e9-64f0-6a44-356d-c70865646bab&amp;u=a1aHR0cHM6Ly93d3cubmlhLm5paC5nb3YvaGVhbHRoL2hvc3BpY2UtYW5kLXBhbGxpYXRpdmUtY2FyZS9mcmVxdWVudGx5LWFza2VkLXF1ZXN0aW9ucy1hYm91dC1ob3NwaWNlLWNhcmU&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=70d723fe52ebd9e103f1e9957346df2977421c5feab36fe49bda9e34479fe1f0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1187d0e9-64f0-6a44-356d-c70865646bab&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vc2VhcmNoP2NmbHQ9aG9zcGljZSZmaW5kX2xvYz1IZXJtaXRhZ2UlMkMrUEErMTYxNDgmbXNvY2tpZD0xMTg3ZDBlOTY0ZjA2YTQ0MzU2ZGM3MDg2NTY0NmJhYg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d7f27c299e91f24808b62248ed8e230d1def95d4f81cef56fffb3266b6f980e4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1187d0e9-64f0-6a44-356d-c70865646bab&amp;u=a1aHR0cHM6Ly9ob3NwaWNlLmlvL2NhcmUvaGVscGluZy1oYW5kcy1ob21lLWNhcmUtc2VydmljZS1oZXJtaXRhZ2UtcGEv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7ef24918bbebe3375ce912c452546b6666e835304728581317e4d85fc1a30cd0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1187d0e9-64f0-6a44-356d-c70865646bab&amp;u=a1aHR0cHM6Ly93d3cuaG9zcGljZWFuZGNvbW11bml0eWNhcmUub3JnLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a6636e13aa2b0448984938b3a11eb4938ad5864268348354004c94da074a5e0eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1187d0e9-64f0-6a44-356d-c70865646bab&amp;u=a1aHR0cHM6Ly93d3cucGEuZ292L2FnZW5jaWVzL2hlYWx0aC9mYWNpbGl0aWVzL291dC1wYXRpZW50LWhlYWx0aGNhcmUtZmFjaWxpdGllcy9ob3NwaWNl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=99e8ad95e526805207bf62f7ae1a6c9145ef6a0ac2d3c835c891acb2d55fd92dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2777366a-2032-666c-2921-218b21d667c8&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L21lbnRhbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0a0dbcf7345724a5a2db1b6e9bcf90cab785c45fd9cc17769b6642bd483bcb73JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2777366a-2032-666c-2921-218b21d667c8&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWVudGFsX2hlYWx0aA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d9b11150ed3d3d70edb4ab8d40c00fa103a25ef839a82faaa72875d403ce25fbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2777366a-2032-666c-2921-218b21d667c8&amp;u=a1aHR0cHM6Ly93d3cuY2RjLmdvdi9tZW50YWwtaGVhbHRoL2Fib3V0L2luZGV4Lmh0bWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=647e9cc207ff87a2ce651be9d3187a24618524e325014a4540b8dd040b22fe37JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2777366a-2032-666c-2921-218b21d667c8&amp;u=a1aHR0cHM6Ly93d3cud2hvLmludC9uZXdzLXJvb20vZmFjdC1zaGVldHMvZGV0YWlsL21lbnRhbC1kaXNvcmRlcnM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a75afe18a8e14a725469f3ac4574b2dd360b633dd1a23b2c8bea0ae7ce46cc3dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2777366a-2032-666c-2921-218b21d667c8&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWVudGFsX2Rpc29yZGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f6f7f73e2ed813a5c017a4d5864726570ec85887ccd0cd77a4fe1cb7e30abb4fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2777366a-2032-666c-2921-218b21d667c8&amp;u=a1aHR0cHM6Ly93d3cuc2FtaHNhLmdvdi9tZW50YWwtaGVhbHRo&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=09fa11873da890e2b2b5bd2da0d4153d9500f20a7f48650f5752a2e19f281148JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2777366a-2032-666c-2921-218b21d667c8&amp;u=a1aHR0cHM6Ly93d3cubWF5b2NsaW5pYy5vcmcvaGVhbHRoeS1saWZlc3R5bGUvYWR1bHQtaGVhbHRoL2luLWRlcHRoL21lbnRhbC1oZWFsdGgvYXJ0LTIwMDQ0MDk4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dffb97a355e6d2e4f39cc31f7220c51694c162e54bf34ee1b992aa9498e0f66eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2777366a-2032-666c-2921-218b21d667c8&amp;u=a1aHR0cHM6Ly9teS5jbGV2ZWxhbmRjbGluaWMub3JnL2hlYWx0aC9hcnRpY2xlcy9tZW50YWwtaGVhbHRo&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6e3d352785cab3c3f1ae858d5b6418eb2a5e2753e489d3fcb3e21e24722e04d6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2777366a-2032-666c-2921-218b21d667c8&amp;u=a1aHR0cHM6Ly9teS5jbGV2ZWxhbmRjbGluaWMub3JnL2hlYWx0aC9kaXNlYXNlcy8yMjI5NS1tZW50YWwtaGVhbHRoLWRpc29yZGVycw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3177498af0068ebe852a7a1832eb2e120a6a382029a408899a9916c962acba5aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2777366a-2032-666c-2921-218b21d667c8&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhbG5ld3N0b2RheS5jb20vYXJ0aWNsZXMvMTU0NTQz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=600fad942eaeaff1859f1b723a3ba587b012de82b957369a9b313e6436d9c4a2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=281b97eb-07c9-6ca7-0799-800a069f6d0e&amp;u=a1aHR0cHM6Ly9pdWhlYWx0aC5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a305c5a4ca702fd7a0a5f66612d85133484902b916021d41181aea4d9ccbc31fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=281b97eb-07c9-6ca7-0799-800a069f6d0e&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvSGVhbHRo&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5a79d3a4b4642fd63af42238a5809dbb3c0370f28c4c36eb3109d33ad8722247JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=281b97eb-07c9-6ca7-0799-800a069f6d0e&amp;u=a1aHR0cHM6Ly9pdWhlYWx0aC5vcmcvZmluZC1sb2NhdGlvbnMvaXUtaGVhbHRoLXByaW1hcnktY2FyZS0yNTMtc2FnYW1vcmUtcGt3eS13LXdlc3QtbGFmYXlldHRl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=53bd5445c46b9742c11f85abf0f70ce806edfe7c1aa31dcd2a8f04ecf5e38b06JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=281b97eb-07c9-6ca7-0799-800a069f6d0e&amp;u=a1aHR0cHM6Ly93d3cucGFya3ZpZXcuY29tL3Bhcmt2aWV3LXdlc3QtbGFmYXlldHRlLWhvc3BpdGFs&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e232d5abbc764574ca6f4a3a361702d634d6f5e6d9668224c3a76c78454f0448JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=281b97eb-07c9-6ca7-0799-800a069f6d0e&amp;u=a1aHR0cHM6Ly9jbGllbnRzLm1hcmF0aG9uLmhlYWx0aC8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bc935b4574ed72d8a4ac384ff9b14af2ea2eb9a5a297091f362212d36838f559JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=281b97eb-07c9-6ca7-0799-800a069f6d0e&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhbG5ld3N0b2RheS5jb20vYXJ0aWNsZXMvMTUwOTk5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6d85ba657ccf6cd881345288585bcb6be824e33cc595fb4ab89841e02effc438JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=281b97eb-07c9-6ca7-0799-800a069f6d0e&amp;u=a1aHR0cHM6Ly93d3cuaGVhbHRoLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b19cce5ac480a38f23e7c1ae1bf00390bac067cd324e2c6c614ddb716d7cb1b7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=281b97eb-07c9-6ca7-0799-800a069f6d0e&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvaGVhbHRo&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3912f4fe5e78d2fbed3b239266288753ae5a29e3e55754fdd7975872030f8ca3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=281b97eb-07c9-6ca7-0799-800a069f6d0e&amp;u=a1aHR0cHM6Ly93d3cud2VibWQuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bf15709d82d7e28b1bd2da09fe1158e777a87d832fd9f7b2644ad2b267705f33JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=281b97eb-07c9-6ca7-0799-800a069f6d0e&amp;u=a1aHR0cHM6Ly93d3cuZXZlcnlkYXloZWFsdGguY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=322861c83a85e4ebb75f5a2e2f830b1cea9fa541fc6c48180f3f8e26b82e24c8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1668cdcc-6733-6bb4-3f87-da2d66586af9&amp;u=a1aHR0cHM6Ly93d3cucHJpbWFyeS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3700f5f04cbc6f6d8db980c0dcdaf00d1ace7ac80c6b77a6e5e5a02efb32ceb3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1668cdcc-6733-6bb4-3f87-da2d66586af9&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3ByaW1hcnk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bcbb89530319830fa428764f1eb5700fc5a5c8ecf561c5ab384338c6e4e85d65JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1668cdcc-6733-6bb4-3f87-da2d66586af9&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3ByaW1hcnk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c60efe3b6620b11a2195a297c6f76303d40295595a0b52550b20491d23d92550JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1668cdcc-6733-6bb4-3f87-da2d66586af9&amp;u=a1aHR0cHM6Ly90aGVwcmltYXJ5LmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1b979535143c57f8d5cd92d08b13784c595d96b9b9c32f26e5e0b166eb41fd82JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1668cdcc-6733-6bb4-3f87-da2d66586af9&amp;u=a1aHR0cHM6Ly93d3cucHJpbWFyeWdhbWVzLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8c2fcb3dc2ba396143f4c599bd6bc0b739c854f2131cab8e506ee67c3ae27265JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1668cdcc-6733-6bb4-3f87-da2d66586af9&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL3ByaW1hcnk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7ace06bb59a86cdbcdef5fc7ea4b8736202672703ddd2df0369816671d3c41e0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1668cdcc-6733-6bb4-3f87-da2d66586af9&amp;u=a1aHR0cHM6Ly93d3cubmJjbmV3cy5jb20vcG9saXRpY3MvMjAyNi1wcmltYXJ5LWVsZWN0aW9ucy9uYXRpb25hbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=681e4a9fd727cdc568ee9b76c9a362f337333227a970503eb6d6b2c40e216f49JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1668cdcc-6733-6bb4-3f87-da2d66586af9&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3ByaW1hcnk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=66a67fdf0fc2f754d2998cdfb7a8c748c49dd7ee1d064d0df45d655a3a61d51dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1668cdcc-6733-6bb4-3f87-da2d66586af9&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9wcmltYXJ5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c469ab6581e182a5d2c76535d87cd72241e397cc17e3a50bdc8a4f3486e53bd8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1668cdcc-6733-6bb4-3f87-da2d66586af9&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvUHJpbWFyeV9lZHVjYXRpb24&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f5c3bfc2220041d5d90a0572f9ebfa8d4af4fda60bf741a623e9a9874b35eac3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=334eb2cc-9852-6c16-2405-a52d990f6d32&amp;u=a1aHR0cHM6Ly93d3cudGhlLXdlbGwuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2b834d09042c1f740c86c8779837f381341e3fd341b3de1b041ca38810388b30JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=334eb2cc-9852-6c16-2405-a52d990f6d32&amp;u=a1aHR0cHM6Ly9nbG9iYWx3ZWxsbmVzc2luc3RpdHV0ZS5vcmcvd2hhdC1pcy13ZWxsbmVzcy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8415a3316c44185240943fee3279ed5254e60eb9203044ff1d4fa919dd881e4eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=334eb2cc-9852-6c16-2405-a52d990f6d32&amp;u=a1aHR0cHM6Ly9vZXIubnkuZ292L3dlbGxOWVMtZXZlcnlkYXk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a4125c8494fdced8fbf81cdf06fc189ff86e4053437d4004db1ce4d9cffaa207JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=334eb2cc-9852-6c16-2405-a52d990f6d32&amp;u=a1aHR0cHM6Ly93d3cubnl0aW1lcy5jb20vc2VjdGlvbi93ZWxs&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1e7f518edc28e18545d9c958fc5b09626ec8f6d6d1a5b38c0e5447b219166c0bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=334eb2cc-9852-6c16-2405-a52d990f6d32&amp;u=a1aHR0cHM6Ly93d3cubnljLmdvdi9zaXRlL29sci93ZWxsbmVzcy93ZWxsbmVzc2hvbWUucGFnZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f0848ab9177b898fadc63e4c2c10f11e5e18c0bcf3604799e258ddd1a1e1862cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=334eb2cc-9852-6c16-2405-a52d990f6d32&amp;u=a1aHR0cHM6Ly9zZWNyZXRueWMuY28vYmVzdC13ZWxsbmVzcy1yZXRyZWF0cy1uZWFyLW55Yy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=afb90d4d55ae7d2850a39044023507cf2109c446bf66ed857b11d8ad49af4904JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=334eb2cc-9852-6c16-2405-a52d990f6d32&amp;u=a1aHR0cHM6Ly93d3cubW9kZXJubHV4dXJ5LmNvbS9iZXN0LXdlbGxuZXNzLXNwb3RzLW55Yy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c6bf0cc7ebd96327dc021096d9f9dee26e23f44704bd2b186a80acd5f56b7696JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=334eb2cc-9852-6c16-2405-a52d990f6d32&amp;u=a1aHR0cHM6Ly93d3cud2FsZG9yZmFzdG9yaWFuZXd5b3JrLmNvbS93ZWxsbmVzcy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=71a1f1124d6445a593a760949912773b5c00b8165005c584cf7c2d986c0607c1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=334eb2cc-9852-6c16-2405-a52d990f6d32&amp;u=a1aHR0cHM6Ly93d3cudHJpcGFkdmlzb3IuY29tL0F0dHJhY3Rpb25zLWc2MDc2My1BY3Rpdml0aWVzLWM0MC1OZXdfWW9ya19DaXR5X05ld19Zb3JrLmh0bWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=82abd803e01af25e33c4aa40f5aad0325a91ae12ecdaa0fda71181c03ce00c41JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=334eb2cc-9852-6c16-2405-a52d990f6d32&amp;u=a1aHR0cHM6Ly93d3cuYW1hbi5jb20vaG90ZWxzL2FtYW4tbmV3LXlvcmsvd2VsbG5lc3M&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e5d9bc389a54491e3be5f2a39ec221543bd0e40b4c298718f9fd95fc918598e9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d67074a-cf7c-60ed-2a7c-10abcee861a0&amp;u=a1aHR0cHM6Ly9ueXBjYy5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a7979254c74460a1e8d676018e3f125242761291cf04fd4c0f781d267b0d69e1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d67074a-cf7c-60ed-2a7c-10abcee861a0&amp;u=a1aHR0cHM6Ly9tYW5oYXR0YW5tZW50YWxoZWFsdGhjb3Vuc2VsaW5nLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1a3941497e5d99980b0cecb9d2888b06741b90ad4a9286cba1d96dadb2446f19JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d67074a-cf7c-60ed-2a7c-10abcee861a0&amp;u=a1aHR0cHM6Ly9ueWNjb3Vuc2VsaW5nLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cdebf7d17c896507e885b02073ca567103c3628478e9f9b86f20ccdc67509099JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d67074a-cf7c-60ed-2a7c-10abcee861a0&amp;u=a1aHR0cHM6Ly9uaGNjLnVzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=072049551dabffd8e095a81b11904db632621d53bb8f4f03b78b3310a3a28994JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d67074a-cf7c-60ed-2a7c-10abcee861a0&amp;u=a1aHR0cHM6Ly9ueWNjb3Vuc2VsaW5nLmNvbS9jb3Vuc2VsaW5nLXNlcnZpY2VzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bdfc1293541fa18171e9f6ebbfa7fc46218dd5dc362d7cd84bc1a749599a1d93JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d67074a-cf7c-60ed-2a7c-10abcee861a0&amp;u=a1aHR0cHM6Ly93d3cucHN5Y2hvbG9neXRvZGF5LmNvbS91cy90aGVyYXBpc3RzL255L25ldy15b3JrP21zb2NraWQ9MWQ2NzA3NGFjZjdjNjBlZDJhN2MxMGFiY2VlODYxYTA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f2efad2d03dacdc0ac4dbe407253555ad94d92ea3b2b03a2b471c235a7da3036JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d67074a-cf7c-60ed-2a7c-10abcee861a0&amp;u=a1aHR0cHM6Ly9teXRoZXJhcHlueWMuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6c4e35c3321c025eb9132b827a1306c6ed74be185ce944f63e0016e1f9245f5eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d67074a-cf7c-60ed-2a7c-10abcee861a0&amp;u=a1aHR0cHM6Ly9jb21wcmVoZW5zaXZlY291bnNlbGluZ2xjc3cuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1c6dbb59d8109ecdbe7cfd97f51f8765f9a99e4b2496814c2d4a9e02aff7fbf3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d67074a-cf7c-60ed-2a7c-10abcee861a0&amp;u=a1aHR0cHM6Ly93d3cubWFuaGF0dGFudGhlcmFweS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c98196797411f2c08badc8713266e1d91dedf80de17f24ef46ff0607faeb8696JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d67074a-cf7c-60ed-2a7c-10abcee861a0&amp;u=a1aHR0cHM6Ly93d3cub3BlbmNvdW5zZWxpbmcuY29tL25ldy15b3JrL25ldy15b3Jr&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6591c50730b42af8b648aa8d30f81f5c98eaa89ba3e499dced6c325f8f6890efJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=331cf818-b7c4-643c-2de8-eff9b629654f&amp;u=a1aHR0cHM6Ly9tZWRsaW5lcGx1cy5nb3YvcmVoYWJpbGl0YXRpb24uaHRtbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5d45062b97d39ecc311b1d71f1e2ffa92b3687c2bb2d0290972c20c0221499e7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=331cf818-b7c4-643c-2de8-eff9b629654f&amp;u=a1aHR0cHM6Ly93d3cud2hvLmludC9uZXdzLXJvb20vZmFjdC1zaGVldHMvZGV0YWlsL3JlaGFiaWxpdGF0aW9u&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=544015e90ce41180934d81b44725b2ecb7aef776a8189821a4f48d8b6ae15bb4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=331cf818-b7c4-643c-2de8-eff9b629654f&amp;u=a1aHR0cHM6Ly93d3cuaW5vdmEub3JnL291ci1zZXJ2aWNlcy9pbm92YS1yZWhhYmlsaXRhdGlvbi1zZXJ2aWNlcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0636522ab0baf07bd8c275eff4a6f23b0c94546443e5d4de9928a27cd04a3786JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=331cf818-b7c4-643c-2de8-eff9b629654f&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3JlaGFiaWxpdGF0aW9u&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d9c56d88e5ea96f901cf962d549bbf2988a629e7c9d9eea7580e1362092a7066JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=331cf818-b7c4-643c-2de8-eff9b629654f&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vc2VhcmNoP2NmbHQ9cmVoYWJpbGl0YXRpb25fY2VudGVyJmZpbmRfbG9jPUFzaGJ1cm4lMkMrVkErMjAxNDcmbXNvY2tpZD0zMzFjZjgxOGI3YzQ2NDNjMmRlOGVmZjliNjI5NjU0Zg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2a80b29a25e0a1fe75646b16a70258e9b133ff524f4791a00fa56d49493d632fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=331cf818-b7c4-643c-2de8-eff9b629654f&amp;u=a1aHR0cHM6Ly9mb3hyZWhhYi5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6af76d62660e9a837cb3c8d47de8e4a46e66fe1a8c2230ddf6a547aad9a411e2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=331cf818-b7c4-643c-2de8-eff9b629654f&amp;u=a1aHR0cHM6Ly93d3cuaW5vdmEub3JnL2xvY2F0aW9ucy9pbm92YS1waHlzaWNhbC10aGVyYXB5LWFzaGJ1cm4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bcd10c4d2491dd17188169ee872b8ac27ffcddbb00a6baa4d97d473be50b7351JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=331cf818-b7c4-643c-2de8-eff9b629654f&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvUmVoYWJpbGl0YXRpb24&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ba2666ba2dfe15fc20205af6ddbb48553610886f53aa3e2ed51a232d5615c42bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=331cf818-b7c4-643c-2de8-eff9b629654f&amp;u=a1aHR0cHM6Ly93d3cuZXJpY2tzb25zZW5pb3JsaXZpbmcuY29tL2FzaGJ5LXBvbmRzL2hlYWx0aC9yZWhhYmlsaXRhdGlvbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f435876fbb581ba43a97ed1901da9522d1a55a9e6dd23423b66724ddc547b497JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=331cf818-b7c4-643c-2de8-eff9b629654f&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vc2VhcmNoP2NmbHQ9cmVoYWJpbGl0YXRpb25fY2VudGVyJmZpbmRfbG9jPUxvdWRvdW4rQ291bnR5JTJDK1ZBJm1zb2NraWQ9MzMxY2Y4MThiN2M0NjQzYzJkZThlZmY5YjYyOTY1NGY&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=253335e844bcc991866269204d9600de79edadb3ae13445f971b503b920bdd3aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=06756adf-9d66-654e-2ee0-7d3e9c416416&amp;u=a1aHR0cHM6Ly93d3cud2VibWQuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6fca65270c554916f6460010913ec3eb9150f6cb167ea351dd9aab5af14a30c2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=06756adf-9d66-654e-2ee0-7d3e9c416416&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWVkaWNpbmU&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9db0ae7caea4cb5a11f2e3c992cbd6d81ac228073d4846d2291a3fb61f7a87a0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=06756adf-9d66-654e-2ee0-7d3e9c416416&amp;u=a1aHR0cHM6Ly93d3cuZm1jdG4uY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dc9bd2bd960ca152e3d2a0004f83f4678bf698caf59ebde3c0a70fa6b82300d1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=06756adf-9d66-654e-2ee0-7d3e9c416416&amp;u=a1aHR0cHM6Ly93d3cubG11bmV0LmVkdS9kZWJ1c2stY29sbGVnZS1vZi1vc3Rlb3BhdGhpYy1tZWRpY2luZS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bc72745b3819d7eaebc11e68cf7a30c7aaa1dbdce240854f549538eee8acd274JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=06756adf-9d66-654e-2ee0-7d3e9c416416&amp;u=a1aHR0cHM6Ly9tY3dlYi5hcHBzLnByZC5jYW1taXMubWVkaS1jYWwuY2EuZ292Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=66cd70aced8ef9b0d0fdcb3bad5b0cd35d1176dbff5a1472ccd57be369cb33c5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=06756adf-9d66-654e-2ee0-7d3e9c416416&amp;u=a1aHR0cHM6Ly93d3cubWF5b2NsaW5pYy5vcmcvZGlzZWFzZXMtY29uZGl0aW9ucw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8d867e20aba3c075d83d42a59c1d092351dfa2c0700defbc95731ceb9d119623JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=06756adf-9d66-654e-2ee0-7d3e9c416416&amp;u=a1aHR0cHM6Ly93d3cuZm1jdG4uY29tL2Fib3V0LW91ci1wcmFjdGljZS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=365880007ac360ac403c761dec0ea55c9ee650f8e05c1f09d4a6c1e88798571eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=06756adf-9d66-654e-2ee0-7d3e9c416416&amp;u=a1aHR0cHM6Ly93d3cuaGVhbHRoZ3JhZGVzLmNvbS9ncm91cC1kaXJlY3RvcnkvdG4tdGVubmVzc2VlL2hhcnJvZ2F0ZS9mYW1pbHktbWVkaWNhbC1jbGluaWMtb2YtaGFycm9nYXRlLXhid25kNw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=63865e4287503c4f4b0a4b462ea0c3d98d557ba5cc42eb8f2796f54dc6ce8bd6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=06756adf-9d66-654e-2ee0-7d3e9c416416&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhcmVsaXN0LmNvbS9wcmltYXJ5LWNhcmUvZmFtaWx5LW1lZGljYWwtY2xpbmljLW9mLWhhcnJvZ2F0ZS1wYy1oYXJyb2dhdGUtdG4v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7ee76484333d84cce6f108f5621aaade80b81b299e5aaacb52988c5db26345b3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=06756adf-9d66-654e-2ee0-7d3e9c416416&amp;u=a1aHR0cHM6Ly91cmdlbnRjYXJlbG9jYXRpb25zLm9yZy90bi9oYXJyb2dhdGUvNDI3NzYtLWxtdS1tZWRpY2FsLWNsaW5pYy1oYXJyb2dhdGU&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a6b089d75ab1baba7d31241c5502d4ade9812eca31a0979282e4ceceeeb7d2f8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fabe878-1062-6457-0b35-ff9911eb653b&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Db21tdW5pdHk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=37b3801965c10f807bf22c31277bde0eec4e75f9a723f17d028d5db2ac4b43d5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fabe878-1062-6457-0b35-ff9911eb653b&amp;u=a1aHR0cHM6Ly9jb21tdW5pdHlwYXJ0bmVycy5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2c570bea5b04afbddfb39bf5b686049ac9a8b705ee674813f0517c3ebcf07161JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fabe878-1062-6457-0b35-ff9911eb653b&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Db21tdW5pdHlfKFRWX3Nlcmllcyk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=83677531f9beab7014cf5791802db4b43a8b215fc6c19660a236f4999b7feeccJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fabe878-1062-6457-0b35-ff9911eb653b&amp;u=a1aHR0cHM6Ly8yMTFsYS5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6a39a06e65dcf51682de8d2340f931acea9b00a3266544e3cd668a4fa188e0afJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fabe878-1062-6457-0b35-ff9911eb653b&amp;u=a1aHR0cHM6Ly93d3cuY2FsZnVuZC5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=74cb9fb7d9bdce9a3a829c84318a529b6768f4ad191f1782747943735a2e363dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fabe878-1062-6457-0b35-ff9911eb653b&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2NvbW11bml0eQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d1e8900148e9a94caeed5745d77eeb8632f95050f8dc76845709dd0b54970b5cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fabe878-1062-6457-0b35-ff9911eb653b&amp;u=a1aHR0cHM6Ly9tLmltZGIuY29tL3RpdGxlL3R0MTQzOTYyOS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1c4085f0d108b6700ae9102bd739e237a365d98bdcafd6094afdcb592f865b1cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fabe878-1062-6457-0b35-ff9911eb653b&amp;u=a1aHR0cHM6Ly9wYXJrcy5sYWNvdW50eS5nb3YvY29tbXVuaXR5Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=064bd57df6f8d9324e60ee2049917230f17f65c986b0ff03f0b64463a448cd02JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fabe878-1062-6457-0b35-ff9911eb653b&amp;u=a1aHR0cHM6Ly93d3cubGFjY2QuZWR1Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=912f0388034b26a47ff86d10372c788ce7e8d05cb89ce15c5e2286afd70c2527JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fabe878-1062-6457-0b35-ff9911eb653b&amp;u=a1aHR0cHM6Ly9uZWlnaGJvcmhvb2RpbmZvLmxhY2l0eS5nb3Yv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9de017733b4266c44fc0e1fb414d76715bc69d3146e8718c836eff454f0482ecJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1b8ccdd9-f839-61e3-01b0-da38f98b6027&amp;u=a1aHR0cHM6Ly9ob3NwaWNlZm91bmRhdGlvbi5vcmcvd2hhdC1pcy1ob3NwaWNlLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3033e4a6721a21e1907c50898f48645e5721eb7e25e2591828fa39badc032361JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1b8ccdd9-f839-61e3-01b0-da38f98b6027&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Ib3NwaWNl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3b3d9225d1aa7f72d846549708d54c93379e96684b7a3abd21475d806dbedaddJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1b8ccdd9-f839-61e3-01b0-da38f98b6027&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vc2VhcmNoP2NmbHQ9aG9zcGljZSZmaW5kX2xvYz1Mb3MrQW5nZWxlcyUyQytDQSZtc29ja2lkPTFiOGNjZGQ5ZjgzOTYxZTMwMWIwZGEzOGY5OGI2MDI3&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b453502156c57359a4987f4c31a6d776b5dd9b749dfe62df4a6cbf7e300f07e8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1b8ccdd9-f839-61e3-01b0-da38f98b6027&amp;u=a1aHR0cHM6Ly93d3cubmlhLm5paC5nb3YvaGVhbHRoL2hvc3BpY2UtYW5kLXBhbGxpYXRpdmUtY2FyZS9mcmVxdWVudGx5LWFza2VkLXF1ZXN0aW9ucy1hYm91dC1ob3NwaWNlLWNhcmU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=423681be81a486159be7035783ead164d2ece4384bf47bf2254193ef6c5b116dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1b8ccdd9-f839-61e3-01b0-da38f98b6027&amp;u=a1aHR0cHM6Ly93d3cuYWdpbmcuY2EuZ292L0NhcmVfT3B0aW9ucy9Ib3NwaWNlX0NhcmUv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=364f8483c0c2110505f16c84191a47a235cdf09732b73877af210cc7dbb2ce58JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1b8ccdd9-f839-61e3-01b0-da38f98b6027&amp;u=a1aHR0cHM6Ly93d3cuY2FsaG9zcGljZS5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f86d7ce9dc23aa4c27820151ebf2d525ddee41c41bd0b6dab67ec709fb45cbafJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1b8ccdd9-f839-61e3-01b0-da38f98b6027&amp;u=a1aHR0cHM6Ly93d3cuc2lsdmVyYWRvaG9zcGljZS5jb20vbG9jYXRpb24vc2lsdmVyYWRvLWhvc3BpY2UtbG9zLWFuZ2VsZXMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7e4e224b1e3944cded409794aed360052adbfe1a550bb0c3f434ae271c6bd7faJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1b8ccdd9-f839-61e3-01b0-da38f98b6027&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vc2VhcmNoP2ZpbmRfZGVzYz1ob3NwaWNlJmZpbmRfbG9jPUxvcytBbmdlbGVzJTJDK0NBJm1zb2NraWQ9MWI4Y2NkZDlmODM5NjFlMzAxYjBkYTM4Zjk4YjYwMjc&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a8a4904b149a4959505bcce9b025866a29714abf7cdf18cb2b7d456c982aff5dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1b8ccdd9-f839-61e3-01b0-da38f98b6027&amp;u=a1aHR0cHM6Ly9nb2xkZW5nYXRlaG9zcGljZS5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=46297c205efef89825cc3632b966088749442929e768203652e1624d0517bdddJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1b8ccdd9-f839-61e3-01b0-da38f98b6027&amp;u=a1aHR0cHM6Ly93d3cuYWdhcGVob3NwaWNlcGMub3JnLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=70c10e16ff684879e4b4fc48809e553ab324ad1adbb49d35dac751b6012dfb4cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=203dbec7-9e3e-646f-0893-a9269f9a656a&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L21lbnRhbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=12bd304567a4bd15fac32fa9b42ea795bce7396297186519a80d74f7bf32150dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=203dbec7-9e3e-646f-0893-a9269f9a656a&amp;u=a1aHR0cHM6Ly93d3cuY2RjLmdvdi9tZW50YWwtaGVhbHRoL2Fib3V0L2luZGV4Lmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3660e3cf133daf7f4a93d8d3c4e6fab8c402bccb43fb62400f5210264970bdecJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=203dbec7-9e3e-646f-0893-a9269f9a656a&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWVudGFsX2hlYWx0aA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fa3bd3c03b9c24f68a67afc03ebb5ed3ba1b959a3805d58eaf06b42b0d1b9d89JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=203dbec7-9e3e-646f-0893-a9269f9a656a&amp;u=a1aHR0cHM6Ly93d3cud2hvLmludC9uZXdzLXJvb20vZmFjdC1zaGVldHMvZGV0YWlsL21lbnRhbC1kaXNvcmRlcnM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=da90f618237263e17166ecafba011db8d883b0fbdc492a13999fcbc244897e82JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=203dbec7-9e3e-646f-0893-a9269f9a656a&amp;u=a1aHR0cHM6Ly93d3cuc2FtaHNhLmdvdi9tZW50YWwtaGVhbHRo&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5f04bf5694c5a124fbdfbb927e7351a2bae73a79acc20b7fcd8135f254b8d8b7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=203dbec7-9e3e-646f-0893-a9269f9a656a&amp;u=a1aHR0cHM6Ly93d3cubWF5b2NsaW5pYy5vcmcvaGVhbHRoeS1saWZlc3R5bGUvYWR1bHQtaGVhbHRoL2luLWRlcHRoL21lbnRhbC1oZWFsdGgvYXJ0LTIwMDQ0MDk4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d0143eab55510c506b3fece67755f66aab3747e87a236923887e07d09866d597JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=203dbec7-9e3e-646f-0893-a9269f9a656a&amp;u=a1aHR0cHM6Ly9teS5jbGV2ZWxhbmRjbGluaWMub3JnL2hlYWx0aC9kaXNlYXNlcy8yMjI5NS1tZW50YWwtaGVhbHRoLWRpc29yZGVycw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=711fb4413faa00c9cc7e10469b741062e14b3956942317a7c76d599407154dbeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=203dbec7-9e3e-646f-0893-a9269f9a656a&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWVudGFsX2Rpc29yZGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fc72a993acdf45d09097d87239395eb5ac475c2a213f90c84cd57a566af12c25JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=203dbec7-9e3e-646f-0893-a9269f9a656a&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhbG5ld3N0b2RheS5jb20vYXJ0aWNsZXMvMTU0NTQz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=485ae0e9ff30dc4f6d1d4eabfd3c875174c1c45ffc19ae0a8176e3cf0d28e83eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=203dbec7-9e3e-646f-0893-a9269f9a656a&amp;u=a1aHR0cHM6Ly93d3cud2VibWQuY29tL21lbnRhbC1oZWFsdGgvZGVmYXVsdC5odG0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7a2081762b5b314dcddf573074392dc8d0138fd25852b1d11c55d2fb5c1a0143JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cd0fd04-c65e-6f7c-390f-eae5c7036e2b&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvSGVhbHRo&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ff2538e86a5dc5c73a5249f8ac10b4106d435dc052c06722538c4963ff89047cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cd0fd04-c65e-6f7c-390f-eae5c7036e2b&amp;u=a1aHR0cHM6Ly9hbGw0aGVhbHRoLm9yZy9jb250YWN0LXVzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=378249eadf1c6938d95b1d789827c088c6809e914b77a5e5f078cb8a0dba4eb8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cd0fd04-c65e-6f7c-390f-eae5c7036e2b&amp;u=a1aHR0cHM6Ly93d3cuaGVhbHRoLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=40f8669f9c275b732835d75c80be77bbbd714e537b6ce192e37d53e597a1704aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cd0fd04-c65e-6f7c-390f-eae5c7036e2b&amp;u=a1aHR0cHM6Ly93d3cuYWR2ZW50aXN0aGVhbHRoLm9yZy9nbGVuZGFsZS9sb2NhdGlvbnMvYWR2ZW50aXN0LWhlYWx0aC1nbGVuZGFsZS1tZWRpY2FsLWNlbnRlci00NDQ2Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f6928efcacb5a5140a84460ac6fb57ff3bd7efe497d9be911766f295d13a0ff8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cd0fd04-c65e-6f7c-390f-eae5c7036e2b&amp;u=a1aHR0cHM6Ly93d3cud2VibWQuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0026e2070b27eceb7ac8d7176205ea464fbb800f92afc83530a7bbb76b51083bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cd0fd04-c65e-6f7c-390f-eae5c7036e2b&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvaGVhbHRo&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=884718313457c6c20d5c0d56e0284490085079f37d88c45bc2c65033defe3e80JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cd0fd04-c65e-6f7c-390f-eae5c7036e2b&amp;u=a1aHR0cHM6Ly93d3cuY29tbW9uc3Bpcml0Lm9yZy9maW5kLWEtbG9jYXRpb24vZGlnbml0eS1oZWFsdGgtZ2xlbmRhbGUtbWVtb3JpYWwtaG9zcGl0YWwtYW5kLWhlYWx0aC1jZW50ZXItMzIwMg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cee2eb438f40e44853f66e76ba59457420dec86f17af85ba0658a4afc791baf9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cd0fd04-c65e-6f7c-390f-eae5c7036e2b&amp;u=a1aHR0cHM6Ly93d3cuY2RwaC5jYS5nb3Yv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a9b1a2faf3decb127e422cb40c794b828fb94801d6ce8881e0e9fd3c874aa974JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cd0fd04-c65e-6f7c-390f-eae5c7036e2b&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhbG5ld3N0b2RheS5jb20vYXJ0aWNsZXMvMTUwOTk5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=33f4c663c75594aed24d7ab55a40f4500d6b1cedee9ad1711407a80e9e6eab21JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cd0fd04-c65e-6f7c-390f-eae5c7036e2b&amp;u=a1aHR0cDovL3d3dy5wdWJsaWNoZWFsdGgubGFjb3VudHkuZ292L2Nocy9TUEEyLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0c21f1dbde76b54470d0f0baeb34c0389a612c5658aae60e058932903d04328eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0450aedf-e260-6b45-0865-b93ee3c46af7&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3ByaW1hcnk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9343c30e0d264d327bd89ea24863fa9bec751273ec8164c39975e737b641ec89JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0450aedf-e260-6b45-0865-b93ee3c46af7&amp;u=a1aHR0cHM6Ly93d3cucHJpbWFyeS5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=53cba9a2deb0fd97f18466df9fade2f72b1d1a4b20ce1443f92d406955793b13JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0450aedf-e260-6b45-0865-b93ee3c46af7&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3ByaW1hcnk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=780d5afbb1565a710983e089efff541a1a61528054a2dbd60b3341434a159d33JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0450aedf-e260-6b45-0865-b93ee3c46af7&amp;u=a1aHR0cHM6Ly93d3cucHJpbWFyeWdhbWVzLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d7bfc98f4042444ca678286468daf4149a82216974bf84ab74d22dc7aad7cbcbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0450aedf-e260-6b45-0865-b93ee3c46af7&amp;u=a1aHR0cHM6Ly93d3cubmJjbmV3cy5jb20vcG9saXRpY3MvMjAyNi1wcmltYXJ5LWVsZWN0aW9ucy9uYXRpb25hbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=abe70edd98ee03354bc8f8c4a24b3e546204b4c4600851530f428b5a762d446bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0450aedf-e260-6b45-0865-b93ee3c46af7&amp;u=a1aHR0cHM6Ly90aGVwcmltYXJ5LmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9e47a7a8d7b2ff173452a0fa170f31a7b20b950d13ab4d15895193ec2ca4ef29JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0450aedf-e260-6b45-0865-b93ee3c46af7&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3ByaW1hcnk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cc5554825cfc6101fe1e38f954c58977581101c8f125b1850627b391af8e9f21JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0450aedf-e260-6b45-0865-b93ee3c46af7&amp;u=a1aHR0cHM6Ly93d3cuY2h1cmNob2ZqZXN1c2NocmlzdC5vcmcvc3R1ZHkvbWFudWFsL2dlbmVyYWwtaGFuZGJvb2svMTItcHJpbWFyeT9sYW5nPWVuZw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ccd8dc29669a08f940106afc37b3f1a8dff60d2d60fb8d23633cf8bb9e40ca1dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0450aedf-e260-6b45-0865-b93ee3c46af7&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9wcmltYXJ5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8f217ec4c2f7636e146a18302dddbe0e3584d4ff00e9f2c2bf91d875dbe7afa1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0450aedf-e260-6b45-0865-b93ee3c46af7&amp;u=a1aHR0cHM6Ly93d3cubmJjbmV3cy5jb20vcG9saXRpY3MvMjAyNi1wcmltYXJ5LWVsZWN0aW9ucy91dGFoLWhvdXNlLXJlc3VsdHM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3255f5954a9408cebfb92f78131734f7556d4d466822112497034bcec97e35e8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a1fa668-9d4d-6610-2ee3-b1899ccf6723&amp;u=a1aHR0cHM6Ly9nbG9iYWx3ZWxsbmVzc2luc3RpdHV0ZS5vcmcvd2hhdC1pcy13ZWxsbmVzcy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6b441dabac122f94bd989a339766a00bd217983c3664bd875feba7d7948d55a5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a1fa668-9d4d-6610-2ee3-b1899ccf6723&amp;u=a1aHR0cHM6Ly93d3cuY29ybmVyb253ZWxsbmVzcy5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=40333e9ab7bc6a75ca4e6a090d00f8751b9673ff1dac003d7678fd9157ac0877JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a1fa668-9d4d-6610-2ee3-b1899ccf6723&amp;u=a1aHR0cHM6Ly9zb3VuZGhlYWx0aHdlbGxuZXNzLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c05f76f271644b68db558167c000f39d0c75c0596ef383bad6b679df46de2985JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a1fa668-9d4d-6610-2ee3-b1899ccf6723&amp;u=a1aHR0cHM6Ly9ib3RoZWxsY2hpcm9wcmFjdGljLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4d86cbbe704d1668607782f2c56beb438dbcba7f29e900a873b4843d8edf9d27JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a1fa668-9d4d-6610-2ee3-b1899ccf6723&amp;u=a1aHR0cHM6Ly93d3cuY29ybmVyb253ZWxsbmVzcy5jb20vYWJvdXQv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e86e0773a3931993aa95c16bc1e5fa3b735bec51699b9b732f50761b5b5f3389JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a1fa668-9d4d-6610-2ee3-b1899ccf6723&amp;u=a1aHR0cHM6Ly93d3cuemVuaGVhcnRjZW50ZXIuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=76602e701e3f3a2efe4cb134e60b55d1d7a9c83c581e5087a52a4ecc4f38fa50JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a1fa668-9d4d-6610-2ee3-b1899ccf6723&amp;u=a1aHR0cHM6Ly93d3cud2VsbG5lc3MuY29tL3doYXQtaXMtd2VsbG5lc3M&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1d1f956a8da176c5cea2a4cfe0c1efe20647d0eafeb15514336a6e6dd78b6c35JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a1fa668-9d4d-6610-2ee3-b1899ccf6723&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vc2VhcmNoP2ZpbmRfZGVzYz1XZWxsbmVzcytDZW50ZXImZmluZF9sb2M9Qm90aGVsbCUyQytXQSZtc29ja2lkPTJhMWZhNjY4OWQ0ZDY2MTAyZWUzYjE4OTljY2Y2NzIz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=960def06a544f8bbfd3f7bed9e55fc8e09a8184f8282d0d17754d272065c4f73JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a1fa668-9d4d-6610-2ee3-b1899ccf6723&amp;u=a1aHR0cHM6Ly93d3cuZnJleXdlbGxuZXNzLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=12d75af221d8c0eb9aab0ba31a64c15a66071ae49a9c6e17fbe96d8c73936457JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a1fa668-9d4d-6610-2ee3-b1899ccf6723&amp;u=a1aHR0cHM6Ly9pc21oZWFsdGgub3JnLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6aa7e6f0797a0af060d137946b02c3bc1399e1c35777305c8278ecb7b96a0e61JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36a2d650-5587-6816-1a09-c1b15458691e&amp;u=a1aHR0cHM6Ly93d3cuc2V2YWRzbS5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c5214ce0e395aa837028bafb043c6ef0bd83f99d1ed2ab2658df824bde935a14JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36a2d650-5587-6816-1a09-c1b15458691e&amp;u=a1aHR0cHM6Ly9pbm5vdmF0aXZlLWNvdW5zZWxpbmcub3JnLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=35bf338f4591551e984fe9d3f7171639c1b88e61a218520acd08e23e572a3a61JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36a2d650-5587-6816-1a09-c1b15458691e&amp;u=a1aHR0cHM6Ly9taW5kc3Bpcml0Y2VudGVyLm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e1f41d7499712a1901d23cc4b04f8d663625ae37199f5ff20529f1501bdf3069JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36a2d650-5587-6816-1a09-c1b15458691e&amp;u=a1aHR0cHM6Ly93d3cuZ3JlZW5jb3Vuc2VsaW5nc2VydmljZS5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6982980e8cd120ea33ecd4d3658b80bec5a2125b9c6abbdb799c2bbc7384e86dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36a2d650-5587-6816-1a09-c1b15458691e&amp;u=a1aHR0cHM6Ly9tb3NhaWNmYW1pbHlpbmMuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=07424e6187b5018f78e139c24f3c813967913a5c744c8be489c698b7a944aef1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36a2d650-5587-6816-1a09-c1b15458691e&amp;u=a1aHR0cHM6Ly9mYW1pbHlsZWdhY3ljb3Vuc2VsaW5nLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dd0980fa1a1b283ccaa321cc97601539c1ae58724db69593bf7e4ac7469f37edJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36a2d650-5587-6816-1a09-c1b15458691e&amp;u=a1aHR0cHM6Ly93d3cub3BlbmNvdW5zZWxpbmcuY29tL2lvd2EvZGVzLW1vaW5lcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c3bec96aa86d0c8f71ac150783410ae4f3af9dadfd3da6d34e58e0f4a89477c1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36a2d650-5587-6816-1a09-c1b15458691e&amp;u=a1aHR0cHM6Ly90dXJuaW5ncG9pbnRjb3Vuc2VsaW5nZHNtLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=866ef26494037189fbe4907577ef3673e58440344d71168ab2fc2d4af863981fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36a2d650-5587-6816-1a09-c1b15458691e&amp;u=a1aHR0cHM6Ly9uZXdsaWZlLWNvdW5zZWxpbmcuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e657e8825ab573fe99cf1773c8f125318e0a87a6e9ca47eec1e99f57cfe7a65dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36a2d650-5587-6816-1a09-c1b15458691e&amp;u=a1aHR0cHM6Ly93d3cucHN5Y2hvbG9neXRvZGF5LmNvbS91cy90aGVyYXBpc3RzL2lhL2Rlcy1tb2luZXM_bXNvY2tpZD0zNmEyZDY1MDU1ODc2ODE2MWEwOWMxYjE1NDU4NjkxZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e0bca3a2a84dace55e674c3bd34f90b73b053baa5d15f60224cdb91135d45c82JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39cd9a92-41f0-6818-0a9a-8d73407269f1&amp;u=a1aHR0cHM6Ly9yZWNvdmVyeS5jb20vbG9zLWFuZ2VsZXMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=df7899950fa6c65ceeb4453eddb08de4518d15fd7e9632a3cf40898cd3d91a4bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39cd9a92-41f0-6818-0a9a-8d73407269f1&amp;u=a1aHR0cHM6Ly93d3cuYWRkaWN0ZWQub3JnL2xvcy1hbmdlbGVzLWFkZGljdGlvbi1zZXJ2aWNlcy5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dcd07ac78036b821aafdea71d99bfb4d00bcbb866c4eb3a790a8f73a6e05150aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39cd9a92-41f0-6818-0a9a-8d73407269f1&amp;u=a1aHR0cHM6Ly9tZWRsaW5lcGx1cy5nb3YvcmVoYWJpbGl0YXRpb24uaHRtbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4e6aa711dc046cc3835df7c75da9cbf4ad490ee0d1f985d8c33926d8bd82262dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39cd9a92-41f0-6818-0a9a-8d73407269f1&amp;u=a1aHR0cHM6Ly93d3cuYWRkaWN0aW9ucmVzb3VyY2UubmV0L2Jlc3QtZHJ1Zy1yZWhhYi1jZW50ZXJzL2NhbGlmb3JuaWEvbG9zLWFuZ2VsZXMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0cf2f24043f47b404a33fed951b334288a1bba178efd2e5767f55d1fd44bbb76JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39cd9a92-41f0-6818-0a9a-8d73407269f1&amp;u=a1aHR0cHM6Ly93d3cuY2FsaWZvcm5pYXJlaGFiaW5zdGl0dXRlLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3cc3b626c8b5ba3bccfdf5e80fe5301dfe7ddb3baa64b8fc260670fcc88504ccJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39cd9a92-41f0-6818-0a9a-8d73407269f1&amp;u=a1aHR0cHM6Ly93d3cuYWRkaWN0ZWQub3JnL3JlaGFicy9jYWxpZm9ybmlhL2xvcy1hbmdlbGVzLWNvdW50eS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e08887f93d790c12c26fe33123905274ef7702f7ce25497d3c30889858f9d1f9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39cd9a92-41f0-6818-0a9a-8d73407269f1&amp;u=a1aHR0cHM6Ly93d3cud2hvLmludC9uZXdzLXJvb20vZmFjdC1zaGVldHMvZGV0YWlsL3JlaGFiaWxpdGF0aW9u&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=43182c9395f2bcb466ba465d0ee17f28487e29aefe2893b6ffc5ae494ca72676JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1596bb5f-606c-635b-2471-acbe61ef62bf&amp;u=a1aHR0cHM6Ly93d3cuZGhjcy5jYS5nb3YvbWVkaS1jYWwv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f93be6b7cbebc5a5af7ea3c1edacb4109b268057774fab7e6dff3b74f1e53502JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1596bb5f-606c-635b-2471-acbe61ef62bf&amp;u=a1aHR0cHM6Ly93d3cuZGhjcy5jYS5nb3YvTWVkaS1DYWwvUGFnZXMvY29udGFjdC5hc3B4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5dc8dbd65232dd75aad98303d3ccb0bac7dac860f30a0fc3eda6b73029db5b23JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1596bb5f-606c-635b-2471-acbe61ef62bf&amp;u=a1aHR0cHM6Ly9iZW5lZml0c2NhbC5jb20vSGVscC9wcm9ncmFtL21lZGljYWwvSENQREU_bGFuZz1lbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1fd67cad0b133688b302e91e6e0f755301252863e9731120df3202f9680ecd41JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1596bb5f-606c-635b-2471-acbe61ef62bf&amp;u=a1aHR0cHM6Ly93d3cubGFjYXJlLm9yZy9oZWFsdGgtcGxhbnMvbWVkaS1jYWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=55e5ff41ac1375d94775793a39d698d2266c32b56031a2e649dcaf940ba37fcaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1596bb5f-606c-635b-2471-acbe61ef62bf&amp;u=a1aHR0cHM6Ly9kcHNzLmxhY291bnR5Lmdvdi9lbi9oZWFsdGguaHRtbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=94908f8d782e6e801811135932bed8a70ec851bdb420bbe8863db081f8327b2eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1596bb5f-606c-635b-2471-acbe61ef62bf&amp;u=a1aHR0cHM6Ly93d3cuaGVhbHRoY2FyZW9wdGlvbnMuZGhjcy5jYS5nb3YvZW4vZmluZC1wcm92aWRlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6ab2deab09f8cd03c2791ad313221ef0a2310d63e7d5f2a47f4c31e7c68fa4acJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1596bb5f-606c-635b-2471-acbe61ef62bf&amp;u=a1aHR0cHM6Ly93d3cuY2EuZ292L2RlcGFydG1lbnRzLzIxNy9zZXJ2aWNlcy8zNy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ab318e9d781007ce6e07bad5905731b234877cece73c645332abb4df26baf462JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1596bb5f-606c-635b-2471-acbe61ef62bf&amp;u=a1aHR0cHM6Ly9tZS5sYWNvdW50eS5nb3Yv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d4cf901e7f00bb642402ffd8d943b43c26e4a37fbd86eedde9c6e41f5bd80f8bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1596bb5f-606c-635b-2471-acbe61ef62bf&amp;u=a1aHR0cHM6Ly9tY3dlYi5hcHBzLnByZC5jYW1taXMubWVkaS1jYWwuY2EuZ292L2NvbnRhY3Q&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=509e97c67b15c5b18ab1b12e225156fb3f047e40ab2043bac0620beadf4c51e4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1596bb5f-606c-635b-2471-acbe61ef62bf&amp;u=a1aHR0cHM6Ly93d3cuYmx1ZXNoaWVsZGNhLmNvbS9lbi9ic3Avb3VyLXBsYW5zL21lZGktY2Fs&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>
@@ -934,7 +916,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -968,19 +950,19 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G2" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H2" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -988,19 +970,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C3" t="s">
-        <v>99</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>101</v>
-      </c>
       <c r="G3" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1008,19 +990,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>102</v>
-      </c>
       <c r="G4" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H4" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1028,19 +1010,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G5" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H5" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1048,19 +1030,19 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G6" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H6" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1068,19 +1050,19 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G7" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H7" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1088,19 +1070,19 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G8" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H8" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1108,19 +1090,19 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G9" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H9" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1128,19 +1110,19 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G10" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H10" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1148,19 +1130,19 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G11" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H11" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1168,19 +1150,19 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G12" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H12" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1188,19 +1170,19 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G13" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H13" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1208,19 +1190,19 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="G14" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H14" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1228,19 +1210,19 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="G15" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H15" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1248,19 +1230,19 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G16" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H16" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1268,19 +1250,19 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G17" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H17" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1288,19 +1270,19 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C18" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="G18" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H18" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1308,19 +1290,19 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="G19" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H19" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1328,19 +1310,19 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C20" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G20" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H20" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1348,19 +1330,19 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C21" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G21" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H21" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1368,19 +1350,19 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C22" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G22" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H22" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1388,19 +1370,19 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C23" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G23" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H23" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1408,19 +1390,19 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G24" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H24" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1428,19 +1410,19 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G25" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H25" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1448,19 +1430,19 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G26" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H26" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1468,19 +1450,19 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G27" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H27" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1488,19 +1470,19 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G28" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H28" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1508,19 +1490,19 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G29" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H29" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1528,19 +1510,19 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G30" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H30" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1548,19 +1530,19 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C31" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G31" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H31" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1568,19 +1550,19 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C32" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G32" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H32" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1588,19 +1570,19 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C33" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G33" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H33" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1608,19 +1590,19 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G34" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H34" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1628,19 +1610,19 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C35" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G35" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H35" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1648,19 +1630,19 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C36" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G36" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H36" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1668,19 +1650,19 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C37" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G37" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H37" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1688,19 +1670,19 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C38" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G38" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H38" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1708,19 +1690,19 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C39" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G39" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H39" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1728,19 +1710,19 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C40" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G40" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H40" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1748,19 +1730,19 @@
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C41" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G41" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H41" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1768,19 +1750,19 @@
         <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C42" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="G42" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H42" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1788,19 +1770,19 @@
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C43" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G43" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H43" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1808,19 +1790,19 @@
         <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C44" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G44" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H44" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1828,19 +1810,19 @@
         <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C45" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G45" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H45" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1848,19 +1830,19 @@
         <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C46" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G46" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H46" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -1868,19 +1850,19 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C47" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G47" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H47" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -1888,19 +1870,19 @@
         <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C48" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G48" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H48" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -1908,19 +1890,19 @@
         <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C49" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G49" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H49" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -1928,19 +1910,19 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C50" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G50" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H50" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -1948,19 +1930,19 @@
         <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C51" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="G51" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H51" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -1968,19 +1950,19 @@
         <v>58</v>
       </c>
       <c r="B52" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C52" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G52" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H52" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -1988,19 +1970,19 @@
         <v>59</v>
       </c>
       <c r="B53" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C53" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G53" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H53" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -2008,19 +1990,19 @@
         <v>60</v>
       </c>
       <c r="B54" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C54" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G54" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H54" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -2028,19 +2010,19 @@
         <v>61</v>
       </c>
       <c r="B55" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C55" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G55" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H55" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -2048,19 +2030,19 @@
         <v>62</v>
       </c>
       <c r="B56" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C56" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G56" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H56" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -2068,19 +2050,19 @@
         <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C57" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G57" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H57" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -2088,19 +2070,19 @@
         <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C58" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G58" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H58" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -2108,19 +2090,19 @@
         <v>65</v>
       </c>
       <c r="B59" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C59" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G59" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H59" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -2128,19 +2110,19 @@
         <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C60" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G60" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H60" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2148,19 +2130,19 @@
         <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C61" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G61" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H61" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2168,19 +2150,19 @@
         <v>68</v>
       </c>
       <c r="B62" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C62" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G62" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H62" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2188,19 +2170,19 @@
         <v>69</v>
       </c>
       <c r="B63" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C63" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G63" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H63" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2208,19 +2190,19 @@
         <v>70</v>
       </c>
       <c r="B64" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C64" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G64" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H64" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2228,19 +2210,19 @@
         <v>71</v>
       </c>
       <c r="B65" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C65" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G65" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H65" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2248,19 +2230,19 @@
         <v>72</v>
       </c>
       <c r="B66" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C66" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G66" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H66" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2268,19 +2250,19 @@
         <v>73</v>
       </c>
       <c r="B67" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C67" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G67" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H67" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2288,19 +2270,19 @@
         <v>74</v>
       </c>
       <c r="B68" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C68" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G68" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H68" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2308,19 +2290,19 @@
         <v>75</v>
       </c>
       <c r="B69" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G69" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H69" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -2328,19 +2310,19 @@
         <v>76</v>
       </c>
       <c r="B70" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C70" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G70" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H70" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2348,19 +2330,19 @@
         <v>77</v>
       </c>
       <c r="B71" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C71" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G71" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H71" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -2368,19 +2350,19 @@
         <v>78</v>
       </c>
       <c r="B72" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C72" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="G72" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H72" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -2388,19 +2370,19 @@
         <v>79</v>
       </c>
       <c r="B73" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C73" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G73" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H73" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -2408,19 +2390,19 @@
         <v>80</v>
       </c>
       <c r="B74" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C74" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G74" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H74" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -2428,19 +2410,19 @@
         <v>81</v>
       </c>
       <c r="B75" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C75" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G75" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H75" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -2448,19 +2430,19 @@
         <v>82</v>
       </c>
       <c r="B76" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C76" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G76" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H76" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -2468,19 +2450,19 @@
         <v>83</v>
       </c>
       <c r="B77" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C77" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G77" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H77" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -2488,19 +2470,19 @@
         <v>84</v>
       </c>
       <c r="B78" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C78" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G78" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H78" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -2508,19 +2490,19 @@
         <v>85</v>
       </c>
       <c r="B79" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C79" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G79" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H79" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -2528,19 +2510,19 @@
         <v>86</v>
       </c>
       <c r="B80" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C80" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G80" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H80" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -2548,19 +2530,19 @@
         <v>87</v>
       </c>
       <c r="B81" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C81" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G81" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H81" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -2568,19 +2550,19 @@
         <v>88</v>
       </c>
       <c r="B82" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C82" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G82" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H82" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -2588,19 +2570,19 @@
         <v>89</v>
       </c>
       <c r="B83" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C83" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G83" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H83" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -2608,19 +2590,19 @@
         <v>90</v>
       </c>
       <c r="B84" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C84" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G84" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H84" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -2628,19 +2610,19 @@
         <v>91</v>
       </c>
       <c r="B85" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C85" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G85" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H85" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -2648,19 +2630,19 @@
         <v>92</v>
       </c>
       <c r="B86" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C86" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G86" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H86" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -2668,19 +2650,19 @@
         <v>93</v>
       </c>
       <c r="B87" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C87" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="G87" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H87" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -2688,79 +2670,19 @@
         <v>94</v>
       </c>
       <c r="B88" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C88" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G88" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H88" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8">
-      <c r="A89" t="s">
-        <v>95</v>
-      </c>
-      <c r="B89" t="s">
-        <v>98</v>
-      </c>
-      <c r="C89" t="s">
-        <v>99</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="G89" t="s">
-        <v>190</v>
-      </c>
-      <c r="H89" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8">
-      <c r="A90" t="s">
-        <v>96</v>
-      </c>
-      <c r="B90" t="s">
-        <v>98</v>
-      </c>
-      <c r="C90" t="s">
-        <v>99</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="G90" t="s">
-        <v>190</v>
-      </c>
-      <c r="H90" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8">
-      <c r="A91" t="s">
-        <v>97</v>
-      </c>
-      <c r="B91" t="s">
-        <v>98</v>
-      </c>
-      <c r="C91" t="s">
-        <v>99</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="G91" t="s">
-        <v>190</v>
-      </c>
-      <c r="H91" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -2852,9 +2774,6 @@
     <hyperlink ref="F86" r:id="rId85"/>
     <hyperlink ref="F87" r:id="rId86"/>
     <hyperlink ref="F88" r:id="rId87"/>
-    <hyperlink ref="F89" r:id="rId88"/>
-    <hyperlink ref="F90" r:id="rId89"/>
-    <hyperlink ref="F91" r:id="rId90"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/scraped_Cape_Town_Health_and_Wellness.xlsx
+++ b/results/scraped_Cape_Town_Health_and_Wellness.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="192">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -43,103 +43,100 @@
     <t>Community-Wikipedia</t>
   </si>
   <si>
-    <t>CommunityPartners - Creating more equitable, just, and vibrant …</t>
+    <t>COMMUNITYDefinition &amp; Meaning -Merriam-Webster</t>
+  </si>
+  <si>
+    <t>City ofSt. Petersburg</t>
   </si>
   <si>
     <t>Community (TV series) -Wikipedia</t>
   </si>
   <si>
-    <t>Home | 211LA</t>
-  </si>
-  <si>
-    <t>California Community Foundation| A Good Life for All</t>
-  </si>
-  <si>
-    <t>COMMUNITYDefinition &amp; Meaning -Merriam-Webster</t>
+    <t>LGBTQ+Community-St. Petersburg, Florida</t>
   </si>
   <si>
     <t>Community(TV Series 2009–2015) - IMDb</t>
   </si>
   <si>
-    <t>Community– Parks &amp; Recreation</t>
-  </si>
-  <si>
-    <t>Homepage |LACCD</t>
-  </si>
-  <si>
-    <t>Home | Neighborhood Info</t>
+    <t>What isCommunity? Basic Concepts in Sociology (updated 2025)</t>
+  </si>
+  <si>
+    <t>55+CommunityHomes for Sale in Saint PetersburgFL- Zillow</t>
+  </si>
+  <si>
+    <t>55Plus Community - Saint Petersburg FLReal Estate -Zillow</t>
+  </si>
+  <si>
+    <t>A 55+CommunityinSt. Petersburg,Florida- Harbor Lights</t>
+  </si>
+  <si>
+    <t>Residential Hospice - Lake Ridge</t>
   </si>
   <si>
     <t>What ishospice? -HospiceFoundation of America</t>
   </si>
   <si>
-    <t>Hospice- Wikipedia</t>
-  </si>
-  <si>
-    <t>THE BEST10 HOSPICE IN LOS ANGELES, CA- Yelp</t>
-  </si>
-  <si>
-    <t>Frequently Asked Questions AboutHospiceCare | National ...</t>
-  </si>
-  <si>
-    <t>Hospice Care- Care Options |CaliforniaDepartment of Aging ...</t>
-  </si>
-  <si>
-    <t>Welcome to theCalifornia Hospiceand Palliative Care Association</t>
-  </si>
-  <si>
-    <t>Hospice&amp; Palliative Care inLos Angeles|Silverado Hospice</t>
-  </si>
-  <si>
-    <t>TOP 10BEST Hospice in Los Angeles, CA- (2026 Guide ... - Yelp</t>
-  </si>
-  <si>
-    <t>HospiceCare and Palliative Care inLos Angeles CA</t>
-  </si>
-  <si>
-    <t>AgapeHospice&amp; Palliative Care in LA &amp; Orange Counties</t>
+    <t>Triniti Home Health &amp;Hospice|Minnesota HospiceCare</t>
+  </si>
+  <si>
+    <t>Hospice CareCoverage - Medicare</t>
+  </si>
+  <si>
+    <t>Frequently Asked Questions AboutHospiceCare - National Institute …</t>
+  </si>
+  <si>
+    <t>20 Hospice Facilities in Buffalo, MN- Find Reviews, Photos</t>
+  </si>
+  <si>
+    <t>Home Health andHospiceServices inBuffalo,MN</t>
+  </si>
+  <si>
+    <t>Triniti Home Health AndHospice-Minnesota's State Portal</t>
+  </si>
+  <si>
+    <t>Hospice- Overview -Mayo Clinic</t>
+  </si>
+  <si>
+    <t>Minnesota Hospice</t>
+  </si>
+  <si>
+    <t>mental是什么意思_mental的翻译_音标_读音_用法_例句_爱词霸在线词典</t>
+  </si>
+  <si>
+    <t>MENTAL中文 (简体)翻译：剑桥词典 - Cambridge Dictionary</t>
+  </si>
+  <si>
+    <t>mental_百度百科</t>
+  </si>
+  <si>
+    <t>Mental health-Wikipedia</t>
   </si>
   <si>
     <t>MENTALDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
+    <t>Mental disorders-World Health Organization(WHO)</t>
+  </si>
+  <si>
     <t>AboutMentalHealth |MentalHealth | CDC</t>
   </si>
   <si>
-    <t>Mental health-Wikipedia</t>
-  </si>
-  <si>
-    <t>Mental disorders-World Health Organization(WHO)</t>
-  </si>
-  <si>
-    <t>MentalHealth: Causes, Symptoms, Treatment &amp; Help | SAMHSA</t>
-  </si>
-  <si>
-    <t>Mentalhealth: What's normal, what's not -Mayo Clinic</t>
-  </si>
-  <si>
-    <t>MentalDisorders: Types, Causes &amp; Symptoms -Cleveland Clinic</t>
+    <t>MENTAL在剑桥英语词典中的解释及翻译 - Cambridge Dictionary</t>
   </si>
   <si>
     <t>Mentaldisorder -Wikipedia</t>
   </si>
   <si>
-    <t>Mental health: Definition, common disorders, early signs, and more</t>
-  </si>
-  <si>
-    <t>Mental HealthDisorders Center: Types, Symptoms, Treatments ... -WebMD</t>
+    <t>MENTAL释义 | 柯林斯英语词典 - Collins Online Dictionary</t>
   </si>
   <si>
     <t>Health- Wikipedia</t>
   </si>
   <si>
-    <t>Contact &amp; Hours - All ForHealth,HealthFor All</t>
-  </si>
-  <si>
     <t>HEALTH: Longevity for All</t>
   </si>
   <si>
-    <t>AdventistHealth GlendaleMedical Center</t>
+    <t>Home |LouisianaDepartment ofHealth</t>
   </si>
   <si>
     <t>WebMD- Better information. Betterhealth.</t>
@@ -148,157 +145,169 @@
     <t>Health| Definition &amp; Importance | Britannica</t>
   </si>
   <si>
-    <t>DignityHealth-GlendaleMemorial Hospital andHealthCenter,CA...</t>
-  </si>
-  <si>
-    <t>CaliforniaDepartment of PublicHealth</t>
+    <t>HealthDepartment - Home -City of New Orleans</t>
   </si>
   <si>
     <t>What ishealth?: Defining and preservinggood health</t>
   </si>
   <si>
-    <t>LA County Department of PublicHealth- SPA 2</t>
+    <t>Healthline: Medical information andhealthadvice you can trust.</t>
+  </si>
+  <si>
+    <t>Health Information| National Institutes ofHealth(NIH)</t>
+  </si>
+  <si>
+    <t>LCMCHealth|New OrleansHospitals, Doctors &amp; Urgent Care</t>
+  </si>
+  <si>
+    <t>PrimaryClothing - Brilliant Basics for Baby &amp; Kids</t>
   </si>
   <si>
     <t>PRIMARYDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
-    <t>PrimaryClothing - Brilliant Basics for Baby &amp; Kids</t>
+    <t>Games, Videos, Holidays &amp; Crafts |PrimaryGames</t>
   </si>
   <si>
     <t>PRIMARY| English meaning - Cambridge Dictionary</t>
   </si>
   <si>
-    <t>Games, Videos, Holidays &amp; Crafts |PrimaryGames</t>
+    <t>Primary— reporting assembled from records</t>
+  </si>
+  <si>
+    <t>PRIMARY| definition in the Cambridge English Dictionary</t>
   </si>
   <si>
     <t>National Elections 2026 Live Results and Map: Delaware Primaries</t>
   </si>
   <si>
-    <t>Primary— reporting assembled from records</t>
-  </si>
-  <si>
     <t>PRIMARYDefinition &amp; Meaning |Dictionary.com</t>
   </si>
   <si>
-    <t>12.Primary- The Church of Jesus Christ of Latter-day Saints</t>
-  </si>
-  <si>
     <t>Primary- Definition, Meaning &amp; Synonyms | Vocabulary.com</t>
   </si>
   <si>
-    <t>Utah HousePrimaryElection 2026 Live Results - NBC News</t>
+    <t>2026PrimaryResults — State-by-State | The Midterm Project</t>
+  </si>
+  <si>
+    <t>Sacred JourneysWellnessCenter: Therapy &amp; Classes of Healing …</t>
   </si>
   <si>
     <t>What is Wellness? -Global Wellness Institute</t>
   </si>
   <si>
-    <t>Corner OnWellness|Bothell,WAChiropractic Office</t>
-  </si>
-  <si>
-    <t>Welcome to Sound Health &amp;WellnessTrust</t>
-  </si>
-  <si>
-    <t>BothellChiropractic andWellnesslocated inBothell,WA</t>
-  </si>
-  <si>
-    <t>Welcome to Corner onWellness- Corner OnWellness</t>
-  </si>
-  <si>
-    <t>HolisticWellnessStudio | Zen Heart Center |Bothell</t>
+    <t>Transitions Counseling &amp;Wellness-Brookville,OH</t>
   </si>
   <si>
     <t>What is Wellness?</t>
   </si>
   <si>
-    <t>TOP 10 BESTWellnessCenter inBothell,WA- Yelp</t>
-  </si>
-  <si>
-    <t>Home - FreyWellness</t>
-  </si>
-  <si>
-    <t>Integrative Naturopathic Medicine Clinic inBothell| ISM Health &amp;Wellness</t>
-  </si>
-  <si>
-    <t>Seva Counseling — Therapists inDes Moines, Iowa</t>
-  </si>
-  <si>
-    <t>Innovative Counseling and Consulting |Des Moines,IA</t>
-  </si>
-  <si>
-    <t>Mind &amp; Spirit Counseling Center | Home</t>
-  </si>
-  <si>
-    <t>Green Counseling Services - Mental Health Counseling inIowa</t>
-  </si>
-  <si>
-    <t>MOSAIC Family Counseling Center | EMDR &amp; Counseling inDes Moines,IA</t>
-  </si>
-  <si>
-    <t>Family Legacy Counseling</t>
-  </si>
-  <si>
-    <t>Free or Low-Cost Counseling in Des Moines,IA- OpenCounseling</t>
-  </si>
-  <si>
-    <t>Turning Point Counseling |Des Moines, Iowa</t>
-  </si>
-  <si>
-    <t>Home | New Life Counseling</t>
-  </si>
-  <si>
-    <t>Therapistsin Des Moines, IA- Psychology Today</t>
-  </si>
-  <si>
-    <t>50 Best Drug &amp; Alcohol Rehab Centers inLos Angeles,CA2026 ...</t>
-  </si>
-  <si>
-    <t>18 Best Drug Rehabs inLos Angeles,CA(2026) - Supe</t>
+    <t>Jodi LynnHale, Licensed Professional Counselor, Brookville, OH, …</t>
+  </si>
+  <si>
+    <t>Transitions Counseling andWellnessinBrookville,OH- Counselor</t>
+  </si>
+  <si>
+    <t>Connect | Sacred Journeys Well</t>
+  </si>
+  <si>
+    <t>Wellness (alternative medicine) - Wikipedia</t>
+  </si>
+  <si>
+    <t>TopWellnessCompanies inBrookville,OH| Birdeye</t>
+  </si>
+  <si>
+    <t>Sacred JourneysWellnessCenter |Brookville OH- Facebook</t>
+  </si>
+  <si>
+    <t>Craig,ColoradoTherapy &amp; Counseling - Health Solutions West</t>
+  </si>
+  <si>
+    <t>Therapists in Craig, CO- Psychology Today</t>
+  </si>
+  <si>
+    <t>Marriage Counseling Therapists inCraig,CO- Psychology Today</t>
+  </si>
+  <si>
+    <t>Steven P. Walls-CraigTherapist | Solving SUD Together</t>
+  </si>
+  <si>
+    <t>A&amp;SCounseling| Trauma-Informed Virtual Care AcrossColorado</t>
+  </si>
+  <si>
+    <t>20 Best Counselors NearCraig,CO- Healthgrades</t>
+  </si>
+  <si>
+    <t>Behavioral Health, Counseling inCraig|Memorial Regional Health</t>
+  </si>
+  <si>
+    <t>A&amp;S Counseling|Craig CO- Facebook</t>
+  </si>
+  <si>
+    <t>Defining theCounseling Processand Its Stages</t>
+  </si>
+  <si>
+    <t>Counseling psychology- Wikipedia</t>
   </si>
   <si>
     <t>Rehabilitation- MedlinePlus</t>
   </si>
   <si>
-    <t>12 BestRehab CentersInLos Angeles,CA- Addiction Resource</t>
-  </si>
-  <si>
-    <t>California RehabilitationInstitute | Home</t>
-  </si>
-  <si>
-    <t>71 Best Drug Rehabs inLos AngelesCounty,CA(2026)</t>
-  </si>
-  <si>
-    <t>Rehabilitation- World Health Organization (WHO)</t>
-  </si>
-  <si>
-    <t>Medi-Cal- DHCS</t>
-  </si>
-  <si>
-    <t>Contact |Medi-Cal- DHCS</t>
-  </si>
-  <si>
-    <t>Program Descriptions A | BenefitsCal. Together, we benefit.</t>
-  </si>
-  <si>
-    <t>Medi-CalPlan | L.A. Care Health Plan</t>
-  </si>
-  <si>
-    <t>Health Care - Department of Public Social Services</t>
-  </si>
-  <si>
-    <t>Find a provider |Medi-CalManaged Care Health Care Options</t>
-  </si>
-  <si>
-    <t>Apply forMedi-Cal|CA.gov</t>
-  </si>
-  <si>
-    <t>County ofLos Angeles MedicalExaminer</t>
-  </si>
-  <si>
-    <t>Medi-CalProviders</t>
-  </si>
-  <si>
-    <t>Medi-Cal| Blue Shield ofCAPromise Health Plan</t>
+    <t>Inpatient Rehabilitationat Beacon Health System</t>
+  </si>
+  <si>
+    <t>6 Best Drug Rehabsin Elkhart,IN(2026) - addicted.org</t>
+  </si>
+  <si>
+    <t>THE BEST 10RehabilitationCenterin ELKHART,IN- (2026 GUIDE …</t>
+  </si>
+  <si>
+    <t>Hubbard Hill -Rehabilitation and Healthcare in Elkhart,IN</t>
+  </si>
+  <si>
+    <t>Top 10 BestRehabilitationNearElkhart,Indiana(Updated 2026)</t>
+  </si>
+  <si>
+    <t>RehabilitationServices at Beacon Health System</t>
+  </si>
+  <si>
+    <t>ElkhartGeneral Hospital InpatientRehabilitationServices</t>
+  </si>
+  <si>
+    <t>DDARS: VocationalRehabilitation-IN.gov</t>
+  </si>
+  <si>
+    <t>East Lake Nursing &amp; RehabilitationCenter -Indiana's Premier Senior ...</t>
+  </si>
+  <si>
+    <t>Fenton MedicalCenter – Patient Centered Healthcare</t>
+  </si>
+  <si>
+    <t>WebMD- Better information. Better health.</t>
+  </si>
+  <si>
+    <t>McLaren FentonHomepage</t>
+  </si>
+  <si>
+    <t>Patient Portal –Fenton MedicalCenter</t>
+  </si>
+  <si>
+    <t>McLaren Flint – Fenton Family Medicine</t>
+  </si>
+  <si>
+    <t>Medicine- Wikipedia</t>
+  </si>
+  <si>
+    <t>Regional Medical Imaging: Advanced ImagingMichigan</t>
+  </si>
+  <si>
+    <t>MedicalEquipment Online Store</t>
+  </si>
+  <si>
+    <t>Fenton MedicalCenter,Fenton,MI- Healthgrades</t>
+  </si>
+  <si>
+    <t>MedicalDiseases &amp;Conditions- Mayo Clinic</t>
   </si>
   <si>
     <t>Health &amp; Wellness</t>
@@ -307,265 +316,274 @@
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a6b089d75ab1baba7d31241c5502d4ade9812eca31a0979282e4ceceeeb7d2f8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fabe878-1062-6457-0b35-ff9911eb653b&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Db21tdW5pdHk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=37b3801965c10f807bf22c31277bde0eec4e75f9a723f17d028d5db2ac4b43d5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fabe878-1062-6457-0b35-ff9911eb653b&amp;u=a1aHR0cHM6Ly9jb21tdW5pdHlwYXJ0bmVycy5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2c570bea5b04afbddfb39bf5b686049ac9a8b705ee674813f0517c3ebcf07161JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fabe878-1062-6457-0b35-ff9911eb653b&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Db21tdW5pdHlfKFRWX3Nlcmllcyk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=83677531f9beab7014cf5791802db4b43a8b215fc6c19660a236f4999b7feeccJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fabe878-1062-6457-0b35-ff9911eb653b&amp;u=a1aHR0cHM6Ly8yMTFsYS5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6a39a06e65dcf51682de8d2340f931acea9b00a3266544e3cd668a4fa188e0afJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fabe878-1062-6457-0b35-ff9911eb653b&amp;u=a1aHR0cHM6Ly93d3cuY2FsZnVuZC5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=74cb9fb7d9bdce9a3a829c84318a529b6768f4ad191f1782747943735a2e363dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fabe878-1062-6457-0b35-ff9911eb653b&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2NvbW11bml0eQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d1e8900148e9a94caeed5745d77eeb8632f95050f8dc76845709dd0b54970b5cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fabe878-1062-6457-0b35-ff9911eb653b&amp;u=a1aHR0cHM6Ly9tLmltZGIuY29tL3RpdGxlL3R0MTQzOTYyOS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1c4085f0d108b6700ae9102bd739e237a365d98bdcafd6094afdcb592f865b1cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fabe878-1062-6457-0b35-ff9911eb653b&amp;u=a1aHR0cHM6Ly9wYXJrcy5sYWNvdW50eS5nb3YvY29tbXVuaXR5Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=064bd57df6f8d9324e60ee2049917230f17f65c986b0ff03f0b64463a448cd02JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fabe878-1062-6457-0b35-ff9911eb653b&amp;u=a1aHR0cHM6Ly93d3cubGFjY2QuZWR1Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=912f0388034b26a47ff86d10372c788ce7e8d05cb89ce15c5e2286afd70c2527JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fabe878-1062-6457-0b35-ff9911eb653b&amp;u=a1aHR0cHM6Ly9uZWlnaGJvcmhvb2RpbmZvLmxhY2l0eS5nb3Yv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9de017733b4266c44fc0e1fb414d76715bc69d3146e8718c836eff454f0482ecJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1b8ccdd9-f839-61e3-01b0-da38f98b6027&amp;u=a1aHR0cHM6Ly9ob3NwaWNlZm91bmRhdGlvbi5vcmcvd2hhdC1pcy1ob3NwaWNlLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3033e4a6721a21e1907c50898f48645e5721eb7e25e2591828fa39badc032361JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1b8ccdd9-f839-61e3-01b0-da38f98b6027&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Ib3NwaWNl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3b3d9225d1aa7f72d846549708d54c93379e96684b7a3abd21475d806dbedaddJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1b8ccdd9-f839-61e3-01b0-da38f98b6027&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vc2VhcmNoP2NmbHQ9aG9zcGljZSZmaW5kX2xvYz1Mb3MrQW5nZWxlcyUyQytDQSZtc29ja2lkPTFiOGNjZGQ5ZjgzOTYxZTMwMWIwZGEzOGY5OGI2MDI3&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b453502156c57359a4987f4c31a6d776b5dd9b749dfe62df4a6cbf7e300f07e8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1b8ccdd9-f839-61e3-01b0-da38f98b6027&amp;u=a1aHR0cHM6Ly93d3cubmlhLm5paC5nb3YvaGVhbHRoL2hvc3BpY2UtYW5kLXBhbGxpYXRpdmUtY2FyZS9mcmVxdWVudGx5LWFza2VkLXF1ZXN0aW9ucy1hYm91dC1ob3NwaWNlLWNhcmU&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=423681be81a486159be7035783ead164d2ece4384bf47bf2254193ef6c5b116dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1b8ccdd9-f839-61e3-01b0-da38f98b6027&amp;u=a1aHR0cHM6Ly93d3cuYWdpbmcuY2EuZ292L0NhcmVfT3B0aW9ucy9Ib3NwaWNlX0NhcmUv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=364f8483c0c2110505f16c84191a47a235cdf09732b73877af210cc7dbb2ce58JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1b8ccdd9-f839-61e3-01b0-da38f98b6027&amp;u=a1aHR0cHM6Ly93d3cuY2FsaG9zcGljZS5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f86d7ce9dc23aa4c27820151ebf2d525ddee41c41bd0b6dab67ec709fb45cbafJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1b8ccdd9-f839-61e3-01b0-da38f98b6027&amp;u=a1aHR0cHM6Ly93d3cuc2lsdmVyYWRvaG9zcGljZS5jb20vbG9jYXRpb24vc2lsdmVyYWRvLWhvc3BpY2UtbG9zLWFuZ2VsZXMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7e4e224b1e3944cded409794aed360052adbfe1a550bb0c3f434ae271c6bd7faJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1b8ccdd9-f839-61e3-01b0-da38f98b6027&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vc2VhcmNoP2ZpbmRfZGVzYz1ob3NwaWNlJmZpbmRfbG9jPUxvcytBbmdlbGVzJTJDK0NBJm1zb2NraWQ9MWI4Y2NkZDlmODM5NjFlMzAxYjBkYTM4Zjk4YjYwMjc&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a8a4904b149a4959505bcce9b025866a29714abf7cdf18cb2b7d456c982aff5dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1b8ccdd9-f839-61e3-01b0-da38f98b6027&amp;u=a1aHR0cHM6Ly9nb2xkZW5nYXRlaG9zcGljZS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=46297c205efef89825cc3632b966088749442929e768203652e1624d0517bdddJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1b8ccdd9-f839-61e3-01b0-da38f98b6027&amp;u=a1aHR0cHM6Ly93d3cuYWdhcGVob3NwaWNlcGMub3JnLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=70c10e16ff684879e4b4fc48809e553ab324ad1adbb49d35dac751b6012dfb4cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=203dbec7-9e3e-646f-0893-a9269f9a656a&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L21lbnRhbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=12bd304567a4bd15fac32fa9b42ea795bce7396297186519a80d74f7bf32150dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=203dbec7-9e3e-646f-0893-a9269f9a656a&amp;u=a1aHR0cHM6Ly93d3cuY2RjLmdvdi9tZW50YWwtaGVhbHRoL2Fib3V0L2luZGV4Lmh0bWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3660e3cf133daf7f4a93d8d3c4e6fab8c402bccb43fb62400f5210264970bdecJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=203dbec7-9e3e-646f-0893-a9269f9a656a&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWVudGFsX2hlYWx0aA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fa3bd3c03b9c24f68a67afc03ebb5ed3ba1b959a3805d58eaf06b42b0d1b9d89JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=203dbec7-9e3e-646f-0893-a9269f9a656a&amp;u=a1aHR0cHM6Ly93d3cud2hvLmludC9uZXdzLXJvb20vZmFjdC1zaGVldHMvZGV0YWlsL21lbnRhbC1kaXNvcmRlcnM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=da90f618237263e17166ecafba011db8d883b0fbdc492a13999fcbc244897e82JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=203dbec7-9e3e-646f-0893-a9269f9a656a&amp;u=a1aHR0cHM6Ly93d3cuc2FtaHNhLmdvdi9tZW50YWwtaGVhbHRo&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5f04bf5694c5a124fbdfbb927e7351a2bae73a79acc20b7fcd8135f254b8d8b7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=203dbec7-9e3e-646f-0893-a9269f9a656a&amp;u=a1aHR0cHM6Ly93d3cubWF5b2NsaW5pYy5vcmcvaGVhbHRoeS1saWZlc3R5bGUvYWR1bHQtaGVhbHRoL2luLWRlcHRoL21lbnRhbC1oZWFsdGgvYXJ0LTIwMDQ0MDk4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d0143eab55510c506b3fece67755f66aab3747e87a236923887e07d09866d597JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=203dbec7-9e3e-646f-0893-a9269f9a656a&amp;u=a1aHR0cHM6Ly9teS5jbGV2ZWxhbmRjbGluaWMub3JnL2hlYWx0aC9kaXNlYXNlcy8yMjI5NS1tZW50YWwtaGVhbHRoLWRpc29yZGVycw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=711fb4413faa00c9cc7e10469b741062e14b3956942317a7c76d599407154dbeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=203dbec7-9e3e-646f-0893-a9269f9a656a&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWVudGFsX2Rpc29yZGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fc72a993acdf45d09097d87239395eb5ac475c2a213f90c84cd57a566af12c25JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=203dbec7-9e3e-646f-0893-a9269f9a656a&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhbG5ld3N0b2RheS5jb20vYXJ0aWNsZXMvMTU0NTQz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=485ae0e9ff30dc4f6d1d4eabfd3c875174c1c45ffc19ae0a8176e3cf0d28e83eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=203dbec7-9e3e-646f-0893-a9269f9a656a&amp;u=a1aHR0cHM6Ly93d3cud2VibWQuY29tL21lbnRhbC1oZWFsdGgvZGVmYXVsdC5odG0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7a2081762b5b314dcddf573074392dc8d0138fd25852b1d11c55d2fb5c1a0143JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cd0fd04-c65e-6f7c-390f-eae5c7036e2b&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvSGVhbHRo&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ff2538e86a5dc5c73a5249f8ac10b4106d435dc052c06722538c4963ff89047cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cd0fd04-c65e-6f7c-390f-eae5c7036e2b&amp;u=a1aHR0cHM6Ly9hbGw0aGVhbHRoLm9yZy9jb250YWN0LXVzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=378249eadf1c6938d95b1d789827c088c6809e914b77a5e5f078cb8a0dba4eb8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cd0fd04-c65e-6f7c-390f-eae5c7036e2b&amp;u=a1aHR0cHM6Ly93d3cuaGVhbHRoLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=40f8669f9c275b732835d75c80be77bbbd714e537b6ce192e37d53e597a1704aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cd0fd04-c65e-6f7c-390f-eae5c7036e2b&amp;u=a1aHR0cHM6Ly93d3cuYWR2ZW50aXN0aGVhbHRoLm9yZy9nbGVuZGFsZS9sb2NhdGlvbnMvYWR2ZW50aXN0LWhlYWx0aC1nbGVuZGFsZS1tZWRpY2FsLWNlbnRlci00NDQ2Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f6928efcacb5a5140a84460ac6fb57ff3bd7efe497d9be911766f295d13a0ff8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cd0fd04-c65e-6f7c-390f-eae5c7036e2b&amp;u=a1aHR0cHM6Ly93d3cud2VibWQuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0026e2070b27eceb7ac8d7176205ea464fbb800f92afc83530a7bbb76b51083bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cd0fd04-c65e-6f7c-390f-eae5c7036e2b&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvaGVhbHRo&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=884718313457c6c20d5c0d56e0284490085079f37d88c45bc2c65033defe3e80JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cd0fd04-c65e-6f7c-390f-eae5c7036e2b&amp;u=a1aHR0cHM6Ly93d3cuY29tbW9uc3Bpcml0Lm9yZy9maW5kLWEtbG9jYXRpb24vZGlnbml0eS1oZWFsdGgtZ2xlbmRhbGUtbWVtb3JpYWwtaG9zcGl0YWwtYW5kLWhlYWx0aC1jZW50ZXItMzIwMg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cee2eb438f40e44853f66e76ba59457420dec86f17af85ba0658a4afc791baf9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cd0fd04-c65e-6f7c-390f-eae5c7036e2b&amp;u=a1aHR0cHM6Ly93d3cuY2RwaC5jYS5nb3Yv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a9b1a2faf3decb127e422cb40c794b828fb94801d6ce8881e0e9fd3c874aa974JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cd0fd04-c65e-6f7c-390f-eae5c7036e2b&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhbG5ld3N0b2RheS5jb20vYXJ0aWNsZXMvMTUwOTk5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=33f4c663c75594aed24d7ab55a40f4500d6b1cedee9ad1711407a80e9e6eab21JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cd0fd04-c65e-6f7c-390f-eae5c7036e2b&amp;u=a1aHR0cDovL3d3dy5wdWJsaWNoZWFsdGgubGFjb3VudHkuZ292L2Nocy9TUEEyLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0c21f1dbde76b54470d0f0baeb34c0389a612c5658aae60e058932903d04328eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0450aedf-e260-6b45-0865-b93ee3c46af7&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3ByaW1hcnk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9343c30e0d264d327bd89ea24863fa9bec751273ec8164c39975e737b641ec89JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0450aedf-e260-6b45-0865-b93ee3c46af7&amp;u=a1aHR0cHM6Ly93d3cucHJpbWFyeS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=53cba9a2deb0fd97f18466df9fade2f72b1d1a4b20ce1443f92d406955793b13JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0450aedf-e260-6b45-0865-b93ee3c46af7&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3ByaW1hcnk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=780d5afbb1565a710983e089efff541a1a61528054a2dbd60b3341434a159d33JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0450aedf-e260-6b45-0865-b93ee3c46af7&amp;u=a1aHR0cHM6Ly93d3cucHJpbWFyeWdhbWVzLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d7bfc98f4042444ca678286468daf4149a82216974bf84ab74d22dc7aad7cbcbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0450aedf-e260-6b45-0865-b93ee3c46af7&amp;u=a1aHR0cHM6Ly93d3cubmJjbmV3cy5jb20vcG9saXRpY3MvMjAyNi1wcmltYXJ5LWVsZWN0aW9ucy9uYXRpb25hbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=abe70edd98ee03354bc8f8c4a24b3e546204b4c4600851530f428b5a762d446bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0450aedf-e260-6b45-0865-b93ee3c46af7&amp;u=a1aHR0cHM6Ly90aGVwcmltYXJ5LmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9e47a7a8d7b2ff173452a0fa170f31a7b20b950d13ab4d15895193ec2ca4ef29JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0450aedf-e260-6b45-0865-b93ee3c46af7&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3ByaW1hcnk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cc5554825cfc6101fe1e38f954c58977581101c8f125b1850627b391af8e9f21JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0450aedf-e260-6b45-0865-b93ee3c46af7&amp;u=a1aHR0cHM6Ly93d3cuY2h1cmNob2ZqZXN1c2NocmlzdC5vcmcvc3R1ZHkvbWFudWFsL2dlbmVyYWwtaGFuZGJvb2svMTItcHJpbWFyeT9sYW5nPWVuZw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ccd8dc29669a08f940106afc37b3f1a8dff60d2d60fb8d23633cf8bb9e40ca1dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0450aedf-e260-6b45-0865-b93ee3c46af7&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9wcmltYXJ5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8f217ec4c2f7636e146a18302dddbe0e3584d4ff00e9f2c2bf91d875dbe7afa1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0450aedf-e260-6b45-0865-b93ee3c46af7&amp;u=a1aHR0cHM6Ly93d3cubmJjbmV3cy5jb20vcG9saXRpY3MvMjAyNi1wcmltYXJ5LWVsZWN0aW9ucy91dGFoLWhvdXNlLXJlc3VsdHM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3255f5954a9408cebfb92f78131734f7556d4d466822112497034bcec97e35e8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a1fa668-9d4d-6610-2ee3-b1899ccf6723&amp;u=a1aHR0cHM6Ly9nbG9iYWx3ZWxsbmVzc2luc3RpdHV0ZS5vcmcvd2hhdC1pcy13ZWxsbmVzcy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6b441dabac122f94bd989a339766a00bd217983c3664bd875feba7d7948d55a5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a1fa668-9d4d-6610-2ee3-b1899ccf6723&amp;u=a1aHR0cHM6Ly93d3cuY29ybmVyb253ZWxsbmVzcy5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=40333e9ab7bc6a75ca4e6a090d00f8751b9673ff1dac003d7678fd9157ac0877JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a1fa668-9d4d-6610-2ee3-b1899ccf6723&amp;u=a1aHR0cHM6Ly9zb3VuZGhlYWx0aHdlbGxuZXNzLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c05f76f271644b68db558167c000f39d0c75c0596ef383bad6b679df46de2985JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a1fa668-9d4d-6610-2ee3-b1899ccf6723&amp;u=a1aHR0cHM6Ly9ib3RoZWxsY2hpcm9wcmFjdGljLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4d86cbbe704d1668607782f2c56beb438dbcba7f29e900a873b4843d8edf9d27JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a1fa668-9d4d-6610-2ee3-b1899ccf6723&amp;u=a1aHR0cHM6Ly93d3cuY29ybmVyb253ZWxsbmVzcy5jb20vYWJvdXQv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e86e0773a3931993aa95c16bc1e5fa3b735bec51699b9b732f50761b5b5f3389JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a1fa668-9d4d-6610-2ee3-b1899ccf6723&amp;u=a1aHR0cHM6Ly93d3cuemVuaGVhcnRjZW50ZXIuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=76602e701e3f3a2efe4cb134e60b55d1d7a9c83c581e5087a52a4ecc4f38fa50JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a1fa668-9d4d-6610-2ee3-b1899ccf6723&amp;u=a1aHR0cHM6Ly93d3cud2VsbG5lc3MuY29tL3doYXQtaXMtd2VsbG5lc3M&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1d1f956a8da176c5cea2a4cfe0c1efe20647d0eafeb15514336a6e6dd78b6c35JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a1fa668-9d4d-6610-2ee3-b1899ccf6723&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vc2VhcmNoP2ZpbmRfZGVzYz1XZWxsbmVzcytDZW50ZXImZmluZF9sb2M9Qm90aGVsbCUyQytXQSZtc29ja2lkPTJhMWZhNjY4OWQ0ZDY2MTAyZWUzYjE4OTljY2Y2NzIz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=960def06a544f8bbfd3f7bed9e55fc8e09a8184f8282d0d17754d272065c4f73JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a1fa668-9d4d-6610-2ee3-b1899ccf6723&amp;u=a1aHR0cHM6Ly93d3cuZnJleXdlbGxuZXNzLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=12d75af221d8c0eb9aab0ba31a64c15a66071ae49a9c6e17fbe96d8c73936457JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a1fa668-9d4d-6610-2ee3-b1899ccf6723&amp;u=a1aHR0cHM6Ly9pc21oZWFsdGgub3JnLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6aa7e6f0797a0af060d137946b02c3bc1399e1c35777305c8278ecb7b96a0e61JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36a2d650-5587-6816-1a09-c1b15458691e&amp;u=a1aHR0cHM6Ly93d3cuc2V2YWRzbS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c5214ce0e395aa837028bafb043c6ef0bd83f99d1ed2ab2658df824bde935a14JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36a2d650-5587-6816-1a09-c1b15458691e&amp;u=a1aHR0cHM6Ly9pbm5vdmF0aXZlLWNvdW5zZWxpbmcub3JnLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=35bf338f4591551e984fe9d3f7171639c1b88e61a218520acd08e23e572a3a61JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36a2d650-5587-6816-1a09-c1b15458691e&amp;u=a1aHR0cHM6Ly9taW5kc3Bpcml0Y2VudGVyLm9yZy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e1f41d7499712a1901d23cc4b04f8d663625ae37199f5ff20529f1501bdf3069JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36a2d650-5587-6816-1a09-c1b15458691e&amp;u=a1aHR0cHM6Ly93d3cuZ3JlZW5jb3Vuc2VsaW5nc2VydmljZS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6982980e8cd120ea33ecd4d3658b80bec5a2125b9c6abbdb799c2bbc7384e86dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36a2d650-5587-6816-1a09-c1b15458691e&amp;u=a1aHR0cHM6Ly9tb3NhaWNmYW1pbHlpbmMuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=07424e6187b5018f78e139c24f3c813967913a5c744c8be489c698b7a944aef1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36a2d650-5587-6816-1a09-c1b15458691e&amp;u=a1aHR0cHM6Ly9mYW1pbHlsZWdhY3ljb3Vuc2VsaW5nLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dd0980fa1a1b283ccaa321cc97601539c1ae58724db69593bf7e4ac7469f37edJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36a2d650-5587-6816-1a09-c1b15458691e&amp;u=a1aHR0cHM6Ly93d3cub3BlbmNvdW5zZWxpbmcuY29tL2lvd2EvZGVzLW1vaW5lcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c3bec96aa86d0c8f71ac150783410ae4f3af9dadfd3da6d34e58e0f4a89477c1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36a2d650-5587-6816-1a09-c1b15458691e&amp;u=a1aHR0cHM6Ly90dXJuaW5ncG9pbnRjb3Vuc2VsaW5nZHNtLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=866ef26494037189fbe4907577ef3673e58440344d71168ab2fc2d4af863981fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36a2d650-5587-6816-1a09-c1b15458691e&amp;u=a1aHR0cHM6Ly9uZXdsaWZlLWNvdW5zZWxpbmcuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e657e8825ab573fe99cf1773c8f125318e0a87a6e9ca47eec1e99f57cfe7a65dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=36a2d650-5587-6816-1a09-c1b15458691e&amp;u=a1aHR0cHM6Ly93d3cucHN5Y2hvbG9neXRvZGF5LmNvbS91cy90aGVyYXBpc3RzL2lhL2Rlcy1tb2luZXM_bXNvY2tpZD0zNmEyZDY1MDU1ODc2ODE2MWEwOWMxYjE1NDU4NjkxZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e0bca3a2a84dace55e674c3bd34f90b73b053baa5d15f60224cdb91135d45c82JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39cd9a92-41f0-6818-0a9a-8d73407269f1&amp;u=a1aHR0cHM6Ly9yZWNvdmVyeS5jb20vbG9zLWFuZ2VsZXMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=df7899950fa6c65ceeb4453eddb08de4518d15fd7e9632a3cf40898cd3d91a4bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39cd9a92-41f0-6818-0a9a-8d73407269f1&amp;u=a1aHR0cHM6Ly93d3cuYWRkaWN0ZWQub3JnL2xvcy1hbmdlbGVzLWFkZGljdGlvbi1zZXJ2aWNlcy5odG1s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dcd07ac78036b821aafdea71d99bfb4d00bcbb866c4eb3a790a8f73a6e05150aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39cd9a92-41f0-6818-0a9a-8d73407269f1&amp;u=a1aHR0cHM6Ly9tZWRsaW5lcGx1cy5nb3YvcmVoYWJpbGl0YXRpb24uaHRtbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4e6aa711dc046cc3835df7c75da9cbf4ad490ee0d1f985d8c33926d8bd82262dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39cd9a92-41f0-6818-0a9a-8d73407269f1&amp;u=a1aHR0cHM6Ly93d3cuYWRkaWN0aW9ucmVzb3VyY2UubmV0L2Jlc3QtZHJ1Zy1yZWhhYi1jZW50ZXJzL2NhbGlmb3JuaWEvbG9zLWFuZ2VsZXMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0cf2f24043f47b404a33fed951b334288a1bba178efd2e5767f55d1fd44bbb76JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39cd9a92-41f0-6818-0a9a-8d73407269f1&amp;u=a1aHR0cHM6Ly93d3cuY2FsaWZvcm5pYXJlaGFiaW5zdGl0dXRlLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3cc3b626c8b5ba3bccfdf5e80fe5301dfe7ddb3baa64b8fc260670fcc88504ccJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39cd9a92-41f0-6818-0a9a-8d73407269f1&amp;u=a1aHR0cHM6Ly93d3cuYWRkaWN0ZWQub3JnL3JlaGFicy9jYWxpZm9ybmlhL2xvcy1hbmdlbGVzLWNvdW50eS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e08887f93d790c12c26fe33123905274ef7702f7ce25497d3c30889858f9d1f9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39cd9a92-41f0-6818-0a9a-8d73407269f1&amp;u=a1aHR0cHM6Ly93d3cud2hvLmludC9uZXdzLXJvb20vZmFjdC1zaGVldHMvZGV0YWlsL3JlaGFiaWxpdGF0aW9u&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=43182c9395f2bcb466ba465d0ee17f28487e29aefe2893b6ffc5ae494ca72676JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1596bb5f-606c-635b-2471-acbe61ef62bf&amp;u=a1aHR0cHM6Ly93d3cuZGhjcy5jYS5nb3YvbWVkaS1jYWwv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f93be6b7cbebc5a5af7ea3c1edacb4109b268057774fab7e6dff3b74f1e53502JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1596bb5f-606c-635b-2471-acbe61ef62bf&amp;u=a1aHR0cHM6Ly93d3cuZGhjcy5jYS5nb3YvTWVkaS1DYWwvUGFnZXMvY29udGFjdC5hc3B4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5dc8dbd65232dd75aad98303d3ccb0bac7dac860f30a0fc3eda6b73029db5b23JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1596bb5f-606c-635b-2471-acbe61ef62bf&amp;u=a1aHR0cHM6Ly9iZW5lZml0c2NhbC5jb20vSGVscC9wcm9ncmFtL21lZGljYWwvSENQREU_bGFuZz1lbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1fd67cad0b133688b302e91e6e0f755301252863e9731120df3202f9680ecd41JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1596bb5f-606c-635b-2471-acbe61ef62bf&amp;u=a1aHR0cHM6Ly93d3cubGFjYXJlLm9yZy9oZWFsdGgtcGxhbnMvbWVkaS1jYWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=55e5ff41ac1375d94775793a39d698d2266c32b56031a2e649dcaf940ba37fcaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1596bb5f-606c-635b-2471-acbe61ef62bf&amp;u=a1aHR0cHM6Ly9kcHNzLmxhY291bnR5Lmdvdi9lbi9oZWFsdGguaHRtbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=94908f8d782e6e801811135932bed8a70ec851bdb420bbe8863db081f8327b2eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1596bb5f-606c-635b-2471-acbe61ef62bf&amp;u=a1aHR0cHM6Ly93d3cuaGVhbHRoY2FyZW9wdGlvbnMuZGhjcy5jYS5nb3YvZW4vZmluZC1wcm92aWRlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6ab2deab09f8cd03c2791ad313221ef0a2310d63e7d5f2a47f4c31e7c68fa4acJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1596bb5f-606c-635b-2471-acbe61ef62bf&amp;u=a1aHR0cHM6Ly93d3cuY2EuZ292L2RlcGFydG1lbnRzLzIxNy9zZXJ2aWNlcy8zNy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ab318e9d781007ce6e07bad5905731b234877cece73c645332abb4df26baf462JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1596bb5f-606c-635b-2471-acbe61ef62bf&amp;u=a1aHR0cHM6Ly9tZS5sYWNvdW50eS5nb3Yv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d4cf901e7f00bb642402ffd8d943b43c26e4a37fbd86eedde9c6e41f5bd80f8bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1596bb5f-606c-635b-2471-acbe61ef62bf&amp;u=a1aHR0cHM6Ly9tY3dlYi5hcHBzLnByZC5jYW1taXMubWVkaS1jYWwuY2EuZ292L2NvbnRhY3Q&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=509e97c67b15c5b18ab1b12e225156fb3f047e40ab2043bac0620beadf4c51e4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1596bb5f-606c-635b-2471-acbe61ef62bf&amp;u=a1aHR0cHM6Ly93d3cuYmx1ZXNoaWVsZGNhLmNvbS9lbi9ic3Avb3VyLXBsYW5zL21lZGktY2Fs&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b0be93d46bf06d2a6efb42ed8d6dd182a36547b76a596c81b9c306ba310d93efJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e85790c-ff6e-63c0-237d-6eedfe936204&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ29tbXVuaXR5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=89ebaac6270ca1dd8c14bc0e4cabd7827f6a5fca2f28122e3ddc75e7c74f3bedJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e85790c-ff6e-63c0-237d-6eedfe936204&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2NvbW11bml0eQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=327a9888bd8d3a384b1bb6359a459274af93fce1d392b741e54341d24ff09017JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e85790c-ff6e-63c0-237d-6eedfe936204&amp;u=a1aHR0cHM6Ly93d3cuc3RwZXRlLm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d5911cefcbf2308e99a978f1a17086c46faa3ceb20710d46bfb282b71018cdcbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e85790c-ff6e-63c0-237d-6eedfe936204&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ29tbXVuaXR5XyhUVl9zZXJpZXMp&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4b9ad3a5a6e57674fabf486db36d265c57713b922ee946ced62a1c12e1dc4705JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e85790c-ff6e-63c0-237d-6eedfe936204&amp;u=a1aHR0cHM6Ly93d3cuc3RwZXRlLm9yZy92aXNpdG9ycy9sZ2J0cV9jb21tdW5pdHkucGhw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d4007e99f3a3fce01c2b5f4415bb718e8dabe6a809bd1fac2ad0f91746c36916JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e85790c-ff6e-63c0-237d-6eedfe936204&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQxNDM5NjI5Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=47b1071a091c81c2aae8a2283750b4cb34e87ce379cd62db0d19ab56bbbd876dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e85790c-ff6e-63c0-237d-6eedfe936204&amp;u=a1aHR0cHM6Ly9wdXJlc29jaW9sb2d5LmNvbS93aGF0LWlzLWNvbW11bml0eS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=54f295106643f3cb3645df9d7a5e17fef9ad0538fda0f4fc77e02fa0f768b3baJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e85790c-ff6e-63c0-237d-6eedfe936204&amp;u=a1aHR0cHM6Ly93d3cuemlsbG93LmNvbS9zYWludC1wZXRlcnNidXJnLWZsLzU1LWNvbW11bml0eS8_bXNvY2tpZD0wZTg1NzkwY2ZmNmU2M2MwMjM3ZDZlZWRmZTkzNjIwNA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ac759ddccecbe412fa0b072a239ac4dca39c42e2ae6a5f9e80a9fd4edb43b9c5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e85790c-ff6e-63c0-237d-6eedfe936204&amp;u=a1aHR0cHM6Ly93d3cuemlsbG93LmNvbS9zYWludC1wZXRlcnNidXJnLWZsLzU1cGx1cy1jb21tdW5pdHlfYXR0Lz9tc29ja2lkPTBlODU3OTBjZmY2ZTYzYzAyMzdkNmVlZGZlOTM2MjA0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=adf5d90cc4974ae5ab2c2ca674329352879a483f67a497cfa8fd18f88a890817JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e85790c-ff6e-63c0-237d-6eedfe936204&amp;u=a1aHR0cHM6Ly9oYXJib3JsaWdodHNjbHViLmNvbS9jb21tdW5pdHkv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8ceef4564720b083d3a67ac4907ef33aed16dda9cd6310c13c1e6c374aa6b819JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c27881a-f5e5-6c21-1016-9ffbf4016d86&amp;u=a1aHR0cHM6Ly93d3cubGFrZXJpZGdlc2VuaW9yLm9yZy9yZXNpZGVudGlhbC1ob3NwaWNlLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0f0d2b8e073ed42cc6868048977999db7df6473a344cf7d47355ab67dfe587e2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c27881a-f5e5-6c21-1016-9ffbf4016d86&amp;u=a1aHR0cHM6Ly9ob3NwaWNlZm91bmRhdGlvbi5vcmcvd2hhdC1pcy1ob3NwaWNlLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=463763c23646d781dbd06bf2cfc055cafb9cb89c3b64160fe1497b293e522fdfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c27881a-f5e5-6c21-1016-9ffbf4016d86&amp;u=a1aHR0cHM6Ly93d3cudHJpbml0aWNhcmluZy5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=42015828bd753ab037e07ec6ebdcadb4eb1af97365832b886bc751f2c3d5038dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c27881a-f5e5-6c21-1016-9ffbf4016d86&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhcmUuZ292L2NvdmVyYWdlL2hvc3BpY2UtY2FyZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fc9e2aaa67352f92f1069db7e4b7d88df5478c786dfae036c39f28c990f6583eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c27881a-f5e5-6c21-1016-9ffbf4016d86&amp;u=a1aHR0cHM6Ly93d3cubmlhLm5paC5nb3YvaGVhbHRoL2hvc3BpY2UtYW5kLXBhbGxpYXRpdmUtY2FyZS9mcmVxdWVudGx5LWFza2VkLXF1ZXN0aW9ucy1hYm91dC1ob3NwaWNlLWNhcmU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ea313d14b67355adc44aa4cabbf762d18ed1c1e07b9e6405dc372a482227983eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c27881a-f5e5-6c21-1016-9ffbf4016d86&amp;u=a1aHR0cHM6Ly93d3cuc2VuaW9yYWR2aWNlLmNvbS9ob3NwaWNlL2J1ZmZhbG8tbW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=229c7565b8a3f7ee9b33a6200550d1405de83075c7b2dd362911a12a4b766c24JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c27881a-f5e5-6c21-1016-9ffbf4016d86&amp;u=a1aHR0cHM6Ly93d3cudHJpbml0aWNhcmluZy5vcmcvc2VydmljZS1hcmVhL2J1ZmZhbG8tbW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=39c42e6ab74d83b947722d59b242c7266f17fbba91c94f3da719d1bf4da9d8cbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c27881a-f5e5-6c21-1016-9ffbf4016d86&amp;u=a1aHR0cHM6Ly9tbi5nb3YvYWRyZXNvdXJjZXMvc2VhcmNoLzlmMDFjYTBhLTU3NzItNWY1MS05MDVjLWY4NmFkM2RhMGI4NS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4069d0c775dfbb544f659e19a1cbc6a11bed79d048bff26774b576e053608293JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c27881a-f5e5-6c21-1016-9ffbf4016d86&amp;u=a1aHR0cHM6Ly93d3cubWF5b2NsaW5pYy5vcmcvZGVwYXJ0bWVudHMtY2VudGVycy9ob3NwaWNlL3NlY3Rpb25zL292ZXJ2aWV3L292Yy0yMDQ4MTc0NQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ac2d7e2f54831db2b3bc27eac59b0815627e5ab1bfb8008ddcd409dd25c3da3dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c27881a-f5e5-6c21-1016-9ffbf4016d86&amp;u=a1aHR0cHM6Ly9taW5uZXNvdGFob3NwaWNlLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5bd68c310def160cfc4316928712222604c84fc537ed83fbc7262edb86307923JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=399161c5-4a15-6afd-3a37-76244be86bab&amp;u=a1aHR0cHM6Ly93d3cuaWNpYmEuY29tL3dvcmQ_dz1tZW50YWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d23b9bc92d67209efd7da8aacad63511748cd4ea51539ccdce27ee81f8407efbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=399161c5-4a15-6afd-3a37-76244be86bab&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvemhzLyVFOCVBRiU4RCVFNSU4NSVCOC8lRTglOEIlQjElRTglQUYlQUQtJUU2JUIxJTg5JUU4JUFGJUFELSVFNyVBRSU4MCVFNCVCRCU5My9tZW50YWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=40ef0a6d7ff1e5999cadfdc0d0ebe87f03e7e48de1cadcdcae2e45b7002bdfb0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=399161c5-4a15-6afd-3a37-76244be86bab&amp;u=a1aHR0cHM6Ly9iYWlrZS5iYWlkdS5jb20vaXRlbS9tZW50YWwvMjI1NTczMA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d9ddd7f5f4e23334bee49caabdd3501050149a498cd243dd09167f8a37318295JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=399161c5-4a15-6afd-3a37-76244be86bab&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWVudGFsX2hlYWx0aA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=59f81c52c946dd884947b36986036e1bda38e9806a2dc6ebe2ed65f9ced50f80JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=399161c5-4a15-6afd-3a37-76244be86bab&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L21lbnRhbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bd8573c0aef449c92734cd196c04fd76a58aef954c2f876eabce44cd9f2f2b0aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=399161c5-4a15-6afd-3a37-76244be86bab&amp;u=a1aHR0cHM6Ly93d3cud2hvLmludC9uZXdzLXJvb20vZmFjdC1zaGVldHMvZGV0YWlsL21lbnRhbC1kaXNvcmRlcnM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=206602d22ecae890fbc9e6ceacccd7af9d2ff0d96d30d8ae0a8e5a244fa50525JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=399161c5-4a15-6afd-3a37-76244be86bab&amp;u=a1aHR0cHM6Ly93d3cuY2RjLmdvdi9tZW50YWwtaGVhbHRoL2Fib3V0L2luZGV4Lmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2ce99489e17e22af7e79e464cad638bbd2557138adbdb7cace04091fc02f2b5bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=399161c5-4a15-6afd-3a37-76244be86bab&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvemhzLyVFOCVBRiU4RCVFNSU4NSVCOC8lRTglOEIlQjElRTglQUYlQUQvbWVudGFs&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=52cd178fa9168c6af9c7b1f98566877a4cae9cbeee50147e430e103f87b8ffe6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=399161c5-4a15-6afd-3a37-76244be86bab&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWVudGFsX2Rpc29yZGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=73a9132cf39da045febf0692dad183a539d9e5e2137d021821e93d29ca9eb76eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=399161c5-4a15-6afd-3a37-76244be86bab&amp;u=a1aHR0cHM6Ly93d3cuY29sbGluc2RpY3Rpb25hcnkuY29tL3poL2RpY3Rpb25hcnkvZW5nbGlzaC9tZW50YWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=22a61c7594e91d72136aec5d41afa9403573e5ca0677fb66267c24a73c25f87bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d8ae9ba-30c6-6f76-0c1d-fe5b31fd6e94&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvSGVhbHRo&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=12990d1fdf3125396a2be8089174765c020578e327e21f405789bd0caf442322JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d8ae9ba-30c6-6f76-0c1d-fe5b31fd6e94&amp;u=a1aHR0cHM6Ly93d3cuaGVhbHRoLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0c3347d6a4f2bd9fcaf78990f84724f8a7f858936aa376e47c2dccc7302de5e6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d8ae9ba-30c6-6f76-0c1d-fe5b31fd6e94&amp;u=a1aHR0cHM6Ly93d3cubGRoLmxhLmdvdi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8f7c332d53e2a1e27924f72dc94dc9609aa8cf006d13a4d595d5536009cfe0d3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d8ae9ba-30c6-6f76-0c1d-fe5b31fd6e94&amp;u=a1aHR0cHM6Ly93d3cud2VibWQuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a6908ddd21b286a03dc674c34f933032e43658b8831e7be51088dcea97ab75b0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d8ae9ba-30c6-6f76-0c1d-fe5b31fd6e94&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvaGVhbHRo&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=162913294e8a3b230c92a1153380ffc097d6ee670658be2d359fb99e71d37623JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d8ae9ba-30c6-6f76-0c1d-fe5b31fd6e94&amp;u=a1aHR0cHM6Ly9ub2xhLmdvdi9uZXh0L2hlYWx0aC9ob21lLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1f1b9eba485e1c9bb194d964b2d35d3bcf2107c07e3560b5ffe1c43a8f23dcebJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d8ae9ba-30c6-6f76-0c1d-fe5b31fd6e94&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhbG5ld3N0b2RheS5jb20vYXJ0aWNsZXMvMTUwOTk5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=75002b831c3b39e662f51f8b5d9e3028669ec1503a18cc8c74e0cf002b348ca2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d8ae9ba-30c6-6f76-0c1d-fe5b31fd6e94&amp;u=a1aHR0cHM6Ly93d3cuaGVhbHRobGluZS5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4cb91124dc1bc5c81c848c2cfcad2ee17868738feb85cdd96ae05fb77ec95a9cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d8ae9ba-30c6-6f76-0c1d-fe5b31fd6e94&amp;u=a1aHR0cHM6Ly93d3cubmloLmdvdi9oZWFsdGgtaW5mb3JtYXRpb24&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6ac5ea6c36456e4eb0816543f95e1047db2c7ee7ef6f2c57e7f3b75d03a75063JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d8ae9ba-30c6-6f76-0c1d-fe5b31fd6e94&amp;u=a1aHR0cHM6Ly93d3cubGNtY2hlYWx0aC5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=34189794a805fc5dd5fa3e421f589a886d893a644252bcefb1e1586500c6874aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3508206e-74af-6795-283c-378f75b766d8&amp;u=a1aHR0cHM6Ly93d3cucHJpbWFyeS5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=623c9f711030f6377f99095cb3e5898a065a4441b879d8ed0c9e9c42944a84b1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3508206e-74af-6795-283c-378f75b766d8&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3ByaW1hcnk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4feb8c4f16a4ae297f5b5103782bbf96be830e9590e531b9f27976b05caade05JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3508206e-74af-6795-283c-378f75b766d8&amp;u=a1aHR0cHM6Ly93d3cucHJpbWFyeWdhbWVzLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=14c30325b8be5927e6e99c0034cdfda9832568eb05319fef9818f21c2289a36fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3508206e-74af-6795-283c-378f75b766d8&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3ByaW1hcnk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b67ca16cbcb011f77bae1c44c6e591d97d3d28b23b172e0319ac99e1a28cdac9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3508206e-74af-6795-283c-378f75b766d8&amp;u=a1aHR0cHM6Ly90aGVwcmltYXJ5LmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b09737362a666c2a0a4cd1c2b2e0621a587e83bc00dcd35b24af6f781717e159JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3508206e-74af-6795-283c-378f75b766d8&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL3ByaW1hcnk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=171ee8f594d9480355b2cbb892289c2d649d005c89aff0c9511f9a385a08607eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3508206e-74af-6795-283c-378f75b766d8&amp;u=a1aHR0cHM6Ly93d3cubmJjbmV3cy5jb20vcG9saXRpY3MvMjAyNi1wcmltYXJ5LWVsZWN0aW9ucy9uYXRpb25hbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3529d2881c35b66a584d1fe763dce23c70a4fba8b4d419f6e0c1738f51d675b4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3508206e-74af-6795-283c-378f75b766d8&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3ByaW1hcnk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=729e6e72cd077ae7870f1ff8feb226158e4e501bcb842cbf99f341201e5d35acJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3508206e-74af-6795-283c-378f75b766d8&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9wcmltYXJ5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=20ae8dbecf1e4b84dfccd7533430da1095471c0a2acde40b14c24c48ac1845a4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3508206e-74af-6795-283c-378f75b766d8&amp;u=a1aHR0cHM6Ly90aGVtaWR0ZXJtcHJvamVjdC5vcmcvcmVzdWx0cy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=09217a3bdcb63398f8c4792e7323c7b126d9474f86e84afb5047372bfdb68b62JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c97744b-6de7-612c-3e12-63aa6cb26065&amp;u=a1aHR0cHM6Ly93d3cuc2FjcmVkam91cm5leXN3ZWxsbmVzc2NlbnRlci5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1cc5d2d5036ccedc7a7362ae14e182aad51bf563dd7c8299f60621d8b10b9689JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c97744b-6de7-612c-3e12-63aa6cb26065&amp;u=a1aHR0cHM6Ly9nbG9iYWx3ZWxsbmVzc2luc3RpdHV0ZS5vcmcvd2hhdC1pcy13ZWxsbmVzcy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=451081d88f09901f00d5c46336b71adfb9b738c6b3d94e904ef12c707aec2783JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c97744b-6de7-612c-3e12-63aa6cb26065&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vYml6L3RyYW5zaXRpb25zLWNvdW5zZWxpbmctYW5kLXdlbGxuZXNzLWJyb29rdmlsbGU_bXNvY2tpZD0wYzk3NzQ0YjZkZTc2MTJjM2UxMjYzYWE2Y2IyNjA2NQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6c4d5312dad4dc523a349a81e35a31015c34dd2a621ab62f2efd71919f9ad23cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c97744b-6de7-612c-3e12-63aa6cb26065&amp;u=a1aHR0cHM6Ly93d3cud2VsbG5lc3MuY29tL3doYXQtaXMtd2VsbG5lc3M&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=34e79c5e72e2b73cccdb7626f4000bb9f909db01a43c1aa5ed7364d402708bb9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c97744b-6de7-612c-3e12-63aa6cb26065&amp;u=a1aHR0cHM6Ly93d3cucHN5Y2hvbG9neXRvZGF5LmNvbS91cy90aGVyYXBpc3RzL2pvZGktbHlubi1oYWxlLWJyb29rdmlsbGUtb2gvMzMzOTE0P21zb2NraWQ9MGM5Nzc0NGI2ZGU3NjEyYzNlMTI2M2FhNmNiMjYwNjU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9edf0e10fb00660c68050d3236bc6240f19b2bd0ced4a33de14d3938331b3b35JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c97744b-6de7-612c-3e12-63aa6cb26065&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhcmVsaXN0LmNvbS9tZW50YWwtaGVhbHRoL3RyYW5zaXRpb25zLWNvdW5zZWxpbmctYW5kLXdlbGxuZXNzLWJyb29rdmlsbGUtb2gv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=139bd85d3fa0b459fe938cba57849a458b3ea78a9488a0adf1e255d07a615736JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c97744b-6de7-612c-3e12-63aa6cb26065&amp;u=a1aHR0cHM6Ly93d3cuc2FjcmVkam91cm5leXN3ZWxsbmVzc2NlbnRlci5jb20vY29udGFjdA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a93a159603d99b56b298680cfba0b42bfc99782c9b602815391d488f6c9a50a5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c97744b-6de7-612c-3e12-63aa6cb26065&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvV2VsbG5lc3NfKGFsdGVybmF0aXZlX21lZGljaW5lKQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=36193181967a82641a27002df46b5959406c4a1aeb5cbddb2f9e13d8255d4871JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c97744b-6de7-612c-3e12-63aa6cb26065&amp;u=a1aHR0cHM6Ly9yZXZpZXdzLmJpcmRleWUuY29tL2Qvd2VsbG5lc3MvYnJvb2t2aWxsZS1vaC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=695fca37e811c924d28d61d6f5873cf37f45d259adc50b46876014d556e65556JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c97744b-6de7-612c-3e12-63aa6cb26065&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL1NhY3JlZEpvdXJuZXlzV2VsbG5lc3NDZW50ZXIv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=077bab3cc0d7a0aabb407dedab233ba4c0e803bc7a8d4ad5eb59dae07b167eccJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07453988-109c-6f97-3d5f-2e69113b6e23&amp;u=a1aHR0cHM6Ly9oZWFsdGhzb2x1dGlvbnN3ZXN0Lm9yZy9jcmFpZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=096a623db6feabf8b1dfe067e8f29078a94aaa09fde21174e8ed5fe2bfff849aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07453988-109c-6f97-3d5f-2e69113b6e23&amp;u=a1aHR0cHM6Ly93d3cucHN5Y2hvbG9neXRvZGF5LmNvbS91cy90aGVyYXBpc3RzL2NvL2NyYWlnP21zb2NraWQ9MDc0NTM5ODgxMDljNmY5NzNkNWYyZTY5MTEzYjZlMjM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c2068b2da3848bb19cea474217ecf26a6563b2600624d174e7b756b49fed2fdaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07453988-109c-6f97-3d5f-2e69113b6e23&amp;u=a1aHR0cHM6Ly93d3cucHN5Y2hvbG9neXRvZGF5LmNvbS91cy90aGVyYXBpc3RzL2NvL2NyYWlnP2NhdGVnb3J5PW1hcnJpYWdlLWNvdW5zZWxpbmcmbXNvY2tpZD0wNzQ1Mzk4ODEwOWM2Zjk3M2Q1ZjJlNjkxMTNiNmUyMw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=70471ad6273e22e526b00dbeea38f61411b449d32c18daf9c97c54f5b4b3258aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07453988-109c-6f97-3d5f-2e69113b6e23&amp;u=a1aHR0cHM6Ly9zb2x2aW5nc3VkdG9nZXRoZXIub3JnL3RoZXJhcGlzdC9zdGV2ZW4tcC13YWxscy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4a39eb6a73f84ea61e46cd06a2d3225e1f32543cf04a83673a2d05e437eacc87JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07453988-109c-6f97-3d5f-2e69113b6e23&amp;u=a1aHR0cDovL2FzY291bnNlbC5jb20vYWJvdXQuaHRtbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=57371535ffb27b4db1818ae2eeee0a5e5a82fb639e4b67a1daf5790acaf01d49JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07453988-109c-6f97-3d5f-2e69113b6e23&amp;u=a1aHR0cHM6Ly93d3cuaGVhbHRoZ3JhZGVzLmNvbS9jb3Vuc2VsaW5nLWRpcmVjdG9yeS9jby1jb2xvcmFkby9jcmFpZw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e016679014ea79010592a17186748fe79ef5a10cc875ce2276612f43631339a2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07453988-109c-6f97-3d5f-2e69113b6e23&amp;u=a1aHR0cHM6Ly9tZW1vcmlhbHJlZ2lvbmFsaGVhbHRoLmNvbS9oZWFsdGhjYXJlLXNlcnZpY2VzL2JlaGF2aW9yYWwtaGVhbHRoLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=27bbd4d8862db1397bbec5e8b3c61c6b547b7100833b0a2b3ef8caca150b9bf0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07453988-109c-6f97-3d5f-2e69113b6e23&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL0FhbmRTY291bnNlbGluZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bec669f1a9e1d0751cfbba625e22a4ad35650f33935b51f0c95d18901e3a73e7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07453988-109c-6f97-3d5f-2e69113b6e23&amp;u=a1aHR0cHM6Ly9wb3NpdGl2ZXBzeWNob2xvZ3kuY29tL2NvdW5zZWxpbmctcHJvY2Vzcy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c2fbc1cb584fc828d028a29dca746f62c3ded25302cfb7c4f8630d050bfe2963JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07453988-109c-6f97-3d5f-2e69113b6e23&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ291bnNlbGluZ19wc3ljaG9sb2d5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e59d3a32b8f955edcfeaf246ee854e4af1677311e70e7c40348581a837f586e5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=341de43b-cfc2-6d91-2347-f3dacea06c5d&amp;u=a1aHR0cHM6Ly9tZWRsaW5lcGx1cy5nb3YvcmVoYWJpbGl0YXRpb24uaHRtbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=820d05f5687377f9ce1ff672f1c539ce167662f55e8889689d97e1aacadb3b34JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=341de43b-cfc2-6d91-2347-f3dacea06c5d&amp;u=a1aHR0cHM6Ly93d3cuYmVhY29uaGVhbHRoc3lzdGVtLm9yZy9pbnBhdGllbnQtcmVoYWJpbGl0YXRpb24v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=95fda1072a6680bd6697cf5f1e5b849db34386e5a819ed183da8c4163f7115a7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=341de43b-cfc2-6d91-2347-f3dacea06c5d&amp;u=a1aHR0cHM6Ly93d3cuYWRkaWN0ZWQub3JnL3JlaGFicy9pbmRpYW5hL2Vsa2hhcnQv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9d598765f4a888fe3c0263a44c3d767dc53b681aee9453fba08b2e459f9a27daJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=341de43b-cfc2-6d91-2347-f3dacea06c5d&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vc2VhcmNoP2NmbHQ9cmVoYWJpbGl0YXRpb25fY2VudGVyJmZpbmRfbG9jPUVsa2hhcnQlMkMrSU4mbXNvY2tpZD0zNDFkZTQzYmNmYzI2ZDkxMjM0N2YzZGFjZWEwNmM1ZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=944497d17b38025da8381e254a7c630df95b840783ca9428d5a2ebdeb9159f50JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=341de43b-cfc2-6d91-2347-f3dacea06c5d&amp;u=a1aHR0cHM6Ly9odWJiYXJkaGlsbC5vcmcvbGl2aW5nLW9wdGlvbnMvcmVoYWJpbGl0YXRpb24tYW5kLWhlYWx0aGNhcmUv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=60abe7ac67389579610a078920160d10f737e1e28f14dd3f1aa4f22f70abb6d7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=341de43b-cfc2-6d91-2347-f3dacea06c5d&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vc2VhcmNoP2ZpbmRfZGVzYz1SZWhhYmlsaXRhdGlvbiZmaW5kX2xvYz1FbGtoYXJ0JTJDK0lOJm1zb2NraWQ9MzQxZGU0M2JjZmMyNmQ5MTIzNDdmM2RhY2VhMDZjNWQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=528b4b41321bfb9f312c52bf49c67dcb538b5302adf487017b4543953653ff71JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=341de43b-cfc2-6d91-2347-f3dacea06c5d&amp;u=a1aHR0cHM6Ly93d3cuYmVhY29uaGVhbHRoc3lzdGVtLm9yZy9yZWhhYmlsaXRhdGlvbi1zZXJ2aWNlcy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0181131e361816e4120d25be2cc477e3e998359f0550d3187e8ca367c15cb9cbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=341de43b-cfc2-6d91-2347-f3dacea06c5d&amp;u=a1aHR0cHM6Ly93d3cuZmluZGhlYWx0aGNsaW5pY3Mub3JnL1VTL0Vsa2hhcnQvNDczNDY5NjY2NDc2ODI3L0Vsa2hhcnQtR2VuZXJhbC1Ib3NwaXRhbC1JbnBhdGllbnQtUmVoYWJpbGl0YXRpb24tU2VydmljZXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=01d0e29b020cffb1cd09874d845ad2c626bdfdff612519d3589321710b648869JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=341de43b-cfc2-6d91-2347-f3dacea06c5d&amp;u=a1aHR0cHM6Ly93d3cuaW4uZ292L2Zzc2EvZGRhcnMvYnJzL3ZvY2F0aW9uYWwtcmVoYWJpbGl0YXRpb24tZW1wbG95bWVudC92b2NhdGlvbmFsLXJlaGFiaWxpdGF0aW9uLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9e079122e6d3c7b39d9a1aa393836e6ca9bd084a2c15a3073a5401e56ac89f6eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=341de43b-cfc2-6d91-2347-f3dacea06c5d&amp;u=a1aHR0cHM6Ly93d3cuYXNjY2FyZS5jb20vY29tbXVuaXR5L2Vhc3QtbGFrZS1udXJzaW5nLXJlaGFiaWxpdGF0aW9uLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ddcae38c38a23db1209820ef180cc04b37345b5594314c4f6e180834f65ecb4bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=299a34ab-20a8-607b-30a6-234a21206167&amp;u=a1aHR0cHM6Ly93d3cuZmVudG9ubWVkaWNhbC5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a905c34f68c942fcbc0c1efbb3c12e17c9c3ac529854f3037a8f9caee1226943JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=299a34ab-20a8-607b-30a6-234a21206167&amp;u=a1aHR0cHM6Ly93d3cud2VibWQuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5d112170aac895027a3839d506c7c965133ef29fce28d6d1571f1bb367e22b96JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=299a34ab-20a8-607b-30a6-234a21206167&amp;u=a1aHR0cHM6Ly93d3cubWNsYXJlbi5vcmcvZmVudG9uL21jbGFyZW4tZmVudG9uLWhvbWU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b4dd33aae71aa6eacc880a02395b938414794ccfb1fbdc0088921367b21946c8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=299a34ab-20a8-607b-30a6-234a21206167&amp;u=a1aHR0cHM6Ly93d3cuZmVudG9ubWVkaWNhbC5jb20vcGF0aWVudHBvcnRhbC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4c41cfe60930c5cea78c6639137f29fabef0f573e5c4e97b5260e9ae7fe08692JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=299a34ab-20a8-607b-30a6-234a21206167&amp;u=a1aHR0cHM6Ly93d3cubWNsYXJlbi5vcmcvbWFpbi9sb2NhdGlvbnMvbWNsYXJlbi1mbGludC1mZW50b24tZmFtaWx5LW1lZGljaW5lLTEzNDU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=73fe4f807e17180db1599790f821b575c670889d161a8eed62823647d3653ad3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=299a34ab-20a8-607b-30a6-234a21206167&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWVkaWNpbmU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cb05358d82ac68a3fea39605b20c82f27f72e6af6b136dd44b96e079a1e9a0d5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=299a34ab-20a8-607b-30a6-234a21206167&amp;u=a1aHR0cHM6Ly93d3cucm1pcGMubmV0Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bac4b62c32f6b24038b4b78c4c7102b6cb8abfe2f4973f05342bf7058a044bf4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=299a34ab-20a8-607b-30a6-234a21206167&amp;u=a1aHR0cHM6Ly9oYXJ0bWVkaWNhbC5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dcdda2489633a568463fc4e8501b692e7d43426688e8c7f188b3adcc5e2dcaf4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=299a34ab-20a8-607b-30a6-234a21206167&amp;u=a1aHR0cHM6Ly93d3cuaGVhbHRoZ3JhZGVzLmNvbS9ncm91cC1kaXJlY3RvcnkvbWktbWljaGlnYW4vZmVudG9uL2ZlbnRvbi1tZWRpY2FsLWNlbnRlci14cnY4NXc&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=175ac8b9202a65d8c66ab3da707970143e7a10aef378cd8a44d217bc73b425b6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=299a34ab-20a8-607b-30a6-234a21206167&amp;u=a1aHR0cHM6Ly93d3cubWF5b2NsaW5pYy5vcmcvZGlzZWFzZXMtY29uZGl0aW9ucw&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>
@@ -916,7 +934,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H88"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -950,19 +968,19 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -970,19 +988,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G3" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -990,19 +1008,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G4" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H4" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1010,19 +1028,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G5" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H5" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1030,19 +1048,19 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G6" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H6" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1050,19 +1068,19 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G7" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H7" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1070,19 +1088,19 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G8" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H8" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1090,19 +1108,19 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G9" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H9" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1110,19 +1128,19 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G10" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H10" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1130,19 +1148,19 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G11" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H11" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1150,19 +1168,19 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G12" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H12" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1170,19 +1188,19 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G13" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H13" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1190,19 +1208,19 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G14" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H14" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1210,19 +1228,19 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G15" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H15" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1230,19 +1248,19 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G16" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H16" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1250,19 +1268,19 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G17" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H17" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1270,19 +1288,19 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G18" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H18" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1290,19 +1308,19 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G19" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H19" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1310,19 +1328,19 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C20" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G20" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H20" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1330,19 +1348,19 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C21" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G21" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H21" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1350,19 +1368,19 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C22" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G22" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H22" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1370,19 +1388,19 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C23" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G23" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H23" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1390,19 +1408,19 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G24" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H24" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1410,19 +1428,19 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C25" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G25" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H25" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1430,19 +1448,19 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C26" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G26" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H26" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1450,19 +1468,19 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C27" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G27" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H27" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1470,19 +1488,19 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C28" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G28" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H28" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1490,19 +1508,19 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G29" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H29" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1510,19 +1528,19 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C30" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G30" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H30" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1530,19 +1548,19 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C31" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G31" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H31" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1550,19 +1568,19 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C32" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G32" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H32" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1570,19 +1588,19 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C33" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G33" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H33" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1590,19 +1608,19 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C34" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G34" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H34" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1610,19 +1628,19 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C35" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G35" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H35" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1630,19 +1648,19 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C36" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G36" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H36" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1650,19 +1668,19 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C37" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G37" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H37" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1670,19 +1688,19 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C38" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="G38" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H38" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1690,19 +1708,19 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C39" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G39" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H39" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1710,19 +1728,19 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C40" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G40" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H40" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1730,19 +1748,19 @@
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C41" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G41" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H41" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1750,19 +1768,19 @@
         <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C42" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G42" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H42" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1770,19 +1788,19 @@
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C43" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G43" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H43" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1790,19 +1808,19 @@
         <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C44" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G44" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H44" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1810,19 +1828,19 @@
         <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C45" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G45" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H45" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1830,19 +1848,19 @@
         <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C46" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G46" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H46" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -1850,19 +1868,19 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C47" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G47" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H47" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -1870,19 +1888,19 @@
         <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C48" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G48" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H48" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -1890,19 +1908,19 @@
         <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C49" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="G49" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H49" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -1910,19 +1928,19 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C50" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="G50" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H50" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -1930,19 +1948,19 @@
         <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C51" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G51" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H51" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -1950,19 +1968,19 @@
         <v>58</v>
       </c>
       <c r="B52" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C52" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="G52" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H52" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -1970,19 +1988,19 @@
         <v>59</v>
       </c>
       <c r="B53" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C53" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G53" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H53" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -1990,19 +2008,19 @@
         <v>60</v>
       </c>
       <c r="B54" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C54" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G54" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H54" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -2010,19 +2028,19 @@
         <v>61</v>
       </c>
       <c r="B55" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C55" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G55" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H55" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -2030,19 +2048,19 @@
         <v>62</v>
       </c>
       <c r="B56" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C56" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G56" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H56" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -2050,19 +2068,19 @@
         <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C57" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G57" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H57" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -2070,19 +2088,19 @@
         <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C58" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="G58" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H58" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -2090,19 +2108,19 @@
         <v>65</v>
       </c>
       <c r="B59" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C59" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G59" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H59" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -2110,19 +2128,19 @@
         <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C60" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="G60" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H60" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2130,19 +2148,19 @@
         <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C61" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G61" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H61" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2150,19 +2168,19 @@
         <v>68</v>
       </c>
       <c r="B62" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C62" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="G62" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H62" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2170,19 +2188,19 @@
         <v>69</v>
       </c>
       <c r="B63" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C63" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="G63" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H63" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2190,19 +2208,19 @@
         <v>70</v>
       </c>
       <c r="B64" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C64" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="G64" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H64" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2210,19 +2228,19 @@
         <v>71</v>
       </c>
       <c r="B65" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C65" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="G65" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H65" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2230,19 +2248,19 @@
         <v>72</v>
       </c>
       <c r="B66" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C66" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G66" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H66" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2250,19 +2268,19 @@
         <v>73</v>
       </c>
       <c r="B67" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C67" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G67" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H67" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2270,19 +2288,19 @@
         <v>74</v>
       </c>
       <c r="B68" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C68" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="G68" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H68" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2290,19 +2308,19 @@
         <v>75</v>
       </c>
       <c r="B69" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C69" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="G69" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H69" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -2310,19 +2328,19 @@
         <v>76</v>
       </c>
       <c r="B70" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C70" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G70" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H70" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2330,19 +2348,19 @@
         <v>77</v>
       </c>
       <c r="B71" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C71" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G71" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H71" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -2350,19 +2368,19 @@
         <v>78</v>
       </c>
       <c r="B72" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C72" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G72" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H72" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -2370,19 +2388,19 @@
         <v>79</v>
       </c>
       <c r="B73" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C73" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="G73" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H73" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -2390,19 +2408,19 @@
         <v>80</v>
       </c>
       <c r="B74" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C74" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G74" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H74" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -2410,19 +2428,19 @@
         <v>81</v>
       </c>
       <c r="B75" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C75" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="G75" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H75" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -2430,19 +2448,19 @@
         <v>82</v>
       </c>
       <c r="B76" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C76" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G76" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H76" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -2450,19 +2468,19 @@
         <v>83</v>
       </c>
       <c r="B77" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C77" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="G77" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H77" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -2470,19 +2488,19 @@
         <v>84</v>
       </c>
       <c r="B78" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C78" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G78" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H78" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -2490,19 +2508,19 @@
         <v>85</v>
       </c>
       <c r="B79" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C79" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G79" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H79" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -2510,19 +2528,19 @@
         <v>86</v>
       </c>
       <c r="B80" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C80" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="G80" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H80" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -2530,19 +2548,19 @@
         <v>87</v>
       </c>
       <c r="B81" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C81" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G81" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H81" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -2550,19 +2568,19 @@
         <v>88</v>
       </c>
       <c r="B82" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C82" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="G82" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H82" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -2570,19 +2588,19 @@
         <v>89</v>
       </c>
       <c r="B83" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C83" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="G83" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H83" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -2590,19 +2608,19 @@
         <v>90</v>
       </c>
       <c r="B84" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C84" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G84" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H84" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -2610,19 +2628,19 @@
         <v>91</v>
       </c>
       <c r="B85" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C85" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G85" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H85" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -2630,19 +2648,19 @@
         <v>92</v>
       </c>
       <c r="B86" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C86" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G86" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H86" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -2650,19 +2668,19 @@
         <v>93</v>
       </c>
       <c r="B87" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C87" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="G87" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H87" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -2670,19 +2688,79 @@
         <v>94</v>
       </c>
       <c r="B88" t="s">
+        <v>98</v>
+      </c>
+      <c r="C88" t="s">
+        <v>99</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="G88" t="s">
+        <v>190</v>
+      </c>
+      <c r="H88" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" t="s">
         <v>95</v>
       </c>
-      <c r="C88" t="s">
+      <c r="B89" t="s">
+        <v>98</v>
+      </c>
+      <c r="C89" t="s">
+        <v>99</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G89" t="s">
+        <v>190</v>
+      </c>
+      <c r="H89" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" t="s">
         <v>96</v>
       </c>
-      <c r="F88" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="G88" t="s">
-        <v>184</v>
-      </c>
-      <c r="H88" t="s">
-        <v>185</v>
+      <c r="B90" t="s">
+        <v>98</v>
+      </c>
+      <c r="C90" t="s">
+        <v>99</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="G90" t="s">
+        <v>190</v>
+      </c>
+      <c r="H90" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" t="s">
+        <v>97</v>
+      </c>
+      <c r="B91" t="s">
+        <v>98</v>
+      </c>
+      <c r="C91" t="s">
+        <v>99</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="G91" t="s">
+        <v>190</v>
+      </c>
+      <c r="H91" t="s">
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -2774,6 +2852,9 @@
     <hyperlink ref="F86" r:id="rId85"/>
     <hyperlink ref="F87" r:id="rId86"/>
     <hyperlink ref="F88" r:id="rId87"/>
+    <hyperlink ref="F89" r:id="rId88"/>
+    <hyperlink ref="F90" r:id="rId89"/>
+    <hyperlink ref="F91" r:id="rId90"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
